--- a/input.xlsx
+++ b/input.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/25a393584c41f6f2/Documents/Mon Patrimoine/Projet Immobilier/2023 Terrasses de Galieni/09 - Copropriété/Site de calcul des charges de copropriété/streamlit-copro-charges/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="381" documentId="13_ncr:1_{BC6B5EAF-A22B-4219-B771-90D3DDB91BC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{202E8FD5-4A59-41BE-AF4A-58D246F5DC77}"/>
+  <xr:revisionPtr revIDLastSave="384" documentId="13_ncr:1_{BC6B5EAF-A22B-4219-B771-90D3DDB91BC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{18B51A76-C012-4788-B7D5-C75B90B7CC76}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Provisions" sheetId="9" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="920" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="920" uniqueCount="238">
   <si>
     <t>Montant</t>
   </si>
@@ -749,19 +749,16 @@
     <t>Tantièmes Stationnement</t>
   </si>
   <si>
-    <t>Lots</t>
-  </si>
-  <si>
     <t>Lot 462 - Parking n°64 au -2</t>
   </si>
   <si>
-    <t>IDTantiemes</t>
-  </si>
-  <si>
     <t>ID</t>
   </si>
   <si>
     <t>ID prestation</t>
+  </si>
+  <si>
+    <t>ID tantiemes</t>
   </si>
 </sst>
 </file>
@@ -869,6 +866,351 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_-* #,##0.00\ &quot;€&quot;_-;\-* #,##0.00\ &quot;€&quot;_-;_-* &quot;-&quot;??\ &quot;€&quot;_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$€-40C]_-;\-* #,##0.00\ [$€-40C]_-;_-* &quot;-&quot;??\ [$€-40C]_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$€-40C]_-;\-* #,##0.00\ [$€-40C]_-;_-* &quot;-&quot;??\ [$€-40C]_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -1173,351 +1515,6 @@
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$€-40C]_-;\-* #,##0.00\ [$€-40C]_-;_-* &quot;-&quot;??\ [$€-40C]_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$€-40C]_-;\-* #,##0.00\ [$€-40C]_-;_-* &quot;-&quot;??\ [$€-40C]_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="34" formatCode="_-* #,##0.00\ &quot;€&quot;_-;\-* #,##0.00\ &quot;€&quot;_-;_-* &quot;-&quot;??\ &quot;€&quot;_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
@@ -1552,10 +1549,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{13C2BCD2-5CEA-4301-A571-688E40226767}" name="BdBudgetPrevisionnel8" displayName="BdBudgetPrevisionnel8" ref="A1:F35" totalsRowCount="1">
   <autoFilter ref="A1:F34" xr:uid="{13C2BCD2-5CEA-4301-A571-688E40226767}"/>
@@ -1563,12 +1556,12 @@
     <sortCondition ref="C1:C34"/>
   </sortState>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{3B91602D-BA59-47C1-AD19-EAA938B961C7}" name="IDTantiemes"/>
+    <tableColumn id="1" xr3:uid="{3B91602D-BA59-47C1-AD19-EAA938B961C7}" name="ID tantiemes"/>
     <tableColumn id="4" xr3:uid="{84F1F30D-4827-43F2-8865-B7957E3E712D}" name="ID"/>
     <tableColumn id="5" xr3:uid="{94753CD6-8AE2-4955-84AD-F394A68DA3B9}" name="Segment"/>
     <tableColumn id="7" xr3:uid="{512EABBD-B863-4251-833D-8B8D1F1626EF}" name="Description"/>
     <tableColumn id="2" xr3:uid="{D09C4BB0-FEBD-4A72-9E87-B5258D8B62D7}" name="Label de la provision"/>
-    <tableColumn id="3" xr3:uid="{347751FB-EF14-4BD7-9D47-427E04136B77}" name="Provision" totalsRowFunction="sum" dataDxfId="1" totalsRowDxfId="0"/>
+    <tableColumn id="3" xr3:uid="{347751FB-EF14-4BD7-9D47-427E04136B77}" name="Provision" totalsRowFunction="sum" dataDxfId="34" totalsRowDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1578,7 +1571,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{74E83642-0ED6-4017-A369-70F6DD3FC748}" name="BdCoproprietaires2" displayName="BdCoproprietaires2" ref="A1:P5" totalsRowShown="0">
   <autoFilter ref="A1:P5" xr:uid="{74E83642-0ED6-4017-A369-70F6DD3FC748}"/>
   <tableColumns count="16">
-    <tableColumn id="3" xr3:uid="{1687C042-C916-4161-82C2-2A915364FCD2}" name="Lots" dataDxfId="49"/>
+    <tableColumn id="3" xr3:uid="{1687C042-C916-4161-82C2-2A915364FCD2}" name="Numéro de lot" dataDxfId="49"/>
     <tableColumn id="1" xr3:uid="{788DBA8C-5B77-4079-8161-FA45C58518AE}" name="Description"/>
     <tableColumn id="2" xr3:uid="{BE5ACA99-AEAF-4E51-BE0A-B3FB8FCCF08B}" name="Tantièmes copropriété" dataDxfId="48">
       <calculatedColumnFormula>7/10000</calculatedColumnFormula>
@@ -1608,16 +1601,16 @@
     <sortCondition ref="B1:B47"/>
   </sortState>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{7753A616-C6B5-4B02-AE3F-2A95253630B8}" name="Type de prestation" dataDxfId="8"/>
-    <tableColumn id="2" xr3:uid="{D7B6EA29-CA0A-4C24-9A81-3DF01785BD0C}" name="Label de la prestation" dataDxfId="7"/>
-    <tableColumn id="8" xr3:uid="{91FE62B8-BF79-4277-91C2-4B3C13901105}" name="ID prestation" dataDxfId="6"/>
+    <tableColumn id="1" xr3:uid="{7753A616-C6B5-4B02-AE3F-2A95253630B8}" name="Type de prestation" dataDxfId="33"/>
+    <tableColumn id="2" xr3:uid="{D7B6EA29-CA0A-4C24-9A81-3DF01785BD0C}" name="Label de la prestation" dataDxfId="32"/>
+    <tableColumn id="8" xr3:uid="{91FE62B8-BF79-4277-91C2-4B3C13901105}" name="ID prestation" dataDxfId="31"/>
     <tableColumn id="3" xr3:uid="{2ADF6FF1-1416-43FA-A9BF-E696654CC8CD}" name="Prestataire"/>
-    <tableColumn id="4" xr3:uid="{1C295B62-0191-41FA-9660-5BADE532BEE7}" name="Cout" dataDxfId="5"/>
-    <tableColumn id="5" xr3:uid="{1E3C456B-12BB-4B06-B366-57CE3DA87819}" name="Taxes" dataDxfId="4"/>
-    <tableColumn id="6" xr3:uid="{20997A37-E6E3-4308-9ACD-8D77B289D813}" name="Total TTC" dataDxfId="3">
+    <tableColumn id="4" xr3:uid="{1C295B62-0191-41FA-9660-5BADE532BEE7}" name="Cout" dataDxfId="30"/>
+    <tableColumn id="5" xr3:uid="{1E3C456B-12BB-4B06-B366-57CE3DA87819}" name="Taxes" dataDxfId="29"/>
+    <tableColumn id="6" xr3:uid="{20997A37-E6E3-4308-9ACD-8D77B289D813}" name="Total TTC" dataDxfId="28">
       <calculatedColumnFormula>IF(BdCompetition9[[#This Row],[Taxes]]="TTC",BdCompetition9[[#This Row],[Cout]],BdCompetition9[[#This Row],[Cout]]*1.2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{6BDB0ED6-23A7-4E1A-A654-9E18B0DA38B5}" name="Description" dataDxfId="2"/>
+    <tableColumn id="7" xr3:uid="{6BDB0ED6-23A7-4E1A-A654-9E18B0DA38B5}" name="Description" dataDxfId="27"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1630,16 +1623,16 @@
     <sortCondition ref="B1:B47"/>
   </sortState>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{304F6CD1-2A85-4CA9-B82A-BF03CDAE07A4}" name="Type de prestation" dataDxfId="31"/>
-    <tableColumn id="2" xr3:uid="{068CBFB8-4A62-4CD4-BDAC-46EED59496BC}" name="Label de la prestation" dataDxfId="30"/>
-    <tableColumn id="8" xr3:uid="{2298CECF-E998-45F7-AABA-B59C715EC51B}" name="ID1" dataDxfId="29"/>
+    <tableColumn id="1" xr3:uid="{304F6CD1-2A85-4CA9-B82A-BF03CDAE07A4}" name="Type de prestation" dataDxfId="26"/>
+    <tableColumn id="2" xr3:uid="{068CBFB8-4A62-4CD4-BDAC-46EED59496BC}" name="Label de la prestation" dataDxfId="25"/>
+    <tableColumn id="8" xr3:uid="{2298CECF-E998-45F7-AABA-B59C715EC51B}" name="ID1" dataDxfId="24"/>
     <tableColumn id="3" xr3:uid="{5B85ADF0-B113-45E5-864A-388F8040031F}" name="Prestataire"/>
-    <tableColumn id="4" xr3:uid="{037769D5-5B3A-4710-A4BD-50FC46B19887}" name="Cout" dataDxfId="28"/>
-    <tableColumn id="5" xr3:uid="{DDF49AF2-6301-4A34-B62A-4933E379FE46}" name="Taxes" dataDxfId="27"/>
-    <tableColumn id="6" xr3:uid="{D3462D22-93DD-4646-AC7F-1B3471D6826C}" name="Total TTC" dataDxfId="26">
+    <tableColumn id="4" xr3:uid="{037769D5-5B3A-4710-A4BD-50FC46B19887}" name="Cout" dataDxfId="23"/>
+    <tableColumn id="5" xr3:uid="{DDF49AF2-6301-4A34-B62A-4933E379FE46}" name="Taxes" dataDxfId="22"/>
+    <tableColumn id="6" xr3:uid="{D3462D22-93DD-4646-AC7F-1B3471D6826C}" name="Total TTC" dataDxfId="21">
       <calculatedColumnFormula>IF(BdCompetition[[#This Row],[Taxes]]="TTC",BdCompetition[[#This Row],[Cout]],BdCompetition[[#This Row],[Cout]]*1.2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{D6BDE268-55D6-4FDC-9C89-14F909955D72}" name="Description" dataDxfId="25"/>
+    <tableColumn id="7" xr3:uid="{D6BDE268-55D6-4FDC-9C89-14F909955D72}" name="Description" dataDxfId="20"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1656,7 +1649,7 @@
     <tableColumn id="5" xr3:uid="{F17C785C-9055-484D-A7EC-C3372D32A622}" name="Segment"/>
     <tableColumn id="7" xr3:uid="{3DB4DC80-D06E-4E70-BFE9-9BB75CB5FA62}" name="Classe de provision"/>
     <tableColumn id="2" xr3:uid="{3B6645ED-EDB5-4F76-9846-790ECF4F680D}" name="Label de la provision"/>
-    <tableColumn id="3" xr3:uid="{EBBDC931-D4B2-4BFA-A08F-7BA2EEB44DAA}" name="Provision" totalsRowFunction="sum" dataDxfId="33" totalsRowDxfId="32"/>
+    <tableColumn id="3" xr3:uid="{EBBDC931-D4B2-4BFA-A08F-7BA2EEB44DAA}" name="Provision" totalsRowFunction="sum" dataDxfId="19" totalsRowDxfId="18"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1669,23 +1662,23 @@
     <tableColumn id="12" xr3:uid="{6157D014-929F-42D7-A4BC-12D951282608}" name="Batiment"/>
     <tableColumn id="4" xr3:uid="{81B9BF77-9818-477B-B3E8-1E987064DFDA}" name="Label de lot"/>
     <tableColumn id="1" xr3:uid="{B1F46291-565B-462F-9110-123FFF38DDEE}" name="Nom du coproprietaire"/>
-    <tableColumn id="2" xr3:uid="{DE7A1664-88F0-47A5-B594-27860729EB7C}" name="Tantièmes copropriété" dataDxfId="24">
+    <tableColumn id="2" xr3:uid="{DE7A1664-88F0-47A5-B594-27860729EB7C}" name="Tantièmes copropriété" dataDxfId="17">
       <calculatedColumnFormula>7/10000</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{6082472F-2D58-4FBE-B207-F4E7921BE9CD}" name="Tantièmes ascenseur 1-1" dataDxfId="23"/>
-    <tableColumn id="9" xr3:uid="{A99085F3-5429-48BD-99D6-C368BEBDE1C5}" name="Tantièmes ascenseur 1-2" dataDxfId="22"/>
-    <tableColumn id="10" xr3:uid="{29D8D538-CA9C-4A95-992C-1A61F5728B38}" name="Tantièmes ascenseur 2" dataDxfId="21"/>
-    <tableColumn id="11" xr3:uid="{A8F24873-3570-4882-AE65-BFA97F5FA58C}" name="Tantièmes ascenseur 3" dataDxfId="20"/>
-    <tableColumn id="14" xr3:uid="{6A0D9C01-B4D3-4227-A105-5BE4105F433C}" name="Tantièmes chauffage" dataDxfId="19"/>
-    <tableColumn id="15" xr3:uid="{DB773FD9-45E5-4A17-9757-9A0D7F7768AA}" name="Tantièmes Batiment 1" dataDxfId="18"/>
-    <tableColumn id="16" xr3:uid="{2CD201B1-8753-466E-8776-252972944B3C}" name="Tantièmes Batiment 2" dataDxfId="17"/>
-    <tableColumn id="17" xr3:uid="{0EB76A3D-2FED-4CE0-9718-92F4FC209896}" name="Tantièmes Batiment 3" dataDxfId="16"/>
-    <tableColumn id="18" xr3:uid="{E820E31C-950D-4D14-8ABF-A71F86753025}" name="Tantièmes Hall 1-1" dataDxfId="15"/>
-    <tableColumn id="19" xr3:uid="{48F0D008-2EAA-4A4F-A6BA-4F8DF16617F8}" name="Tantièmes Hall 1-2" dataDxfId="14"/>
-    <tableColumn id="20" xr3:uid="{DD9B9883-76BB-4950-9FFB-0863C2F256EA}" name="Tantièmes Hall 2" dataDxfId="13"/>
-    <tableColumn id="21" xr3:uid="{BF704940-4EA2-48AF-8BBA-B1F4C695A5E2}" name="Tantièmes Logement/Stationnements" dataDxfId="12"/>
-    <tableColumn id="6" xr3:uid="{23C5575F-C8F7-420A-A8AC-4CD0404C3FB6}" name="Stationnement" dataDxfId="11"/>
-    <tableColumn id="13" xr3:uid="{4AF86A31-E98F-489D-ABE5-CCD678E7BE8D}" name="Numéro de lot" dataDxfId="10"/>
+    <tableColumn id="8" xr3:uid="{6082472F-2D58-4FBE-B207-F4E7921BE9CD}" name="Tantièmes ascenseur 1-1" dataDxfId="16"/>
+    <tableColumn id="9" xr3:uid="{A99085F3-5429-48BD-99D6-C368BEBDE1C5}" name="Tantièmes ascenseur 1-2" dataDxfId="15"/>
+    <tableColumn id="10" xr3:uid="{29D8D538-CA9C-4A95-992C-1A61F5728B38}" name="Tantièmes ascenseur 2" dataDxfId="14"/>
+    <tableColumn id="11" xr3:uid="{A8F24873-3570-4882-AE65-BFA97F5FA58C}" name="Tantièmes ascenseur 3" dataDxfId="13"/>
+    <tableColumn id="14" xr3:uid="{6A0D9C01-B4D3-4227-A105-5BE4105F433C}" name="Tantièmes chauffage" dataDxfId="12"/>
+    <tableColumn id="15" xr3:uid="{DB773FD9-45E5-4A17-9757-9A0D7F7768AA}" name="Tantièmes Batiment 1" dataDxfId="11"/>
+    <tableColumn id="16" xr3:uid="{2CD201B1-8753-466E-8776-252972944B3C}" name="Tantièmes Batiment 2" dataDxfId="10"/>
+    <tableColumn id="17" xr3:uid="{0EB76A3D-2FED-4CE0-9718-92F4FC209896}" name="Tantièmes Batiment 3" dataDxfId="9"/>
+    <tableColumn id="18" xr3:uid="{E820E31C-950D-4D14-8ABF-A71F86753025}" name="Tantièmes Hall 1-1" dataDxfId="8"/>
+    <tableColumn id="19" xr3:uid="{48F0D008-2EAA-4A4F-A6BA-4F8DF16617F8}" name="Tantièmes Hall 1-2" dataDxfId="7"/>
+    <tableColumn id="20" xr3:uid="{DD9B9883-76BB-4950-9FFB-0863C2F256EA}" name="Tantièmes Hall 2" dataDxfId="6"/>
+    <tableColumn id="21" xr3:uid="{BF704940-4EA2-48AF-8BBA-B1F4C695A5E2}" name="Tantièmes Logement/Stationnements" dataDxfId="5"/>
+    <tableColumn id="6" xr3:uid="{23C5575F-C8F7-420A-A8AC-4CD0404C3FB6}" name="Stationnement" dataDxfId="4"/>
+    <tableColumn id="13" xr3:uid="{4AF86A31-E98F-489D-ABE5-CCD678E7BE8D}" name="Numéro de lot" dataDxfId="3"/>
     <tableColumn id="3" xr3:uid="{71861424-FDE4-4C97-8393-5794B9911F90}" name="Lot Nexity"/>
     <tableColumn id="5" xr3:uid="{99825B0E-48FC-48C3-B40C-A8763FC406C7}" name="Etage"/>
   </tableColumns>
@@ -1698,7 +1691,7 @@
   <autoFilter ref="A1:D9" xr:uid="{594FE941-6967-448D-B161-1A22202460B2}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{8584E7DE-3397-4839-B3F7-5BE29387C4A6}" name="Label des règles"/>
-    <tableColumn id="2" xr3:uid="{2DAB5E09-C6DA-4A52-9D36-12A8D2B9BE1E}" name="Limite" dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{2DAB5E09-C6DA-4A52-9D36-12A8D2B9BE1E}" name="Limite" dataDxfId="2"/>
     <tableColumn id="3" xr3:uid="{4C91DD63-5027-4E87-B95E-BCB801F28C1C}" name="Taxes"/>
     <tableColumn id="4" xr3:uid="{41CB6CC9-60A9-4712-874D-13D61D2EB5DE}" name="Total TTC">
       <calculatedColumnFormula>IF(BdRegles[[#This Row],[Taxes]]="HT",BdRegles[[#This Row],[Limite]]*1.2,BdRegles[[#This Row],[Limite]])</calculatedColumnFormula>
@@ -1713,7 +1706,7 @@
   <autoFilter ref="A1:B2" xr:uid="{B8BAE385-571F-4715-A042-0AD7A1FDF085}"/>
   <tableColumns count="2">
     <tableColumn id="2" xr3:uid="{75AB35E7-AA7F-46C7-B30C-DC2E9C862FFF}" name="Label du revenu"/>
-    <tableColumn id="3" xr3:uid="{4F014B57-0040-4CC7-87A1-9B988F634586}" name="Montant" dataDxfId="34"/>
+    <tableColumn id="3" xr3:uid="{4F014B57-0040-4CC7-87A1-9B988F634586}" name="Montant" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1998,10 +1991,10 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B1" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C1" t="s">
         <v>114</v>
@@ -2712,7 +2705,7 @@
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>234</v>
+        <v>122</v>
       </c>
       <c r="B1" t="s">
         <v>164</v>
@@ -2865,7 +2858,7 @@
         <v>462</v>
       </c>
       <c r="B5" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C5" s="10">
         <v>7</v>
@@ -2924,7 +2917,7 @@
         <v>113</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="D1" t="s">
         <v>112</v>

--- a/input.xlsx
+++ b/input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/25a393584c41f6f2/Documents/Mon Patrimoine/Projet Immobilier/2023 Terrasses de Galieni/09 - Copropriété/Site de calcul des charges de copropriété/streamlit-copro-charges/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="384" documentId="13_ncr:1_{BC6B5EAF-A22B-4219-B771-90D3DDB91BC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{18B51A76-C012-4788-B7D5-C75B90B7CC76}"/>
+  <xr:revisionPtr revIDLastSave="398" documentId="13_ncr:1_{BC6B5EAF-A22B-4219-B771-90D3DDB91BC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BD57C84B-8071-43E9-B1D5-8EE826D5B0A1}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="920" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="889" uniqueCount="240">
   <si>
     <t>Montant</t>
   </si>
@@ -759,6 +759,12 @@
   </si>
   <si>
     <t>ID tantiemes</t>
+  </si>
+  <si>
+    <t>Top consommation chauffage</t>
+  </si>
+  <si>
+    <t>X</t>
   </si>
 </sst>
 </file>
@@ -846,9 +852,6 @@
     <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
   <dxfs count="50">
-    <dxf>
-      <numFmt numFmtId="34" formatCode="_-* #,##0.00\ &quot;€&quot;_-;\-* #,##0.00\ &quot;€&quot;_-;_-* &quot;-&quot;??\ &quot;€&quot;_-;_-@_-"/>
-    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -1266,24 +1269,6 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
@@ -1536,6 +1521,27 @@
       </font>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_-* #,##0.00\ &quot;€&quot;_-;\-* #,##0.00\ &quot;€&quot;_-;_-* &quot;-&quot;??\ &quot;€&quot;_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1550,18 +1556,15 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{13C2BCD2-5CEA-4301-A571-688E40226767}" name="BdBudgetPrevisionnel8" displayName="BdBudgetPrevisionnel8" ref="A1:F35" totalsRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{13C2BCD2-5CEA-4301-A571-688E40226767}" name="BdBudgetPrevisionnel8" displayName="BdBudgetPrevisionnel8" ref="A1:F34">
   <autoFilter ref="A1:F34" xr:uid="{13C2BCD2-5CEA-4301-A571-688E40226767}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:F34">
-    <sortCondition ref="C1:C34"/>
-  </sortState>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{3B91602D-BA59-47C1-AD19-EAA938B961C7}" name="ID tantiemes"/>
     <tableColumn id="4" xr3:uid="{84F1F30D-4827-43F2-8865-B7957E3E712D}" name="ID"/>
-    <tableColumn id="5" xr3:uid="{94753CD6-8AE2-4955-84AD-F394A68DA3B9}" name="Segment"/>
     <tableColumn id="7" xr3:uid="{512EABBD-B863-4251-833D-8B8D1F1626EF}" name="Description"/>
     <tableColumn id="2" xr3:uid="{D09C4BB0-FEBD-4A72-9E87-B5258D8B62D7}" name="Label de la provision"/>
-    <tableColumn id="3" xr3:uid="{347751FB-EF14-4BD7-9D47-427E04136B77}" name="Provision" totalsRowFunction="sum" dataDxfId="34" totalsRowDxfId="0"/>
+    <tableColumn id="3" xr3:uid="{347751FB-EF14-4BD7-9D47-427E04136B77}" name="Provision" totalsRowFunction="sum" dataDxfId="49" totalsRowDxfId="48"/>
+    <tableColumn id="5" xr3:uid="{2D489B7F-CE46-4597-8866-46E6A31D6BF8}" name="Top consommation chauffage"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1571,24 +1574,24 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{74E83642-0ED6-4017-A369-70F6DD3FC748}" name="BdCoproprietaires2" displayName="BdCoproprietaires2" ref="A1:P5" totalsRowShown="0">
   <autoFilter ref="A1:P5" xr:uid="{74E83642-0ED6-4017-A369-70F6DD3FC748}"/>
   <tableColumns count="16">
-    <tableColumn id="3" xr3:uid="{1687C042-C916-4161-82C2-2A915364FCD2}" name="Numéro de lot" dataDxfId="49"/>
+    <tableColumn id="3" xr3:uid="{1687C042-C916-4161-82C2-2A915364FCD2}" name="Numéro de lot" dataDxfId="47"/>
     <tableColumn id="1" xr3:uid="{788DBA8C-5B77-4079-8161-FA45C58518AE}" name="Description"/>
-    <tableColumn id="2" xr3:uid="{BE5ACA99-AEAF-4E51-BE0A-B3FB8FCCF08B}" name="Tantièmes copropriété" dataDxfId="48">
+    <tableColumn id="2" xr3:uid="{BE5ACA99-AEAF-4E51-BE0A-B3FB8FCCF08B}" name="Tantièmes copropriété" dataDxfId="46">
       <calculatedColumnFormula>7/10000</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{D62FAA89-C46E-4AF6-A14F-7FD6F46E7F00}" name="Tantièmes ascenseur 1-1" dataDxfId="47"/>
-    <tableColumn id="9" xr3:uid="{C3B9BDED-CB2A-4305-9CBF-418F5971AC1E}" name="Tantièmes ascenseur 1-2" dataDxfId="46"/>
-    <tableColumn id="10" xr3:uid="{C2291DE1-C707-4F83-846E-F914B4B42E52}" name="Tantièmes ascenseur 2" dataDxfId="45"/>
-    <tableColumn id="11" xr3:uid="{4F70F08A-4C2F-41B0-88EB-711B1A0760CD}" name="Tantièmes ascenseur 3" dataDxfId="44"/>
-    <tableColumn id="14" xr3:uid="{80D23396-716C-46AC-9B55-BCBC6C981351}" name="Tantièmes chauffage" dataDxfId="43"/>
-    <tableColumn id="15" xr3:uid="{E3955139-B619-4DD0-8FC1-ECA97048DFE4}" name="Tantièmes Batiment 1" dataDxfId="42"/>
-    <tableColumn id="16" xr3:uid="{C73E9407-A858-4EF7-81C2-6C70C4B157A2}" name="Tantièmes Batiment 2" dataDxfId="41"/>
-    <tableColumn id="17" xr3:uid="{A07338CA-0096-4091-89B2-A46FF2D323C2}" name="Tantièmes Batiment 3" dataDxfId="40"/>
-    <tableColumn id="18" xr3:uid="{7A3012D8-2375-4F10-9E84-F2F5060C6A99}" name="Tantièmes Hall 1-1" dataDxfId="39"/>
-    <tableColumn id="19" xr3:uid="{67961B6E-B577-4A49-B099-623FB85519B4}" name="Tantièmes Hall 1-2" dataDxfId="38"/>
-    <tableColumn id="20" xr3:uid="{03C201C1-F8AA-4D3C-AEBC-425B180BC2D7}" name="Tantièmes Hall 2" dataDxfId="37"/>
-    <tableColumn id="21" xr3:uid="{4826FC05-81A9-4020-8D1D-83D3D5C5A05A}" name="Tantièmes Logement/Stationnements" dataDxfId="36"/>
-    <tableColumn id="6" xr3:uid="{7B87787E-3595-42D5-B815-AF76B67432D8}" name="Tantièmes Stationnement" dataDxfId="35"/>
+    <tableColumn id="8" xr3:uid="{D62FAA89-C46E-4AF6-A14F-7FD6F46E7F00}" name="Tantièmes ascenseur 1-1" dataDxfId="45"/>
+    <tableColumn id="9" xr3:uid="{C3B9BDED-CB2A-4305-9CBF-418F5971AC1E}" name="Tantièmes ascenseur 1-2" dataDxfId="44"/>
+    <tableColumn id="10" xr3:uid="{C2291DE1-C707-4F83-846E-F914B4B42E52}" name="Tantièmes ascenseur 2" dataDxfId="43"/>
+    <tableColumn id="11" xr3:uid="{4F70F08A-4C2F-41B0-88EB-711B1A0760CD}" name="Tantièmes ascenseur 3" dataDxfId="42"/>
+    <tableColumn id="14" xr3:uid="{80D23396-716C-46AC-9B55-BCBC6C981351}" name="Tantièmes chauffage" dataDxfId="41"/>
+    <tableColumn id="15" xr3:uid="{E3955139-B619-4DD0-8FC1-ECA97048DFE4}" name="Tantièmes Batiment 1" dataDxfId="40"/>
+    <tableColumn id="16" xr3:uid="{C73E9407-A858-4EF7-81C2-6C70C4B157A2}" name="Tantièmes Batiment 2" dataDxfId="39"/>
+    <tableColumn id="17" xr3:uid="{A07338CA-0096-4091-89B2-A46FF2D323C2}" name="Tantièmes Batiment 3" dataDxfId="38"/>
+    <tableColumn id="18" xr3:uid="{7A3012D8-2375-4F10-9E84-F2F5060C6A99}" name="Tantièmes Hall 1-1" dataDxfId="37"/>
+    <tableColumn id="19" xr3:uid="{67961B6E-B577-4A49-B099-623FB85519B4}" name="Tantièmes Hall 1-2" dataDxfId="36"/>
+    <tableColumn id="20" xr3:uid="{03C201C1-F8AA-4D3C-AEBC-425B180BC2D7}" name="Tantièmes Hall 2" dataDxfId="35"/>
+    <tableColumn id="21" xr3:uid="{4826FC05-81A9-4020-8D1D-83D3D5C5A05A}" name="Tantièmes Logement/Stationnements" dataDxfId="34"/>
+    <tableColumn id="6" xr3:uid="{7B87787E-3595-42D5-B815-AF76B67432D8}" name="Tantièmes Stationnement" dataDxfId="33"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1596,21 +1599,27 @@
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{AFF80A4D-E18B-42B5-9271-DD654E188D32}" name="BdCompetition9" displayName="BdCompetition9" ref="A1:H47" totalsRowShown="0">
-  <autoFilter ref="A1:H47" xr:uid="{AFF80A4D-E18B-42B5-9271-DD654E188D32}"/>
+  <autoFilter ref="A1:H47" xr:uid="{AFF80A4D-E18B-42B5-9271-DD654E188D32}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="Fourniture de granulé de bois"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H47">
     <sortCondition ref="B1:B47"/>
   </sortState>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{7753A616-C6B5-4B02-AE3F-2A95253630B8}" name="Type de prestation" dataDxfId="33"/>
-    <tableColumn id="2" xr3:uid="{D7B6EA29-CA0A-4C24-9A81-3DF01785BD0C}" name="Label de la prestation" dataDxfId="32"/>
-    <tableColumn id="8" xr3:uid="{91FE62B8-BF79-4277-91C2-4B3C13901105}" name="ID prestation" dataDxfId="31"/>
+    <tableColumn id="1" xr3:uid="{7753A616-C6B5-4B02-AE3F-2A95253630B8}" name="Type de prestation" dataDxfId="32"/>
+    <tableColumn id="2" xr3:uid="{D7B6EA29-CA0A-4C24-9A81-3DF01785BD0C}" name="Label de la prestation" dataDxfId="31"/>
+    <tableColumn id="8" xr3:uid="{91FE62B8-BF79-4277-91C2-4B3C13901105}" name="ID prestation" dataDxfId="30"/>
     <tableColumn id="3" xr3:uid="{2ADF6FF1-1416-43FA-A9BF-E696654CC8CD}" name="Prestataire"/>
-    <tableColumn id="4" xr3:uid="{1C295B62-0191-41FA-9660-5BADE532BEE7}" name="Cout" dataDxfId="30"/>
-    <tableColumn id="5" xr3:uid="{1E3C456B-12BB-4B06-B366-57CE3DA87819}" name="Taxes" dataDxfId="29"/>
-    <tableColumn id="6" xr3:uid="{20997A37-E6E3-4308-9ACD-8D77B289D813}" name="Total TTC" dataDxfId="28">
+    <tableColumn id="4" xr3:uid="{1C295B62-0191-41FA-9660-5BADE532BEE7}" name="Cout" dataDxfId="29"/>
+    <tableColumn id="5" xr3:uid="{1E3C456B-12BB-4B06-B366-57CE3DA87819}" name="Taxes" dataDxfId="28"/>
+    <tableColumn id="6" xr3:uid="{20997A37-E6E3-4308-9ACD-8D77B289D813}" name="Total TTC" dataDxfId="27">
       <calculatedColumnFormula>IF(BdCompetition9[[#This Row],[Taxes]]="TTC",BdCompetition9[[#This Row],[Cout]],BdCompetition9[[#This Row],[Cout]]*1.2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{6BDB0ED6-23A7-4E1A-A654-9E18B0DA38B5}" name="Description" dataDxfId="27"/>
+    <tableColumn id="7" xr3:uid="{6BDB0ED6-23A7-4E1A-A654-9E18B0DA38B5}" name="Description" dataDxfId="26"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1623,16 +1632,16 @@
     <sortCondition ref="B1:B47"/>
   </sortState>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{304F6CD1-2A85-4CA9-B82A-BF03CDAE07A4}" name="Type de prestation" dataDxfId="26"/>
-    <tableColumn id="2" xr3:uid="{068CBFB8-4A62-4CD4-BDAC-46EED59496BC}" name="Label de la prestation" dataDxfId="25"/>
-    <tableColumn id="8" xr3:uid="{2298CECF-E998-45F7-AABA-B59C715EC51B}" name="ID1" dataDxfId="24"/>
+    <tableColumn id="1" xr3:uid="{304F6CD1-2A85-4CA9-B82A-BF03CDAE07A4}" name="Type de prestation" dataDxfId="25"/>
+    <tableColumn id="2" xr3:uid="{068CBFB8-4A62-4CD4-BDAC-46EED59496BC}" name="Label de la prestation" dataDxfId="24"/>
+    <tableColumn id="8" xr3:uid="{2298CECF-E998-45F7-AABA-B59C715EC51B}" name="ID1" dataDxfId="23"/>
     <tableColumn id="3" xr3:uid="{5B85ADF0-B113-45E5-864A-388F8040031F}" name="Prestataire"/>
-    <tableColumn id="4" xr3:uid="{037769D5-5B3A-4710-A4BD-50FC46B19887}" name="Cout" dataDxfId="23"/>
-    <tableColumn id="5" xr3:uid="{DDF49AF2-6301-4A34-B62A-4933E379FE46}" name="Taxes" dataDxfId="22"/>
-    <tableColumn id="6" xr3:uid="{D3462D22-93DD-4646-AC7F-1B3471D6826C}" name="Total TTC" dataDxfId="21">
+    <tableColumn id="4" xr3:uid="{037769D5-5B3A-4710-A4BD-50FC46B19887}" name="Cout" dataDxfId="22"/>
+    <tableColumn id="5" xr3:uid="{DDF49AF2-6301-4A34-B62A-4933E379FE46}" name="Taxes" dataDxfId="21"/>
+    <tableColumn id="6" xr3:uid="{D3462D22-93DD-4646-AC7F-1B3471D6826C}" name="Total TTC" dataDxfId="20">
       <calculatedColumnFormula>IF(BdCompetition[[#This Row],[Taxes]]="TTC",BdCompetition[[#This Row],[Cout]],BdCompetition[[#This Row],[Cout]]*1.2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{D6BDE268-55D6-4FDC-9C89-14F909955D72}" name="Description" dataDxfId="20"/>
+    <tableColumn id="7" xr3:uid="{D6BDE268-55D6-4FDC-9C89-14F909955D72}" name="Description" dataDxfId="19"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1649,7 +1658,7 @@
     <tableColumn id="5" xr3:uid="{F17C785C-9055-484D-A7EC-C3372D32A622}" name="Segment"/>
     <tableColumn id="7" xr3:uid="{3DB4DC80-D06E-4E70-BFE9-9BB75CB5FA62}" name="Classe de provision"/>
     <tableColumn id="2" xr3:uid="{3B6645ED-EDB5-4F76-9846-790ECF4F680D}" name="Label de la provision"/>
-    <tableColumn id="3" xr3:uid="{EBBDC931-D4B2-4BFA-A08F-7BA2EEB44DAA}" name="Provision" totalsRowFunction="sum" dataDxfId="19" totalsRowDxfId="18"/>
+    <tableColumn id="3" xr3:uid="{EBBDC931-D4B2-4BFA-A08F-7BA2EEB44DAA}" name="Provision" totalsRowFunction="sum" dataDxfId="18" totalsRowDxfId="17"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1662,23 +1671,23 @@
     <tableColumn id="12" xr3:uid="{6157D014-929F-42D7-A4BC-12D951282608}" name="Batiment"/>
     <tableColumn id="4" xr3:uid="{81B9BF77-9818-477B-B3E8-1E987064DFDA}" name="Label de lot"/>
     <tableColumn id="1" xr3:uid="{B1F46291-565B-462F-9110-123FFF38DDEE}" name="Nom du coproprietaire"/>
-    <tableColumn id="2" xr3:uid="{DE7A1664-88F0-47A5-B594-27860729EB7C}" name="Tantièmes copropriété" dataDxfId="17">
+    <tableColumn id="2" xr3:uid="{DE7A1664-88F0-47A5-B594-27860729EB7C}" name="Tantièmes copropriété" dataDxfId="16">
       <calculatedColumnFormula>7/10000</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{6082472F-2D58-4FBE-B207-F4E7921BE9CD}" name="Tantièmes ascenseur 1-1" dataDxfId="16"/>
-    <tableColumn id="9" xr3:uid="{A99085F3-5429-48BD-99D6-C368BEBDE1C5}" name="Tantièmes ascenseur 1-2" dataDxfId="15"/>
-    <tableColumn id="10" xr3:uid="{29D8D538-CA9C-4A95-992C-1A61F5728B38}" name="Tantièmes ascenseur 2" dataDxfId="14"/>
-    <tableColumn id="11" xr3:uid="{A8F24873-3570-4882-AE65-BFA97F5FA58C}" name="Tantièmes ascenseur 3" dataDxfId="13"/>
-    <tableColumn id="14" xr3:uid="{6A0D9C01-B4D3-4227-A105-5BE4105F433C}" name="Tantièmes chauffage" dataDxfId="12"/>
-    <tableColumn id="15" xr3:uid="{DB773FD9-45E5-4A17-9757-9A0D7F7768AA}" name="Tantièmes Batiment 1" dataDxfId="11"/>
-    <tableColumn id="16" xr3:uid="{2CD201B1-8753-466E-8776-252972944B3C}" name="Tantièmes Batiment 2" dataDxfId="10"/>
-    <tableColumn id="17" xr3:uid="{0EB76A3D-2FED-4CE0-9718-92F4FC209896}" name="Tantièmes Batiment 3" dataDxfId="9"/>
-    <tableColumn id="18" xr3:uid="{E820E31C-950D-4D14-8ABF-A71F86753025}" name="Tantièmes Hall 1-1" dataDxfId="8"/>
-    <tableColumn id="19" xr3:uid="{48F0D008-2EAA-4A4F-A6BA-4F8DF16617F8}" name="Tantièmes Hall 1-2" dataDxfId="7"/>
-    <tableColumn id="20" xr3:uid="{DD9B9883-76BB-4950-9FFB-0863C2F256EA}" name="Tantièmes Hall 2" dataDxfId="6"/>
-    <tableColumn id="21" xr3:uid="{BF704940-4EA2-48AF-8BBA-B1F4C695A5E2}" name="Tantièmes Logement/Stationnements" dataDxfId="5"/>
-    <tableColumn id="6" xr3:uid="{23C5575F-C8F7-420A-A8AC-4CD0404C3FB6}" name="Stationnement" dataDxfId="4"/>
-    <tableColumn id="13" xr3:uid="{4AF86A31-E98F-489D-ABE5-CCD678E7BE8D}" name="Numéro de lot" dataDxfId="3"/>
+    <tableColumn id="8" xr3:uid="{6082472F-2D58-4FBE-B207-F4E7921BE9CD}" name="Tantièmes ascenseur 1-1" dataDxfId="15"/>
+    <tableColumn id="9" xr3:uid="{A99085F3-5429-48BD-99D6-C368BEBDE1C5}" name="Tantièmes ascenseur 1-2" dataDxfId="14"/>
+    <tableColumn id="10" xr3:uid="{29D8D538-CA9C-4A95-992C-1A61F5728B38}" name="Tantièmes ascenseur 2" dataDxfId="13"/>
+    <tableColumn id="11" xr3:uid="{A8F24873-3570-4882-AE65-BFA97F5FA58C}" name="Tantièmes ascenseur 3" dataDxfId="12"/>
+    <tableColumn id="14" xr3:uid="{6A0D9C01-B4D3-4227-A105-5BE4105F433C}" name="Tantièmes chauffage" dataDxfId="11"/>
+    <tableColumn id="15" xr3:uid="{DB773FD9-45E5-4A17-9757-9A0D7F7768AA}" name="Tantièmes Batiment 1" dataDxfId="10"/>
+    <tableColumn id="16" xr3:uid="{2CD201B1-8753-466E-8776-252972944B3C}" name="Tantièmes Batiment 2" dataDxfId="9"/>
+    <tableColumn id="17" xr3:uid="{0EB76A3D-2FED-4CE0-9718-92F4FC209896}" name="Tantièmes Batiment 3" dataDxfId="8"/>
+    <tableColumn id="18" xr3:uid="{E820E31C-950D-4D14-8ABF-A71F86753025}" name="Tantièmes Hall 1-1" dataDxfId="7"/>
+    <tableColumn id="19" xr3:uid="{48F0D008-2EAA-4A4F-A6BA-4F8DF16617F8}" name="Tantièmes Hall 1-2" dataDxfId="6"/>
+    <tableColumn id="20" xr3:uid="{DD9B9883-76BB-4950-9FFB-0863C2F256EA}" name="Tantièmes Hall 2" dataDxfId="5"/>
+    <tableColumn id="21" xr3:uid="{BF704940-4EA2-48AF-8BBA-B1F4C695A5E2}" name="Tantièmes Logement/Stationnements" dataDxfId="4"/>
+    <tableColumn id="6" xr3:uid="{23C5575F-C8F7-420A-A8AC-4CD0404C3FB6}" name="Stationnement" dataDxfId="3"/>
+    <tableColumn id="13" xr3:uid="{4AF86A31-E98F-489D-ABE5-CCD678E7BE8D}" name="Numéro de lot" dataDxfId="2"/>
     <tableColumn id="3" xr3:uid="{71861424-FDE4-4C97-8393-5794B9911F90}" name="Lot Nexity"/>
     <tableColumn id="5" xr3:uid="{99825B0E-48FC-48C3-B40C-A8763FC406C7}" name="Etage"/>
   </tableColumns>
@@ -1691,7 +1700,7 @@
   <autoFilter ref="A1:D9" xr:uid="{594FE941-6967-448D-B161-1A22202460B2}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{8584E7DE-3397-4839-B3F7-5BE29387C4A6}" name="Label des règles"/>
-    <tableColumn id="2" xr3:uid="{2DAB5E09-C6DA-4A52-9D36-12A8D2B9BE1E}" name="Limite" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{2DAB5E09-C6DA-4A52-9D36-12A8D2B9BE1E}" name="Limite" dataDxfId="1"/>
     <tableColumn id="3" xr3:uid="{4C91DD63-5027-4E87-B95E-BCB801F28C1C}" name="Taxes"/>
     <tableColumn id="4" xr3:uid="{41CB6CC9-60A9-4712-874D-13D61D2EB5DE}" name="Total TTC">
       <calculatedColumnFormula>IF(BdRegles[[#This Row],[Taxes]]="HT",BdRegles[[#This Row],[Limite]]*1.2,BdRegles[[#This Row],[Limite]])</calculatedColumnFormula>
@@ -1706,7 +1715,7 @@
   <autoFilter ref="A1:B2" xr:uid="{B8BAE385-571F-4715-A042-0AD7A1FDF085}"/>
   <tableColumns count="2">
     <tableColumn id="2" xr3:uid="{75AB35E7-AA7F-46C7-B30C-DC2E9C862FFF}" name="Label du revenu"/>
-    <tableColumn id="3" xr3:uid="{4F014B57-0040-4CC7-87A1-9B988F634586}" name="Montant" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{4F014B57-0040-4CC7-87A1-9B988F634586}" name="Montant" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1978,15 +1987,15 @@
   <sheetPr>
     <tabColor theme="9" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="32.453125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="29.26953125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="42.7265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="42.7265625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="42.7265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.54296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="28.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
@@ -1997,16 +2006,16 @@
         <v>235</v>
       </c>
       <c r="C1" t="s">
-        <v>114</v>
+        <v>164</v>
       </c>
       <c r="D1" t="s">
-        <v>164</v>
-      </c>
-      <c r="E1" t="s">
         <v>116</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>117</v>
+      </c>
+      <c r="F1" t="s">
+        <v>238</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
@@ -2017,15 +2026,12 @@
         <v>104</v>
       </c>
       <c r="C2" t="s">
-        <v>58</v>
+        <v>194</v>
       </c>
       <c r="D2" t="s">
-        <v>194</v>
-      </c>
-      <c r="E2" t="s">
         <v>101</v>
       </c>
-      <c r="F2" s="1">
+      <c r="E2" s="1">
         <v>1500</v>
       </c>
     </row>
@@ -2037,15 +2043,12 @@
         <v>105</v>
       </c>
       <c r="C3" t="s">
-        <v>58</v>
+        <v>195</v>
       </c>
       <c r="D3" t="s">
-        <v>195</v>
-      </c>
-      <c r="E3" t="s">
         <v>100</v>
       </c>
-      <c r="F3" s="1">
+      <c r="E3" s="1">
         <v>1500</v>
       </c>
     </row>
@@ -2057,15 +2060,12 @@
         <v>191</v>
       </c>
       <c r="C4" t="s">
-        <v>58</v>
+        <v>198</v>
       </c>
       <c r="D4" t="s">
         <v>198</v>
       </c>
-      <c r="E4" t="s">
-        <v>198</v>
-      </c>
-      <c r="F4" s="1">
+      <c r="E4" s="1">
         <v>2000</v>
       </c>
     </row>
@@ -2077,15 +2077,12 @@
         <v>106</v>
       </c>
       <c r="C5" t="s">
-        <v>60</v>
+        <v>196</v>
       </c>
       <c r="D5" t="s">
-        <v>196</v>
-      </c>
-      <c r="E5" t="s">
         <v>102</v>
       </c>
-      <c r="F5" s="1">
+      <c r="E5" s="1">
         <v>2900</v>
       </c>
     </row>
@@ -2097,15 +2094,12 @@
         <v>192</v>
       </c>
       <c r="C6" t="s">
-        <v>60</v>
+        <v>199</v>
       </c>
       <c r="D6" t="s">
         <v>199</v>
       </c>
-      <c r="E6" t="s">
-        <v>199</v>
-      </c>
-      <c r="F6" s="1">
+      <c r="E6" s="1">
         <v>1000</v>
       </c>
     </row>
@@ -2117,15 +2111,12 @@
         <v>107</v>
       </c>
       <c r="C7" t="s">
-        <v>59</v>
+        <v>197</v>
       </c>
       <c r="D7" t="s">
-        <v>197</v>
-      </c>
-      <c r="E7" t="s">
         <v>103</v>
       </c>
-      <c r="F7" s="1">
+      <c r="E7" s="1">
         <v>2900</v>
       </c>
     </row>
@@ -2137,15 +2128,12 @@
         <v>193</v>
       </c>
       <c r="C8" t="s">
-        <v>59</v>
+        <v>200</v>
       </c>
       <c r="D8" t="s">
         <v>200</v>
       </c>
-      <c r="E8" t="s">
-        <v>200</v>
-      </c>
-      <c r="F8" s="1">
+      <c r="E8" s="1">
         <v>1000</v>
       </c>
     </row>
@@ -2157,15 +2145,12 @@
         <v>85</v>
       </c>
       <c r="C9" t="s">
-        <v>220</v>
+        <v>54</v>
       </c>
       <c r="D9" t="s">
         <v>54</v>
       </c>
-      <c r="E9" t="s">
-        <v>54</v>
-      </c>
-      <c r="F9" s="1">
+      <c r="E9" s="1">
         <v>750</v>
       </c>
     </row>
@@ -2177,15 +2162,12 @@
         <v>84</v>
       </c>
       <c r="C10" t="s">
-        <v>220</v>
+        <v>53</v>
       </c>
       <c r="D10" t="s">
         <v>53</v>
       </c>
-      <c r="E10" t="s">
-        <v>53</v>
-      </c>
-      <c r="F10" s="1">
+      <c r="E10" s="1">
         <v>6200</v>
       </c>
     </row>
@@ -2197,15 +2179,12 @@
         <v>81</v>
       </c>
       <c r="C11" t="s">
-        <v>220</v>
+        <v>50</v>
       </c>
       <c r="D11" t="s">
         <v>50</v>
       </c>
-      <c r="E11" t="s">
-        <v>50</v>
-      </c>
-      <c r="F11" s="1">
+      <c r="E11" s="1">
         <v>1050</v>
       </c>
     </row>
@@ -2217,15 +2196,12 @@
         <v>80</v>
       </c>
       <c r="C12" t="s">
-        <v>220</v>
+        <v>49</v>
       </c>
       <c r="D12" t="s">
         <v>49</v>
       </c>
-      <c r="E12" t="s">
-        <v>49</v>
-      </c>
-      <c r="F12" s="1">
+      <c r="E12" s="1">
         <v>900</v>
       </c>
     </row>
@@ -2237,15 +2213,12 @@
         <v>79</v>
       </c>
       <c r="C13" t="s">
-        <v>220</v>
+        <v>48</v>
       </c>
       <c r="D13" t="s">
         <v>48</v>
       </c>
-      <c r="E13" t="s">
-        <v>48</v>
-      </c>
-      <c r="F13" s="1">
+      <c r="E13" s="1">
         <v>920</v>
       </c>
     </row>
@@ -2257,15 +2230,12 @@
         <v>72</v>
       </c>
       <c r="C14" t="s">
-        <v>220</v>
+        <v>41</v>
       </c>
       <c r="D14" t="s">
         <v>41</v>
       </c>
-      <c r="E14" t="s">
-        <v>41</v>
-      </c>
-      <c r="F14" s="1">
+      <c r="E14" s="1">
         <v>35000</v>
       </c>
     </row>
@@ -2277,15 +2247,12 @@
         <v>73</v>
       </c>
       <c r="C15" t="s">
-        <v>220</v>
+        <v>124</v>
       </c>
       <c r="D15" t="s">
-        <v>124</v>
-      </c>
-      <c r="E15" t="s">
         <v>42</v>
       </c>
-      <c r="F15" s="1">
+      <c r="E15" s="1">
         <v>1500</v>
       </c>
     </row>
@@ -2297,15 +2264,12 @@
         <v>82</v>
       </c>
       <c r="C16" t="s">
-        <v>220</v>
+        <v>51</v>
       </c>
       <c r="D16" t="s">
         <v>51</v>
       </c>
-      <c r="E16" t="s">
-        <v>51</v>
-      </c>
-      <c r="F16" s="1">
+      <c r="E16" s="1">
         <v>580</v>
       </c>
     </row>
@@ -2317,15 +2281,12 @@
         <v>87</v>
       </c>
       <c r="C17" t="s">
-        <v>220</v>
+        <v>56</v>
       </c>
       <c r="D17" t="s">
         <v>56</v>
       </c>
-      <c r="E17" t="s">
-        <v>56</v>
-      </c>
-      <c r="F17" s="1">
+      <c r="E17" s="1">
         <v>570</v>
       </c>
     </row>
@@ -2337,15 +2298,12 @@
         <v>88</v>
       </c>
       <c r="C18" t="s">
-        <v>220</v>
+        <v>57</v>
       </c>
       <c r="D18" t="s">
         <v>57</v>
       </c>
-      <c r="E18" t="s">
-        <v>57</v>
-      </c>
-      <c r="F18" s="1">
+      <c r="E18" s="1">
         <v>850</v>
       </c>
     </row>
@@ -2357,15 +2315,12 @@
         <v>77</v>
       </c>
       <c r="C19" t="s">
-        <v>220</v>
+        <v>46</v>
       </c>
       <c r="D19" t="s">
         <v>46</v>
       </c>
-      <c r="E19" t="s">
-        <v>46</v>
-      </c>
-      <c r="F19" s="1">
+      <c r="E19" s="1">
         <v>240</v>
       </c>
     </row>
@@ -2377,15 +2332,12 @@
         <v>76</v>
       </c>
       <c r="C20" t="s">
-        <v>220</v>
+        <v>45</v>
       </c>
       <c r="D20" t="s">
         <v>45</v>
       </c>
-      <c r="E20" t="s">
-        <v>45</v>
-      </c>
-      <c r="F20" s="1">
+      <c r="E20" s="1">
         <v>220</v>
       </c>
     </row>
@@ -2397,15 +2349,12 @@
         <v>74</v>
       </c>
       <c r="C21" t="s">
-        <v>220</v>
+        <v>43</v>
       </c>
       <c r="D21" t="s">
         <v>43</v>
       </c>
-      <c r="E21" t="s">
-        <v>43</v>
-      </c>
-      <c r="F21" s="1">
+      <c r="E21" s="1">
         <v>18000</v>
       </c>
     </row>
@@ -2417,15 +2366,12 @@
         <v>78</v>
       </c>
       <c r="C22" t="s">
-        <v>220</v>
+        <v>47</v>
       </c>
       <c r="D22" t="s">
         <v>47</v>
       </c>
-      <c r="E22" t="s">
-        <v>47</v>
-      </c>
-      <c r="F22" s="1"/>
+      <c r="E22" s="1"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
@@ -2435,15 +2381,12 @@
         <v>75</v>
       </c>
       <c r="C23" t="s">
-        <v>220</v>
+        <v>44</v>
       </c>
       <c r="D23" t="s">
         <v>44</v>
       </c>
-      <c r="E23" t="s">
-        <v>44</v>
-      </c>
-      <c r="F23" s="1">
+      <c r="E23" s="1">
         <v>650</v>
       </c>
     </row>
@@ -2455,15 +2398,12 @@
         <v>83</v>
       </c>
       <c r="C24" t="s">
-        <v>220</v>
+        <v>52</v>
       </c>
       <c r="D24" t="s">
         <v>52</v>
       </c>
-      <c r="E24" t="s">
-        <v>52</v>
-      </c>
-      <c r="F24" s="1">
+      <c r="E24" s="1">
         <v>3500</v>
       </c>
     </row>
@@ -2475,15 +2415,12 @@
         <v>86</v>
       </c>
       <c r="C25" t="s">
-        <v>220</v>
+        <v>55</v>
       </c>
       <c r="D25" t="s">
         <v>55</v>
       </c>
-      <c r="E25" t="s">
-        <v>55</v>
-      </c>
-      <c r="F25" s="1">
+      <c r="E25" s="1">
         <v>16800</v>
       </c>
     </row>
@@ -2495,15 +2432,12 @@
         <v>96</v>
       </c>
       <c r="C26" t="s">
-        <v>219</v>
+        <v>97</v>
       </c>
       <c r="D26" t="s">
         <v>97</v>
       </c>
-      <c r="E26" t="s">
-        <v>97</v>
-      </c>
-      <c r="F26" s="1">
+      <c r="E26" s="1">
         <v>4000</v>
       </c>
     </row>
@@ -2514,17 +2448,17 @@
       <c r="B27" t="s">
         <v>90</v>
       </c>
-      <c r="C27" t="s">
-        <v>64</v>
+      <c r="C27" s="1" t="s">
+        <v>190</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="E27" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="F27" s="1">
+      <c r="E27" s="1">
         <v>23100</v>
+      </c>
+      <c r="F27" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
@@ -2534,17 +2468,17 @@
       <c r="B28" t="s">
         <v>89</v>
       </c>
-      <c r="C28" t="s">
-        <v>64</v>
+      <c r="C28" s="1" t="s">
+        <v>189</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="E28" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="F28" s="1">
+      <c r="E28" s="1">
         <v>27000</v>
+      </c>
+      <c r="F28" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.35">
@@ -2554,16 +2488,13 @@
       <c r="B29" t="s">
         <v>91</v>
       </c>
-      <c r="C29" t="s">
-        <v>64</v>
+      <c r="C29" s="1" t="s">
+        <v>63</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="E29" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="F29" s="1">
+      <c r="E29" s="1">
         <v>17650</v>
       </c>
     </row>
@@ -2575,15 +2506,12 @@
         <v>93</v>
       </c>
       <c r="C30" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D30" t="s">
         <v>67</v>
       </c>
-      <c r="E30" t="s">
-        <v>67</v>
-      </c>
-      <c r="F30" s="1">
+      <c r="E30" s="1">
         <v>90</v>
       </c>
     </row>
@@ -2595,15 +2523,12 @@
         <v>92</v>
       </c>
       <c r="C31" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D31" t="s">
         <v>66</v>
       </c>
-      <c r="E31" t="s">
-        <v>66</v>
-      </c>
-      <c r="F31" s="1">
+      <c r="E31" s="1">
         <v>450</v>
       </c>
     </row>
@@ -2615,19 +2540,16 @@
         <v>94</v>
       </c>
       <c r="C32" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D32" t="s">
         <v>68</v>
       </c>
-      <c r="E32" t="s">
-        <v>68</v>
-      </c>
-      <c r="F32" s="1">
+      <c r="E32" s="1">
         <v>320</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>233</v>
       </c>
@@ -2635,19 +2557,16 @@
         <v>108</v>
       </c>
       <c r="C33" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="D33" t="s">
         <v>70</v>
       </c>
-      <c r="E33" t="s">
-        <v>70</v>
-      </c>
-      <c r="F33" s="1">
+      <c r="E33" s="1">
         <v>1500</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>233</v>
       </c>
@@ -2655,23 +2574,13 @@
         <v>95</v>
       </c>
       <c r="C34" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D34" t="s">
         <v>69</v>
       </c>
-      <c r="E34" t="s">
-        <v>69</v>
-      </c>
-      <c r="F34" s="1">
+      <c r="E34" s="1">
         <v>360</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="D35"/>
-      <c r="F35" s="4">
-        <f>SUBTOTAL(109,BdBudgetPrevisionnel8[Provision])</f>
-        <v>175000</v>
       </c>
     </row>
   </sheetData>
@@ -2935,7 +2844,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>29</v>
       </c>
@@ -2956,7 +2865,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>210</v>
       </c>
@@ -3010,7 +2919,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>201</v>
       </c>
@@ -3037,7 +2946,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>210</v>
       </c>
@@ -3091,7 +3000,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>201</v>
       </c>
@@ -3118,7 +3027,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>210</v>
       </c>
@@ -3172,7 +3081,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>201</v>
       </c>
@@ -3199,7 +3108,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>210</v>
       </c>
@@ -3253,7 +3162,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
         <v>15</v>
       </c>
@@ -3274,7 +3183,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
         <v>15</v>
       </c>
@@ -3295,7 +3204,7 @@
         <v>2460</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
         <v>34</v>
       </c>
@@ -3322,7 +3231,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
         <v>14</v>
       </c>
@@ -3349,7 +3258,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
         <v>11</v>
       </c>
@@ -3376,7 +3285,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
         <v>11</v>
       </c>
@@ -3403,7 +3312,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
         <v>26</v>
       </c>
@@ -3431,7 +3340,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
         <v>26</v>
       </c>
@@ -3459,7 +3368,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
         <v>26</v>
       </c>
@@ -3483,7 +3392,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
         <v>26</v>
       </c>
@@ -3507,7 +3416,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
         <v>18</v>
       </c>
@@ -3535,7 +3444,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
         <v>18</v>
       </c>
@@ -3563,7 +3472,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
         <v>18</v>
       </c>
@@ -3591,7 +3500,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
         <v>24</v>
       </c>
@@ -3618,7 +3527,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
         <v>24</v>
       </c>
@@ -3645,7 +3554,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="87" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:8" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
         <v>24</v>
       </c>
@@ -3672,7 +3581,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
         <v>19</v>
       </c>
@@ -3699,7 +3608,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
         <v>19</v>
       </c>
@@ -3726,7 +3635,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
         <v>19</v>
       </c>
@@ -3753,7 +3662,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
         <v>19</v>
       </c>
@@ -3780,7 +3689,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
         <v>31</v>
       </c>
@@ -3801,7 +3710,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="s">
         <v>18</v>
       </c>
@@ -3829,7 +3738,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
         <v>18</v>
       </c>
@@ -3857,7 +3766,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A37" s="2" t="s">
         <v>20</v>
       </c>
@@ -3878,7 +3787,7 @@
         <v>3198.13</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
         <v>20</v>
       </c>
@@ -3899,7 +3808,7 @@
         <v>3322.8</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A39" s="2" t="s">
         <v>20</v>
       </c>
@@ -3920,7 +3829,7 @@
         <v>3138.27</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
         <v>19</v>
       </c>
@@ -3947,7 +3856,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A41" s="2" t="s">
         <v>19</v>
       </c>
@@ -3974,7 +3883,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A42" s="2" t="s">
         <v>19</v>
       </c>
@@ -4001,7 +3910,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A43" s="2" t="s">
         <v>19</v>
       </c>
@@ -4028,7 +3937,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A44" s="2" t="s">
         <v>125</v>
       </c>
@@ -4054,7 +3963,7 @@
       <c r="H44" s="5"/>
       <c r="I44" s="2"/>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A45" s="2" t="s">
         <v>125</v>
       </c>
@@ -4080,7 +3989,7 @@
       <c r="H45" s="5"/>
       <c r="I45" s="2"/>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A46" s="2" t="s">
         <v>125</v>
       </c>
@@ -4106,7 +4015,7 @@
       <c r="H46" s="5"/>
       <c r="I46" s="2"/>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A47" s="2" t="s">
         <v>125</v>
       </c>

--- a/input.xlsx
+++ b/input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/25a393584c41f6f2/Documents/Mon Patrimoine/Projet Immobilier/2023 Terrasses de Galieni/09 - Copropriété/Site de calcul des charges de copropriété/streamlit-copro-charges/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="398" documentId="13_ncr:1_{BC6B5EAF-A22B-4219-B771-90D3DDB91BC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BD57C84B-8071-43E9-B1D5-8EE826D5B0A1}"/>
+  <xr:revisionPtr revIDLastSave="406" documentId="13_ncr:1_{BC6B5EAF-A22B-4219-B771-90D3DDB91BC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CBB2A207-7565-4E45-A442-BD117D0B57EF}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -852,6 +852,9 @@
     <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
   <dxfs count="50">
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_-* #,##0.00\ &quot;€&quot;_-;\-* #,##0.00\ &quot;€&quot;_-;_-* &quot;-&quot;??\ &quot;€&quot;_-;_-@_-"/>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -1522,9 +1525,6 @@
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="34" formatCode="_-* #,##0.00\ &quot;€&quot;_-;\-* #,##0.00\ &quot;€&quot;_-;_-* &quot;-&quot;??\ &quot;€&quot;_-;_-@_-"/>
-    </dxf>
-    <dxf>
       <font>
         <b val="0"/>
         <i val="0"/>
@@ -1555,6 +1555,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{13C2BCD2-5CEA-4301-A571-688E40226767}" name="BdBudgetPrevisionnel8" displayName="BdBudgetPrevisionnel8" ref="A1:F34">
   <autoFilter ref="A1:F34" xr:uid="{13C2BCD2-5CEA-4301-A571-688E40226767}"/>
@@ -1563,7 +1567,7 @@
     <tableColumn id="4" xr3:uid="{84F1F30D-4827-43F2-8865-B7957E3E712D}" name="ID"/>
     <tableColumn id="7" xr3:uid="{512EABBD-B863-4251-833D-8B8D1F1626EF}" name="Description"/>
     <tableColumn id="2" xr3:uid="{D09C4BB0-FEBD-4A72-9E87-B5258D8B62D7}" name="Label de la provision"/>
-    <tableColumn id="3" xr3:uid="{347751FB-EF14-4BD7-9D47-427E04136B77}" name="Provision" totalsRowFunction="sum" dataDxfId="49" totalsRowDxfId="48"/>
+    <tableColumn id="3" xr3:uid="{347751FB-EF14-4BD7-9D47-427E04136B77}" name="Provision" totalsRowFunction="sum" dataDxfId="49" totalsRowDxfId="0"/>
     <tableColumn id="5" xr3:uid="{2D489B7F-CE46-4597-8866-46E6A31D6BF8}" name="Top consommation chauffage"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1574,24 +1578,24 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{74E83642-0ED6-4017-A369-70F6DD3FC748}" name="BdCoproprietaires2" displayName="BdCoproprietaires2" ref="A1:P5" totalsRowShown="0">
   <autoFilter ref="A1:P5" xr:uid="{74E83642-0ED6-4017-A369-70F6DD3FC748}"/>
   <tableColumns count="16">
-    <tableColumn id="3" xr3:uid="{1687C042-C916-4161-82C2-2A915364FCD2}" name="Numéro de lot" dataDxfId="47"/>
+    <tableColumn id="3" xr3:uid="{1687C042-C916-4161-82C2-2A915364FCD2}" name="Numéro de lot" dataDxfId="48"/>
     <tableColumn id="1" xr3:uid="{788DBA8C-5B77-4079-8161-FA45C58518AE}" name="Description"/>
-    <tableColumn id="2" xr3:uid="{BE5ACA99-AEAF-4E51-BE0A-B3FB8FCCF08B}" name="Tantièmes copropriété" dataDxfId="46">
+    <tableColumn id="2" xr3:uid="{BE5ACA99-AEAF-4E51-BE0A-B3FB8FCCF08B}" name="Tantièmes copropriété" dataDxfId="47">
       <calculatedColumnFormula>7/10000</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{D62FAA89-C46E-4AF6-A14F-7FD6F46E7F00}" name="Tantièmes ascenseur 1-1" dataDxfId="45"/>
-    <tableColumn id="9" xr3:uid="{C3B9BDED-CB2A-4305-9CBF-418F5971AC1E}" name="Tantièmes ascenseur 1-2" dataDxfId="44"/>
-    <tableColumn id="10" xr3:uid="{C2291DE1-C707-4F83-846E-F914B4B42E52}" name="Tantièmes ascenseur 2" dataDxfId="43"/>
-    <tableColumn id="11" xr3:uid="{4F70F08A-4C2F-41B0-88EB-711B1A0760CD}" name="Tantièmes ascenseur 3" dataDxfId="42"/>
-    <tableColumn id="14" xr3:uid="{80D23396-716C-46AC-9B55-BCBC6C981351}" name="Tantièmes chauffage" dataDxfId="41"/>
-    <tableColumn id="15" xr3:uid="{E3955139-B619-4DD0-8FC1-ECA97048DFE4}" name="Tantièmes Batiment 1" dataDxfId="40"/>
-    <tableColumn id="16" xr3:uid="{C73E9407-A858-4EF7-81C2-6C70C4B157A2}" name="Tantièmes Batiment 2" dataDxfId="39"/>
-    <tableColumn id="17" xr3:uid="{A07338CA-0096-4091-89B2-A46FF2D323C2}" name="Tantièmes Batiment 3" dataDxfId="38"/>
-    <tableColumn id="18" xr3:uid="{7A3012D8-2375-4F10-9E84-F2F5060C6A99}" name="Tantièmes Hall 1-1" dataDxfId="37"/>
-    <tableColumn id="19" xr3:uid="{67961B6E-B577-4A49-B099-623FB85519B4}" name="Tantièmes Hall 1-2" dataDxfId="36"/>
-    <tableColumn id="20" xr3:uid="{03C201C1-F8AA-4D3C-AEBC-425B180BC2D7}" name="Tantièmes Hall 2" dataDxfId="35"/>
-    <tableColumn id="21" xr3:uid="{4826FC05-81A9-4020-8D1D-83D3D5C5A05A}" name="Tantièmes Logement/Stationnements" dataDxfId="34"/>
-    <tableColumn id="6" xr3:uid="{7B87787E-3595-42D5-B815-AF76B67432D8}" name="Tantièmes Stationnement" dataDxfId="33"/>
+    <tableColumn id="8" xr3:uid="{D62FAA89-C46E-4AF6-A14F-7FD6F46E7F00}" name="Tantièmes ascenseur 1-1" dataDxfId="46"/>
+    <tableColumn id="9" xr3:uid="{C3B9BDED-CB2A-4305-9CBF-418F5971AC1E}" name="Tantièmes ascenseur 1-2" dataDxfId="45"/>
+    <tableColumn id="10" xr3:uid="{C2291DE1-C707-4F83-846E-F914B4B42E52}" name="Tantièmes ascenseur 2" dataDxfId="44"/>
+    <tableColumn id="11" xr3:uid="{4F70F08A-4C2F-41B0-88EB-711B1A0760CD}" name="Tantièmes ascenseur 3" dataDxfId="43"/>
+    <tableColumn id="14" xr3:uid="{80D23396-716C-46AC-9B55-BCBC6C981351}" name="Tantièmes chauffage" dataDxfId="42"/>
+    <tableColumn id="15" xr3:uid="{E3955139-B619-4DD0-8FC1-ECA97048DFE4}" name="Tantièmes Batiment 1" dataDxfId="41"/>
+    <tableColumn id="16" xr3:uid="{C73E9407-A858-4EF7-81C2-6C70C4B157A2}" name="Tantièmes Batiment 2" dataDxfId="40"/>
+    <tableColumn id="17" xr3:uid="{A07338CA-0096-4091-89B2-A46FF2D323C2}" name="Tantièmes Batiment 3" dataDxfId="39"/>
+    <tableColumn id="18" xr3:uid="{7A3012D8-2375-4F10-9E84-F2F5060C6A99}" name="Tantièmes Hall 1-1" dataDxfId="38"/>
+    <tableColumn id="19" xr3:uid="{67961B6E-B577-4A49-B099-623FB85519B4}" name="Tantièmes Hall 1-2" dataDxfId="37"/>
+    <tableColumn id="20" xr3:uid="{03C201C1-F8AA-4D3C-AEBC-425B180BC2D7}" name="Tantièmes Hall 2" dataDxfId="36"/>
+    <tableColumn id="21" xr3:uid="{4826FC05-81A9-4020-8D1D-83D3D5C5A05A}" name="Tantièmes Logement/Stationnements" dataDxfId="35"/>
+    <tableColumn id="6" xr3:uid="{7B87787E-3595-42D5-B815-AF76B67432D8}" name="Tantièmes Stationnement" dataDxfId="34"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1610,16 +1614,16 @@
     <sortCondition ref="B1:B47"/>
   </sortState>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{7753A616-C6B5-4B02-AE3F-2A95253630B8}" name="Type de prestation" dataDxfId="32"/>
-    <tableColumn id="2" xr3:uid="{D7B6EA29-CA0A-4C24-9A81-3DF01785BD0C}" name="Label de la prestation" dataDxfId="31"/>
-    <tableColumn id="8" xr3:uid="{91FE62B8-BF79-4277-91C2-4B3C13901105}" name="ID prestation" dataDxfId="30"/>
+    <tableColumn id="1" xr3:uid="{7753A616-C6B5-4B02-AE3F-2A95253630B8}" name="Type de prestation" dataDxfId="33"/>
+    <tableColumn id="2" xr3:uid="{D7B6EA29-CA0A-4C24-9A81-3DF01785BD0C}" name="Label de la prestation" dataDxfId="32"/>
+    <tableColumn id="8" xr3:uid="{91FE62B8-BF79-4277-91C2-4B3C13901105}" name="ID prestation" dataDxfId="31"/>
     <tableColumn id="3" xr3:uid="{2ADF6FF1-1416-43FA-A9BF-E696654CC8CD}" name="Prestataire"/>
-    <tableColumn id="4" xr3:uid="{1C295B62-0191-41FA-9660-5BADE532BEE7}" name="Cout" dataDxfId="29"/>
-    <tableColumn id="5" xr3:uid="{1E3C456B-12BB-4B06-B366-57CE3DA87819}" name="Taxes" dataDxfId="28"/>
-    <tableColumn id="6" xr3:uid="{20997A37-E6E3-4308-9ACD-8D77B289D813}" name="Total TTC" dataDxfId="27">
+    <tableColumn id="4" xr3:uid="{1C295B62-0191-41FA-9660-5BADE532BEE7}" name="Cout" dataDxfId="30"/>
+    <tableColumn id="5" xr3:uid="{1E3C456B-12BB-4B06-B366-57CE3DA87819}" name="Taxes" dataDxfId="29"/>
+    <tableColumn id="6" xr3:uid="{20997A37-E6E3-4308-9ACD-8D77B289D813}" name="Total TTC" dataDxfId="28">
       <calculatedColumnFormula>IF(BdCompetition9[[#This Row],[Taxes]]="TTC",BdCompetition9[[#This Row],[Cout]],BdCompetition9[[#This Row],[Cout]]*1.2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{6BDB0ED6-23A7-4E1A-A654-9E18B0DA38B5}" name="Description" dataDxfId="26"/>
+    <tableColumn id="7" xr3:uid="{6BDB0ED6-23A7-4E1A-A654-9E18B0DA38B5}" name="Description" dataDxfId="27"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1632,16 +1636,16 @@
     <sortCondition ref="B1:B47"/>
   </sortState>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{304F6CD1-2A85-4CA9-B82A-BF03CDAE07A4}" name="Type de prestation" dataDxfId="25"/>
-    <tableColumn id="2" xr3:uid="{068CBFB8-4A62-4CD4-BDAC-46EED59496BC}" name="Label de la prestation" dataDxfId="24"/>
-    <tableColumn id="8" xr3:uid="{2298CECF-E998-45F7-AABA-B59C715EC51B}" name="ID1" dataDxfId="23"/>
+    <tableColumn id="1" xr3:uid="{304F6CD1-2A85-4CA9-B82A-BF03CDAE07A4}" name="Type de prestation" dataDxfId="26"/>
+    <tableColumn id="2" xr3:uid="{068CBFB8-4A62-4CD4-BDAC-46EED59496BC}" name="Label de la prestation" dataDxfId="25"/>
+    <tableColumn id="8" xr3:uid="{2298CECF-E998-45F7-AABA-B59C715EC51B}" name="ID1" dataDxfId="24"/>
     <tableColumn id="3" xr3:uid="{5B85ADF0-B113-45E5-864A-388F8040031F}" name="Prestataire"/>
-    <tableColumn id="4" xr3:uid="{037769D5-5B3A-4710-A4BD-50FC46B19887}" name="Cout" dataDxfId="22"/>
-    <tableColumn id="5" xr3:uid="{DDF49AF2-6301-4A34-B62A-4933E379FE46}" name="Taxes" dataDxfId="21"/>
-    <tableColumn id="6" xr3:uid="{D3462D22-93DD-4646-AC7F-1B3471D6826C}" name="Total TTC" dataDxfId="20">
+    <tableColumn id="4" xr3:uid="{037769D5-5B3A-4710-A4BD-50FC46B19887}" name="Cout" dataDxfId="23"/>
+    <tableColumn id="5" xr3:uid="{DDF49AF2-6301-4A34-B62A-4933E379FE46}" name="Taxes" dataDxfId="22"/>
+    <tableColumn id="6" xr3:uid="{D3462D22-93DD-4646-AC7F-1B3471D6826C}" name="Total TTC" dataDxfId="21">
       <calculatedColumnFormula>IF(BdCompetition[[#This Row],[Taxes]]="TTC",BdCompetition[[#This Row],[Cout]],BdCompetition[[#This Row],[Cout]]*1.2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{D6BDE268-55D6-4FDC-9C89-14F909955D72}" name="Description" dataDxfId="19"/>
+    <tableColumn id="7" xr3:uid="{D6BDE268-55D6-4FDC-9C89-14F909955D72}" name="Description" dataDxfId="20"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1658,7 +1662,7 @@
     <tableColumn id="5" xr3:uid="{F17C785C-9055-484D-A7EC-C3372D32A622}" name="Segment"/>
     <tableColumn id="7" xr3:uid="{3DB4DC80-D06E-4E70-BFE9-9BB75CB5FA62}" name="Classe de provision"/>
     <tableColumn id="2" xr3:uid="{3B6645ED-EDB5-4F76-9846-790ECF4F680D}" name="Label de la provision"/>
-    <tableColumn id="3" xr3:uid="{EBBDC931-D4B2-4BFA-A08F-7BA2EEB44DAA}" name="Provision" totalsRowFunction="sum" dataDxfId="18" totalsRowDxfId="17"/>
+    <tableColumn id="3" xr3:uid="{EBBDC931-D4B2-4BFA-A08F-7BA2EEB44DAA}" name="Provision" totalsRowFunction="sum" dataDxfId="19" totalsRowDxfId="18"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1671,23 +1675,23 @@
     <tableColumn id="12" xr3:uid="{6157D014-929F-42D7-A4BC-12D951282608}" name="Batiment"/>
     <tableColumn id="4" xr3:uid="{81B9BF77-9818-477B-B3E8-1E987064DFDA}" name="Label de lot"/>
     <tableColumn id="1" xr3:uid="{B1F46291-565B-462F-9110-123FFF38DDEE}" name="Nom du coproprietaire"/>
-    <tableColumn id="2" xr3:uid="{DE7A1664-88F0-47A5-B594-27860729EB7C}" name="Tantièmes copropriété" dataDxfId="16">
+    <tableColumn id="2" xr3:uid="{DE7A1664-88F0-47A5-B594-27860729EB7C}" name="Tantièmes copropriété" dataDxfId="17">
       <calculatedColumnFormula>7/10000</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{6082472F-2D58-4FBE-B207-F4E7921BE9CD}" name="Tantièmes ascenseur 1-1" dataDxfId="15"/>
-    <tableColumn id="9" xr3:uid="{A99085F3-5429-48BD-99D6-C368BEBDE1C5}" name="Tantièmes ascenseur 1-2" dataDxfId="14"/>
-    <tableColumn id="10" xr3:uid="{29D8D538-CA9C-4A95-992C-1A61F5728B38}" name="Tantièmes ascenseur 2" dataDxfId="13"/>
-    <tableColumn id="11" xr3:uid="{A8F24873-3570-4882-AE65-BFA97F5FA58C}" name="Tantièmes ascenseur 3" dataDxfId="12"/>
-    <tableColumn id="14" xr3:uid="{6A0D9C01-B4D3-4227-A105-5BE4105F433C}" name="Tantièmes chauffage" dataDxfId="11"/>
-    <tableColumn id="15" xr3:uid="{DB773FD9-45E5-4A17-9757-9A0D7F7768AA}" name="Tantièmes Batiment 1" dataDxfId="10"/>
-    <tableColumn id="16" xr3:uid="{2CD201B1-8753-466E-8776-252972944B3C}" name="Tantièmes Batiment 2" dataDxfId="9"/>
-    <tableColumn id="17" xr3:uid="{0EB76A3D-2FED-4CE0-9718-92F4FC209896}" name="Tantièmes Batiment 3" dataDxfId="8"/>
-    <tableColumn id="18" xr3:uid="{E820E31C-950D-4D14-8ABF-A71F86753025}" name="Tantièmes Hall 1-1" dataDxfId="7"/>
-    <tableColumn id="19" xr3:uid="{48F0D008-2EAA-4A4F-A6BA-4F8DF16617F8}" name="Tantièmes Hall 1-2" dataDxfId="6"/>
-    <tableColumn id="20" xr3:uid="{DD9B9883-76BB-4950-9FFB-0863C2F256EA}" name="Tantièmes Hall 2" dataDxfId="5"/>
-    <tableColumn id="21" xr3:uid="{BF704940-4EA2-48AF-8BBA-B1F4C695A5E2}" name="Tantièmes Logement/Stationnements" dataDxfId="4"/>
-    <tableColumn id="6" xr3:uid="{23C5575F-C8F7-420A-A8AC-4CD0404C3FB6}" name="Stationnement" dataDxfId="3"/>
-    <tableColumn id="13" xr3:uid="{4AF86A31-E98F-489D-ABE5-CCD678E7BE8D}" name="Numéro de lot" dataDxfId="2"/>
+    <tableColumn id="8" xr3:uid="{6082472F-2D58-4FBE-B207-F4E7921BE9CD}" name="Tantièmes ascenseur 1-1" dataDxfId="16"/>
+    <tableColumn id="9" xr3:uid="{A99085F3-5429-48BD-99D6-C368BEBDE1C5}" name="Tantièmes ascenseur 1-2" dataDxfId="15"/>
+    <tableColumn id="10" xr3:uid="{29D8D538-CA9C-4A95-992C-1A61F5728B38}" name="Tantièmes ascenseur 2" dataDxfId="14"/>
+    <tableColumn id="11" xr3:uid="{A8F24873-3570-4882-AE65-BFA97F5FA58C}" name="Tantièmes ascenseur 3" dataDxfId="13"/>
+    <tableColumn id="14" xr3:uid="{6A0D9C01-B4D3-4227-A105-5BE4105F433C}" name="Tantièmes chauffage" dataDxfId="12"/>
+    <tableColumn id="15" xr3:uid="{DB773FD9-45E5-4A17-9757-9A0D7F7768AA}" name="Tantièmes Batiment 1" dataDxfId="11"/>
+    <tableColumn id="16" xr3:uid="{2CD201B1-8753-466E-8776-252972944B3C}" name="Tantièmes Batiment 2" dataDxfId="10"/>
+    <tableColumn id="17" xr3:uid="{0EB76A3D-2FED-4CE0-9718-92F4FC209896}" name="Tantièmes Batiment 3" dataDxfId="9"/>
+    <tableColumn id="18" xr3:uid="{E820E31C-950D-4D14-8ABF-A71F86753025}" name="Tantièmes Hall 1-1" dataDxfId="8"/>
+    <tableColumn id="19" xr3:uid="{48F0D008-2EAA-4A4F-A6BA-4F8DF16617F8}" name="Tantièmes Hall 1-2" dataDxfId="7"/>
+    <tableColumn id="20" xr3:uid="{DD9B9883-76BB-4950-9FFB-0863C2F256EA}" name="Tantièmes Hall 2" dataDxfId="6"/>
+    <tableColumn id="21" xr3:uid="{BF704940-4EA2-48AF-8BBA-B1F4C695A5E2}" name="Tantièmes Logement/Stationnements" dataDxfId="5"/>
+    <tableColumn id="6" xr3:uid="{23C5575F-C8F7-420A-A8AC-4CD0404C3FB6}" name="Stationnement" dataDxfId="4"/>
+    <tableColumn id="13" xr3:uid="{4AF86A31-E98F-489D-ABE5-CCD678E7BE8D}" name="Numéro de lot" dataDxfId="3"/>
     <tableColumn id="3" xr3:uid="{71861424-FDE4-4C97-8393-5794B9911F90}" name="Lot Nexity"/>
     <tableColumn id="5" xr3:uid="{99825B0E-48FC-48C3-B40C-A8763FC406C7}" name="Etage"/>
   </tableColumns>
@@ -1700,7 +1704,7 @@
   <autoFilter ref="A1:D9" xr:uid="{594FE941-6967-448D-B161-1A22202460B2}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{8584E7DE-3397-4839-B3F7-5BE29387C4A6}" name="Label des règles"/>
-    <tableColumn id="2" xr3:uid="{2DAB5E09-C6DA-4A52-9D36-12A8D2B9BE1E}" name="Limite" dataDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{2DAB5E09-C6DA-4A52-9D36-12A8D2B9BE1E}" name="Limite" dataDxfId="2"/>
     <tableColumn id="3" xr3:uid="{4C91DD63-5027-4E87-B95E-BCB801F28C1C}" name="Taxes"/>
     <tableColumn id="4" xr3:uid="{41CB6CC9-60A9-4712-874D-13D61D2EB5DE}" name="Total TTC">
       <calculatedColumnFormula>IF(BdRegles[[#This Row],[Taxes]]="HT",BdRegles[[#This Row],[Limite]]*1.2,BdRegles[[#This Row],[Limite]])</calculatedColumnFormula>
@@ -1715,7 +1719,7 @@
   <autoFilter ref="A1:B2" xr:uid="{B8BAE385-571F-4715-A042-0AD7A1FDF085}"/>
   <tableColumns count="2">
     <tableColumn id="2" xr3:uid="{75AB35E7-AA7F-46C7-B30C-DC2E9C862FFF}" name="Label du revenu"/>
-    <tableColumn id="3" xr3:uid="{4F014B57-0040-4CC7-87A1-9B988F634586}" name="Montant" dataDxfId="0"/>
+    <tableColumn id="3" xr3:uid="{4F014B57-0040-4CC7-87A1-9B988F634586}" name="Montant" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2032,7 +2036,7 @@
         <v>101</v>
       </c>
       <c r="E2" s="1">
-        <v>1500</v>
+        <v>2900</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
@@ -2049,7 +2053,7 @@
         <v>100</v>
       </c>
       <c r="E3" s="1">
-        <v>1500</v>
+        <v>2900</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
@@ -2083,7 +2087,7 @@
         <v>102</v>
       </c>
       <c r="E5" s="1">
-        <v>2900</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
@@ -2117,7 +2121,7 @@
         <v>103</v>
       </c>
       <c r="E7" s="1">
-        <v>2900</v>
+        <v>2700</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">

--- a/input.xlsx
+++ b/input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/25a393584c41f6f2/Documents/Mon Patrimoine/Projet Immobilier/2023 Terrasses de Galieni/09 - Copropriété/Site de calcul des charges de copropriété/streamlit-copro-charges/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="406" documentId="13_ncr:1_{BC6B5EAF-A22B-4219-B771-90D3DDB91BC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CBB2A207-7565-4E45-A442-BD117D0B57EF}"/>
+  <xr:revisionPtr revIDLastSave="409" documentId="13_ncr:1_{BC6B5EAF-A22B-4219-B771-90D3DDB91BC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DD8E2B95-9F2F-4054-AC1A-699781D7F669}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="889" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="887" uniqueCount="239">
   <si>
     <t>Montant</t>
   </si>
@@ -762,9 +762,6 @@
   </si>
   <si>
     <t>Top consommation chauffage</t>
-  </si>
-  <si>
-    <t>X</t>
   </si>
 </sst>
 </file>
@@ -852,9 +849,6 @@
     <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
   <dxfs count="50">
-    <dxf>
-      <numFmt numFmtId="34" formatCode="_-* #,##0.00\ &quot;€&quot;_-;\-* #,##0.00\ &quot;€&quot;_-;_-* &quot;-&quot;??\ &quot;€&quot;_-;_-@_-"/>
-    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -1525,6 +1519,9 @@
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="34" formatCode="_-* #,##0.00\ &quot;€&quot;_-;\-* #,##0.00\ &quot;€&quot;_-;_-* &quot;-&quot;??\ &quot;€&quot;_-;_-@_-"/>
+    </dxf>
+    <dxf>
       <font>
         <b val="0"/>
         <i val="0"/>
@@ -1567,7 +1564,7 @@
     <tableColumn id="4" xr3:uid="{84F1F30D-4827-43F2-8865-B7957E3E712D}" name="ID"/>
     <tableColumn id="7" xr3:uid="{512EABBD-B863-4251-833D-8B8D1F1626EF}" name="Description"/>
     <tableColumn id="2" xr3:uid="{D09C4BB0-FEBD-4A72-9E87-B5258D8B62D7}" name="Label de la provision"/>
-    <tableColumn id="3" xr3:uid="{347751FB-EF14-4BD7-9D47-427E04136B77}" name="Provision" totalsRowFunction="sum" dataDxfId="49" totalsRowDxfId="0"/>
+    <tableColumn id="3" xr3:uid="{347751FB-EF14-4BD7-9D47-427E04136B77}" name="Provision" totalsRowFunction="sum" dataDxfId="49" totalsRowDxfId="48"/>
     <tableColumn id="5" xr3:uid="{2D489B7F-CE46-4597-8866-46E6A31D6BF8}" name="Top consommation chauffage"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1578,24 +1575,24 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{74E83642-0ED6-4017-A369-70F6DD3FC748}" name="BdCoproprietaires2" displayName="BdCoproprietaires2" ref="A1:P5" totalsRowShown="0">
   <autoFilter ref="A1:P5" xr:uid="{74E83642-0ED6-4017-A369-70F6DD3FC748}"/>
   <tableColumns count="16">
-    <tableColumn id="3" xr3:uid="{1687C042-C916-4161-82C2-2A915364FCD2}" name="Numéro de lot" dataDxfId="48"/>
+    <tableColumn id="3" xr3:uid="{1687C042-C916-4161-82C2-2A915364FCD2}" name="Numéro de lot" dataDxfId="47"/>
     <tableColumn id="1" xr3:uid="{788DBA8C-5B77-4079-8161-FA45C58518AE}" name="Description"/>
-    <tableColumn id="2" xr3:uid="{BE5ACA99-AEAF-4E51-BE0A-B3FB8FCCF08B}" name="Tantièmes copropriété" dataDxfId="47">
+    <tableColumn id="2" xr3:uid="{BE5ACA99-AEAF-4E51-BE0A-B3FB8FCCF08B}" name="Tantièmes copropriété" dataDxfId="46">
       <calculatedColumnFormula>7/10000</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{D62FAA89-C46E-4AF6-A14F-7FD6F46E7F00}" name="Tantièmes ascenseur 1-1" dataDxfId="46"/>
-    <tableColumn id="9" xr3:uid="{C3B9BDED-CB2A-4305-9CBF-418F5971AC1E}" name="Tantièmes ascenseur 1-2" dataDxfId="45"/>
-    <tableColumn id="10" xr3:uid="{C2291DE1-C707-4F83-846E-F914B4B42E52}" name="Tantièmes ascenseur 2" dataDxfId="44"/>
-    <tableColumn id="11" xr3:uid="{4F70F08A-4C2F-41B0-88EB-711B1A0760CD}" name="Tantièmes ascenseur 3" dataDxfId="43"/>
-    <tableColumn id="14" xr3:uid="{80D23396-716C-46AC-9B55-BCBC6C981351}" name="Tantièmes chauffage" dataDxfId="42"/>
-    <tableColumn id="15" xr3:uid="{E3955139-B619-4DD0-8FC1-ECA97048DFE4}" name="Tantièmes Batiment 1" dataDxfId="41"/>
-    <tableColumn id="16" xr3:uid="{C73E9407-A858-4EF7-81C2-6C70C4B157A2}" name="Tantièmes Batiment 2" dataDxfId="40"/>
-    <tableColumn id="17" xr3:uid="{A07338CA-0096-4091-89B2-A46FF2D323C2}" name="Tantièmes Batiment 3" dataDxfId="39"/>
-    <tableColumn id="18" xr3:uid="{7A3012D8-2375-4F10-9E84-F2F5060C6A99}" name="Tantièmes Hall 1-1" dataDxfId="38"/>
-    <tableColumn id="19" xr3:uid="{67961B6E-B577-4A49-B099-623FB85519B4}" name="Tantièmes Hall 1-2" dataDxfId="37"/>
-    <tableColumn id="20" xr3:uid="{03C201C1-F8AA-4D3C-AEBC-425B180BC2D7}" name="Tantièmes Hall 2" dataDxfId="36"/>
-    <tableColumn id="21" xr3:uid="{4826FC05-81A9-4020-8D1D-83D3D5C5A05A}" name="Tantièmes Logement/Stationnements" dataDxfId="35"/>
-    <tableColumn id="6" xr3:uid="{7B87787E-3595-42D5-B815-AF76B67432D8}" name="Tantièmes Stationnement" dataDxfId="34"/>
+    <tableColumn id="8" xr3:uid="{D62FAA89-C46E-4AF6-A14F-7FD6F46E7F00}" name="Tantièmes ascenseur 1-1" dataDxfId="45"/>
+    <tableColumn id="9" xr3:uid="{C3B9BDED-CB2A-4305-9CBF-418F5971AC1E}" name="Tantièmes ascenseur 1-2" dataDxfId="44"/>
+    <tableColumn id="10" xr3:uid="{C2291DE1-C707-4F83-846E-F914B4B42E52}" name="Tantièmes ascenseur 2" dataDxfId="43"/>
+    <tableColumn id="11" xr3:uid="{4F70F08A-4C2F-41B0-88EB-711B1A0760CD}" name="Tantièmes ascenseur 3" dataDxfId="42"/>
+    <tableColumn id="14" xr3:uid="{80D23396-716C-46AC-9B55-BCBC6C981351}" name="Tantièmes chauffage" dataDxfId="41"/>
+    <tableColumn id="15" xr3:uid="{E3955139-B619-4DD0-8FC1-ECA97048DFE4}" name="Tantièmes Batiment 1" dataDxfId="40"/>
+    <tableColumn id="16" xr3:uid="{C73E9407-A858-4EF7-81C2-6C70C4B157A2}" name="Tantièmes Batiment 2" dataDxfId="39"/>
+    <tableColumn id="17" xr3:uid="{A07338CA-0096-4091-89B2-A46FF2D323C2}" name="Tantièmes Batiment 3" dataDxfId="38"/>
+    <tableColumn id="18" xr3:uid="{7A3012D8-2375-4F10-9E84-F2F5060C6A99}" name="Tantièmes Hall 1-1" dataDxfId="37"/>
+    <tableColumn id="19" xr3:uid="{67961B6E-B577-4A49-B099-623FB85519B4}" name="Tantièmes Hall 1-2" dataDxfId="36"/>
+    <tableColumn id="20" xr3:uid="{03C201C1-F8AA-4D3C-AEBC-425B180BC2D7}" name="Tantièmes Hall 2" dataDxfId="35"/>
+    <tableColumn id="21" xr3:uid="{4826FC05-81A9-4020-8D1D-83D3D5C5A05A}" name="Tantièmes Logement/Stationnements" dataDxfId="34"/>
+    <tableColumn id="6" xr3:uid="{7B87787E-3595-42D5-B815-AF76B67432D8}" name="Tantièmes Stationnement" dataDxfId="33"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1614,16 +1611,16 @@
     <sortCondition ref="B1:B47"/>
   </sortState>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{7753A616-C6B5-4B02-AE3F-2A95253630B8}" name="Type de prestation" dataDxfId="33"/>
-    <tableColumn id="2" xr3:uid="{D7B6EA29-CA0A-4C24-9A81-3DF01785BD0C}" name="Label de la prestation" dataDxfId="32"/>
-    <tableColumn id="8" xr3:uid="{91FE62B8-BF79-4277-91C2-4B3C13901105}" name="ID prestation" dataDxfId="31"/>
+    <tableColumn id="1" xr3:uid="{7753A616-C6B5-4B02-AE3F-2A95253630B8}" name="Type de prestation" dataDxfId="32"/>
+    <tableColumn id="2" xr3:uid="{D7B6EA29-CA0A-4C24-9A81-3DF01785BD0C}" name="Label de la prestation" dataDxfId="31"/>
+    <tableColumn id="8" xr3:uid="{91FE62B8-BF79-4277-91C2-4B3C13901105}" name="ID prestation" dataDxfId="30"/>
     <tableColumn id="3" xr3:uid="{2ADF6FF1-1416-43FA-A9BF-E696654CC8CD}" name="Prestataire"/>
-    <tableColumn id="4" xr3:uid="{1C295B62-0191-41FA-9660-5BADE532BEE7}" name="Cout" dataDxfId="30"/>
-    <tableColumn id="5" xr3:uid="{1E3C456B-12BB-4B06-B366-57CE3DA87819}" name="Taxes" dataDxfId="29"/>
-    <tableColumn id="6" xr3:uid="{20997A37-E6E3-4308-9ACD-8D77B289D813}" name="Total TTC" dataDxfId="28">
+    <tableColumn id="4" xr3:uid="{1C295B62-0191-41FA-9660-5BADE532BEE7}" name="Cout" dataDxfId="29"/>
+    <tableColumn id="5" xr3:uid="{1E3C456B-12BB-4B06-B366-57CE3DA87819}" name="Taxes" dataDxfId="28"/>
+    <tableColumn id="6" xr3:uid="{20997A37-E6E3-4308-9ACD-8D77B289D813}" name="Total TTC" dataDxfId="27">
       <calculatedColumnFormula>IF(BdCompetition9[[#This Row],[Taxes]]="TTC",BdCompetition9[[#This Row],[Cout]],BdCompetition9[[#This Row],[Cout]]*1.2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{6BDB0ED6-23A7-4E1A-A654-9E18B0DA38B5}" name="Description" dataDxfId="27"/>
+    <tableColumn id="7" xr3:uid="{6BDB0ED6-23A7-4E1A-A654-9E18B0DA38B5}" name="Description" dataDxfId="26"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1636,16 +1633,16 @@
     <sortCondition ref="B1:B47"/>
   </sortState>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{304F6CD1-2A85-4CA9-B82A-BF03CDAE07A4}" name="Type de prestation" dataDxfId="26"/>
-    <tableColumn id="2" xr3:uid="{068CBFB8-4A62-4CD4-BDAC-46EED59496BC}" name="Label de la prestation" dataDxfId="25"/>
-    <tableColumn id="8" xr3:uid="{2298CECF-E998-45F7-AABA-B59C715EC51B}" name="ID1" dataDxfId="24"/>
+    <tableColumn id="1" xr3:uid="{304F6CD1-2A85-4CA9-B82A-BF03CDAE07A4}" name="Type de prestation" dataDxfId="25"/>
+    <tableColumn id="2" xr3:uid="{068CBFB8-4A62-4CD4-BDAC-46EED59496BC}" name="Label de la prestation" dataDxfId="24"/>
+    <tableColumn id="8" xr3:uid="{2298CECF-E998-45F7-AABA-B59C715EC51B}" name="ID1" dataDxfId="23"/>
     <tableColumn id="3" xr3:uid="{5B85ADF0-B113-45E5-864A-388F8040031F}" name="Prestataire"/>
-    <tableColumn id="4" xr3:uid="{037769D5-5B3A-4710-A4BD-50FC46B19887}" name="Cout" dataDxfId="23"/>
-    <tableColumn id="5" xr3:uid="{DDF49AF2-6301-4A34-B62A-4933E379FE46}" name="Taxes" dataDxfId="22"/>
-    <tableColumn id="6" xr3:uid="{D3462D22-93DD-4646-AC7F-1B3471D6826C}" name="Total TTC" dataDxfId="21">
+    <tableColumn id="4" xr3:uid="{037769D5-5B3A-4710-A4BD-50FC46B19887}" name="Cout" dataDxfId="22"/>
+    <tableColumn id="5" xr3:uid="{DDF49AF2-6301-4A34-B62A-4933E379FE46}" name="Taxes" dataDxfId="21"/>
+    <tableColumn id="6" xr3:uid="{D3462D22-93DD-4646-AC7F-1B3471D6826C}" name="Total TTC" dataDxfId="20">
       <calculatedColumnFormula>IF(BdCompetition[[#This Row],[Taxes]]="TTC",BdCompetition[[#This Row],[Cout]],BdCompetition[[#This Row],[Cout]]*1.2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{D6BDE268-55D6-4FDC-9C89-14F909955D72}" name="Description" dataDxfId="20"/>
+    <tableColumn id="7" xr3:uid="{D6BDE268-55D6-4FDC-9C89-14F909955D72}" name="Description" dataDxfId="19"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1662,7 +1659,7 @@
     <tableColumn id="5" xr3:uid="{F17C785C-9055-484D-A7EC-C3372D32A622}" name="Segment"/>
     <tableColumn id="7" xr3:uid="{3DB4DC80-D06E-4E70-BFE9-9BB75CB5FA62}" name="Classe de provision"/>
     <tableColumn id="2" xr3:uid="{3B6645ED-EDB5-4F76-9846-790ECF4F680D}" name="Label de la provision"/>
-    <tableColumn id="3" xr3:uid="{EBBDC931-D4B2-4BFA-A08F-7BA2EEB44DAA}" name="Provision" totalsRowFunction="sum" dataDxfId="19" totalsRowDxfId="18"/>
+    <tableColumn id="3" xr3:uid="{EBBDC931-D4B2-4BFA-A08F-7BA2EEB44DAA}" name="Provision" totalsRowFunction="sum" dataDxfId="18" totalsRowDxfId="17"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1675,23 +1672,23 @@
     <tableColumn id="12" xr3:uid="{6157D014-929F-42D7-A4BC-12D951282608}" name="Batiment"/>
     <tableColumn id="4" xr3:uid="{81B9BF77-9818-477B-B3E8-1E987064DFDA}" name="Label de lot"/>
     <tableColumn id="1" xr3:uid="{B1F46291-565B-462F-9110-123FFF38DDEE}" name="Nom du coproprietaire"/>
-    <tableColumn id="2" xr3:uid="{DE7A1664-88F0-47A5-B594-27860729EB7C}" name="Tantièmes copropriété" dataDxfId="17">
+    <tableColumn id="2" xr3:uid="{DE7A1664-88F0-47A5-B594-27860729EB7C}" name="Tantièmes copropriété" dataDxfId="16">
       <calculatedColumnFormula>7/10000</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{6082472F-2D58-4FBE-B207-F4E7921BE9CD}" name="Tantièmes ascenseur 1-1" dataDxfId="16"/>
-    <tableColumn id="9" xr3:uid="{A99085F3-5429-48BD-99D6-C368BEBDE1C5}" name="Tantièmes ascenseur 1-2" dataDxfId="15"/>
-    <tableColumn id="10" xr3:uid="{29D8D538-CA9C-4A95-992C-1A61F5728B38}" name="Tantièmes ascenseur 2" dataDxfId="14"/>
-    <tableColumn id="11" xr3:uid="{A8F24873-3570-4882-AE65-BFA97F5FA58C}" name="Tantièmes ascenseur 3" dataDxfId="13"/>
-    <tableColumn id="14" xr3:uid="{6A0D9C01-B4D3-4227-A105-5BE4105F433C}" name="Tantièmes chauffage" dataDxfId="12"/>
-    <tableColumn id="15" xr3:uid="{DB773FD9-45E5-4A17-9757-9A0D7F7768AA}" name="Tantièmes Batiment 1" dataDxfId="11"/>
-    <tableColumn id="16" xr3:uid="{2CD201B1-8753-466E-8776-252972944B3C}" name="Tantièmes Batiment 2" dataDxfId="10"/>
-    <tableColumn id="17" xr3:uid="{0EB76A3D-2FED-4CE0-9718-92F4FC209896}" name="Tantièmes Batiment 3" dataDxfId="9"/>
-    <tableColumn id="18" xr3:uid="{E820E31C-950D-4D14-8ABF-A71F86753025}" name="Tantièmes Hall 1-1" dataDxfId="8"/>
-    <tableColumn id="19" xr3:uid="{48F0D008-2EAA-4A4F-A6BA-4F8DF16617F8}" name="Tantièmes Hall 1-2" dataDxfId="7"/>
-    <tableColumn id="20" xr3:uid="{DD9B9883-76BB-4950-9FFB-0863C2F256EA}" name="Tantièmes Hall 2" dataDxfId="6"/>
-    <tableColumn id="21" xr3:uid="{BF704940-4EA2-48AF-8BBA-B1F4C695A5E2}" name="Tantièmes Logement/Stationnements" dataDxfId="5"/>
-    <tableColumn id="6" xr3:uid="{23C5575F-C8F7-420A-A8AC-4CD0404C3FB6}" name="Stationnement" dataDxfId="4"/>
-    <tableColumn id="13" xr3:uid="{4AF86A31-E98F-489D-ABE5-CCD678E7BE8D}" name="Numéro de lot" dataDxfId="3"/>
+    <tableColumn id="8" xr3:uid="{6082472F-2D58-4FBE-B207-F4E7921BE9CD}" name="Tantièmes ascenseur 1-1" dataDxfId="15"/>
+    <tableColumn id="9" xr3:uid="{A99085F3-5429-48BD-99D6-C368BEBDE1C5}" name="Tantièmes ascenseur 1-2" dataDxfId="14"/>
+    <tableColumn id="10" xr3:uid="{29D8D538-CA9C-4A95-992C-1A61F5728B38}" name="Tantièmes ascenseur 2" dataDxfId="13"/>
+    <tableColumn id="11" xr3:uid="{A8F24873-3570-4882-AE65-BFA97F5FA58C}" name="Tantièmes ascenseur 3" dataDxfId="12"/>
+    <tableColumn id="14" xr3:uid="{6A0D9C01-B4D3-4227-A105-5BE4105F433C}" name="Tantièmes chauffage" dataDxfId="11"/>
+    <tableColumn id="15" xr3:uid="{DB773FD9-45E5-4A17-9757-9A0D7F7768AA}" name="Tantièmes Batiment 1" dataDxfId="10"/>
+    <tableColumn id="16" xr3:uid="{2CD201B1-8753-466E-8776-252972944B3C}" name="Tantièmes Batiment 2" dataDxfId="9"/>
+    <tableColumn id="17" xr3:uid="{0EB76A3D-2FED-4CE0-9718-92F4FC209896}" name="Tantièmes Batiment 3" dataDxfId="8"/>
+    <tableColumn id="18" xr3:uid="{E820E31C-950D-4D14-8ABF-A71F86753025}" name="Tantièmes Hall 1-1" dataDxfId="7"/>
+    <tableColumn id="19" xr3:uid="{48F0D008-2EAA-4A4F-A6BA-4F8DF16617F8}" name="Tantièmes Hall 1-2" dataDxfId="6"/>
+    <tableColumn id="20" xr3:uid="{DD9B9883-76BB-4950-9FFB-0863C2F256EA}" name="Tantièmes Hall 2" dataDxfId="5"/>
+    <tableColumn id="21" xr3:uid="{BF704940-4EA2-48AF-8BBA-B1F4C695A5E2}" name="Tantièmes Logement/Stationnements" dataDxfId="4"/>
+    <tableColumn id="6" xr3:uid="{23C5575F-C8F7-420A-A8AC-4CD0404C3FB6}" name="Stationnement" dataDxfId="3"/>
+    <tableColumn id="13" xr3:uid="{4AF86A31-E98F-489D-ABE5-CCD678E7BE8D}" name="Numéro de lot" dataDxfId="2"/>
     <tableColumn id="3" xr3:uid="{71861424-FDE4-4C97-8393-5794B9911F90}" name="Lot Nexity"/>
     <tableColumn id="5" xr3:uid="{99825B0E-48FC-48C3-B40C-A8763FC406C7}" name="Etage"/>
   </tableColumns>
@@ -1704,7 +1701,7 @@
   <autoFilter ref="A1:D9" xr:uid="{594FE941-6967-448D-B161-1A22202460B2}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{8584E7DE-3397-4839-B3F7-5BE29387C4A6}" name="Label des règles"/>
-    <tableColumn id="2" xr3:uid="{2DAB5E09-C6DA-4A52-9D36-12A8D2B9BE1E}" name="Limite" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{2DAB5E09-C6DA-4A52-9D36-12A8D2B9BE1E}" name="Limite" dataDxfId="1"/>
     <tableColumn id="3" xr3:uid="{4C91DD63-5027-4E87-B95E-BCB801F28C1C}" name="Taxes"/>
     <tableColumn id="4" xr3:uid="{41CB6CC9-60A9-4712-874D-13D61D2EB5DE}" name="Total TTC">
       <calculatedColumnFormula>IF(BdRegles[[#This Row],[Taxes]]="HT",BdRegles[[#This Row],[Limite]]*1.2,BdRegles[[#This Row],[Limite]])</calculatedColumnFormula>
@@ -1719,7 +1716,7 @@
   <autoFilter ref="A1:B2" xr:uid="{B8BAE385-571F-4715-A042-0AD7A1FDF085}"/>
   <tableColumns count="2">
     <tableColumn id="2" xr3:uid="{75AB35E7-AA7F-46C7-B30C-DC2E9C862FFF}" name="Label du revenu"/>
-    <tableColumn id="3" xr3:uid="{4F014B57-0040-4CC7-87A1-9B988F634586}" name="Montant" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{4F014B57-0040-4CC7-87A1-9B988F634586}" name="Montant" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1998,7 +1995,7 @@
     <col min="2" max="2" width="15.7265625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="42.7265625" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="42.7265625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.54296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.08984375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="28.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2461,8 +2458,8 @@
       <c r="E27" s="1">
         <v>23100</v>
       </c>
-      <c r="F27" t="s">
-        <v>239</v>
+      <c r="F27">
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
@@ -2481,8 +2478,8 @@
       <c r="E28" s="1">
         <v>27000</v>
       </c>
-      <c r="F28" t="s">
-        <v>239</v>
+      <c r="F28">
+        <v>2</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.35">

--- a/input.xlsx
+++ b/input.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/25a393584c41f6f2/Documents/Mon Patrimoine/Projet Immobilier/2023 Terrasses de Galieni/09 - Copropriété/Site de calcul des charges de copropriété/streamlit-copro-charges/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Victor Diné\OneDrive\Documents\Mon Patrimoine\Projet Immobilier\2023 Terrasses de Galieni\09 - Copropriété\Site de calcul des charges de copropriété\streamlit-copro-charges\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="493" documentId="13_ncr:1_{BC6B5EAF-A22B-4219-B771-90D3DDB91BC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{294AA836-5EE7-44F2-8CB2-D18602EDAD37}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{471232EB-3AAB-4D08-BC1C-7B7CD1C1D853}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Provisions" sheetId="9" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="438" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="439" uniqueCount="217">
   <si>
     <t>Taxes</t>
   </si>
@@ -455,9 +455,6 @@
     <t>Estimation faite car absent du contrat; 1ère année offerte</t>
   </si>
   <si>
-    <t>Eontrat  P2, engagement sur 3 ans</t>
-  </si>
-  <si>
     <t>Option traitement adoucissant eau avec engagement sur 3 ans</t>
   </si>
   <si>
@@ -690,6 +687,12 @@
   </si>
   <si>
     <t>Terrasses de Gallieni</t>
+  </si>
+  <si>
+    <t>Ordre d'utilisation</t>
+  </si>
+  <si>
+    <t>Contrat  P2, engagement sur 3 ans</t>
   </si>
 </sst>
 </file>
@@ -1140,10 +1143,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{13C2BCD2-5CEA-4301-A571-688E40226767}" name="Provisions" displayName="Provisions" ref="A1:E34">
   <autoFilter ref="A1:E34" xr:uid="{13C2BCD2-5CEA-4301-A571-688E40226767}"/>
@@ -1221,13 +1220,14 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{587622F4-20CE-4A1D-A4F7-C9DCD51AF751}" name="Chauffage" displayName="Chauffage" ref="A1:D3" totalsRowShown="0">
-  <autoFilter ref="A1:D3" xr:uid="{587622F4-20CE-4A1D-A4F7-C9DCD51AF751}"/>
-  <tableColumns count="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{587622F4-20CE-4A1D-A4F7-C9DCD51AF751}" name="Chauffage" displayName="Chauffage" ref="A1:E3" totalsRowShown="0">
+  <autoFilter ref="A1:E3" xr:uid="{587622F4-20CE-4A1D-A4F7-C9DCD51AF751}"/>
+  <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{455C30A6-2C19-4BD7-B8A4-D1C6252917DD}" name="Type de chaudière"/>
     <tableColumn id="2" xr3:uid="{FAAC8507-DC80-422C-8508-496178C23374}" name="ID poste de provision"/>
     <tableColumn id="3" xr3:uid="{17764D71-05D7-4B37-8536-4004CBBE2CD4}" name="Prix unitaire du kWh" dataDxfId="24" dataCellStyle="Currency"/>
     <tableColumn id="4" xr3:uid="{FECEDA0B-3F17-4D04-AB3F-B1B848AA5DB2}" name="Production maximum en kWh"/>
+    <tableColumn id="5" xr3:uid="{ED1B8FB3-6899-430D-BDC7-A9BDBA679526}" name="Ordre d'utilisation"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1500,25 +1500,25 @@
     <tabColor theme="9" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:E34"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="32.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="42.7265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="42.7265625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.08984375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="28.26953125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="42.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="28.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D1" t="s">
         <v>96</v>
@@ -1527,15 +1527,15 @@
         <v>97</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B2" t="s">
         <v>87</v>
       </c>
       <c r="C2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D2" t="s">
         <v>84</v>
@@ -1544,15 +1544,15 @@
         <v>2900</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B3" t="s">
         <v>88</v>
       </c>
       <c r="C3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D3" t="s">
         <v>83</v>
@@ -1561,32 +1561,32 @@
         <v>2900</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E4" s="1">
         <v>2000</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B5" t="s">
         <v>89</v>
       </c>
       <c r="C5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D5" t="s">
         <v>85</v>
@@ -1595,32 +1595,32 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E6" s="1">
         <v>1000</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B7" t="s">
         <v>90</v>
       </c>
       <c r="C7" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D7" t="s">
         <v>86</v>
@@ -1629,26 +1629,26 @@
         <v>2700</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B8" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C8" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D8" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E8" s="1">
         <v>1000</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B9" t="s">
         <v>68</v>
@@ -1663,9 +1663,9 @@
         <v>750</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B10" t="s">
         <v>67</v>
@@ -1680,9 +1680,9 @@
         <v>6200</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B11" t="s">
         <v>64</v>
@@ -1697,9 +1697,9 @@
         <v>1050</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B12" t="s">
         <v>63</v>
@@ -1714,9 +1714,9 @@
         <v>900</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B13" t="s">
         <v>62</v>
@@ -1731,9 +1731,9 @@
         <v>920</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B14" t="s">
         <v>55</v>
@@ -1748,9 +1748,9 @@
         <v>35000</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B15" t="s">
         <v>56</v>
@@ -1765,9 +1765,9 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B16" t="s">
         <v>65</v>
@@ -1782,9 +1782,9 @@
         <v>580</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B17" t="s">
         <v>70</v>
@@ -1799,9 +1799,9 @@
         <v>570</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B18" t="s">
         <v>71</v>
@@ -1816,9 +1816,9 @@
         <v>850</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B19" t="s">
         <v>60</v>
@@ -1833,9 +1833,9 @@
         <v>240</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B20" t="s">
         <v>59</v>
@@ -1850,9 +1850,9 @@
         <v>220</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B21" t="s">
         <v>57</v>
@@ -1867,9 +1867,9 @@
         <v>18000</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B22" t="s">
         <v>61</v>
@@ -1882,9 +1882,9 @@
       </c>
       <c r="E22" s="1"/>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B23" t="s">
         <v>58</v>
@@ -1899,9 +1899,9 @@
         <v>650</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B24" t="s">
         <v>66</v>
@@ -1916,9 +1916,9 @@
         <v>3500</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B25" t="s">
         <v>69</v>
@@ -1933,9 +1933,9 @@
         <v>16800</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B26" t="s">
         <v>79</v>
@@ -1950,15 +1950,15 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B27" t="s">
         <v>73</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>48</v>
@@ -1967,15 +1967,15 @@
         <v>23100</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B28" t="s">
         <v>72</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>47</v>
@@ -1984,9 +1984,9 @@
         <v>27000</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B29" t="s">
         <v>74</v>
@@ -2001,9 +2001,9 @@
         <v>17650</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B30" t="s">
         <v>76</v>
@@ -2018,9 +2018,9 @@
         <v>90</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B31" t="s">
         <v>75</v>
@@ -2035,9 +2035,9 @@
         <v>450</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B32" t="s">
         <v>77</v>
@@ -2052,9 +2052,9 @@
         <v>320</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B33" t="s">
         <v>91</v>
@@ -2069,9 +2069,9 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B34" t="s">
         <v>78</v>
@@ -2100,77 +2100,77 @@
     <tabColor theme="9" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:P5"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.54296875" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="46.36328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.26953125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.5703125" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="46.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="24" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="22.26953125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.6328125" bestFit="1" customWidth="1"/>
-    <col min="9" max="11" width="21.6328125" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="18.6328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="11" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="18.5703125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="17" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="35.1796875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="25.08984375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="35.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="25.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>98</v>
       </c>
       <c r="B1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C1" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="D1" s="9" t="s">
         <v>148</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="E1" s="9" t="s">
         <v>149</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="F1" s="9" t="s">
         <v>150</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="G1" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="H1" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="G1" s="9" t="s">
-        <v>188</v>
-      </c>
-      <c r="H1" s="9" t="s">
+      <c r="I1" s="9" t="s">
         <v>152</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="J1" s="9" t="s">
         <v>153</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="K1" s="9" t="s">
         <v>154</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="L1" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="L1" s="9" t="s">
+      <c r="M1" s="9" t="s">
         <v>156</v>
       </c>
-      <c r="M1" s="9" t="s">
+      <c r="N1" s="9" t="s">
         <v>157</v>
       </c>
-      <c r="N1" s="9" t="s">
+      <c r="O1" s="9" t="s">
         <v>158</v>
       </c>
-      <c r="O1" s="9" t="s">
-        <v>159</v>
-      </c>
       <c r="P1" s="9" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.35">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>225</v>
       </c>
       <c r="B2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C2" s="9">
         <v>217</v>
@@ -2199,12 +2199,12 @@
       </c>
       <c r="P2" s="9"/>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>308</v>
       </c>
       <c r="B3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C3" s="9">
         <v>82</v>
@@ -2231,12 +2231,12 @@
       </c>
       <c r="P3" s="9"/>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>113</v>
       </c>
       <c r="B4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C4" s="9">
         <v>86</v>
@@ -2265,12 +2265,12 @@
       </c>
       <c r="P4" s="9"/>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>462</v>
       </c>
       <c r="B5" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C5" s="9">
         <v>7</v>
@@ -2309,19 +2309,19 @@
     <tabColor theme="9" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:I47"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="48.1796875" customWidth="1"/>
-    <col min="2" max="2" width="66.54296875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="15.54296875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="32.81640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.81640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.26953125" style="7" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.7265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="159.7265625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="48.140625" customWidth="1"/>
+    <col min="2" max="2" width="66.5703125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="15.5703125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="32.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.85546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.28515625" style="7" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="159.7109375" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>106</v>
       </c>
@@ -2329,7 +2329,7 @@
         <v>95</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D1" t="s">
         <v>94</v>
@@ -2344,10 +2344,10 @@
         <v>3</v>
       </c>
       <c r="H1" s="10" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>23</v>
       </c>
@@ -2368,18 +2368,18 @@
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>73</v>
       </c>
       <c r="D3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E3" s="5">
         <v>0</v>
@@ -2392,21 +2392,21 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>72</v>
       </c>
       <c r="D4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E4" s="5">
         <v>10000</v>
@@ -2419,21 +2419,21 @@
         <v>10000</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>55</v>
       </c>
       <c r="D5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E5" s="5">
         <v>16000</v>
@@ -2446,21 +2446,21 @@
         <v>16000</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>73</v>
       </c>
       <c r="D6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E6" s="5">
         <v>1940</v>
@@ -2473,21 +2473,21 @@
         <v>1940</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>72</v>
       </c>
       <c r="D7" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E7" s="5">
         <v>18000</v>
@@ -2500,21 +2500,21 @@
         <v>18000</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>55</v>
       </c>
       <c r="D8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E8" s="5">
         <v>24000</v>
@@ -2527,21 +2527,21 @@
         <v>24000</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>73</v>
       </c>
       <c r="D9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E9" s="5">
         <v>5710</v>
@@ -2554,21 +2554,21 @@
         <v>5710</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>72</v>
       </c>
       <c r="D10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E10" s="5">
         <v>20000</v>
@@ -2581,21 +2581,21 @@
         <v>20000</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>55</v>
       </c>
       <c r="D11" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E11" s="5">
         <v>37000</v>
@@ -2608,21 +2608,21 @@
         <v>37000</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>73</v>
       </c>
       <c r="D12" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E12" s="5">
         <v>10770</v>
@@ -2635,21 +2635,21 @@
         <v>10770</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>72</v>
       </c>
       <c r="D13" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E13" s="5">
         <v>25000</v>
@@ -2662,10 +2662,10 @@
         <v>25000</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>9</v>
       </c>
@@ -2686,7 +2686,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>9</v>
       </c>
@@ -2707,7 +2707,7 @@
         <v>2460</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>28</v>
       </c>
@@ -2734,7 +2734,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>8</v>
       </c>
@@ -2761,7 +2761,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>5</v>
       </c>
@@ -2788,7 +2788,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>5</v>
       </c>
@@ -2815,7 +2815,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>20</v>
       </c>
@@ -2840,10 +2840,10 @@
         <v>16750</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>20</v>
       </c>
@@ -2868,10 +2868,10 @@
         <v>887</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>20</v>
       </c>
@@ -2895,7 +2895,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>20</v>
       </c>
@@ -2919,7 +2919,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>12</v>
       </c>
@@ -2947,7 +2947,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>12</v>
       </c>
@@ -2975,7 +2975,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>12</v>
       </c>
@@ -3003,7 +3003,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>18</v>
       </c>
@@ -3030,7 +3030,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>18</v>
       </c>
@@ -3057,7 +3057,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="87" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:8" ht="120" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>18</v>
       </c>
@@ -3084,12 +3084,12 @@
         <v>133</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C30" t="s">
         <v>87</v>
@@ -3111,12 +3111,12 @@
         <v>135</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C31" t="s">
         <v>88</v>
@@ -3138,12 +3138,12 @@
         <v>135</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C32" t="s">
         <v>89</v>
@@ -3165,12 +3165,12 @@
         <v>135</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C33" t="s">
         <v>90</v>
@@ -3192,7 +3192,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>25</v>
       </c>
@@ -3213,7 +3213,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>12</v>
       </c>
@@ -3241,7 +3241,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>12</v>
       </c>
@@ -3269,7 +3269,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>14</v>
       </c>
@@ -3290,7 +3290,7 @@
         <v>3198.13</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>14</v>
       </c>
@@ -3311,7 +3311,7 @@
         <v>3322.8</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>14</v>
       </c>
@@ -3332,12 +3332,12 @@
         <v>3138.27</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C40" t="s">
         <v>87</v>
@@ -3359,12 +3359,12 @@
         <v>135</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C41" t="s">
         <v>88</v>
@@ -3386,12 +3386,12 @@
         <v>135</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C42" t="s">
         <v>89</v>
@@ -3413,12 +3413,12 @@
         <v>135</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C43" t="s">
         <v>90</v>
@@ -3440,18 +3440,18 @@
         <v>135</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>100</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>69</v>
       </c>
       <c r="D44" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E44" s="6">
         <v>10000</v>
@@ -3466,18 +3466,18 @@
       <c r="H44" s="4"/>
       <c r="I44" s="2"/>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>100</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>69</v>
       </c>
       <c r="D45" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E45" s="6">
         <v>12500</v>
@@ -3492,18 +3492,18 @@
       <c r="H45" s="4"/>
       <c r="I45" s="2"/>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>100</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>69</v>
       </c>
       <c r="D46" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E46" s="6">
         <v>15000</v>
@@ -3518,7 +3518,7 @@
       <c r="H46" s="4"/>
       <c r="I46" s="2"/>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>100</v>
       </c>
@@ -3565,30 +3565,31 @@
     <tabColor theme="9" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.08984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.1796875" customWidth="1"/>
-    <col min="3" max="3" width="21" customWidth="1"/>
+    <col min="1" max="1" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>213</v>
+      </c>
+      <c r="B1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C1" t="s">
+        <v>212</v>
+      </c>
+      <c r="D1" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>214</v>
-      </c>
-      <c r="B1" t="s">
-        <v>205</v>
-      </c>
-      <c r="C1" t="s">
-        <v>213</v>
-      </c>
-      <c r="D1" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>215</v>
       </c>
       <c r="B2">
         <v>10007</v>
@@ -3613,32 +3614,36 @@
   <sheetPr>
     <tabColor theme="9" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.54296875" customWidth="1"/>
-    <col min="3" max="3" width="21.26953125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="28.6328125" customWidth="1"/>
+    <col min="2" max="2" width="20.5703125" customWidth="1"/>
+    <col min="3" max="3" width="21.28515625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="28.5703125" customWidth="1"/>
+    <col min="5" max="5" width="24.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B1" t="s">
         <v>207</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" t="s">
         <v>209</v>
       </c>
-      <c r="D1" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E1" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B2" s="12" t="s">
         <v>72</v>
@@ -3650,10 +3655,13 @@
       <c r="D2">
         <v>150</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B3" t="s">
         <v>73</v>
@@ -3663,6 +3671,9 @@
       </c>
       <c r="D3">
         <v>225</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/input.xlsx
+++ b/input.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Victor Diné\OneDrive\Documents\Mon Patrimoine\Projet Immobilier\2023 Terrasses de Galieni\09 - Copropriété\Site de calcul des charges de copropriété\streamlit-copro-charges\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/25a393584c41f6f2/Documents/Mon Patrimoine/Projet Immobilier/2023 Terrasses de Galieni/09 - Copropriété/Site de calcul des charges de copropriété/streamlit-copro-charges/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{471232EB-3AAB-4D08-BC1C-7B7CD1C1D853}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{471232EB-3AAB-4D08-BC1C-7B7CD1C1D853}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{292F8C4A-B358-465D-91BA-601DADA9744A}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="439" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="439" uniqueCount="218">
   <si>
     <t>Taxes</t>
   </si>
@@ -671,9 +671,6 @@
     <t>Prix unitaire du kWh</t>
   </si>
   <si>
-    <t>Production maximum en kWh</t>
-  </si>
-  <si>
     <t>Atlantic Varmax 2 225</t>
   </si>
   <si>
@@ -693,6 +690,12 @@
   </si>
   <si>
     <t>Contrat  P2, engagement sur 3 ans</t>
+  </si>
+  <si>
+    <t>Production maximum en kW</t>
+  </si>
+  <si>
+    <t>Option adoucissant eau CRAM</t>
   </si>
 </sst>
 </file>
@@ -1143,6 +1146,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{13C2BCD2-5CEA-4301-A571-688E40226767}" name="Provisions" displayName="Provisions" ref="A1:E34">
   <autoFilter ref="A1:E34" xr:uid="{13C2BCD2-5CEA-4301-A571-688E40226767}"/>
@@ -1226,7 +1233,7 @@
     <tableColumn id="1" xr3:uid="{455C30A6-2C19-4BD7-B8A4-D1C6252917DD}" name="Type de chaudière"/>
     <tableColumn id="2" xr3:uid="{FAAC8507-DC80-422C-8508-496178C23374}" name="ID poste de provision"/>
     <tableColumn id="3" xr3:uid="{17764D71-05D7-4B37-8536-4004CBBE2CD4}" name="Prix unitaire du kWh" dataDxfId="24" dataCellStyle="Currency"/>
-    <tableColumn id="4" xr3:uid="{FECEDA0B-3F17-4D04-AB3F-B1B848AA5DB2}" name="Production maximum en kWh"/>
+    <tableColumn id="4" xr3:uid="{FECEDA0B-3F17-4D04-AB3F-B1B848AA5DB2}" name="Production maximum en kW"/>
     <tableColumn id="5" xr3:uid="{ED1B8FB3-6899-430D-BDC7-A9BDBA679526}" name="Ordre d'utilisation"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -2840,7 +2847,7 @@
         <v>16750</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="30" x14ac:dyDescent="0.25">
@@ -2848,7 +2855,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>128</v>
+        <v>217</v>
       </c>
       <c r="C21" t="s">
         <v>74</v>
@@ -3575,13 +3582,13 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B1" t="s">
         <v>204</v>
       </c>
       <c r="C1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D1" t="s">
         <v>205</v>
@@ -3589,7 +3596,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B2">
         <v>10007</v>
@@ -3620,7 +3627,7 @@
     <col min="1" max="1" width="19" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20.5703125" customWidth="1"/>
     <col min="3" max="3" width="21.28515625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="28.5703125" customWidth="1"/>
+    <col min="4" max="4" width="30.140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="24.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3635,15 +3642,15 @@
         <v>208</v>
       </c>
       <c r="D1" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="E1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B2" s="12" t="s">
         <v>72</v>
@@ -3661,7 +3668,7 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B3" t="s">
         <v>73</v>

--- a/input.xlsx
+++ b/input.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/25a393584c41f6f2/Documents/Mon Patrimoine/Projet Immobilier/2023 Terrasses de Galieni/09 - Copropriété/Site de calcul des charges de copropriété/streamlit-copro-charges/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{471232EB-3AAB-4D08-BC1C-7B7CD1C1D853}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{292F8C4A-B358-465D-91BA-601DADA9744A}"/>
+  <xr:revisionPtr revIDLastSave="55" documentId="13_ncr:1_{471232EB-3AAB-4D08-BC1C-7B7CD1C1D853}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{65E87D2B-FC20-4094-AC79-916EE09F4D58}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Provisions" sheetId="9" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="439" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="467" uniqueCount="234">
   <si>
     <t>Taxes</t>
   </si>
@@ -674,9 +674,6 @@
     <t>Atlantic Varmax 2 225</t>
   </si>
   <si>
-    <t>Herz Firematic 150</t>
-  </si>
-  <si>
     <t>Volume à chauffer en m3</t>
   </si>
   <si>
@@ -696,6 +693,68 @@
   </si>
   <si>
     <t>Option adoucissant eau CRAM</t>
+  </si>
+  <si>
+    <t>Prix du granulé: Gruchy = 310€/t, CRAM = 392€/t et Prochalor 500€/t</t>
+  </si>
+  <si>
+    <t>Herz Firematic 20-60</t>
+  </si>
+  <si>
+    <t>Chaudière d'appoint au gaz</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>Entretien porte de parking Eurosofia</t>
+  </si>
+  <si>
+    <t>Eurosofia</t>
+  </si>
+  <si>
+    <t>Rajouté</t>
+  </si>
+  <si>
+    <t>Prestation choisie actuellement</t>
+  </si>
+  <si>
+    <t>Un contrat « ferme-porte » (souvent appelé contrat fermé, par opposition à un contrat « ouvert ») est une modalité de contrat de maintenance et d'entretien, généralement souscrit par le syndicat des copropriétaires pour certains équipements communs (le plus souvent la porte automatique de garage / parking, le portail, ou parfois l'ascenseur).</t>
+  </si>
+  <si>
+    <t>C'est un pot commun d'heures ou d'interventions attribué à un sous-traitant (ou au gardien/maintenance) pour effectuer de petits travaux courants sans avoir à repasser par une demande de devis, un vote du conseil syndical ou un ordre de service formel du syndic à chaque micro-problème.
+Le prestataire dispose d'une marge de manœuvre (le « bac à sable ») pour agir en autonomie ou sur simple signalement dans la limite du forfait.</t>
+  </si>
+  <si>
+    <t>Un contrat de maintenance du désenfumage est une prestation souscrite par le syndicat des copropriétaires pour assurer le bon fonctionnement, la vérification périodique et l'entretien des installations de désenfumage de l'immeuble (les exutoires de fumée en cage d'escalier, les volets, les gaines et les centrales de commande).
+C'est un contrat de maintenance obligatoire et réglementaire, essentiel pour la sécurité incendie de la copropriété.</t>
+  </si>
+  <si>
+    <t>Un contrat de maintenance pour pompe de relevage est une convention souscrite par la copropriété auprès d'un prestataire spécialisé (assainissement, plomberie industrielle) pour assurer l'entretien, le contrôle et le dépannage de la ou des pompes situées dans les sous-sols de l'immeuble.
+C'est un contrat critique pour la salubrité de l'immeuble et la prévention des inondations, en particulier au niveau des sous-sols et des parkings.</t>
+  </si>
+  <si>
+    <t>Un contrat de maintenance de la ventilation de parking (aussi appelée désenfumage mécanique ou extraction du parking) est une prestation souscrite par le syndicat des copropriétaires pour assurer l'entretien et le bon fonctionnement des équipements d'aération et d'extraction d'air dans les sous-sols et garages de l'immeuble.
+C'est un contrat de sécurité obligatoire et réglementaire dès lors que le parking répond à certaines caractéristiques (nombre de niveaux ou de places).</t>
+  </si>
+  <si>
+    <t>Un contrat de maintenance des colonnes sèches est une prestation obligatoire souscrite par le syndicat des copropriétaires pour garantir le bon état de fonctionnement et la résistance sous pression des tuyauteries d'incendie installées dans l'immeuble.
+🚒 À quoi sert une colonne sèche ?
+Une colonne sèche est un tuyau vide fixé verticalement dans la cage d'escalier (ou une gaine technique) reliant le rez-de-chaussée (ou l'extérieur) aux différents étages de l'immeuble.
+En temps normal : La conduite est vide d'eau (d'où le terme « sèche »).
+En cas d'incendie : Les pompiers raccordent leur camion-citerne à l'orifice d'alimentation situé au bas de l'immeuble pour y injecter de l'eau sous forte pression. Ils n'ont plus qu'à monter aux étages concernés et brancher leurs lances directement sur la prise d'étage.
+L'objectif principal : Éviter aux pompiers de devoir dérouler des centaines de mètres de tuyaux dans les escaliers, ce qui fait gagner des minutes précieuses.</t>
+  </si>
+  <si>
+    <t>Un contrat de maintenance du désenfumage en circulation est la prestation souscrite par la copropriété pour contrôler et entretenir les installations d'évacuation de fumée spécifiques aux espaces communs horizontaux de l'immeuble (couloirs, coursives, sas d'accès).
+Il s'agit d'une déclinaison précise du contrat de sécurité incendie global, axée sur les zones de passage qui relient les appartements à la cage d'escalier ou aux sorties.</t>
+  </si>
+  <si>
+    <t>Un contrat de maintenance des blocs de secours (souvent abrégé BAES pour Blocs Autonomes d'Éclairage de Sécurité) est un contrat souscrit par la copropriété pour assurer le bon fonctionnement, la vérification réglementaire et le remplacement des boîtiers lumineux d'urgence installés dans les parties communes.
+Ce sont les petits boîtiers rectangulaires blancs (souvent dotés d'un pictogramme vert avec un bonhomme qui court) situés au-dessus des portes de sortie, dans les cages d'escalier, les couloirs et les sous-sols/parkings.</t>
+  </si>
+  <si>
+    <t>Description longue</t>
   </si>
 </sst>
 </file>
@@ -787,7 +846,31 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="25">
+  <dxfs count="27">
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -1115,24 +1198,6 @@
         <scheme val="minor"/>
       </font>
     </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1151,14 +1216,18 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{13C2BCD2-5CEA-4301-A571-688E40226767}" name="Provisions" displayName="Provisions" ref="A1:E34">
-  <autoFilter ref="A1:E34" xr:uid="{13C2BCD2-5CEA-4301-A571-688E40226767}"/>
-  <tableColumns count="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{13C2BCD2-5CEA-4301-A571-688E40226767}" name="Provisions" displayName="Provisions" ref="A1:F34">
+  <autoFilter ref="A1:F34" xr:uid="{13C2BCD2-5CEA-4301-A571-688E40226767}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F34">
+    <sortCondition descending="1" ref="E1:E34"/>
+  </sortState>
+  <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{3B91602D-BA59-47C1-AD19-EAA938B961C7}" name="ID tantiemes"/>
     <tableColumn id="4" xr3:uid="{84F1F30D-4827-43F2-8865-B7957E3E712D}" name="ID"/>
     <tableColumn id="7" xr3:uid="{512EABBD-B863-4251-833D-8B8D1F1626EF}" name="Description"/>
     <tableColumn id="2" xr3:uid="{D09C4BB0-FEBD-4A72-9E87-B5258D8B62D7}" name="Label de la provision"/>
-    <tableColumn id="3" xr3:uid="{347751FB-EF14-4BD7-9D47-427E04136B77}" name="Provision" totalsRowFunction="sum" dataDxfId="23" totalsRowDxfId="22"/>
+    <tableColumn id="3" xr3:uid="{347751FB-EF14-4BD7-9D47-427E04136B77}" name="Provision" totalsRowFunction="sum" dataDxfId="1" totalsRowDxfId="25"/>
+    <tableColumn id="5" xr3:uid="{CA26B6F8-88AD-418A-B213-749ABA66E926}" name="Description longue" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1168,46 +1237,47 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{74E83642-0ED6-4017-A369-70F6DD3FC748}" name="Lots" displayName="Lots" ref="A1:P5" totalsRowShown="0">
   <autoFilter ref="A1:P5" xr:uid="{74E83642-0ED6-4017-A369-70F6DD3FC748}"/>
   <tableColumns count="16">
-    <tableColumn id="3" xr3:uid="{1687C042-C916-4161-82C2-2A915364FCD2}" name="Numéro de lot" dataDxfId="21"/>
+    <tableColumn id="3" xr3:uid="{1687C042-C916-4161-82C2-2A915364FCD2}" name="Numéro de lot" dataDxfId="24"/>
     <tableColumn id="1" xr3:uid="{788DBA8C-5B77-4079-8161-FA45C58518AE}" name="Description"/>
-    <tableColumn id="2" xr3:uid="{BE5ACA99-AEAF-4E51-BE0A-B3FB8FCCF08B}" name="Tantièmes copropriété" dataDxfId="20">
+    <tableColumn id="2" xr3:uid="{BE5ACA99-AEAF-4E51-BE0A-B3FB8FCCF08B}" name="Tantièmes copropriété" dataDxfId="23">
       <calculatedColumnFormula>7/10000</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{D62FAA89-C46E-4AF6-A14F-7FD6F46E7F00}" name="Tantièmes ascenseur 1-1" dataDxfId="19"/>
-    <tableColumn id="9" xr3:uid="{C3B9BDED-CB2A-4305-9CBF-418F5971AC1E}" name="Tantièmes ascenseur 1-2" dataDxfId="18"/>
-    <tableColumn id="10" xr3:uid="{C2291DE1-C707-4F83-846E-F914B4B42E52}" name="Tantièmes ascenseur 2" dataDxfId="17"/>
-    <tableColumn id="11" xr3:uid="{4F70F08A-4C2F-41B0-88EB-711B1A0760CD}" name="Tantièmes ascenseur 3" dataDxfId="16"/>
-    <tableColumn id="14" xr3:uid="{80D23396-716C-46AC-9B55-BCBC6C981351}" name="Tantièmes chauffage" dataDxfId="15"/>
-    <tableColumn id="15" xr3:uid="{E3955139-B619-4DD0-8FC1-ECA97048DFE4}" name="Tantièmes Batiment 1" dataDxfId="14"/>
-    <tableColumn id="16" xr3:uid="{C73E9407-A858-4EF7-81C2-6C70C4B157A2}" name="Tantièmes Batiment 2" dataDxfId="13"/>
-    <tableColumn id="17" xr3:uid="{A07338CA-0096-4091-89B2-A46FF2D323C2}" name="Tantièmes Batiment 3" dataDxfId="12"/>
-    <tableColumn id="18" xr3:uid="{7A3012D8-2375-4F10-9E84-F2F5060C6A99}" name="Tantièmes Hall 1-1" dataDxfId="11"/>
-    <tableColumn id="19" xr3:uid="{67961B6E-B577-4A49-B099-623FB85519B4}" name="Tantièmes Hall 1-2" dataDxfId="10"/>
-    <tableColumn id="20" xr3:uid="{03C201C1-F8AA-4D3C-AEBC-425B180BC2D7}" name="Tantièmes Hall 2" dataDxfId="9"/>
-    <tableColumn id="21" xr3:uid="{4826FC05-81A9-4020-8D1D-83D3D5C5A05A}" name="Tantièmes Logement/Stationnements" dataDxfId="8"/>
-    <tableColumn id="6" xr3:uid="{7B87787E-3595-42D5-B815-AF76B67432D8}" name="Tantièmes Stationnement" dataDxfId="7"/>
+    <tableColumn id="8" xr3:uid="{D62FAA89-C46E-4AF6-A14F-7FD6F46E7F00}" name="Tantièmes ascenseur 1-1" dataDxfId="22"/>
+    <tableColumn id="9" xr3:uid="{C3B9BDED-CB2A-4305-9CBF-418F5971AC1E}" name="Tantièmes ascenseur 1-2" dataDxfId="21"/>
+    <tableColumn id="10" xr3:uid="{C2291DE1-C707-4F83-846E-F914B4B42E52}" name="Tantièmes ascenseur 2" dataDxfId="20"/>
+    <tableColumn id="11" xr3:uid="{4F70F08A-4C2F-41B0-88EB-711B1A0760CD}" name="Tantièmes ascenseur 3" dataDxfId="19"/>
+    <tableColumn id="14" xr3:uid="{80D23396-716C-46AC-9B55-BCBC6C981351}" name="Tantièmes chauffage" dataDxfId="18"/>
+    <tableColumn id="15" xr3:uid="{E3955139-B619-4DD0-8FC1-ECA97048DFE4}" name="Tantièmes Batiment 1" dataDxfId="17"/>
+    <tableColumn id="16" xr3:uid="{C73E9407-A858-4EF7-81C2-6C70C4B157A2}" name="Tantièmes Batiment 2" dataDxfId="16"/>
+    <tableColumn id="17" xr3:uid="{A07338CA-0096-4091-89B2-A46FF2D323C2}" name="Tantièmes Batiment 3" dataDxfId="15"/>
+    <tableColumn id="18" xr3:uid="{7A3012D8-2375-4F10-9E84-F2F5060C6A99}" name="Tantièmes Hall 1-1" dataDxfId="14"/>
+    <tableColumn id="19" xr3:uid="{67961B6E-B577-4A49-B099-623FB85519B4}" name="Tantièmes Hall 1-2" dataDxfId="13"/>
+    <tableColumn id="20" xr3:uid="{03C201C1-F8AA-4D3C-AEBC-425B180BC2D7}" name="Tantièmes Hall 2" dataDxfId="12"/>
+    <tableColumn id="21" xr3:uid="{4826FC05-81A9-4020-8D1D-83D3D5C5A05A}" name="Tantièmes Logement/Stationnements" dataDxfId="11"/>
+    <tableColumn id="6" xr3:uid="{7B87787E-3595-42D5-B815-AF76B67432D8}" name="Tantièmes Stationnement" dataDxfId="10"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{AFF80A4D-E18B-42B5-9271-DD654E188D32}" name="Prestations" displayName="Prestations" ref="A1:H47" totalsRowShown="0">
-  <autoFilter ref="A1:H47" xr:uid="{AFF80A4D-E18B-42B5-9271-DD654E188D32}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H47">
-    <sortCondition ref="B1:B47"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{AFF80A4D-E18B-42B5-9271-DD654E188D32}" name="Prestations" displayName="Prestations" ref="A1:I48" totalsRowShown="0">
+  <autoFilter ref="A1:I48" xr:uid="{AFF80A4D-E18B-42B5-9271-DD654E188D32}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H48">
+    <sortCondition ref="B1:B48"/>
   </sortState>
-  <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{7753A616-C6B5-4B02-AE3F-2A95253630B8}" name="Type de prestation" dataDxfId="6"/>
-    <tableColumn id="2" xr3:uid="{D7B6EA29-CA0A-4C24-9A81-3DF01785BD0C}" name="Label de la prestation" dataDxfId="5"/>
-    <tableColumn id="8" xr3:uid="{91FE62B8-BF79-4277-91C2-4B3C13901105}" name="ID prestation" dataDxfId="4"/>
+  <tableColumns count="9">
+    <tableColumn id="1" xr3:uid="{7753A616-C6B5-4B02-AE3F-2A95253630B8}" name="Type de prestation" dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{D7B6EA29-CA0A-4C24-9A81-3DF01785BD0C}" name="Label de la prestation" dataDxfId="8"/>
+    <tableColumn id="8" xr3:uid="{91FE62B8-BF79-4277-91C2-4B3C13901105}" name="ID prestation" dataDxfId="7"/>
     <tableColumn id="3" xr3:uid="{2ADF6FF1-1416-43FA-A9BF-E696654CC8CD}" name="Prestataire"/>
-    <tableColumn id="4" xr3:uid="{1C295B62-0191-41FA-9660-5BADE532BEE7}" name="Cout" dataDxfId="3"/>
-    <tableColumn id="5" xr3:uid="{1E3C456B-12BB-4B06-B366-57CE3DA87819}" name="Taxes" dataDxfId="2"/>
-    <tableColumn id="6" xr3:uid="{20997A37-E6E3-4308-9ACD-8D77B289D813}" name="Total TTC" dataDxfId="1">
+    <tableColumn id="4" xr3:uid="{1C295B62-0191-41FA-9660-5BADE532BEE7}" name="Cout" dataDxfId="6"/>
+    <tableColumn id="5" xr3:uid="{1E3C456B-12BB-4B06-B366-57CE3DA87819}" name="Taxes" dataDxfId="5"/>
+    <tableColumn id="6" xr3:uid="{20997A37-E6E3-4308-9ACD-8D77B289D813}" name="Total TTC" dataDxfId="4">
       <calculatedColumnFormula>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{6BDB0ED6-23A7-4E1A-A654-9E18B0DA38B5}" name="Description" dataDxfId="0"/>
+    <tableColumn id="7" xr3:uid="{6BDB0ED6-23A7-4E1A-A654-9E18B0DA38B5}" name="Description" dataDxfId="3"/>
+    <tableColumn id="9" xr3:uid="{C919E254-DE7F-4D3B-8CF6-79E643BBF97F}" name="Prestation choisie actuellement" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1227,14 +1297,15 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{587622F4-20CE-4A1D-A4F7-C9DCD51AF751}" name="Chauffage" displayName="Chauffage" ref="A1:E3" totalsRowShown="0">
-  <autoFilter ref="A1:E3" xr:uid="{587622F4-20CE-4A1D-A4F7-C9DCD51AF751}"/>
-  <tableColumns count="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{587622F4-20CE-4A1D-A4F7-C9DCD51AF751}" name="Chauffage" displayName="Chauffage" ref="A1:F3" totalsRowShown="0">
+  <autoFilter ref="A1:F3" xr:uid="{587622F4-20CE-4A1D-A4F7-C9DCD51AF751}"/>
+  <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{455C30A6-2C19-4BD7-B8A4-D1C6252917DD}" name="Type de chaudière"/>
     <tableColumn id="2" xr3:uid="{FAAC8507-DC80-422C-8508-496178C23374}" name="ID poste de provision"/>
-    <tableColumn id="3" xr3:uid="{17764D71-05D7-4B37-8536-4004CBBE2CD4}" name="Prix unitaire du kWh" dataDxfId="24" dataCellStyle="Currency"/>
+    <tableColumn id="3" xr3:uid="{17764D71-05D7-4B37-8536-4004CBBE2CD4}" name="Prix unitaire du kWh" dataDxfId="26" dataCellStyle="Currency"/>
     <tableColumn id="4" xr3:uid="{FECEDA0B-3F17-4D04-AB3F-B1B848AA5DB2}" name="Production maximum en kW"/>
     <tableColumn id="5" xr3:uid="{ED1B8FB3-6899-430D-BDC7-A9BDBA679526}" name="Ordre d'utilisation"/>
+    <tableColumn id="6" xr3:uid="{F8EB0843-7F05-427F-9B41-0852730F32C9}" name="Description"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1506,7 +1577,7 @@
   <sheetPr>
     <tabColor theme="9" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32.42578125" bestFit="1" customWidth="1"/>
@@ -1514,10 +1585,10 @@
     <col min="3" max="3" width="42.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="42.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="28.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="147" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>203</v>
       </c>
@@ -1533,565 +1604,617 @@
       <c r="E1" s="1" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F1" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B2" t="s">
-        <v>87</v>
+        <v>55</v>
       </c>
       <c r="C2" t="s">
-        <v>164</v>
+        <v>30</v>
       </c>
       <c r="D2" t="s">
-        <v>84</v>
+        <v>30</v>
       </c>
       <c r="E2" s="1">
-        <v>2900</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+        <v>35000</v>
+      </c>
+      <c r="F2" s="2"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B3" t="s">
-        <v>88</v>
-      </c>
-      <c r="C3" t="s">
-        <v>165</v>
-      </c>
-      <c r="D3" t="s">
-        <v>83</v>
+        <v>72</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>47</v>
       </c>
       <c r="E3" s="1">
-        <v>2900</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+        <v>27000</v>
+      </c>
+      <c r="F3" s="2"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B4" t="s">
-        <v>161</v>
-      </c>
-      <c r="C4" t="s">
-        <v>168</v>
-      </c>
-      <c r="D4" t="s">
-        <v>168</v>
+        <v>73</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>48</v>
       </c>
       <c r="E4" s="1">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+        <v>23100</v>
+      </c>
+      <c r="F4" s="2"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="B5" t="s">
-        <v>89</v>
+        <v>57</v>
       </c>
       <c r="C5" t="s">
-        <v>166</v>
+        <v>32</v>
       </c>
       <c r="D5" t="s">
-        <v>85</v>
+        <v>32</v>
       </c>
       <c r="E5" s="1">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+        <v>18000</v>
+      </c>
+      <c r="F5" s="2"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B6" t="s">
-        <v>162</v>
-      </c>
-      <c r="C6" t="s">
-        <v>169</v>
-      </c>
-      <c r="D6" t="s">
-        <v>169</v>
+        <v>74</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="E6" s="1">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+        <v>17650</v>
+      </c>
+      <c r="F6" s="2"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>187</v>
+        <v>147</v>
       </c>
       <c r="B7" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="C7" t="s">
-        <v>167</v>
+        <v>44</v>
       </c>
       <c r="D7" t="s">
-        <v>86</v>
+        <v>44</v>
       </c>
       <c r="E7" s="1">
-        <v>2700</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+        <v>16800</v>
+      </c>
+      <c r="F7" s="2"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="B8" t="s">
-        <v>163</v>
+        <v>67</v>
       </c>
       <c r="C8" t="s">
-        <v>170</v>
+        <v>42</v>
       </c>
       <c r="D8" t="s">
-        <v>170</v>
+        <v>42</v>
       </c>
       <c r="E8" s="1">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+        <v>6200</v>
+      </c>
+      <c r="F8" s="2"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="B9" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="C9" t="s">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="D9" t="s">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="E9" s="1">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+        <v>4000</v>
+      </c>
+      <c r="F9" s="2"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>147</v>
       </c>
       <c r="B10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E10" s="1">
-        <v>6200</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+        <v>3500</v>
+      </c>
+      <c r="F10" s="2"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="B11" t="s">
-        <v>64</v>
+        <v>89</v>
       </c>
       <c r="C11" t="s">
-        <v>39</v>
+        <v>166</v>
       </c>
       <c r="D11" t="s">
-        <v>39</v>
+        <v>85</v>
       </c>
       <c r="E11" s="1">
-        <v>1050</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+        <v>3000</v>
+      </c>
+      <c r="F11" s="2"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B12" t="s">
-        <v>63</v>
+        <v>87</v>
       </c>
       <c r="C12" t="s">
-        <v>38</v>
+        <v>164</v>
       </c>
       <c r="D12" t="s">
-        <v>38</v>
+        <v>84</v>
       </c>
       <c r="E12" s="1">
-        <v>900</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2900</v>
+      </c>
+      <c r="F12" s="2"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B13" t="s">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="C13" t="s">
-        <v>37</v>
+        <v>165</v>
       </c>
       <c r="D13" t="s">
-        <v>37</v>
+        <v>83</v>
       </c>
       <c r="E13" s="1">
-        <v>920</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2900</v>
+      </c>
+      <c r="F13" s="2"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>147</v>
+        <v>187</v>
       </c>
       <c r="B14" t="s">
-        <v>55</v>
+        <v>90</v>
       </c>
       <c r="C14" t="s">
-        <v>30</v>
+        <v>167</v>
       </c>
       <c r="D14" t="s">
-        <v>30</v>
+        <v>86</v>
       </c>
       <c r="E14" s="1">
-        <v>35000</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2700</v>
+      </c>
+      <c r="F14" s="2"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="B15" t="s">
-        <v>56</v>
+        <v>161</v>
       </c>
       <c r="C15" t="s">
-        <v>99</v>
+        <v>168</v>
       </c>
       <c r="D15" t="s">
-        <v>31</v>
+        <v>168</v>
       </c>
       <c r="E15" s="1">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2000</v>
+      </c>
+      <c r="F15" s="2"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>147</v>
       </c>
       <c r="B16" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="C16" t="s">
-        <v>40</v>
+        <v>99</v>
       </c>
       <c r="D16" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="E16" s="1">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+        <v>1500</v>
+      </c>
+      <c r="F16" s="2"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>147</v>
+        <v>199</v>
       </c>
       <c r="B17" t="s">
-        <v>70</v>
+        <v>91</v>
       </c>
       <c r="C17" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="D17" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="E17" s="1">
-        <v>570</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+        <v>1500</v>
+      </c>
+      <c r="F17" s="2"/>
+    </row>
+    <row r="18" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>147</v>
       </c>
       <c r="B18" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="C18" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="D18" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="E18" s="1">
-        <v>850</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+        <v>1050</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="B19" t="s">
-        <v>60</v>
+        <v>162</v>
       </c>
       <c r="C19" t="s">
-        <v>35</v>
+        <v>169</v>
       </c>
       <c r="D19" t="s">
-        <v>35</v>
+        <v>169</v>
       </c>
       <c r="E19" s="1">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+        <v>1000</v>
+      </c>
+      <c r="F19" s="2"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="B20" t="s">
-        <v>59</v>
+        <v>163</v>
       </c>
       <c r="C20" t="s">
-        <v>34</v>
+        <v>170</v>
       </c>
       <c r="D20" t="s">
-        <v>34</v>
+        <v>170</v>
       </c>
       <c r="E20" s="1">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+        <v>1000</v>
+      </c>
+      <c r="F20" s="2"/>
+    </row>
+    <row r="21" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>147</v>
       </c>
       <c r="B21" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C21" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="D21" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="E21" s="1">
-        <v>18000</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+        <v>920</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="135" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>147</v>
       </c>
       <c r="B22" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C22" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D22" t="s">
-        <v>36</v>
-      </c>
-      <c r="E22" s="1"/>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+      <c r="E22" s="1">
+        <v>900</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>147</v>
       </c>
       <c r="B23" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="C23" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="D23" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="E23" s="1">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+        <v>850</v>
+      </c>
+      <c r="F23" s="2"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>147</v>
       </c>
       <c r="B24" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C24" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D24" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E24" s="1">
-        <v>3500</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+        <v>750</v>
+      </c>
+      <c r="F24" s="2"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>147</v>
       </c>
       <c r="B25" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="C25" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="D25" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="E25" s="1">
-        <v>16800</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+        <v>650</v>
+      </c>
+      <c r="F25" s="2"/>
+    </row>
+    <row r="26" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="B26" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="C26" t="s">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="D26" t="s">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="E26" s="1">
-        <v>4000</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+        <v>580</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="B27" t="s">
-        <v>73</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>48</v>
+        <v>70</v>
+      </c>
+      <c r="C27" t="s">
+        <v>45</v>
+      </c>
+      <c r="D27" t="s">
+        <v>45</v>
       </c>
       <c r="E27" s="1">
-        <v>23100</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+        <v>570</v>
+      </c>
+      <c r="F27" s="2"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>151</v>
+        <v>199</v>
       </c>
       <c r="B28" t="s">
-        <v>72</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>47</v>
+        <v>75</v>
+      </c>
+      <c r="C28" t="s">
+        <v>50</v>
+      </c>
+      <c r="D28" t="s">
+        <v>50</v>
       </c>
       <c r="E28" s="1">
-        <v>27000</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+        <v>450</v>
+      </c>
+      <c r="F28" s="2"/>
+    </row>
+    <row r="29" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>151</v>
+        <v>199</v>
       </c>
       <c r="B29" t="s">
-        <v>74</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>49</v>
+        <v>78</v>
+      </c>
+      <c r="C29" t="s">
+        <v>53</v>
+      </c>
+      <c r="D29" t="s">
+        <v>53</v>
       </c>
       <c r="E29" s="1">
-        <v>17650</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+        <v>360</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>199</v>
       </c>
       <c r="B30" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C30" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D30" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E30" s="1">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+        <v>320</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>199</v>
+        <v>147</v>
       </c>
       <c r="B31" t="s">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="C31" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="D31" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="E31" s="1">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+        <v>240</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>199</v>
+        <v>147</v>
       </c>
       <c r="B32" t="s">
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="C32" t="s">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="D32" t="s">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="E32" s="1">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+        <v>220</v>
+      </c>
+      <c r="F32" s="2"/>
+    </row>
+    <row r="33" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>199</v>
       </c>
       <c r="B33" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="C33" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D33" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E33" s="1">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>199</v>
+        <v>147</v>
       </c>
       <c r="B34" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="C34" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="D34" t="s">
-        <v>53</v>
-      </c>
-      <c r="E34" s="1">
-        <v>360</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="E34" s="1"/>
+      <c r="F34" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2315,7 +2438,7 @@
   <sheetPr>
     <tabColor theme="9" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:I47"/>
+  <dimension ref="A1:I48"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="48.140625" customWidth="1"/>
@@ -2325,10 +2448,11 @@
     <col min="5" max="5" width="11.85546875" style="5" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="8.28515625" style="7" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="159.7109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="71.5703125" style="2" customWidth="1"/>
+    <col min="9" max="9" width="48.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>106</v>
       </c>
@@ -2353,8 +2477,11 @@
       <c r="H1" s="10" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="I1" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>23</v>
       </c>
@@ -2375,7 +2502,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>180</v>
       </c>
@@ -2402,7 +2529,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>179</v>
       </c>
@@ -2429,7 +2556,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>171</v>
       </c>
@@ -2456,7 +2583,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>180</v>
       </c>
@@ -2483,7 +2610,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>179</v>
       </c>
@@ -2510,7 +2637,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>171</v>
       </c>
@@ -2537,7 +2664,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>180</v>
       </c>
@@ -2564,7 +2691,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>179</v>
       </c>
@@ -2591,7 +2718,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>171</v>
       </c>
@@ -2618,7 +2745,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>180</v>
       </c>
@@ -2645,7 +2772,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>179</v>
       </c>
@@ -2672,7 +2799,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>9</v>
       </c>
@@ -2693,7 +2820,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>9</v>
       </c>
@@ -2714,7 +2841,7 @@
         <v>2460</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>28</v>
       </c>
@@ -2741,7 +2868,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>8</v>
       </c>
@@ -2767,8 +2894,11 @@
       <c r="H17" s="2" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I17" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>5</v>
       </c>
@@ -2794,8 +2924,11 @@
       <c r="H18" s="2" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I18" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>5</v>
       </c>
@@ -2822,7 +2955,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>20</v>
       </c>
@@ -2847,15 +2980,15 @@
         <v>16750</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C21" t="s">
         <v>74</v>
@@ -2878,7 +3011,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>20</v>
       </c>
@@ -2902,7 +3035,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>20</v>
       </c>
@@ -2926,7 +3059,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>12</v>
       </c>
@@ -2954,7 +3087,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>12</v>
       </c>
@@ -2982,7 +3115,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>12</v>
       </c>
@@ -3009,8 +3142,11 @@
       <c r="H26" s="2" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="27" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="I26" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>18</v>
       </c>
@@ -3037,7 +3173,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>18</v>
       </c>
@@ -3064,7 +3200,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="120" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" ht="225" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>18</v>
       </c>
@@ -3091,42 +3227,45 @@
         <v>133</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>139</v>
+        <v>221</v>
       </c>
       <c r="C30" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="D30" t="s">
-        <v>81</v>
+        <v>222</v>
       </c>
       <c r="E30" s="5">
-        <v>2400</v>
+        <v>434.5</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G30" s="5">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>2880</v>
+        <v>434.5</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C31" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D31" t="s">
         <v>81</v>
@@ -3144,32 +3283,38 @@
       <c r="H31" s="2" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I31" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C32" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D32" t="s">
         <v>81</v>
       </c>
       <c r="E32" s="5">
-        <v>2450</v>
+        <v>2400</v>
       </c>
       <c r="F32" s="7" t="s">
         <v>1</v>
       </c>
       <c r="G32" s="5">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>2940</v>
+        <v>2880</v>
       </c>
       <c r="H32" s="2" t="s">
         <v>135</v>
+      </c>
+      <c r="I32" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
@@ -3177,75 +3322,80 @@
         <v>13</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C33" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D33" t="s">
         <v>81</v>
       </c>
       <c r="E33" s="5">
-        <v>2200</v>
+        <v>2450</v>
       </c>
       <c r="F33" s="7" t="s">
         <v>1</v>
       </c>
       <c r="G33" s="5">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>2640</v>
+        <v>2940</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
+      </c>
+      <c r="I33" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>25</v>
+        <v>146</v>
+      </c>
+      <c r="C34" t="s">
+        <v>90</v>
       </c>
       <c r="D34" t="s">
-        <v>26</v>
+        <v>81</v>
       </c>
       <c r="E34" s="5">
-        <v>160</v>
+        <v>2200</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G34" s="5">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>160</v>
+        <v>2640</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="I34" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="C35" t="s">
-        <v>57</v>
+        <v>25</v>
       </c>
       <c r="D35" t="s">
-        <v>110</v>
+        <v>26</v>
       </c>
       <c r="E35" s="5">
-        <f>2400*12</f>
-        <v>28800</v>
+        <v>160</v>
       </c>
       <c r="F35" s="7" t="s">
         <v>2</v>
       </c>
       <c r="G35" s="5">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>28800</v>
-      </c>
-      <c r="H35" s="2" t="s">
-        <v>109</v>
+        <v>160</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
@@ -3253,7 +3403,7 @@
         <v>12</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C36" t="s">
         <v>57</v>
@@ -3262,39 +3412,46 @@
         <v>110</v>
       </c>
       <c r="E36" s="5">
+        <f>2400*12</f>
+        <v>28800</v>
+      </c>
+      <c r="F36" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="G36" s="5">
+        <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
+        <v>28800</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A37" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C37" t="s">
+        <v>57</v>
+      </c>
+      <c r="D37" t="s">
+        <v>110</v>
+      </c>
+      <c r="E37" s="5">
         <f>1320*12</f>
         <v>15840</v>
       </c>
-      <c r="F36" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="G36" s="5">
+      <c r="F37" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="G37" s="5">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
         <v>15840</v>
       </c>
-      <c r="H36" s="2" t="s">
+      <c r="H37" s="2" t="s">
         <v>108</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A37" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="D37" t="s">
-        <v>17</v>
-      </c>
-      <c r="E37" s="5">
-        <v>3198.13</v>
-      </c>
-      <c r="F37" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="G37" s="5">
-        <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>3198.13</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
@@ -3302,20 +3459,20 @@
         <v>14</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D38" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E38" s="5">
-        <v>3322.8</v>
+        <v>3198.13</v>
       </c>
       <c r="F38" s="7" t="s">
         <v>2</v>
       </c>
       <c r="G38" s="5">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>3322.8</v>
+        <v>3198.13</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
@@ -3323,47 +3480,41 @@
         <v>14</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D39" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E39" s="5">
-        <v>3138.27</v>
+        <v>3322.8</v>
       </c>
       <c r="F39" s="7" t="s">
         <v>2</v>
       </c>
       <c r="G39" s="5">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>3138.27</v>
+        <v>3322.8</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="C40" t="s">
-        <v>87</v>
+        <v>122</v>
       </c>
       <c r="D40" t="s">
-        <v>81</v>
+        <v>15</v>
       </c>
       <c r="E40" s="5">
-        <v>240</v>
+        <v>3138.27</v>
       </c>
       <c r="F40" s="7" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G40" s="5">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>288</v>
-      </c>
-      <c r="H40" s="2" t="s">
-        <v>135</v>
+        <v>3138.27</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
@@ -3371,10 +3522,10 @@
         <v>13</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C41" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D41" t="s">
         <v>81</v>
@@ -3398,10 +3549,10 @@
         <v>13</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C42" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D42" t="s">
         <v>81</v>
@@ -3425,10 +3576,10 @@
         <v>13</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C43" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D43" t="s">
         <v>81</v>
@@ -3449,36 +3600,37 @@
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>69</v>
+        <v>145</v>
+      </c>
+      <c r="C44" t="s">
+        <v>90</v>
       </c>
       <c r="D44" t="s">
-        <v>188</v>
-      </c>
-      <c r="E44" s="6">
-        <v>10000</v>
-      </c>
-      <c r="F44" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="G44" s="6">
-        <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>10000</v>
-      </c>
-      <c r="H44" s="4"/>
-      <c r="I44" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="E44" s="5">
+        <v>240</v>
+      </c>
+      <c r="F44" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="G44" s="5">
+        <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
+        <v>288</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>135</v>
+      </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>100</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>69</v>
@@ -3487,14 +3639,14 @@
         <v>188</v>
       </c>
       <c r="E45" s="6">
-        <v>12500</v>
+        <v>10000</v>
       </c>
       <c r="F45" s="8" t="s">
         <v>2</v>
       </c>
       <c r="G45" s="6">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>12500</v>
+        <v>10000</v>
       </c>
       <c r="H45" s="4"/>
       <c r="I45" s="2"/>
@@ -3504,7 +3656,7 @@
         <v>100</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>69</v>
@@ -3513,14 +3665,14 @@
         <v>188</v>
       </c>
       <c r="E46" s="6">
-        <v>15000</v>
+        <v>12500</v>
       </c>
       <c r="F46" s="8" t="s">
         <v>2</v>
       </c>
       <c r="G46" s="6">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>15000</v>
+        <v>12500</v>
       </c>
       <c r="H46" s="4"/>
       <c r="I46" s="2"/>
@@ -3530,32 +3682,60 @@
         <v>100</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>100</v>
+        <v>190</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>69</v>
       </c>
       <c r="D47" t="s">
+        <v>188</v>
+      </c>
+      <c r="E47" s="6">
+        <v>15000</v>
+      </c>
+      <c r="F47" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="G47" s="6">
+        <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
+        <v>15000</v>
+      </c>
+      <c r="H47" s="4"/>
+      <c r="I47" s="2"/>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A48" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D48" t="s">
         <v>27</v>
       </c>
-      <c r="E47" s="6">
+      <c r="E48" s="6">
         <v>16800</v>
       </c>
-      <c r="F47" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="G47" s="6">
+      <c r="F48" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="G48" s="6">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
         <v>16800</v>
       </c>
-      <c r="H47" s="4" t="s">
+      <c r="H48" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="I47" s="2"/>
+      <c r="I48" s="2" t="s">
+        <v>220</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C47" xr:uid="{10A37FDE-E67C-425C-BC79-E21761381591}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C48" xr:uid="{10A37FDE-E67C-425C-BC79-E21761381591}">
       <formula1>#REF!</formula1>
     </dataValidation>
   </dataValidations>
@@ -3582,13 +3762,13 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B1" t="s">
         <v>204</v>
       </c>
       <c r="C1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D1" t="s">
         <v>205</v>
@@ -3596,7 +3776,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B2">
         <v>10007</v>
@@ -3621,17 +3801,18 @@
   <sheetPr>
     <tabColor theme="9" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20.5703125" customWidth="1"/>
     <col min="3" max="3" width="21.28515625" style="1" customWidth="1"/>
     <col min="4" max="4" width="30.140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="24.7109375" customWidth="1"/>
+    <col min="6" max="6" width="61.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>206</v>
       </c>
@@ -3642,31 +3823,37 @@
         <v>208</v>
       </c>
       <c r="D1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E1" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+        <v>213</v>
+      </c>
+      <c r="F1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="B2" s="12" t="s">
         <v>72</v>
       </c>
       <c r="C2" s="1">
-        <f>392/4600</f>
-        <v>8.5217391304347828E-2</v>
+        <f>310*1.2/4600</f>
+        <v>8.0869565217391304E-2</v>
       </c>
       <c r="D2">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F2" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>209</v>
       </c>
@@ -3681,6 +3868,9 @@
       </c>
       <c r="E3">
         <v>2</v>
+      </c>
+      <c r="F3" t="s">
+        <v>219</v>
       </c>
     </row>
   </sheetData>

--- a/input.xlsx
+++ b/input.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/25a393584c41f6f2/Documents/Mon Patrimoine/Projet Immobilier/2023 Terrasses de Galieni/09 - Copropriété/Site de calcul des charges de copropriété/streamlit-copro-charges/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="55" documentId="13_ncr:1_{471232EB-3AAB-4D08-BC1C-7B7CD1C1D853}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{65E87D2B-FC20-4094-AC79-916EE09F4D58}"/>
+  <xr:revisionPtr revIDLastSave="690" documentId="13_ncr:1_{471232EB-3AAB-4D08-BC1C-7B7CD1C1D853}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8042C2AA-65EE-4305-8FA3-CD53475E7F32}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Provisions" sheetId="9" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="467" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="477" uniqueCount="244">
   <si>
     <t>Taxes</t>
   </si>
@@ -638,15 +638,9 @@
     <t>Lot 308 - T2 2ème étage Batiment 3 exposé ouest</t>
   </si>
   <si>
-    <t>Lot 113 - T2 3ème étage Batiment 1.1 exposé nord/est</t>
-  </si>
-  <si>
     <t>Tantièmes Stationnement</t>
   </si>
   <si>
-    <t>Lot 462 - Parking n°64 au -2</t>
-  </si>
-  <si>
     <t>ID</t>
   </si>
   <si>
@@ -654,9 +648,6 @@
   </si>
   <si>
     <t>ID tantiemes</t>
-  </si>
-  <si>
-    <t>Tantiemes totaux</t>
   </si>
   <si>
     <t>Coefficient d'isolation</t>
@@ -755,6 +746,45 @@
   </si>
   <si>
     <t>Description longue</t>
+  </si>
+  <si>
+    <t>Lot 101</t>
+  </si>
+  <si>
+    <t>Lot 102</t>
+  </si>
+  <si>
+    <t>Lot 103</t>
+  </si>
+  <si>
+    <t>Lot 104</t>
+  </si>
+  <si>
+    <t>Lot 105</t>
+  </si>
+  <si>
+    <t>Lot 106</t>
+  </si>
+  <si>
+    <t>Lot 107</t>
+  </si>
+  <si>
+    <t>Lot 108</t>
+  </si>
+  <si>
+    <t>Lot 109</t>
+  </si>
+  <si>
+    <t>Lot 110</t>
+  </si>
+  <si>
+    <t>Lot 111</t>
+  </si>
+  <si>
+    <t>Lot 112</t>
+  </si>
+  <si>
+    <t>Lot 113 - T2 45m2 3ème étage Batiment 1.1 exposé nord/est</t>
   </si>
 </sst>
 </file>
@@ -820,13 +850,12 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -847,9 +876,6 @@
     <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
   <dxfs count="27">
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -1178,6 +1204,9 @@
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="34" formatCode="_-* #,##0.00\ &quot;€&quot;_-;\-* #,##0.00\ &quot;€&quot;_-;_-* &quot;-&quot;??\ &quot;€&quot;_-;_-@_-"/>
     </dxf>
     <dxf>
@@ -1211,10 +1240,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{13C2BCD2-5CEA-4301-A571-688E40226767}" name="Provisions" displayName="Provisions" ref="A1:F34">
   <autoFilter ref="A1:F34" xr:uid="{13C2BCD2-5CEA-4301-A571-688E40226767}"/>
@@ -1226,35 +1251,38 @@
     <tableColumn id="4" xr3:uid="{84F1F30D-4827-43F2-8865-B7957E3E712D}" name="ID"/>
     <tableColumn id="7" xr3:uid="{512EABBD-B863-4251-833D-8B8D1F1626EF}" name="Description"/>
     <tableColumn id="2" xr3:uid="{D09C4BB0-FEBD-4A72-9E87-B5258D8B62D7}" name="Label de la provision"/>
-    <tableColumn id="3" xr3:uid="{347751FB-EF14-4BD7-9D47-427E04136B77}" name="Provision" totalsRowFunction="sum" dataDxfId="1" totalsRowDxfId="25"/>
-    <tableColumn id="5" xr3:uid="{CA26B6F8-88AD-418A-B213-749ABA66E926}" name="Description longue" dataDxfId="0"/>
+    <tableColumn id="3" xr3:uid="{347751FB-EF14-4BD7-9D47-427E04136B77}" name="Provision" totalsRowFunction="sum" dataDxfId="26" totalsRowDxfId="25"/>
+    <tableColumn id="5" xr3:uid="{CA26B6F8-88AD-418A-B213-749ABA66E926}" name="Description longue" dataDxfId="24"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{74E83642-0ED6-4017-A369-70F6DD3FC748}" name="Lots" displayName="Lots" ref="A1:P5" totalsRowShown="0">
-  <autoFilter ref="A1:P5" xr:uid="{74E83642-0ED6-4017-A369-70F6DD3FC748}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{74E83642-0ED6-4017-A369-70F6DD3FC748}" name="Lots" displayName="Lots" ref="A1:P180" totalsRowShown="0">
+  <autoFilter ref="A1:P180" xr:uid="{74E83642-0ED6-4017-A369-70F6DD3FC748}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:P180">
+    <sortCondition ref="B1:B180"/>
+  </sortState>
   <tableColumns count="16">
-    <tableColumn id="3" xr3:uid="{1687C042-C916-4161-82C2-2A915364FCD2}" name="Numéro de lot" dataDxfId="24"/>
+    <tableColumn id="3" xr3:uid="{1687C042-C916-4161-82C2-2A915364FCD2}" name="Numéro de lot" dataDxfId="23"/>
     <tableColumn id="1" xr3:uid="{788DBA8C-5B77-4079-8161-FA45C58518AE}" name="Description"/>
-    <tableColumn id="2" xr3:uid="{BE5ACA99-AEAF-4E51-BE0A-B3FB8FCCF08B}" name="Tantièmes copropriété" dataDxfId="23">
+    <tableColumn id="2" xr3:uid="{BE5ACA99-AEAF-4E51-BE0A-B3FB8FCCF08B}" name="Tantièmes copropriété" dataDxfId="22">
       <calculatedColumnFormula>7/10000</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{D62FAA89-C46E-4AF6-A14F-7FD6F46E7F00}" name="Tantièmes ascenseur 1-1" dataDxfId="22"/>
-    <tableColumn id="9" xr3:uid="{C3B9BDED-CB2A-4305-9CBF-418F5971AC1E}" name="Tantièmes ascenseur 1-2" dataDxfId="21"/>
-    <tableColumn id="10" xr3:uid="{C2291DE1-C707-4F83-846E-F914B4B42E52}" name="Tantièmes ascenseur 2" dataDxfId="20"/>
-    <tableColumn id="11" xr3:uid="{4F70F08A-4C2F-41B0-88EB-711B1A0760CD}" name="Tantièmes ascenseur 3" dataDxfId="19"/>
-    <tableColumn id="14" xr3:uid="{80D23396-716C-46AC-9B55-BCBC6C981351}" name="Tantièmes chauffage" dataDxfId="18"/>
-    <tableColumn id="15" xr3:uid="{E3955139-B619-4DD0-8FC1-ECA97048DFE4}" name="Tantièmes Batiment 1" dataDxfId="17"/>
-    <tableColumn id="16" xr3:uid="{C73E9407-A858-4EF7-81C2-6C70C4B157A2}" name="Tantièmes Batiment 2" dataDxfId="16"/>
-    <tableColumn id="17" xr3:uid="{A07338CA-0096-4091-89B2-A46FF2D323C2}" name="Tantièmes Batiment 3" dataDxfId="15"/>
-    <tableColumn id="18" xr3:uid="{7A3012D8-2375-4F10-9E84-F2F5060C6A99}" name="Tantièmes Hall 1-1" dataDxfId="14"/>
-    <tableColumn id="19" xr3:uid="{67961B6E-B577-4A49-B099-623FB85519B4}" name="Tantièmes Hall 1-2" dataDxfId="13"/>
-    <tableColumn id="20" xr3:uid="{03C201C1-F8AA-4D3C-AEBC-425B180BC2D7}" name="Tantièmes Hall 2" dataDxfId="12"/>
-    <tableColumn id="21" xr3:uid="{4826FC05-81A9-4020-8D1D-83D3D5C5A05A}" name="Tantièmes Logement/Stationnements" dataDxfId="11"/>
-    <tableColumn id="6" xr3:uid="{7B87787E-3595-42D5-B815-AF76B67432D8}" name="Tantièmes Stationnement" dataDxfId="10"/>
+    <tableColumn id="8" xr3:uid="{D62FAA89-C46E-4AF6-A14F-7FD6F46E7F00}" name="Tantièmes ascenseur 1-1" dataDxfId="21"/>
+    <tableColumn id="9" xr3:uid="{C3B9BDED-CB2A-4305-9CBF-418F5971AC1E}" name="Tantièmes ascenseur 1-2" dataDxfId="20"/>
+    <tableColumn id="10" xr3:uid="{C2291DE1-C707-4F83-846E-F914B4B42E52}" name="Tantièmes ascenseur 2" dataDxfId="19"/>
+    <tableColumn id="11" xr3:uid="{4F70F08A-4C2F-41B0-88EB-711B1A0760CD}" name="Tantièmes ascenseur 3" dataDxfId="18"/>
+    <tableColumn id="14" xr3:uid="{80D23396-716C-46AC-9B55-BCBC6C981351}" name="Tantièmes chauffage" dataDxfId="17"/>
+    <tableColumn id="15" xr3:uid="{E3955139-B619-4DD0-8FC1-ECA97048DFE4}" name="Tantièmes Batiment 1" dataDxfId="16"/>
+    <tableColumn id="16" xr3:uid="{C73E9407-A858-4EF7-81C2-6C70C4B157A2}" name="Tantièmes Batiment 2" dataDxfId="15"/>
+    <tableColumn id="17" xr3:uid="{A07338CA-0096-4091-89B2-A46FF2D323C2}" name="Tantièmes Batiment 3" dataDxfId="14"/>
+    <tableColumn id="18" xr3:uid="{7A3012D8-2375-4F10-9E84-F2F5060C6A99}" name="Tantièmes Hall 1-1" dataDxfId="13"/>
+    <tableColumn id="19" xr3:uid="{67961B6E-B577-4A49-B099-623FB85519B4}" name="Tantièmes Hall 1-2" dataDxfId="12"/>
+    <tableColumn id="20" xr3:uid="{03C201C1-F8AA-4D3C-AEBC-425B180BC2D7}" name="Tantièmes Hall 2" dataDxfId="11"/>
+    <tableColumn id="21" xr3:uid="{4826FC05-81A9-4020-8D1D-83D3D5C5A05A}" name="Tantièmes Logement/Stationnements" dataDxfId="10"/>
+    <tableColumn id="6" xr3:uid="{7B87787E-3595-42D5-B815-AF76B67432D8}" name="Tantièmes Stationnement" dataDxfId="9"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1267,28 +1295,27 @@
     <sortCondition ref="B1:B48"/>
   </sortState>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{7753A616-C6B5-4B02-AE3F-2A95253630B8}" name="Type de prestation" dataDxfId="9"/>
-    <tableColumn id="2" xr3:uid="{D7B6EA29-CA0A-4C24-9A81-3DF01785BD0C}" name="Label de la prestation" dataDxfId="8"/>
-    <tableColumn id="8" xr3:uid="{91FE62B8-BF79-4277-91C2-4B3C13901105}" name="ID prestation" dataDxfId="7"/>
+    <tableColumn id="1" xr3:uid="{7753A616-C6B5-4B02-AE3F-2A95253630B8}" name="Type de prestation" dataDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{D7B6EA29-CA0A-4C24-9A81-3DF01785BD0C}" name="Label de la prestation" dataDxfId="7"/>
+    <tableColumn id="8" xr3:uid="{91FE62B8-BF79-4277-91C2-4B3C13901105}" name="ID prestation" dataDxfId="6"/>
     <tableColumn id="3" xr3:uid="{2ADF6FF1-1416-43FA-A9BF-E696654CC8CD}" name="Prestataire"/>
-    <tableColumn id="4" xr3:uid="{1C295B62-0191-41FA-9660-5BADE532BEE7}" name="Cout" dataDxfId="6"/>
-    <tableColumn id="5" xr3:uid="{1E3C456B-12BB-4B06-B366-57CE3DA87819}" name="Taxes" dataDxfId="5"/>
-    <tableColumn id="6" xr3:uid="{20997A37-E6E3-4308-9ACD-8D77B289D813}" name="Total TTC" dataDxfId="4">
+    <tableColumn id="4" xr3:uid="{1C295B62-0191-41FA-9660-5BADE532BEE7}" name="Cout" dataDxfId="5"/>
+    <tableColumn id="5" xr3:uid="{1E3C456B-12BB-4B06-B366-57CE3DA87819}" name="Taxes" dataDxfId="4"/>
+    <tableColumn id="6" xr3:uid="{20997A37-E6E3-4308-9ACD-8D77B289D813}" name="Total TTC" dataDxfId="3">
       <calculatedColumnFormula>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{6BDB0ED6-23A7-4E1A-A654-9E18B0DA38B5}" name="Description" dataDxfId="3"/>
-    <tableColumn id="9" xr3:uid="{C919E254-DE7F-4D3B-8CF6-79E643BBF97F}" name="Prestation choisie actuellement" dataDxfId="2"/>
+    <tableColumn id="7" xr3:uid="{6BDB0ED6-23A7-4E1A-A654-9E18B0DA38B5}" name="Description" dataDxfId="2"/>
+    <tableColumn id="9" xr3:uid="{C919E254-DE7F-4D3B-8CF6-79E643BBF97F}" name="Prestation choisie actuellement" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{0628909A-75FF-41C1-9EE4-F3C649717216}" name="Residence" displayName="Residence" ref="A1:D2" totalsRowShown="0">
-  <autoFilter ref="A1:D2" xr:uid="{0628909A-75FF-41C1-9EE4-F3C649717216}"/>
-  <tableColumns count="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{0628909A-75FF-41C1-9EE4-F3C649717216}" name="Residence" displayName="Residence" ref="A1:C2" totalsRowShown="0">
+  <autoFilter ref="A1:C2" xr:uid="{0628909A-75FF-41C1-9EE4-F3C649717216}"/>
+  <tableColumns count="3">
     <tableColumn id="4" xr3:uid="{B1EE509D-2894-4393-AA6B-5D042BB6CCBA}" name="Label"/>
-    <tableColumn id="1" xr3:uid="{B2976FCD-016A-46C0-B2A0-0C96EF6E4CA8}" name="Tantiemes totaux"/>
     <tableColumn id="2" xr3:uid="{0EB0E801-9DD6-4459-8AAC-AA0D5AC1F393}" name="Volume à chauffer en m3"/>
     <tableColumn id="3" xr3:uid="{194ABB34-607A-43C7-8DED-8E1BDC9DD34E}" name="Coefficient d'isolation"/>
   </tableColumns>
@@ -1302,7 +1329,7 @@
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{455C30A6-2C19-4BD7-B8A4-D1C6252917DD}" name="Type de chaudière"/>
     <tableColumn id="2" xr3:uid="{FAAC8507-DC80-422C-8508-496178C23374}" name="ID poste de provision"/>
-    <tableColumn id="3" xr3:uid="{17764D71-05D7-4B37-8536-4004CBBE2CD4}" name="Prix unitaire du kWh" dataDxfId="26" dataCellStyle="Currency"/>
+    <tableColumn id="3" xr3:uid="{17764D71-05D7-4B37-8536-4004CBBE2CD4}" name="Prix unitaire du kWh" dataDxfId="0" dataCellStyle="Currency"/>
     <tableColumn id="4" xr3:uid="{FECEDA0B-3F17-4D04-AB3F-B1B848AA5DB2}" name="Production maximum en kW"/>
     <tableColumn id="5" xr3:uid="{ED1B8FB3-6899-430D-BDC7-A9BDBA679526}" name="Ordre d'utilisation"/>
     <tableColumn id="6" xr3:uid="{F8EB0843-7F05-427F-9B41-0852730F32C9}" name="Description"/>
@@ -1590,10 +1617,10 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B1" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C1" t="s">
         <v>138</v>
@@ -1605,7 +1632,7 @@
         <v>97</v>
       </c>
       <c r="F1" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -1880,7 +1907,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B17" t="s">
         <v>91</v>
@@ -1913,7 +1940,7 @@
         <v>1050</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -1969,7 +1996,7 @@
         <v>920</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="135" x14ac:dyDescent="0.25">
@@ -1989,7 +2016,7 @@
         <v>900</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -2063,7 +2090,7 @@
         <v>580</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -2086,7 +2113,7 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B28" t="s">
         <v>75</v>
@@ -2104,7 +2131,7 @@
     </row>
     <row r="29" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B29" t="s">
         <v>78</v>
@@ -2119,12 +2146,12 @@
         <v>360</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B30" t="s">
         <v>77</v>
@@ -2139,7 +2166,7 @@
         <v>320</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="60" x14ac:dyDescent="0.25">
@@ -2159,7 +2186,7 @@
         <v>240</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -2182,7 +2209,7 @@
     </row>
     <row r="33" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B33" t="s">
         <v>76</v>
@@ -2197,7 +2224,7 @@
         <v>90</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -2229,20 +2256,20 @@
   <sheetPr>
     <tabColor theme="9" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:P5"/>
+  <dimension ref="A1:P180"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="46.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="24" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="22.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="11" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="17" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="35.140625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="25.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.28515625" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="54.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="25.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="23.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="22" bestFit="1" customWidth="1"/>
+    <col min="9" max="11" width="22.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="18" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="37.7109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="26.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
@@ -2252,177 +2279,4165 @@
       <c r="B1" t="s">
         <v>138</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="8" t="s">
         <v>147</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="8" t="s">
         <v>148</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="8" t="s">
         <v>187</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H1" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I1" s="8" t="s">
         <v>152</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="J1" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="K1" s="8" t="s">
         <v>154</v>
       </c>
-      <c r="L1" s="9" t="s">
+      <c r="L1" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="M1" s="9" t="s">
+      <c r="M1" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="N1" s="9" t="s">
+      <c r="N1" s="8" t="s">
         <v>157</v>
       </c>
-      <c r="O1" s="9" t="s">
+      <c r="O1" s="8" t="s">
         <v>158</v>
       </c>
-      <c r="P1" s="9" t="s">
+      <c r="P1" s="8" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2" s="8">
+        <v>101</v>
+      </c>
+      <c r="B2" t="s">
+        <v>231</v>
+      </c>
+      <c r="C2">
+        <v>462</v>
+      </c>
+      <c r="I2">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A3" s="8">
+        <v>102</v>
+      </c>
+      <c r="B3" t="s">
+        <v>232</v>
+      </c>
+      <c r="C3">
+        <v>119</v>
+      </c>
+      <c r="D3">
+        <v>389</v>
+      </c>
+      <c r="H3">
+        <v>156</v>
+      </c>
+      <c r="I3">
+        <v>272</v>
+      </c>
+      <c r="L3">
+        <v>585</v>
+      </c>
+      <c r="O3">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A4" s="8">
+        <v>103</v>
+      </c>
+      <c r="B4" t="s">
+        <v>233</v>
+      </c>
+      <c r="C4">
+        <v>83</v>
+      </c>
+      <c r="D4">
+        <v>292</v>
+      </c>
+      <c r="H4">
+        <v>108</v>
+      </c>
+      <c r="I4">
+        <v>191</v>
+      </c>
+      <c r="L4">
+        <v>411</v>
+      </c>
+      <c r="O4">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A5" s="8">
+        <v>104</v>
+      </c>
+      <c r="B5" t="s">
+        <v>234</v>
+      </c>
+      <c r="C5">
+        <v>130</v>
+      </c>
+      <c r="D5">
+        <v>389</v>
+      </c>
+      <c r="H5">
+        <v>157</v>
+      </c>
+      <c r="I5">
+        <v>297</v>
+      </c>
+      <c r="L5">
+        <v>639</v>
+      </c>
+      <c r="O5">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A6" s="8">
+        <v>105</v>
+      </c>
+      <c r="B6" t="s">
+        <v>235</v>
+      </c>
+      <c r="C6">
+        <v>123</v>
+      </c>
+      <c r="D6">
+        <v>389</v>
+      </c>
+      <c r="H6">
+        <v>145</v>
+      </c>
+      <c r="I6">
+        <v>282</v>
+      </c>
+      <c r="L6">
+        <v>607</v>
+      </c>
+      <c r="O6">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A7" s="8">
+        <v>106</v>
+      </c>
+      <c r="B7" t="s">
+        <v>236</v>
+      </c>
+      <c r="C7">
+        <v>122</v>
+      </c>
+      <c r="D7">
+        <v>455</v>
+      </c>
+      <c r="H7">
+        <v>156</v>
+      </c>
+      <c r="I7">
+        <v>280</v>
+      </c>
+      <c r="L7">
+        <v>604</v>
+      </c>
+      <c r="O7">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A8" s="8">
+        <v>107</v>
+      </c>
+      <c r="B8" t="s">
+        <v>237</v>
+      </c>
+      <c r="C8">
+        <v>55</v>
+      </c>
+      <c r="D8">
+        <v>227</v>
+      </c>
+      <c r="H8">
+        <v>69</v>
+      </c>
+      <c r="I8">
+        <v>126</v>
+      </c>
+      <c r="L8">
+        <v>273</v>
+      </c>
+      <c r="O8">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A9" s="8">
+        <v>108</v>
+      </c>
+      <c r="B9" t="s">
+        <v>238</v>
+      </c>
+      <c r="C9">
+        <v>96</v>
+      </c>
+      <c r="D9">
+        <v>341</v>
+      </c>
+      <c r="H9">
+        <v>115</v>
+      </c>
+      <c r="I9">
+        <v>220</v>
+      </c>
+      <c r="L9">
+        <v>474</v>
+      </c>
+      <c r="O9">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A10" s="8">
+        <v>109</v>
+      </c>
+      <c r="B10" t="s">
+        <v>239</v>
+      </c>
+      <c r="C10">
+        <v>123</v>
+      </c>
+      <c r="D10">
+        <v>455</v>
+      </c>
+      <c r="H10">
+        <v>150</v>
+      </c>
+      <c r="I10">
+        <v>282</v>
+      </c>
+      <c r="L10">
+        <v>607</v>
+      </c>
+      <c r="O10">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A11" s="8">
+        <v>110</v>
+      </c>
+      <c r="B11" t="s">
+        <v>240</v>
+      </c>
+      <c r="C11">
+        <v>129</v>
+      </c>
+      <c r="D11">
+        <v>521</v>
+      </c>
+      <c r="H11">
+        <v>156</v>
+      </c>
+      <c r="I11">
+        <v>295</v>
+      </c>
+      <c r="L11">
+        <v>635</v>
+      </c>
+      <c r="O11">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A12" s="8">
+        <v>111</v>
+      </c>
+      <c r="B12" t="s">
+        <v>241</v>
+      </c>
+      <c r="C12">
+        <v>58</v>
+      </c>
+      <c r="D12">
+        <v>260</v>
+      </c>
+      <c r="H12">
+        <v>69</v>
+      </c>
+      <c r="I12">
+        <v>133</v>
+      </c>
+      <c r="L12">
+        <v>287</v>
+      </c>
+      <c r="O12">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A13" s="8">
+        <v>112</v>
+      </c>
+      <c r="B13" t="s">
+        <v>242</v>
+      </c>
+      <c r="C13">
+        <v>91</v>
+      </c>
+      <c r="D13">
+        <v>391</v>
+      </c>
+      <c r="H13">
+        <v>101</v>
+      </c>
+      <c r="I13">
+        <v>209</v>
+      </c>
+      <c r="L13">
+        <v>449</v>
+      </c>
+      <c r="O13">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>113</v>
+      </c>
+      <c r="B14" t="s">
+        <v>243</v>
+      </c>
+      <c r="C14" s="8">
+        <v>86</v>
+      </c>
+      <c r="D14" s="8">
+        <v>391</v>
+      </c>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8">
+        <v>101</v>
+      </c>
+      <c r="I14" s="8">
+        <v>197</v>
+      </c>
+      <c r="J14" s="8"/>
+      <c r="K14" s="8"/>
+      <c r="L14" s="8">
+        <v>425</v>
+      </c>
+      <c r="M14" s="8"/>
+      <c r="N14" s="8"/>
+      <c r="O14" s="8">
+        <v>95</v>
+      </c>
+      <c r="P14" s="8"/>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A15" s="8">
+        <v>114</v>
+      </c>
+      <c r="B15" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 114</v>
+      </c>
+      <c r="C15">
+        <v>94</v>
+      </c>
+      <c r="D15">
+        <v>440</v>
+      </c>
+      <c r="H15">
+        <v>111</v>
+      </c>
+      <c r="I15">
+        <v>215</v>
+      </c>
+      <c r="L15">
+        <v>464</v>
+      </c>
+      <c r="O15">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A16" s="8">
+        <v>115</v>
+      </c>
+      <c r="B16" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 115</v>
+      </c>
+      <c r="C16">
+        <v>60</v>
+      </c>
+      <c r="D16">
+        <v>293</v>
+      </c>
+      <c r="H16">
+        <v>70</v>
+      </c>
+      <c r="I16">
+        <v>139</v>
+      </c>
+      <c r="L16">
+        <v>299</v>
+      </c>
+      <c r="O16">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A17" s="8">
+        <v>116</v>
+      </c>
+      <c r="B17" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 116</v>
+      </c>
+      <c r="C17">
+        <v>162</v>
+      </c>
+      <c r="D17">
+        <v>733</v>
+      </c>
+      <c r="H17">
+        <v>175</v>
+      </c>
+      <c r="I17">
+        <v>371</v>
+      </c>
+      <c r="L17">
+        <v>798</v>
+      </c>
+      <c r="O17">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A18" s="8">
+        <v>117</v>
+      </c>
+      <c r="B18" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 117</v>
+      </c>
+      <c r="C18">
+        <v>202</v>
+      </c>
+      <c r="D18">
+        <v>816</v>
+      </c>
+      <c r="H18">
+        <v>187</v>
+      </c>
+      <c r="I18">
+        <v>463</v>
+      </c>
+      <c r="L18">
+        <v>997</v>
+      </c>
+      <c r="O18">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A19" s="8">
+        <v>118</v>
+      </c>
+      <c r="B19" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 118</v>
+      </c>
+      <c r="C19">
+        <v>294</v>
+      </c>
+      <c r="D19">
+        <v>1020</v>
+      </c>
+      <c r="H19">
+        <v>282</v>
+      </c>
+      <c r="I19">
+        <v>672</v>
+      </c>
+      <c r="L19">
+        <v>1446</v>
+      </c>
+      <c r="O19">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A20" s="8">
+        <v>119</v>
+      </c>
+      <c r="B20" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 119</v>
+      </c>
+      <c r="C20">
+        <v>81</v>
+      </c>
+      <c r="E20">
+        <v>337</v>
+      </c>
+      <c r="H20">
+        <v>101</v>
+      </c>
+      <c r="I20">
+        <v>184</v>
+      </c>
+      <c r="M20">
+        <v>429</v>
+      </c>
+      <c r="O20">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A21" s="8">
+        <v>120</v>
+      </c>
+      <c r="B21" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 120</v>
+      </c>
+      <c r="C21">
+        <v>115</v>
+      </c>
+      <c r="E21">
+        <v>449</v>
+      </c>
+      <c r="H21">
+        <v>149</v>
+      </c>
+      <c r="I21">
+        <v>264</v>
+      </c>
+      <c r="M21">
+        <v>614</v>
+      </c>
+      <c r="O21">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A22" s="8">
+        <v>121</v>
+      </c>
+      <c r="B22" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 121</v>
+      </c>
+      <c r="C22">
+        <v>112</v>
+      </c>
+      <c r="E22">
+        <v>449</v>
+      </c>
+      <c r="H22">
+        <v>148</v>
+      </c>
+      <c r="I22">
+        <v>257</v>
+      </c>
+      <c r="M22">
+        <v>596</v>
+      </c>
+      <c r="O22">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A23" s="8">
+        <v>122</v>
+      </c>
+      <c r="B23" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 122</v>
+      </c>
+      <c r="C23">
+        <v>83</v>
+      </c>
+      <c r="E23">
+        <v>394</v>
+      </c>
+      <c r="H23">
+        <v>100</v>
+      </c>
+      <c r="I23">
+        <v>191</v>
+      </c>
+      <c r="M23">
+        <v>442</v>
+      </c>
+      <c r="O23">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A24" s="8">
+        <v>123</v>
+      </c>
+      <c r="B24" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 123</v>
+      </c>
+      <c r="C24">
+        <v>118</v>
+      </c>
+      <c r="E24">
+        <v>526</v>
+      </c>
+      <c r="H24">
+        <v>149</v>
+      </c>
+      <c r="I24">
+        <v>271</v>
+      </c>
+      <c r="M24">
+        <v>630</v>
+      </c>
+      <c r="O24">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A25" s="8">
+        <v>124</v>
+      </c>
+      <c r="B25" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 124</v>
+      </c>
+      <c r="C25">
+        <v>117</v>
+      </c>
+      <c r="E25">
+        <v>526</v>
+      </c>
+      <c r="H25">
+        <v>148</v>
+      </c>
+      <c r="I25">
+        <v>269</v>
+      </c>
+      <c r="M25">
+        <v>625</v>
+      </c>
+      <c r="O25">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A26" s="8">
+        <v>125</v>
+      </c>
+      <c r="B26" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 125</v>
+      </c>
+      <c r="C26">
+        <v>87</v>
+      </c>
+      <c r="E26">
+        <v>451</v>
+      </c>
+      <c r="H26">
+        <v>100</v>
+      </c>
+      <c r="I26">
+        <v>200</v>
+      </c>
+      <c r="M26">
+        <v>465</v>
+      </c>
+      <c r="O26">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A27" s="8">
+        <v>126</v>
+      </c>
+      <c r="B27" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 126</v>
+      </c>
+      <c r="C27">
+        <v>125</v>
+      </c>
+      <c r="E27">
+        <v>602</v>
+      </c>
+      <c r="H27">
+        <v>149</v>
+      </c>
+      <c r="I27">
+        <v>285</v>
+      </c>
+      <c r="M27">
+        <v>662</v>
+      </c>
+      <c r="O27">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A28" s="8">
+        <v>127</v>
+      </c>
+      <c r="B28" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 127</v>
+      </c>
+      <c r="C28">
+        <v>123</v>
+      </c>
+      <c r="E28">
+        <v>602</v>
+      </c>
+      <c r="H28">
+        <v>148</v>
+      </c>
+      <c r="I28">
+        <v>282</v>
+      </c>
+      <c r="M28">
+        <v>656</v>
+      </c>
+      <c r="O28">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A29" s="8">
+        <v>128</v>
+      </c>
+      <c r="B29" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 128</v>
+      </c>
+      <c r="C29">
+        <v>88</v>
+      </c>
+      <c r="E29">
+        <v>509</v>
+      </c>
+      <c r="H29">
+        <v>100</v>
+      </c>
+      <c r="I29">
+        <v>202</v>
+      </c>
+      <c r="M29">
+        <v>471</v>
+      </c>
+      <c r="O29">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A30" s="8">
+        <v>129</v>
+      </c>
+      <c r="B30" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 129</v>
+      </c>
+      <c r="C30">
+        <v>127</v>
+      </c>
+      <c r="E30">
+        <v>678</v>
+      </c>
+      <c r="H30">
+        <v>148</v>
+      </c>
+      <c r="I30">
+        <v>291</v>
+      </c>
+      <c r="M30">
+        <v>678</v>
+      </c>
+      <c r="O30">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A31" s="8">
+        <v>130</v>
+      </c>
+      <c r="B31" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 130</v>
+      </c>
+      <c r="C31">
+        <v>127</v>
+      </c>
+      <c r="E31">
+        <v>678</v>
+      </c>
+      <c r="H31">
+        <v>148</v>
+      </c>
+      <c r="I31">
+        <v>290</v>
+      </c>
+      <c r="M31">
+        <v>675</v>
+      </c>
+      <c r="O31">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A32" s="8">
+        <v>132</v>
+      </c>
+      <c r="B32" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 132</v>
+      </c>
+      <c r="C32">
+        <v>172</v>
+      </c>
+      <c r="E32">
+        <v>943</v>
+      </c>
+      <c r="H32">
+        <v>189</v>
+      </c>
+      <c r="I32">
+        <v>395</v>
+      </c>
+      <c r="M32">
+        <v>917</v>
+      </c>
+      <c r="O32">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A33" s="8">
+        <v>133</v>
+      </c>
+      <c r="B33" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 133</v>
+      </c>
+      <c r="C33">
+        <v>218</v>
+      </c>
+      <c r="E33">
+        <v>1179</v>
+      </c>
+      <c r="H33">
+        <v>278</v>
+      </c>
+      <c r="I33">
+        <v>499</v>
+      </c>
+      <c r="M33">
+        <v>1158</v>
+      </c>
+      <c r="O33">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A34" s="8">
+        <v>134</v>
+      </c>
+      <c r="B34" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 134</v>
+      </c>
+      <c r="C34">
+        <v>102</v>
+      </c>
+      <c r="E34">
+        <v>566</v>
+      </c>
+      <c r="H34">
+        <v>98</v>
+      </c>
+      <c r="I34">
+        <v>232</v>
+      </c>
+      <c r="M34">
+        <v>541</v>
+      </c>
+      <c r="O34">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A35" s="8">
+        <v>135</v>
+      </c>
+      <c r="B35" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 135</v>
+      </c>
+      <c r="C35">
+        <v>83</v>
+      </c>
+      <c r="E35">
+        <v>566</v>
+      </c>
+      <c r="H35">
+        <v>87</v>
+      </c>
+      <c r="I35">
+        <v>189</v>
+      </c>
+      <c r="M35">
+        <v>441</v>
+      </c>
+      <c r="O35">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A36" s="8">
+        <v>201</v>
+      </c>
+      <c r="B36" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 201</v>
+      </c>
+      <c r="C36">
+        <v>401</v>
+      </c>
+      <c r="J36">
+        <v>1210</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A37" s="8">
+        <v>202</v>
+      </c>
+      <c r="B37" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 202</v>
+      </c>
+      <c r="C37">
+        <v>114</v>
+      </c>
+      <c r="F37">
+        <v>286</v>
+      </c>
+      <c r="H37">
+        <v>153</v>
+      </c>
+      <c r="J37">
+        <v>344</v>
+      </c>
+      <c r="N37">
+        <v>392</v>
+      </c>
+      <c r="O37">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A38" s="8">
+        <v>203</v>
+      </c>
+      <c r="B38" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 203</v>
+      </c>
+      <c r="C38">
+        <v>84</v>
+      </c>
+      <c r="F38">
+        <v>214</v>
+      </c>
+      <c r="H38">
+        <v>106</v>
+      </c>
+      <c r="J38">
+        <v>255</v>
+      </c>
+      <c r="N38">
+        <v>290</v>
+      </c>
+      <c r="O38">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A39" s="8">
+        <v>204</v>
+      </c>
+      <c r="B39" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 204</v>
+      </c>
+      <c r="C39">
+        <v>81</v>
+      </c>
+      <c r="F39">
+        <v>214</v>
+      </c>
+      <c r="H39">
+        <v>105</v>
+      </c>
+      <c r="J39">
+        <v>246</v>
+      </c>
+      <c r="N39">
+        <v>279</v>
+      </c>
+      <c r="O39">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A40" s="8">
+        <v>205</v>
+      </c>
+      <c r="B40" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 205</v>
+      </c>
+      <c r="C40">
+        <v>118</v>
+      </c>
+      <c r="F40">
+        <v>286</v>
+      </c>
+      <c r="H40">
+        <v>156</v>
+      </c>
+      <c r="J40">
+        <v>356</v>
+      </c>
+      <c r="N40">
+        <v>405</v>
+      </c>
+      <c r="O40">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A41" s="8">
+        <v>206</v>
+      </c>
+      <c r="B41" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 206</v>
+      </c>
+      <c r="C41">
+        <v>120</v>
+      </c>
+      <c r="F41">
+        <v>335</v>
+      </c>
+      <c r="H41">
+        <v>153</v>
+      </c>
+      <c r="J41">
+        <v>363</v>
+      </c>
+      <c r="N41">
+        <v>413</v>
+      </c>
+      <c r="O41">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A42" s="8">
+        <v>207</v>
+      </c>
+      <c r="B42" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 207</v>
+      </c>
+      <c r="C42">
+        <v>89</v>
+      </c>
+      <c r="F42">
+        <v>251</v>
+      </c>
+      <c r="H42">
+        <v>106</v>
+      </c>
+      <c r="J42">
+        <v>269</v>
+      </c>
+      <c r="N42">
+        <v>306</v>
+      </c>
+      <c r="O42">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A43" s="8">
+        <v>208</v>
+      </c>
+      <c r="B43" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 208</v>
+      </c>
+      <c r="C43">
+        <v>84</v>
+      </c>
+      <c r="F43">
+        <v>251</v>
+      </c>
+      <c r="H43">
+        <v>105</v>
+      </c>
+      <c r="J43">
+        <v>254</v>
+      </c>
+      <c r="N43">
+        <v>290</v>
+      </c>
+      <c r="O43">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A44" s="8">
+        <v>209</v>
+      </c>
+      <c r="B44" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 209</v>
+      </c>
+      <c r="C44">
+        <v>124</v>
+      </c>
+      <c r="F44">
+        <v>335</v>
+      </c>
+      <c r="H44">
+        <v>156</v>
+      </c>
+      <c r="J44">
+        <v>376</v>
+      </c>
+      <c r="N44">
+        <v>427</v>
+      </c>
+      <c r="O44">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A45" s="8">
+        <v>210</v>
+      </c>
+      <c r="B45" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 210</v>
+      </c>
+      <c r="C45">
+        <v>126</v>
+      </c>
+      <c r="F45">
+        <v>385</v>
+      </c>
+      <c r="H45">
+        <v>153</v>
+      </c>
+      <c r="J45">
+        <v>381</v>
+      </c>
+      <c r="N45">
+        <v>434</v>
+      </c>
+      <c r="O45">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A46" s="8">
+        <v>211</v>
+      </c>
+      <c r="B46" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 211</v>
+      </c>
+      <c r="C46">
+        <v>91</v>
+      </c>
+      <c r="F46">
+        <v>289</v>
+      </c>
+      <c r="H46">
+        <v>106</v>
+      </c>
+      <c r="J46">
+        <v>275</v>
+      </c>
+      <c r="N46">
+        <v>313</v>
+      </c>
+      <c r="O46">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A47" s="8">
+        <v>212</v>
+      </c>
+      <c r="B47" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 212</v>
+      </c>
+      <c r="C47">
+        <v>88</v>
+      </c>
+      <c r="F47">
+        <v>289</v>
+      </c>
+      <c r="H47">
+        <v>105</v>
+      </c>
+      <c r="J47">
+        <v>267</v>
+      </c>
+      <c r="N47">
+        <v>304</v>
+      </c>
+      <c r="O47">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A48" s="8">
+        <v>213</v>
+      </c>
+      <c r="B48" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 213</v>
+      </c>
+      <c r="C48">
+        <v>131</v>
+      </c>
+      <c r="F48">
+        <v>385</v>
+      </c>
+      <c r="H48">
+        <v>156</v>
+      </c>
+      <c r="J48">
+        <v>394</v>
+      </c>
+      <c r="N48">
+        <v>449</v>
+      </c>
+      <c r="O48">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A49" s="8">
+        <v>214</v>
+      </c>
+      <c r="B49" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 214</v>
+      </c>
+      <c r="C49">
+        <v>130</v>
+      </c>
+      <c r="F49">
+        <v>434</v>
+      </c>
+      <c r="H49">
+        <v>153</v>
+      </c>
+      <c r="J49">
+        <v>392</v>
+      </c>
+      <c r="N49">
+        <v>446</v>
+      </c>
+      <c r="O49">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A50" s="8">
+        <v>215</v>
+      </c>
+      <c r="B50" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 215</v>
+      </c>
+      <c r="C50">
+        <v>93</v>
+      </c>
+      <c r="F50">
+        <v>325</v>
+      </c>
+      <c r="H50">
+        <v>106</v>
+      </c>
+      <c r="J50">
+        <v>281</v>
+      </c>
+      <c r="N50">
+        <v>319</v>
+      </c>
+      <c r="O50">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A51" s="8">
+        <v>216</v>
+      </c>
+      <c r="B51" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 216</v>
+      </c>
+      <c r="C51">
+        <v>59</v>
+      </c>
+      <c r="F51">
+        <v>217</v>
+      </c>
+      <c r="H51">
+        <v>69</v>
+      </c>
+      <c r="J51">
+        <v>180</v>
+      </c>
+      <c r="N51">
+        <v>205</v>
+      </c>
+      <c r="O51">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A52" s="8">
+        <v>217</v>
+      </c>
+      <c r="B52" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 217</v>
+      </c>
+      <c r="C52">
+        <v>166</v>
+      </c>
+      <c r="F52">
+        <v>542</v>
+      </c>
+      <c r="H52">
+        <v>194</v>
+      </c>
+      <c r="J52">
+        <v>501</v>
+      </c>
+      <c r="N52">
+        <v>570</v>
+      </c>
+      <c r="O52">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A53" s="8">
+        <v>218</v>
+      </c>
+      <c r="B53" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 218</v>
+      </c>
+      <c r="C53">
+        <v>186</v>
+      </c>
+      <c r="F53">
+        <v>603</v>
+      </c>
+      <c r="H53">
+        <v>201</v>
+      </c>
+      <c r="J53">
+        <v>561</v>
+      </c>
+      <c r="N53">
+        <v>638</v>
+      </c>
+      <c r="O53">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A54" s="8">
+        <v>219</v>
+      </c>
+      <c r="B54" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 219</v>
+      </c>
+      <c r="C54">
+        <v>61</v>
+      </c>
+      <c r="F54">
+        <v>241</v>
+      </c>
+      <c r="H54">
+        <v>69</v>
+      </c>
+      <c r="J54">
+        <v>185</v>
+      </c>
+      <c r="N54">
+        <v>210</v>
+      </c>
+      <c r="O54">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A55" s="8">
+        <v>220</v>
+      </c>
+      <c r="B55" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 220</v>
+      </c>
+      <c r="C55">
+        <v>171</v>
+      </c>
+      <c r="F55">
+        <v>603</v>
+      </c>
+      <c r="H55">
+        <v>194</v>
+      </c>
+      <c r="J55">
+        <v>515</v>
+      </c>
+      <c r="N55">
+        <v>586</v>
+      </c>
+      <c r="O55">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A56" s="8">
+        <v>221</v>
+      </c>
+      <c r="B56" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 221</v>
+      </c>
+      <c r="C56">
+        <v>178</v>
+      </c>
+      <c r="F56">
+        <v>628</v>
+      </c>
+      <c r="H56">
+        <v>201</v>
+      </c>
+      <c r="J56">
+        <v>538</v>
+      </c>
+      <c r="N56">
+        <v>612</v>
+      </c>
+      <c r="O56">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A57" s="8">
+        <v>222</v>
+      </c>
+      <c r="B57" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 222</v>
+      </c>
+      <c r="C57">
+        <v>62</v>
+      </c>
+      <c r="F57">
+        <v>251</v>
+      </c>
+      <c r="H57">
+        <v>69</v>
+      </c>
+      <c r="J57">
+        <v>189</v>
+      </c>
+      <c r="N57">
+        <v>214</v>
+      </c>
+      <c r="O57">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A58" s="8">
+        <v>223</v>
+      </c>
+      <c r="B58" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 223</v>
+      </c>
+      <c r="C58">
+        <v>174</v>
+      </c>
+      <c r="F58">
+        <v>628</v>
+      </c>
+      <c r="H58">
+        <v>194</v>
+      </c>
+      <c r="J58">
+        <v>525</v>
+      </c>
+      <c r="N58">
+        <v>596</v>
+      </c>
+      <c r="O58">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A59" s="8">
+        <v>224</v>
+      </c>
+      <c r="B59" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 224</v>
+      </c>
+      <c r="C59">
+        <v>181</v>
+      </c>
+      <c r="F59">
+        <v>646</v>
+      </c>
+      <c r="H59">
+        <v>201</v>
+      </c>
+      <c r="J59">
+        <v>547</v>
+      </c>
+      <c r="N59">
+        <v>623</v>
+      </c>
+      <c r="O59">
         <v>199</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A2">
+    <row r="60" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A60">
         <v>225</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B60" t="s">
         <v>192</v>
       </c>
-      <c r="C2" s="9">
+      <c r="C60" s="8">
+        <v>197</v>
+      </c>
+      <c r="D60" s="8"/>
+      <c r="E60" s="8"/>
+      <c r="F60" s="8">
+        <v>646</v>
+      </c>
+      <c r="G60" s="8"/>
+      <c r="H60" s="8">
+        <v>198</v>
+      </c>
+      <c r="I60" s="8"/>
+      <c r="J60" s="8">
+        <v>596</v>
+      </c>
+      <c r="K60" s="8"/>
+      <c r="L60" s="8"/>
+      <c r="M60" s="8"/>
+      <c r="N60" s="8">
+        <v>679</v>
+      </c>
+      <c r="O60" s="8">
         <v>217</v>
       </c>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9">
-        <v>646</v>
-      </c>
-      <c r="G2" s="9"/>
-      <c r="H2" s="9">
-        <v>198</v>
-      </c>
-      <c r="I2" s="9"/>
-      <c r="J2" s="9"/>
-      <c r="K2" s="9">
-        <v>596</v>
-      </c>
-      <c r="L2" s="9"/>
-      <c r="M2" s="9"/>
-      <c r="N2" s="9">
-        <v>679</v>
-      </c>
-      <c r="O2" s="9">
-        <v>217</v>
-      </c>
-      <c r="P2" s="9"/>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3">
+      <c r="P60" s="8"/>
+    </row>
+    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A61" s="8">
+        <v>301</v>
+      </c>
+      <c r="B61" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 301</v>
+      </c>
+      <c r="C61">
+        <v>169</v>
+      </c>
+      <c r="H61">
+        <v>255</v>
+      </c>
+      <c r="K61">
+        <v>1031</v>
+      </c>
+      <c r="O61">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A62" s="8">
+        <v>302</v>
+      </c>
+      <c r="B62" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 302</v>
+      </c>
+      <c r="C62">
+        <v>158</v>
+      </c>
+      <c r="H62">
+        <v>223</v>
+      </c>
+      <c r="K62">
+        <v>958</v>
+      </c>
+      <c r="O62">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="63" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A63" s="8">
+        <v>303</v>
+      </c>
+      <c r="B63" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 303</v>
+      </c>
+      <c r="C63">
+        <v>71</v>
+      </c>
+      <c r="H63">
+        <v>96</v>
+      </c>
+      <c r="K63">
+        <v>429</v>
+      </c>
+      <c r="O63">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="64" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A64" s="8">
+        <v>305</v>
+      </c>
+      <c r="B64" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 305</v>
+      </c>
+      <c r="C64">
+        <v>134</v>
+      </c>
+      <c r="G64">
+        <v>1076</v>
+      </c>
+      <c r="H64">
+        <v>182</v>
+      </c>
+      <c r="K64">
+        <v>839</v>
+      </c>
+      <c r="O64">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="65" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A65" s="8">
+        <v>306</v>
+      </c>
+      <c r="B65" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 306</v>
+      </c>
+      <c r="C65">
+        <v>147</v>
+      </c>
+      <c r="G65">
+        <v>1076</v>
+      </c>
+      <c r="H65">
+        <v>181</v>
+      </c>
+      <c r="K65">
+        <v>924</v>
+      </c>
+      <c r="O65">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="66" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A66" s="8">
+        <v>307</v>
+      </c>
+      <c r="B66" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 307</v>
+      </c>
+      <c r="C66">
+        <v>155</v>
+      </c>
+      <c r="G66">
+        <v>1258</v>
+      </c>
+      <c r="H66">
+        <v>194</v>
+      </c>
+      <c r="K66">
+        <v>971</v>
+      </c>
+      <c r="O66">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="67" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A67">
         <v>308</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B67" t="s">
         <v>197</v>
       </c>
-      <c r="C3" s="9">
+      <c r="C67" s="8">
+        <v>75</v>
+      </c>
+      <c r="D67" s="8"/>
+      <c r="E67" s="8"/>
+      <c r="F67" s="8"/>
+      <c r="G67" s="8">
+        <v>755</v>
+      </c>
+      <c r="H67" s="8">
+        <v>93</v>
+      </c>
+      <c r="I67" s="8"/>
+      <c r="J67" s="8"/>
+      <c r="K67" s="8">
+        <v>469</v>
+      </c>
+      <c r="L67" s="8"/>
+      <c r="M67" s="8"/>
+      <c r="N67" s="8"/>
+      <c r="O67" s="8">
         <v>82</v>
       </c>
-      <c r="D3" s="9"/>
-      <c r="E3" s="9"/>
-      <c r="F3" s="9"/>
-      <c r="G3" s="9">
+      <c r="P67" s="8"/>
+    </row>
+    <row r="68" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A68" s="8">
+        <v>310</v>
+      </c>
+      <c r="B68" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 310</v>
+      </c>
+      <c r="C68">
+        <v>52</v>
+      </c>
+      <c r="G68">
+        <v>577</v>
+      </c>
+      <c r="H68">
+        <v>64</v>
+      </c>
+      <c r="K68">
+        <v>330</v>
+      </c>
+      <c r="O68">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="69" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A69" s="8">
+        <v>311</v>
+      </c>
+      <c r="B69" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 311</v>
+      </c>
+      <c r="C69">
+        <v>193</v>
+      </c>
+      <c r="G69">
+        <v>1729</v>
+      </c>
+      <c r="H69">
+        <v>222</v>
+      </c>
+      <c r="K69">
+        <v>1210</v>
+      </c>
+      <c r="O69">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="70" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A70" s="8">
+        <v>312</v>
+      </c>
+      <c r="B70" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 312</v>
+      </c>
+      <c r="C70">
+        <v>133</v>
+      </c>
+      <c r="G70">
+        <v>1153</v>
+      </c>
+      <c r="H70">
+        <v>148</v>
+      </c>
+      <c r="K70">
+        <v>834</v>
+      </c>
+      <c r="O70">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="71" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A71" s="8">
+        <v>313</v>
+      </c>
+      <c r="B71" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 313</v>
+      </c>
+      <c r="C71">
+        <v>72</v>
+      </c>
+      <c r="H71">
+        <v>97</v>
+      </c>
+      <c r="K71">
+        <v>434</v>
+      </c>
+      <c r="O71">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="72" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A72" s="8">
+        <v>314</v>
+      </c>
+      <c r="B72" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 314</v>
+      </c>
+      <c r="C72">
+        <v>79</v>
+      </c>
+      <c r="H72">
+        <v>105</v>
+      </c>
+      <c r="K72">
+        <v>477</v>
+      </c>
+      <c r="O72">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="73" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A73" s="8">
+        <v>315</v>
+      </c>
+      <c r="B73" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 315</v>
+      </c>
+      <c r="C73">
+        <v>85</v>
+      </c>
+      <c r="G73">
         <v>755</v>
       </c>
-      <c r="H3" s="9">
+      <c r="H73">
+        <v>96</v>
+      </c>
+      <c r="K73">
+        <v>531</v>
+      </c>
+      <c r="O73">
         <v>93</v>
       </c>
-      <c r="I3" s="9"/>
-      <c r="J3" s="9"/>
-      <c r="K3" s="9">
+    </row>
+    <row r="74" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A74" s="8">
+        <v>316</v>
+      </c>
+      <c r="B74" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 316</v>
+      </c>
+      <c r="C74">
+        <v>90</v>
+      </c>
+      <c r="G74">
+        <v>755</v>
+      </c>
+      <c r="H74">
+        <v>87</v>
+      </c>
+      <c r="K74">
+        <v>563</v>
+      </c>
+      <c r="O74">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="75" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A75" s="8">
+        <v>401</v>
+      </c>
+      <c r="B75" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 401</v>
+      </c>
+      <c r="C75">
+        <v>7</v>
+      </c>
+      <c r="E75">
+        <v>45</v>
+      </c>
+      <c r="O75">
+        <v>7</v>
+      </c>
+      <c r="P75" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A76" s="8">
+        <v>402</v>
+      </c>
+      <c r="B76" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 402</v>
+      </c>
+      <c r="C76">
+        <v>7</v>
+      </c>
+      <c r="E76">
+        <v>45</v>
+      </c>
+      <c r="O76">
+        <v>7</v>
+      </c>
+      <c r="P76" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A77" s="8">
+        <v>403</v>
+      </c>
+      <c r="B77" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 403</v>
+      </c>
+      <c r="C77">
+        <v>7</v>
+      </c>
+      <c r="D77">
+        <v>39</v>
+      </c>
+      <c r="O77">
+        <v>7</v>
+      </c>
+      <c r="P77" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A78" s="8">
+        <v>404</v>
+      </c>
+      <c r="B78" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 404</v>
+      </c>
+      <c r="C78">
+        <v>7</v>
+      </c>
+      <c r="D78">
+        <v>39</v>
+      </c>
+      <c r="O78">
+        <v>7</v>
+      </c>
+      <c r="P78" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A79" s="8">
+        <v>405</v>
+      </c>
+      <c r="B79" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 405</v>
+      </c>
+      <c r="C79">
+        <v>7</v>
+      </c>
+      <c r="D79">
+        <v>39</v>
+      </c>
+      <c r="O79">
+        <v>7</v>
+      </c>
+      <c r="P79" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A80" s="8">
+        <v>406</v>
+      </c>
+      <c r="B80" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 406</v>
+      </c>
+      <c r="C80">
+        <v>7</v>
+      </c>
+      <c r="D80">
+        <v>39</v>
+      </c>
+      <c r="O80">
+        <v>7</v>
+      </c>
+      <c r="P80" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A81" s="8">
+        <v>407</v>
+      </c>
+      <c r="B81" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 407</v>
+      </c>
+      <c r="C81">
+        <v>7</v>
+      </c>
+      <c r="E81">
+        <v>45</v>
+      </c>
+      <c r="O81">
+        <v>7</v>
+      </c>
+      <c r="P81" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A82" s="8">
+        <v>408</v>
+      </c>
+      <c r="B82" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 408</v>
+      </c>
+      <c r="C82">
+        <v>7</v>
+      </c>
+      <c r="D82">
+        <v>39</v>
+      </c>
+      <c r="O82">
+        <v>7</v>
+      </c>
+      <c r="P82" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A83" s="8">
+        <v>409</v>
+      </c>
+      <c r="B83" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 409</v>
+      </c>
+      <c r="C83">
+        <v>7</v>
+      </c>
+      <c r="E83">
+        <v>45</v>
+      </c>
+      <c r="O83">
+        <v>7</v>
+      </c>
+      <c r="P83" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A84" s="8">
+        <v>410</v>
+      </c>
+      <c r="B84" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 410</v>
+      </c>
+      <c r="C84">
+        <v>7</v>
+      </c>
+      <c r="E84">
+        <v>45</v>
+      </c>
+      <c r="O84">
+        <v>7</v>
+      </c>
+      <c r="P84" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A85" s="8">
+        <v>411</v>
+      </c>
+      <c r="B85" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 411</v>
+      </c>
+      <c r="C85">
+        <v>7</v>
+      </c>
+      <c r="E85">
+        <v>45</v>
+      </c>
+      <c r="O85">
+        <v>7</v>
+      </c>
+      <c r="P85" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A86" s="8">
+        <v>412</v>
+      </c>
+      <c r="B86" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 412</v>
+      </c>
+      <c r="C86">
+        <v>7</v>
+      </c>
+      <c r="E86">
+        <v>45</v>
+      </c>
+      <c r="O86">
+        <v>7</v>
+      </c>
+      <c r="P86" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A87" s="8">
+        <v>413</v>
+      </c>
+      <c r="B87" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 413</v>
+      </c>
+      <c r="C87">
+        <v>7</v>
+      </c>
+      <c r="E87">
+        <v>45</v>
+      </c>
+      <c r="O87">
+        <v>7</v>
+      </c>
+      <c r="P87" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A88" s="8">
+        <v>414</v>
+      </c>
+      <c r="B88" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 414</v>
+      </c>
+      <c r="C88">
+        <v>7</v>
+      </c>
+      <c r="E88">
+        <v>45</v>
+      </c>
+      <c r="O88">
+        <v>7</v>
+      </c>
+      <c r="P88" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A89" s="8">
+        <v>415</v>
+      </c>
+      <c r="B89" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 415</v>
+      </c>
+      <c r="C89">
+        <v>7</v>
+      </c>
+      <c r="E89">
+        <v>45</v>
+      </c>
+      <c r="O89">
+        <v>7</v>
+      </c>
+      <c r="P89" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A90" s="8">
+        <v>416</v>
+      </c>
+      <c r="B90" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 416</v>
+      </c>
+      <c r="C90">
+        <v>7</v>
+      </c>
+      <c r="E90">
+        <v>45</v>
+      </c>
+      <c r="O90">
+        <v>7</v>
+      </c>
+      <c r="P90" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A91" s="8">
+        <v>417</v>
+      </c>
+      <c r="B91" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 417</v>
+      </c>
+      <c r="C91">
+        <v>7</v>
+      </c>
+      <c r="E91">
+        <v>45</v>
+      </c>
+      <c r="O91">
+        <v>7</v>
+      </c>
+      <c r="P91" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A92" s="8">
+        <v>418</v>
+      </c>
+      <c r="B92" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 418</v>
+      </c>
+      <c r="C92">
+        <v>7</v>
+      </c>
+      <c r="E92">
+        <v>45</v>
+      </c>
+      <c r="O92">
+        <v>7</v>
+      </c>
+      <c r="P92" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A93" s="8">
+        <v>419</v>
+      </c>
+      <c r="B93" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 419</v>
+      </c>
+      <c r="C93">
+        <v>7</v>
+      </c>
+      <c r="F93">
+        <v>29</v>
+      </c>
+      <c r="O93">
+        <v>7</v>
+      </c>
+      <c r="P93" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A94" s="8">
+        <v>420</v>
+      </c>
+      <c r="B94" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 420</v>
+      </c>
+      <c r="C94">
+        <v>7</v>
+      </c>
+      <c r="F94">
+        <v>29</v>
+      </c>
+      <c r="O94">
+        <v>7</v>
+      </c>
+      <c r="P94" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A95" s="8">
+        <v>421</v>
+      </c>
+      <c r="B95" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 421</v>
+      </c>
+      <c r="C95">
+        <v>7</v>
+      </c>
+      <c r="F95">
+        <v>29</v>
+      </c>
+      <c r="O95">
+        <v>7</v>
+      </c>
+      <c r="P95" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A96" s="8">
+        <v>422</v>
+      </c>
+      <c r="B96" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 422</v>
+      </c>
+      <c r="C96">
+        <v>7</v>
+      </c>
+      <c r="F96">
+        <v>29</v>
+      </c>
+      <c r="O96">
+        <v>7</v>
+      </c>
+      <c r="P96" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A97" s="8">
+        <v>423</v>
+      </c>
+      <c r="B97" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 423</v>
+      </c>
+      <c r="C97">
+        <v>7</v>
+      </c>
+      <c r="F97">
+        <v>29</v>
+      </c>
+      <c r="O97">
+        <v>7</v>
+      </c>
+      <c r="P97" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A98" s="8">
+        <v>424</v>
+      </c>
+      <c r="B98" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 424</v>
+      </c>
+      <c r="C98">
+        <v>7</v>
+      </c>
+      <c r="F98">
+        <v>29</v>
+      </c>
+      <c r="O98">
+        <v>7</v>
+      </c>
+      <c r="P98" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A99" s="8">
+        <v>425</v>
+      </c>
+      <c r="B99" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 425</v>
+      </c>
+      <c r="C99">
+        <v>7</v>
+      </c>
+      <c r="F99">
+        <v>29</v>
+      </c>
+      <c r="O99">
+        <v>7</v>
+      </c>
+      <c r="P99" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A100" s="8">
+        <v>426</v>
+      </c>
+      <c r="B100" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 426</v>
+      </c>
+      <c r="C100">
+        <v>7</v>
+      </c>
+      <c r="F100">
+        <v>29</v>
+      </c>
+      <c r="O100">
+        <v>7</v>
+      </c>
+      <c r="P100" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A101" s="8">
+        <v>427</v>
+      </c>
+      <c r="B101" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 427</v>
+      </c>
+      <c r="C101">
+        <v>7</v>
+      </c>
+      <c r="F101">
+        <v>29</v>
+      </c>
+      <c r="O101">
+        <v>7</v>
+      </c>
+      <c r="P101" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A102" s="8">
+        <v>428</v>
+      </c>
+      <c r="B102" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 428</v>
+      </c>
+      <c r="C102">
+        <v>7</v>
+      </c>
+      <c r="F102">
+        <v>29</v>
+      </c>
+      <c r="O102">
+        <v>7</v>
+      </c>
+      <c r="P102" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A103" s="8">
+        <v>429</v>
+      </c>
+      <c r="B103" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 429</v>
+      </c>
+      <c r="C103">
+        <v>7</v>
+      </c>
+      <c r="F103">
+        <v>29</v>
+      </c>
+      <c r="O103">
+        <v>7</v>
+      </c>
+      <c r="P103" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A104" s="8">
+        <v>430</v>
+      </c>
+      <c r="B104" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 430</v>
+      </c>
+      <c r="C104">
+        <v>7</v>
+      </c>
+      <c r="F104">
+        <v>29</v>
+      </c>
+      <c r="O104">
+        <v>7</v>
+      </c>
+      <c r="P104" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A105" s="8">
+        <v>431</v>
+      </c>
+      <c r="B105" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 431</v>
+      </c>
+      <c r="C105">
+        <v>7</v>
+      </c>
+      <c r="F105">
+        <v>29</v>
+      </c>
+      <c r="O105">
+        <v>7</v>
+      </c>
+      <c r="P105" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A106" s="8">
+        <v>432</v>
+      </c>
+      <c r="B106" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 432</v>
+      </c>
+      <c r="C106">
+        <v>7</v>
+      </c>
+      <c r="F106">
+        <v>29</v>
+      </c>
+      <c r="O106">
+        <v>7</v>
+      </c>
+      <c r="P106" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A107" s="8">
+        <v>433</v>
+      </c>
+      <c r="B107" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 433</v>
+      </c>
+      <c r="C107">
+        <v>7</v>
+      </c>
+      <c r="G107">
+        <v>86</v>
+      </c>
+      <c r="O107">
+        <v>7</v>
+      </c>
+      <c r="P107" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A108" s="8">
+        <v>434</v>
+      </c>
+      <c r="B108" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 434</v>
+      </c>
+      <c r="C108">
+        <v>7</v>
+      </c>
+      <c r="G108">
+        <v>86</v>
+      </c>
+      <c r="O108">
+        <v>7</v>
+      </c>
+      <c r="P108" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A109" s="8">
+        <v>435</v>
+      </c>
+      <c r="B109" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 435</v>
+      </c>
+      <c r="C109">
+        <v>7</v>
+      </c>
+      <c r="G109">
+        <v>86</v>
+      </c>
+      <c r="O109">
+        <v>7</v>
+      </c>
+      <c r="P109" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A110" s="8">
+        <v>436</v>
+      </c>
+      <c r="B110" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 436</v>
+      </c>
+      <c r="C110">
+        <v>7</v>
+      </c>
+      <c r="G110">
+        <v>86</v>
+      </c>
+      <c r="O110">
+        <v>7</v>
+      </c>
+      <c r="P110" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A111" s="8">
+        <v>437</v>
+      </c>
+      <c r="B111" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 437</v>
+      </c>
+      <c r="C111">
+        <v>7</v>
+      </c>
+      <c r="G111">
+        <v>86</v>
+      </c>
+      <c r="O111">
+        <v>7</v>
+      </c>
+      <c r="P111" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A112" s="8">
+        <v>438</v>
+      </c>
+      <c r="B112" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 438</v>
+      </c>
+      <c r="C112">
+        <v>7</v>
+      </c>
+      <c r="G112">
+        <v>86</v>
+      </c>
+      <c r="O112">
+        <v>7</v>
+      </c>
+      <c r="P112" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A113" s="8">
+        <v>439</v>
+      </c>
+      <c r="B113" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 439</v>
+      </c>
+      <c r="C113">
+        <v>7</v>
+      </c>
+      <c r="G113">
+        <v>86</v>
+      </c>
+      <c r="O113">
+        <v>7</v>
+      </c>
+      <c r="P113" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A114" s="8">
+        <v>440</v>
+      </c>
+      <c r="B114" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 440</v>
+      </c>
+      <c r="C114">
+        <v>7</v>
+      </c>
+      <c r="G114">
+        <v>86</v>
+      </c>
+      <c r="O114">
+        <v>7</v>
+      </c>
+      <c r="P114" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A115" s="8">
+        <v>441</v>
+      </c>
+      <c r="B115" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 441</v>
+      </c>
+      <c r="C115">
+        <v>7</v>
+      </c>
+      <c r="G115">
+        <v>86</v>
+      </c>
+      <c r="O115">
+        <v>7</v>
+      </c>
+      <c r="P115" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A116" s="8">
+        <v>442</v>
+      </c>
+      <c r="B116" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 442</v>
+      </c>
+      <c r="C116">
+        <v>7</v>
+      </c>
+      <c r="G116">
+        <v>86</v>
+      </c>
+      <c r="O116">
+        <v>7</v>
+      </c>
+      <c r="P116" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A117" s="8">
+        <v>443</v>
+      </c>
+      <c r="B117" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 443</v>
+      </c>
+      <c r="C117">
+        <v>7</v>
+      </c>
+      <c r="G117">
+        <v>86</v>
+      </c>
+      <c r="O117">
+        <v>7</v>
+      </c>
+      <c r="P117" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A118" s="8">
+        <v>444</v>
+      </c>
+      <c r="B118" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 444</v>
+      </c>
+      <c r="C118">
+        <v>7</v>
+      </c>
+      <c r="G118">
+        <v>86</v>
+      </c>
+      <c r="O118">
+        <v>7</v>
+      </c>
+      <c r="P118" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A119" s="8">
+        <v>445</v>
+      </c>
+      <c r="B119" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 445</v>
+      </c>
+      <c r="C119">
+        <v>7</v>
+      </c>
+      <c r="G119">
+        <v>86</v>
+      </c>
+      <c r="O119">
+        <v>7</v>
+      </c>
+      <c r="P119" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A120" s="8">
+        <v>446</v>
+      </c>
+      <c r="B120" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 446</v>
+      </c>
+      <c r="C120">
+        <v>7</v>
+      </c>
+      <c r="F120">
+        <v>29</v>
+      </c>
+      <c r="O120">
+        <v>7</v>
+      </c>
+      <c r="P120" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A121" s="8">
+        <v>447</v>
+      </c>
+      <c r="B121" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 447</v>
+      </c>
+      <c r="C121">
+        <v>7</v>
+      </c>
+      <c r="F121">
+        <v>29</v>
+      </c>
+      <c r="O121">
+        <v>7</v>
+      </c>
+      <c r="P121" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A122" s="8">
+        <v>448</v>
+      </c>
+      <c r="B122" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 448</v>
+      </c>
+      <c r="C122">
+        <v>7</v>
+      </c>
+      <c r="F122">
+        <v>29</v>
+      </c>
+      <c r="O122">
+        <v>7</v>
+      </c>
+      <c r="P122" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A123" s="8">
+        <v>449</v>
+      </c>
+      <c r="B123" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 449</v>
+      </c>
+      <c r="C123">
+        <v>7</v>
+      </c>
+      <c r="F123">
+        <v>29</v>
+      </c>
+      <c r="O123">
+        <v>7</v>
+      </c>
+      <c r="P123" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A124" s="8">
+        <v>450</v>
+      </c>
+      <c r="B124" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 450</v>
+      </c>
+      <c r="C124">
+        <v>7</v>
+      </c>
+      <c r="F124">
+        <v>29</v>
+      </c>
+      <c r="O124">
+        <v>7</v>
+      </c>
+      <c r="P124" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A125" s="8">
+        <v>451</v>
+      </c>
+      <c r="B125" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 451</v>
+      </c>
+      <c r="C125">
+        <v>7</v>
+      </c>
+      <c r="E125">
+        <v>45</v>
+      </c>
+      <c r="O125">
+        <v>7</v>
+      </c>
+      <c r="P125" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A126" s="8">
+        <v>452</v>
+      </c>
+      <c r="B126" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 452</v>
+      </c>
+      <c r="C126">
+        <v>7</v>
+      </c>
+      <c r="F126">
+        <v>29</v>
+      </c>
+      <c r="O126">
+        <v>7</v>
+      </c>
+      <c r="P126" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A127" s="8">
+        <v>453</v>
+      </c>
+      <c r="B127" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 453</v>
+      </c>
+      <c r="C127">
+        <v>7</v>
+      </c>
+      <c r="D127">
+        <v>45</v>
+      </c>
+      <c r="O127">
+        <v>7</v>
+      </c>
+      <c r="P127" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A128" s="8">
+        <v>454</v>
+      </c>
+      <c r="B128" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 454</v>
+      </c>
+      <c r="C128">
+        <v>7</v>
+      </c>
+      <c r="D128">
+        <v>45</v>
+      </c>
+      <c r="O128">
+        <v>7</v>
+      </c>
+      <c r="P128" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A129" s="8">
+        <v>455</v>
+      </c>
+      <c r="B129" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 455</v>
+      </c>
+      <c r="C129">
+        <v>7</v>
+      </c>
+      <c r="D129">
+        <v>45</v>
+      </c>
+      <c r="O129">
+        <v>7</v>
+      </c>
+      <c r="P129" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A130" s="8">
+        <v>456</v>
+      </c>
+      <c r="B130" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 456</v>
+      </c>
+      <c r="C130">
+        <v>7</v>
+      </c>
+      <c r="D130">
+        <v>45</v>
+      </c>
+      <c r="O130">
+        <v>7</v>
+      </c>
+      <c r="P130" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A131" s="8">
+        <v>457</v>
+      </c>
+      <c r="B131" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 457</v>
+      </c>
+      <c r="C131">
+        <v>7</v>
+      </c>
+      <c r="E131">
+        <v>52</v>
+      </c>
+      <c r="O131">
+        <v>7</v>
+      </c>
+      <c r="P131" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A132" s="8">
+        <v>458</v>
+      </c>
+      <c r="B132" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 458</v>
+      </c>
+      <c r="C132">
+        <v>7</v>
+      </c>
+      <c r="D132">
+        <v>45</v>
+      </c>
+      <c r="O132">
+        <v>7</v>
+      </c>
+      <c r="P132" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A133" s="8">
+        <v>459</v>
+      </c>
+      <c r="B133" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 459</v>
+      </c>
+      <c r="C133">
+        <v>7</v>
+      </c>
+      <c r="D133">
+        <v>45</v>
+      </c>
+      <c r="O133">
+        <v>7</v>
+      </c>
+      <c r="P133" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A134" s="8">
+        <v>460</v>
+      </c>
+      <c r="B134" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 460</v>
+      </c>
+      <c r="C134">
+        <v>7</v>
+      </c>
+      <c r="D134">
+        <v>45</v>
+      </c>
+      <c r="O134">
+        <v>7</v>
+      </c>
+      <c r="P134" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="135" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A135" s="8">
+        <v>461</v>
+      </c>
+      <c r="B135" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 461</v>
+      </c>
+      <c r="C135">
+        <v>7</v>
+      </c>
+      <c r="D135">
+        <v>45</v>
+      </c>
+      <c r="O135">
+        <v>7</v>
+      </c>
+      <c r="P135" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A136" s="8">
+        <v>462</v>
+      </c>
+      <c r="B136" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 462</v>
+      </c>
+      <c r="C136">
+        <v>7</v>
+      </c>
+      <c r="D136">
+        <v>45</v>
+      </c>
+      <c r="O136">
+        <v>7</v>
+      </c>
+      <c r="P136" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A137" s="8">
+        <v>463</v>
+      </c>
+      <c r="B137" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 463</v>
+      </c>
+      <c r="C137">
+        <v>7</v>
+      </c>
+      <c r="E137">
+        <v>52</v>
+      </c>
+      <c r="O137">
+        <v>7</v>
+      </c>
+      <c r="P137" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A138" s="8">
+        <v>464</v>
+      </c>
+      <c r="B138" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 464</v>
+      </c>
+      <c r="C138">
+        <v>7</v>
+      </c>
+      <c r="D138">
+        <v>45</v>
+      </c>
+      <c r="O138">
+        <v>7</v>
+      </c>
+      <c r="P138" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A139" s="8">
+        <v>465</v>
+      </c>
+      <c r="B139" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 465</v>
+      </c>
+      <c r="C139">
+        <v>7</v>
+      </c>
+      <c r="D139">
+        <v>45</v>
+      </c>
+      <c r="O139">
+        <v>7</v>
+      </c>
+      <c r="P139" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A140" s="8">
+        <v>466</v>
+      </c>
+      <c r="B140" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 466</v>
+      </c>
+      <c r="C140">
+        <v>7</v>
+      </c>
+      <c r="F140">
+        <v>34</v>
+      </c>
+      <c r="O140">
+        <v>7</v>
+      </c>
+      <c r="P140" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="141" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A141" s="8">
+        <v>467</v>
+      </c>
+      <c r="B141" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 467</v>
+      </c>
+      <c r="C141">
+        <v>7</v>
+      </c>
+      <c r="F141">
+        <v>34</v>
+      </c>
+      <c r="O141">
+        <v>7</v>
+      </c>
+      <c r="P141" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="142" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A142" s="8">
+        <v>468</v>
+      </c>
+      <c r="B142" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 468</v>
+      </c>
+      <c r="C142">
+        <v>7</v>
+      </c>
+      <c r="F142">
+        <v>34</v>
+      </c>
+      <c r="O142">
+        <v>7</v>
+      </c>
+      <c r="P142" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A143" s="8">
         <v>469</v>
       </c>
-      <c r="L3" s="9"/>
-      <c r="M3" s="9"/>
-      <c r="N3" s="9"/>
-      <c r="O3" s="9">
-        <v>82</v>
-      </c>
-      <c r="P3" s="9"/>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>113</v>
-      </c>
-      <c r="B4" t="s">
-        <v>198</v>
-      </c>
-      <c r="C4" s="9">
+      <c r="B143" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 469</v>
+      </c>
+      <c r="C143">
+        <v>7</v>
+      </c>
+      <c r="F143">
+        <v>34</v>
+      </c>
+      <c r="O143">
+        <v>7</v>
+      </c>
+      <c r="P143" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A144" s="8">
+        <v>470</v>
+      </c>
+      <c r="B144" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 470</v>
+      </c>
+      <c r="C144">
+        <v>7</v>
+      </c>
+      <c r="D144">
+        <v>45</v>
+      </c>
+      <c r="O144">
+        <v>7</v>
+      </c>
+      <c r="P144" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="145" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A145" s="8">
+        <v>471</v>
+      </c>
+      <c r="B145" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 471</v>
+      </c>
+      <c r="C145">
+        <v>7</v>
+      </c>
+      <c r="D145">
+        <v>45</v>
+      </c>
+      <c r="O145">
+        <v>7</v>
+      </c>
+      <c r="P145" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="146" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A146" s="8">
+        <v>472</v>
+      </c>
+      <c r="B146" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 472</v>
+      </c>
+      <c r="C146">
+        <v>7</v>
+      </c>
+      <c r="D146">
+        <v>45</v>
+      </c>
+      <c r="O146">
+        <v>7</v>
+      </c>
+      <c r="P146" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="147" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A147" s="8">
+        <v>473</v>
+      </c>
+      <c r="B147" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 473</v>
+      </c>
+      <c r="C147">
+        <v>7</v>
+      </c>
+      <c r="D147">
+        <v>45</v>
+      </c>
+      <c r="O147">
+        <v>7</v>
+      </c>
+      <c r="P147" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="148" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A148" s="8">
+        <v>474</v>
+      </c>
+      <c r="B148" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 474</v>
+      </c>
+      <c r="C148">
+        <v>7</v>
+      </c>
+      <c r="D148">
+        <v>45</v>
+      </c>
+      <c r="O148">
+        <v>7</v>
+      </c>
+      <c r="P148" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="149" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A149" s="8">
+        <v>475</v>
+      </c>
+      <c r="B149" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 475</v>
+      </c>
+      <c r="C149">
+        <v>7</v>
+      </c>
+      <c r="D149">
+        <v>45</v>
+      </c>
+      <c r="O149">
+        <v>7</v>
+      </c>
+      <c r="P149" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="150" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A150" s="8">
+        <v>476</v>
+      </c>
+      <c r="B150" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 476</v>
+      </c>
+      <c r="C150">
+        <v>7</v>
+      </c>
+      <c r="D150">
+        <v>45</v>
+      </c>
+      <c r="O150">
+        <v>7</v>
+      </c>
+      <c r="P150" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="151" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A151" s="8">
+        <v>477</v>
+      </c>
+      <c r="B151" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 477</v>
+      </c>
+      <c r="C151">
+        <v>7</v>
+      </c>
+      <c r="D151">
+        <v>45</v>
+      </c>
+      <c r="O151">
+        <v>7</v>
+      </c>
+      <c r="P151" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="152" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A152" s="8">
+        <v>478</v>
+      </c>
+      <c r="B152" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 478</v>
+      </c>
+      <c r="C152">
+        <v>7</v>
+      </c>
+      <c r="D152">
+        <v>45</v>
+      </c>
+      <c r="O152">
+        <v>7</v>
+      </c>
+      <c r="P152" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="153" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A153" s="8">
+        <v>479</v>
+      </c>
+      <c r="B153" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 479</v>
+      </c>
+      <c r="C153">
+        <v>7</v>
+      </c>
+      <c r="D153">
+        <v>45</v>
+      </c>
+      <c r="O153">
+        <v>7</v>
+      </c>
+      <c r="P153" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="154" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A154" s="8">
+        <v>480</v>
+      </c>
+      <c r="B154" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 480</v>
+      </c>
+      <c r="C154">
+        <v>7</v>
+      </c>
+      <c r="D154">
+        <v>45</v>
+      </c>
+      <c r="O154">
+        <v>7</v>
+      </c>
+      <c r="P154" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="155" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A155" s="8">
+        <v>481</v>
+      </c>
+      <c r="B155" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 481</v>
+      </c>
+      <c r="C155">
+        <v>7</v>
+      </c>
+      <c r="D155">
+        <v>45</v>
+      </c>
+      <c r="O155">
+        <v>7</v>
+      </c>
+      <c r="P155" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="156" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A156" s="8">
+        <v>482</v>
+      </c>
+      <c r="B156" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 482</v>
+      </c>
+      <c r="C156">
+        <v>7</v>
+      </c>
+      <c r="D156">
+        <v>45</v>
+      </c>
+      <c r="O156">
+        <v>7</v>
+      </c>
+      <c r="P156" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="157" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A157" s="8">
+        <v>483</v>
+      </c>
+      <c r="B157" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 483</v>
+      </c>
+      <c r="C157">
+        <v>7</v>
+      </c>
+      <c r="D157">
+        <v>45</v>
+      </c>
+      <c r="O157">
+        <v>7</v>
+      </c>
+      <c r="P157" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="158" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A158" s="8">
+        <v>484</v>
+      </c>
+      <c r="B158" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 484</v>
+      </c>
+      <c r="C158">
+        <v>7</v>
+      </c>
+      <c r="D158">
+        <v>45</v>
+      </c>
+      <c r="O158">
+        <v>7</v>
+      </c>
+      <c r="P158" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="159" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A159" s="8">
+        <v>485</v>
+      </c>
+      <c r="B159" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 485</v>
+      </c>
+      <c r="C159">
+        <v>7</v>
+      </c>
+      <c r="D159">
+        <v>45</v>
+      </c>
+      <c r="O159">
+        <v>7</v>
+      </c>
+      <c r="P159" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="160" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A160" s="8">
+        <v>486</v>
+      </c>
+      <c r="B160" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 486</v>
+      </c>
+      <c r="C160">
+        <v>7</v>
+      </c>
+      <c r="D160">
+        <v>45</v>
+      </c>
+      <c r="O160">
+        <v>7</v>
+      </c>
+      <c r="P160" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="161" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A161" s="8">
+        <v>487</v>
+      </c>
+      <c r="B161" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 487</v>
+      </c>
+      <c r="C161">
+        <v>7</v>
+      </c>
+      <c r="D161">
+        <v>45</v>
+      </c>
+      <c r="O161">
+        <v>7</v>
+      </c>
+      <c r="P161" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="162" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A162" s="8">
+        <v>488</v>
+      </c>
+      <c r="B162" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 488</v>
+      </c>
+      <c r="C162">
+        <v>7</v>
+      </c>
+      <c r="D162">
+        <v>45</v>
+      </c>
+      <c r="O162">
+        <v>7</v>
+      </c>
+      <c r="P162" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="163" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A163" s="8">
+        <v>489</v>
+      </c>
+      <c r="B163" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 489</v>
+      </c>
+      <c r="C163">
+        <v>7</v>
+      </c>
+      <c r="D163">
+        <v>45</v>
+      </c>
+      <c r="O163">
+        <v>7</v>
+      </c>
+      <c r="P163" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="164" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A164" s="8">
+        <v>490</v>
+      </c>
+      <c r="B164" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 490</v>
+      </c>
+      <c r="C164">
+        <v>7</v>
+      </c>
+      <c r="D164">
+        <v>45</v>
+      </c>
+      <c r="O164">
+        <v>7</v>
+      </c>
+      <c r="P164" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="165" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A165" s="8">
+        <v>491</v>
+      </c>
+      <c r="B165" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 491</v>
+      </c>
+      <c r="C165">
+        <v>7</v>
+      </c>
+      <c r="D165">
+        <v>45</v>
+      </c>
+      <c r="O165">
+        <v>7</v>
+      </c>
+      <c r="P165" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="166" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A166" s="8">
+        <v>492</v>
+      </c>
+      <c r="B166" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 492</v>
+      </c>
+      <c r="C166">
+        <v>7</v>
+      </c>
+      <c r="D166">
+        <v>45</v>
+      </c>
+      <c r="O166">
+        <v>7</v>
+      </c>
+      <c r="P166" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="167" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A167" s="8">
+        <v>493</v>
+      </c>
+      <c r="B167" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 493</v>
+      </c>
+      <c r="C167">
+        <v>7</v>
+      </c>
+      <c r="D167">
+        <v>45</v>
+      </c>
+      <c r="O167">
+        <v>7</v>
+      </c>
+      <c r="P167" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="168" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A168" s="8">
+        <v>494</v>
+      </c>
+      <c r="B168" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 494</v>
+      </c>
+      <c r="C168">
+        <v>7</v>
+      </c>
+      <c r="D168">
+        <v>45</v>
+      </c>
+      <c r="O168">
+        <v>7</v>
+      </c>
+      <c r="P168" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="169" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A169" s="8">
+        <v>495</v>
+      </c>
+      <c r="B169" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 495</v>
+      </c>
+      <c r="C169">
+        <v>7</v>
+      </c>
+      <c r="D169">
+        <v>45</v>
+      </c>
+      <c r="O169">
+        <v>7</v>
+      </c>
+      <c r="P169" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="170" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A170" s="8">
+        <v>496</v>
+      </c>
+      <c r="B170" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 496</v>
+      </c>
+      <c r="C170">
+        <v>7</v>
+      </c>
+      <c r="D170">
+        <v>45</v>
+      </c>
+      <c r="O170">
+        <v>7</v>
+      </c>
+      <c r="P170" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="171" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A171" s="8">
+        <v>497</v>
+      </c>
+      <c r="B171" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 497</v>
+      </c>
+      <c r="C171">
+        <v>7</v>
+      </c>
+      <c r="D171">
+        <v>45</v>
+      </c>
+      <c r="O171">
+        <v>7</v>
+      </c>
+      <c r="P171" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="172" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A172" s="8">
+        <v>498</v>
+      </c>
+      <c r="B172" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 498</v>
+      </c>
+      <c r="C172">
+        <v>7</v>
+      </c>
+      <c r="D172">
+        <v>45</v>
+      </c>
+      <c r="O172">
+        <v>7</v>
+      </c>
+      <c r="P172" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="173" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A173" s="8">
+        <v>499</v>
+      </c>
+      <c r="B173" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 499</v>
+      </c>
+      <c r="C173">
+        <v>7</v>
+      </c>
+      <c r="D173">
+        <v>45</v>
+      </c>
+      <c r="O173">
+        <v>7</v>
+      </c>
+      <c r="P173" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="174" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A174" s="8">
+        <v>500</v>
+      </c>
+      <c r="B174" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 500</v>
+      </c>
+      <c r="C174">
+        <v>7</v>
+      </c>
+      <c r="D174">
+        <v>45</v>
+      </c>
+      <c r="O174">
+        <v>7</v>
+      </c>
+      <c r="P174" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="175" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A175" s="8">
+        <v>501</v>
+      </c>
+      <c r="B175" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 501</v>
+      </c>
+      <c r="C175">
+        <v>7</v>
+      </c>
+      <c r="D175">
+        <v>45</v>
+      </c>
+      <c r="O175">
+        <v>7</v>
+      </c>
+      <c r="P175" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="176" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A176" s="8">
+        <v>502</v>
+      </c>
+      <c r="B176" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 502</v>
+      </c>
+      <c r="C176">
+        <v>1</v>
+      </c>
+      <c r="D176">
+        <v>17</v>
+      </c>
+      <c r="O176">
+        <v>2</v>
+      </c>
+      <c r="P176" s="8"/>
+    </row>
+    <row r="177" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A177" s="8">
+        <v>503</v>
+      </c>
+      <c r="B177" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 503</v>
+      </c>
+      <c r="C177">
+        <v>1</v>
+      </c>
+      <c r="D177">
+        <v>17</v>
+      </c>
+      <c r="O177">
+        <v>2</v>
+      </c>
+      <c r="P177" s="8"/>
+    </row>
+    <row r="178" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A178" s="8">
+        <v>504</v>
+      </c>
+      <c r="B178" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 504</v>
+      </c>
+      <c r="C178">
+        <v>1</v>
+      </c>
+      <c r="D178">
+        <v>17</v>
+      </c>
+      <c r="O178">
+        <v>2</v>
+      </c>
+      <c r="P178" s="8"/>
+    </row>
+    <row r="179" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A179" s="8">
+        <v>505</v>
+      </c>
+      <c r="B179" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 505</v>
+      </c>
+      <c r="C179">
+        <v>1</v>
+      </c>
+      <c r="D179">
+        <v>17</v>
+      </c>
+      <c r="O179">
+        <v>2</v>
+      </c>
+      <c r="P179" s="8"/>
+    </row>
+    <row r="180" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A180" s="8">
+        <v>506</v>
+      </c>
+      <c r="B180" t="str">
+        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
+        <v>Lot 506</v>
+      </c>
+      <c r="C180">
+        <v>7</v>
+      </c>
+      <c r="G180">
         <v>86</v>
       </c>
-      <c r="D4" s="9">
-        <v>391</v>
-      </c>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="9">
-        <v>101</v>
-      </c>
-      <c r="I4" s="9">
-        <v>197</v>
-      </c>
-      <c r="J4" s="9"/>
-      <c r="K4" s="9"/>
-      <c r="L4" s="9">
-        <v>425</v>
-      </c>
-      <c r="M4" s="9"/>
-      <c r="N4" s="9"/>
-      <c r="O4" s="9">
-        <v>95</v>
-      </c>
-      <c r="P4" s="9"/>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>462</v>
-      </c>
-      <c r="B5" t="s">
-        <v>200</v>
-      </c>
-      <c r="C5" s="9">
-        <v>7</v>
-      </c>
-      <c r="D5" s="9">
-        <v>45</v>
-      </c>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="9"/>
-      <c r="J5" s="9"/>
-      <c r="K5" s="9"/>
-      <c r="L5" s="9"/>
-      <c r="M5" s="9"/>
-      <c r="N5" s="9"/>
-      <c r="O5" s="9">
-        <v>7</v>
-      </c>
-      <c r="P5" s="9">
-        <v>99</v>
+      <c r="O180">
+        <v>7</v>
+      </c>
+      <c r="P180" s="8">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -2445,8 +6460,8 @@
     <col min="2" max="2" width="66.5703125" style="2" customWidth="1"/>
     <col min="3" max="3" width="15.5703125" style="2" customWidth="1"/>
     <col min="4" max="4" width="32.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.85546875" style="5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.85546875" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.28515625" style="6" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="71.5703125" style="2" customWidth="1"/>
     <col min="9" max="9" width="48.85546875" customWidth="1"/>
@@ -2456,29 +6471,29 @@
       <c r="A1" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="C1" s="10" t="s">
-        <v>202</v>
+      <c r="C1" s="9" t="s">
+        <v>200</v>
       </c>
       <c r="D1" t="s">
         <v>94</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="G1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="10" t="s">
+      <c r="H1" s="9" t="s">
         <v>138</v>
       </c>
       <c r="I1" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="45" x14ac:dyDescent="0.25">
@@ -2491,10 +6506,10 @@
       <c r="D2" t="s">
         <v>24</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="5">
+      <c r="G2" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
         <v>0</v>
       </c>
@@ -2515,13 +6530,13 @@
       <c r="D3" t="s">
         <v>188</v>
       </c>
-      <c r="E3" s="5">
+      <c r="E3" s="4">
         <v>0</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="G3" s="5">
+      <c r="G3" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
         <v>0</v>
       </c>
@@ -2542,13 +6557,13 @@
       <c r="D4" t="s">
         <v>188</v>
       </c>
-      <c r="E4" s="5">
+      <c r="E4" s="4">
         <v>10000</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="G4" s="5">
+      <c r="G4" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
         <v>10000</v>
       </c>
@@ -2569,13 +6584,13 @@
       <c r="D5" t="s">
         <v>172</v>
       </c>
-      <c r="E5" s="5">
+      <c r="E5" s="4">
         <v>16000</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="G5" s="5">
+      <c r="G5" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
         <v>16000</v>
       </c>
@@ -2596,13 +6611,13 @@
       <c r="D6" t="s">
         <v>188</v>
       </c>
-      <c r="E6" s="5">
+      <c r="E6" s="4">
         <v>1940</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F6" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="G6" s="5">
+      <c r="G6" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
         <v>1940</v>
       </c>
@@ -2623,13 +6638,13 @@
       <c r="D7" t="s">
         <v>188</v>
       </c>
-      <c r="E7" s="5">
+      <c r="E7" s="4">
         <v>18000</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="F7" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="G7" s="5">
+      <c r="G7" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
         <v>18000</v>
       </c>
@@ -2650,13 +6665,13 @@
       <c r="D8" t="s">
         <v>172</v>
       </c>
-      <c r="E8" s="5">
+      <c r="E8" s="4">
         <v>24000</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="F8" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="G8" s="5">
+      <c r="G8" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
         <v>24000</v>
       </c>
@@ -2677,13 +6692,13 @@
       <c r="D9" t="s">
         <v>188</v>
       </c>
-      <c r="E9" s="5">
+      <c r="E9" s="4">
         <v>5710</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F9" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="G9" s="5">
+      <c r="G9" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
         <v>5710</v>
       </c>
@@ -2704,13 +6719,13 @@
       <c r="D10" t="s">
         <v>188</v>
       </c>
-      <c r="E10" s="5">
+      <c r="E10" s="4">
         <v>20000</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="F10" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="G10" s="5">
+      <c r="G10" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
         <v>20000</v>
       </c>
@@ -2731,13 +6746,13 @@
       <c r="D11" t="s">
         <v>172</v>
       </c>
-      <c r="E11" s="5">
+      <c r="E11" s="4">
         <v>37000</v>
       </c>
-      <c r="F11" s="7" t="s">
+      <c r="F11" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="G11" s="5">
+      <c r="G11" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
         <v>37000</v>
       </c>
@@ -2758,13 +6773,13 @@
       <c r="D12" t="s">
         <v>188</v>
       </c>
-      <c r="E12" s="5">
+      <c r="E12" s="4">
         <v>10770</v>
       </c>
-      <c r="F12" s="7" t="s">
+      <c r="F12" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="G12" s="5">
+      <c r="G12" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
         <v>10770</v>
       </c>
@@ -2785,13 +6800,13 @@
       <c r="D13" t="s">
         <v>188</v>
       </c>
-      <c r="E13" s="5">
+      <c r="E13" s="4">
         <v>25000</v>
       </c>
-      <c r="F13" s="7" t="s">
+      <c r="F13" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="G13" s="5">
+      <c r="G13" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
         <v>25000</v>
       </c>
@@ -2809,13 +6824,13 @@
       <c r="D14" t="s">
         <v>10</v>
       </c>
-      <c r="E14" s="5">
+      <c r="E14" s="4">
         <v>3000</v>
       </c>
-      <c r="F14" s="7" t="s">
+      <c r="F14" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="G14" s="5">
+      <c r="G14" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
         <v>3000</v>
       </c>
@@ -2830,13 +6845,13 @@
       <c r="D15" t="s">
         <v>11</v>
       </c>
-      <c r="E15" s="5">
+      <c r="E15" s="4">
         <v>2460</v>
       </c>
-      <c r="F15" s="7" t="s">
+      <c r="F15" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="G15" s="5">
+      <c r="G15" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
         <v>2460</v>
       </c>
@@ -2854,13 +6869,13 @@
       <c r="D16" t="s">
         <v>27</v>
       </c>
-      <c r="E16" s="5">
+      <c r="E16" s="4">
         <v>1051.2</v>
       </c>
-      <c r="F16" s="7" t="s">
+      <c r="F16" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="G16" s="5">
+      <c r="G16" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
         <v>1051.2</v>
       </c>
@@ -2881,13 +6896,13 @@
       <c r="D17" t="s">
         <v>92</v>
       </c>
-      <c r="E17" s="5">
+      <c r="E17" s="4">
         <v>748.15</v>
       </c>
-      <c r="F17" s="7" t="s">
+      <c r="F17" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="G17" s="5">
+      <c r="G17" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
         <v>748.15</v>
       </c>
@@ -2895,7 +6910,7 @@
         <v>93</v>
       </c>
       <c r="I17" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -2911,13 +6926,13 @@
       <c r="D18" t="s">
         <v>6</v>
       </c>
-      <c r="E18" s="5">
+      <c r="E18" s="4">
         <v>6096.65</v>
       </c>
-      <c r="F18" s="7" t="s">
+      <c r="F18" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="G18" s="5">
+      <c r="G18" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
         <v>6096.65</v>
       </c>
@@ -2925,7 +6940,7 @@
         <v>102</v>
       </c>
       <c r="I18" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
@@ -2941,13 +6956,13 @@
       <c r="D19" t="s">
         <v>7</v>
       </c>
-      <c r="E19" s="5">
+      <c r="E19" s="4">
         <v>7502.9</v>
       </c>
-      <c r="F19" s="7" t="s">
+      <c r="F19" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="G19" s="5">
+      <c r="G19" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
         <v>7502.9</v>
       </c>
@@ -2968,19 +6983,19 @@
       <c r="D20" t="s">
         <v>82</v>
       </c>
-      <c r="E20" s="5">
+      <c r="E20" s="4">
         <f>16750</f>
         <v>16750</v>
       </c>
-      <c r="F20" s="7" t="s">
+      <c r="F20" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="G20" s="5">
+      <c r="G20" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
         <v>16750</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -2988,7 +7003,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="C21" t="s">
         <v>74</v>
@@ -2996,14 +7011,14 @@
       <c r="D21" t="s">
         <v>82</v>
       </c>
-      <c r="E21" s="5">
+      <c r="E21" s="4">
         <f>887</f>
         <v>887</v>
       </c>
-      <c r="F21" s="7" t="s">
+      <c r="F21" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="G21" s="5">
+      <c r="G21" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
         <v>887</v>
       </c>
@@ -3024,10 +7039,10 @@
       <c r="D22" t="s">
         <v>22</v>
       </c>
-      <c r="F22" s="7" t="s">
+      <c r="F22" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="G22" s="5">
+      <c r="G22" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
         <v>0</v>
       </c>
@@ -3048,10 +7063,10 @@
       <c r="D23" t="s">
         <v>21</v>
       </c>
-      <c r="F23" s="7" t="s">
+      <c r="F23" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="G23" s="5">
+      <c r="G23" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
         <v>0</v>
       </c>
@@ -3072,14 +7087,14 @@
       <c r="D24" t="s">
         <v>107</v>
       </c>
-      <c r="E24" s="5">
+      <c r="E24" s="4">
         <f>1140*12</f>
         <v>13680</v>
       </c>
-      <c r="F24" s="7" t="s">
+      <c r="F24" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="G24" s="5">
+      <c r="G24" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
         <v>13680</v>
       </c>
@@ -3100,14 +7115,14 @@
       <c r="D25" t="s">
         <v>110</v>
       </c>
-      <c r="E25" s="5">
+      <c r="E25" s="4">
         <f>2836.8*12</f>
         <v>34041.600000000006</v>
       </c>
-      <c r="F25" s="7" t="s">
+      <c r="F25" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="G25" s="5">
+      <c r="G25" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
         <v>34041.600000000006</v>
       </c>
@@ -3128,14 +7143,14 @@
       <c r="D26" t="s">
         <v>107</v>
       </c>
-      <c r="E26" s="5">
+      <c r="E26" s="4">
         <f>1518*12</f>
         <v>18216</v>
       </c>
-      <c r="F26" s="7" t="s">
+      <c r="F26" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="G26" s="5">
+      <c r="G26" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
         <v>18216</v>
       </c>
@@ -3143,7 +7158,7 @@
         <v>105</v>
       </c>
       <c r="I26" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="60" x14ac:dyDescent="0.25">
@@ -3159,13 +7174,13 @@
       <c r="D27" t="s">
         <v>111</v>
       </c>
-      <c r="E27" s="5">
+      <c r="E27" s="4">
         <v>516</v>
       </c>
-      <c r="F27" s="7" t="s">
+      <c r="F27" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="G27" s="5">
+      <c r="G27" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
         <v>516</v>
       </c>
@@ -3186,13 +7201,13 @@
       <c r="D28" t="s">
         <v>111</v>
       </c>
-      <c r="E28" s="5">
+      <c r="E28" s="4">
         <v>456</v>
       </c>
-      <c r="F28" s="7" t="s">
+      <c r="F28" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="G28" s="5">
+      <c r="G28" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
         <v>456</v>
       </c>
@@ -3213,13 +7228,13 @@
       <c r="D29" t="s">
         <v>19</v>
       </c>
-      <c r="E29" s="5">
+      <c r="E29" s="4">
         <v>660</v>
       </c>
-      <c r="F29" s="7" t="s">
+      <c r="F29" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="G29" s="5">
+      <c r="G29" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
         <v>660</v>
       </c>
@@ -3232,29 +7247,29 @@
         <v>18</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="C30" t="s">
         <v>75</v>
       </c>
       <c r="D30" t="s">
-        <v>222</v>
-      </c>
-      <c r="E30" s="5">
+        <v>219</v>
+      </c>
+      <c r="E30" s="4">
         <v>434.5</v>
       </c>
-      <c r="F30" s="7" t="s">
+      <c r="F30" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="G30" s="5">
+      <c r="G30" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
         <v>434.5</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
@@ -3270,13 +7285,13 @@
       <c r="D31" t="s">
         <v>81</v>
       </c>
-      <c r="E31" s="5">
+      <c r="E31" s="4">
         <v>2400</v>
       </c>
-      <c r="F31" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="G31" s="5">
+      <c r="F31" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="G31" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
         <v>2880</v>
       </c>
@@ -3284,7 +7299,7 @@
         <v>135</v>
       </c>
       <c r="I31" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
@@ -3300,13 +7315,13 @@
       <c r="D32" t="s">
         <v>81</v>
       </c>
-      <c r="E32" s="5">
+      <c r="E32" s="4">
         <v>2400</v>
       </c>
-      <c r="F32" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="G32" s="5">
+      <c r="F32" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="G32" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
         <v>2880</v>
       </c>
@@ -3314,7 +7329,7 @@
         <v>135</v>
       </c>
       <c r="I32" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
@@ -3330,13 +7345,13 @@
       <c r="D33" t="s">
         <v>81</v>
       </c>
-      <c r="E33" s="5">
+      <c r="E33" s="4">
         <v>2450</v>
       </c>
-      <c r="F33" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="G33" s="5">
+      <c r="F33" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="G33" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
         <v>2940</v>
       </c>
@@ -3344,7 +7359,7 @@
         <v>135</v>
       </c>
       <c r="I33" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
@@ -3360,13 +7375,13 @@
       <c r="D34" t="s">
         <v>81</v>
       </c>
-      <c r="E34" s="5">
+      <c r="E34" s="4">
         <v>2200</v>
       </c>
-      <c r="F34" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="G34" s="5">
+      <c r="F34" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="G34" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
         <v>2640</v>
       </c>
@@ -3374,7 +7389,7 @@
         <v>136</v>
       </c>
       <c r="I34" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
@@ -3387,13 +7402,13 @@
       <c r="D35" t="s">
         <v>26</v>
       </c>
-      <c r="E35" s="5">
+      <c r="E35" s="4">
         <v>160</v>
       </c>
-      <c r="F35" s="7" t="s">
+      <c r="F35" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="G35" s="5">
+      <c r="G35" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
         <v>160</v>
       </c>
@@ -3411,14 +7426,14 @@
       <c r="D36" t="s">
         <v>110</v>
       </c>
-      <c r="E36" s="5">
+      <c r="E36" s="4">
         <f>2400*12</f>
         <v>28800</v>
       </c>
-      <c r="F36" s="7" t="s">
+      <c r="F36" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="G36" s="5">
+      <c r="G36" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
         <v>28800</v>
       </c>
@@ -3439,14 +7454,14 @@
       <c r="D37" t="s">
         <v>110</v>
       </c>
-      <c r="E37" s="5">
+      <c r="E37" s="4">
         <f>1320*12</f>
         <v>15840</v>
       </c>
-      <c r="F37" s="7" t="s">
+      <c r="F37" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="G37" s="5">
+      <c r="G37" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
         <v>15840</v>
       </c>
@@ -3464,13 +7479,13 @@
       <c r="D38" t="s">
         <v>17</v>
       </c>
-      <c r="E38" s="5">
+      <c r="E38" s="4">
         <v>3198.13</v>
       </c>
-      <c r="F38" s="7" t="s">
+      <c r="F38" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="G38" s="5">
+      <c r="G38" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
         <v>3198.13</v>
       </c>
@@ -3485,13 +7500,13 @@
       <c r="D39" t="s">
         <v>16</v>
       </c>
-      <c r="E39" s="5">
+      <c r="E39" s="4">
         <v>3322.8</v>
       </c>
-      <c r="F39" s="7" t="s">
+      <c r="F39" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="G39" s="5">
+      <c r="G39" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
         <v>3322.8</v>
       </c>
@@ -3506,13 +7521,13 @@
       <c r="D40" t="s">
         <v>15</v>
       </c>
-      <c r="E40" s="5">
+      <c r="E40" s="4">
         <v>3138.27</v>
       </c>
-      <c r="F40" s="7" t="s">
+      <c r="F40" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="G40" s="5">
+      <c r="G40" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
         <v>3138.27</v>
       </c>
@@ -3530,13 +7545,13 @@
       <c r="D41" t="s">
         <v>81</v>
       </c>
-      <c r="E41" s="5">
+      <c r="E41" s="4">
         <v>240</v>
       </c>
-      <c r="F41" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="G41" s="5">
+      <c r="F41" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="G41" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
         <v>288</v>
       </c>
@@ -3557,13 +7572,13 @@
       <c r="D42" t="s">
         <v>81</v>
       </c>
-      <c r="E42" s="5">
+      <c r="E42" s="4">
         <v>240</v>
       </c>
-      <c r="F42" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="G42" s="5">
+      <c r="F42" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="G42" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
         <v>288</v>
       </c>
@@ -3584,13 +7599,13 @@
       <c r="D43" t="s">
         <v>81</v>
       </c>
-      <c r="E43" s="5">
+      <c r="E43" s="4">
         <v>240</v>
       </c>
-      <c r="F43" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="G43" s="5">
+      <c r="F43" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="G43" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
         <v>288</v>
       </c>
@@ -3611,13 +7626,13 @@
       <c r="D44" t="s">
         <v>81</v>
       </c>
-      <c r="E44" s="5">
+      <c r="E44" s="4">
         <v>240</v>
       </c>
-      <c r="F44" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="G44" s="5">
+      <c r="F44" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="G44" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
         <v>288</v>
       </c>
@@ -3638,17 +7653,17 @@
       <c r="D45" t="s">
         <v>188</v>
       </c>
-      <c r="E45" s="6">
+      <c r="E45" s="5">
         <v>10000</v>
       </c>
-      <c r="F45" s="8" t="s">
+      <c r="F45" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="G45" s="6">
+      <c r="G45" s="5">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
         <v>10000</v>
       </c>
-      <c r="H45" s="4"/>
+      <c r="H45" s="3"/>
       <c r="I45" s="2"/>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
@@ -3664,17 +7679,17 @@
       <c r="D46" t="s">
         <v>188</v>
       </c>
-      <c r="E46" s="6">
+      <c r="E46" s="5">
         <v>12500</v>
       </c>
-      <c r="F46" s="8" t="s">
+      <c r="F46" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="G46" s="6">
+      <c r="G46" s="5">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
         <v>12500</v>
       </c>
-      <c r="H46" s="4"/>
+      <c r="H46" s="3"/>
       <c r="I46" s="2"/>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
@@ -3690,17 +7705,17 @@
       <c r="D47" t="s">
         <v>188</v>
       </c>
-      <c r="E47" s="6">
+      <c r="E47" s="5">
         <v>15000</v>
       </c>
-      <c r="F47" s="8" t="s">
+      <c r="F47" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="G47" s="6">
+      <c r="G47" s="5">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
         <v>15000</v>
       </c>
-      <c r="H47" s="4"/>
+      <c r="H47" s="3"/>
       <c r="I47" s="2"/>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
@@ -3716,21 +7731,21 @@
       <c r="D48" t="s">
         <v>27</v>
       </c>
-      <c r="E48" s="6">
+      <c r="E48" s="5">
         <v>16800</v>
       </c>
-      <c r="F48" s="8" t="s">
+      <c r="F48" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="G48" s="6">
+      <c r="G48" s="5">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
         <v>16800</v>
       </c>
-      <c r="H48" s="4" t="s">
+      <c r="H48" s="3" t="s">
         <v>101</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
     </row>
   </sheetData>
@@ -3751,40 +7766,33 @@
   <sheetPr>
     <tabColor theme="9" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="25.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="B1" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="C1" t="s">
-        <v>210</v>
-      </c>
-      <c r="D1" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="B2">
-        <v>10007</v>
+        <v>10142</v>
       </c>
       <c r="C2">
-        <v>10142</v>
-      </c>
-      <c r="D2">
         <v>0.5</v>
       </c>
     </row>
@@ -3814,19 +7822,19 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="B1" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="D1" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="E1" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="F1" t="s">
         <v>138</v>
@@ -3834,9 +7842,9 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>218</v>
-      </c>
-      <c r="B2" s="12" t="s">
+        <v>215</v>
+      </c>
+      <c r="B2" s="11" t="s">
         <v>72</v>
       </c>
       <c r="C2" s="1">
@@ -3850,12 +7858,12 @@
         <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="B3" t="s">
         <v>73</v>
@@ -3870,7 +7878,7 @@
         <v>2</v>
       </c>
       <c r="F3" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
     </row>
   </sheetData>

--- a/input.xlsx
+++ b/input.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/25a393584c41f6f2/Documents/Mon Patrimoine/Projet Immobilier/2023 Terrasses de Galieni/09 - Copropriété/Site de calcul des charges de copropriété/streamlit-copro-charges/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="690" documentId="13_ncr:1_{471232EB-3AAB-4D08-BC1C-7B7CD1C1D853}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8042C2AA-65EE-4305-8FA3-CD53475E7F32}"/>
+  <xr:revisionPtr revIDLastSave="708" documentId="13_ncr:1_{471232EB-3AAB-4D08-BC1C-7B7CD1C1D853}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6A140CCE-984B-4FAC-939A-1C0CB3B44D57}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Provisions" sheetId="9" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="477" uniqueCount="244">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="484" uniqueCount="251">
   <si>
     <t>Taxes</t>
   </si>
@@ -687,9 +687,6 @@
   </si>
   <si>
     <t>Prix du granulé: Gruchy = 310€/t, CRAM = 392€/t et Prochalor 500€/t</t>
-  </si>
-  <si>
-    <t>Herz Firematic 20-60</t>
   </si>
   <si>
     <t>Chaudière d'appoint au gaz</t>
@@ -785,6 +782,31 @@
   </si>
   <si>
     <t>Lot 113 - T2 45m2 3ème étage Batiment 1.1 exposé nord/est</t>
+  </si>
+  <si>
+    <t>Herz Firematic 130</t>
+  </si>
+  <si>
+    <t>De 310€/t pour Gruchy à 500€/t pour Prochalor</t>
+  </si>
+  <si>
+    <t>Contrat associé à la porte principale du parking souterrain</t>
+  </si>
+  <si>
+    <t>Assistance juridique à la copropriété</t>
+  </si>
+  <si>
+    <t>Electricité du bâtiment 1: éclairages couloirs, éclairages hall, interphones. Relié aux panneaux solaires, avec revente du surplus d'électricité.</t>
+  </si>
+  <si>
+    <t>Electricité du bâtiment 2: éclairages couloirs, éclairages hall, interphones. Relié aux panneaux solaires, avec revente du surplus d'électricité.</t>
+  </si>
+  <si>
+    <t>Electricité du bâtiment 3: éclairages couloirs, éclairages hall, interphones. Relié aux panneaux solaires, avec revente du surplus d'électricité.</t>
+  </si>
+  <si>
+    <t>La facturation par Est Ensemble est progressive, gratuit jusqu'à 10m3, puis de 10 à 28 m³ = 1,1988 € HT / m³, de 28 à 86 m³ = 1,3320 € HT / m³, de 86 à 101 m³ = 1,3720 € HT / m³, de 101 à 131 m³ = 1,4200 € HT / m³, de 131 à 140 m³ = 1,4919 € HT / m³ et Plus de 140 m³ = 1,5366 € HT / m³
+On rajoute la redevance (3,3€/m3) et la TVA (8%)</t>
   </si>
 </sst>
 </file>
@@ -1240,6 +1262,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{13C2BCD2-5CEA-4301-A571-688E40226767}" name="Provisions" displayName="Provisions" ref="A1:F34">
   <autoFilter ref="A1:F34" xr:uid="{13C2BCD2-5CEA-4301-A571-688E40226767}"/>
@@ -1632,10 +1658,10 @@
         <v>97</v>
       </c>
       <c r="F1" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>147</v>
       </c>
@@ -1651,7 +1677,9 @@
       <c r="E2" s="1">
         <v>35000</v>
       </c>
-      <c r="F2" s="2"/>
+      <c r="F2" s="2" t="s">
+        <v>250</v>
+      </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
@@ -1669,7 +1697,9 @@
       <c r="E3" s="1">
         <v>27000</v>
       </c>
-      <c r="F3" s="2"/>
+      <c r="F3" s="2" t="s">
+        <v>244</v>
+      </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
@@ -1885,7 +1915,9 @@
       <c r="E15" s="1">
         <v>2000</v>
       </c>
-      <c r="F15" s="2"/>
+      <c r="F15" s="2" t="s">
+        <v>247</v>
+      </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
@@ -1940,7 +1972,7 @@
         <v>1050</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -1959,7 +1991,9 @@
       <c r="E19" s="1">
         <v>1000</v>
       </c>
-      <c r="F19" s="2"/>
+      <c r="F19" s="2" t="s">
+        <v>248</v>
+      </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
@@ -1977,7 +2011,9 @@
       <c r="E20" s="1">
         <v>1000</v>
       </c>
-      <c r="F20" s="2"/>
+      <c r="F20" s="2" t="s">
+        <v>249</v>
+      </c>
     </row>
     <row r="21" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
@@ -1996,7 +2032,7 @@
         <v>920</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="135" x14ac:dyDescent="0.25">
@@ -2016,7 +2052,7 @@
         <v>900</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -2053,7 +2089,9 @@
       <c r="E24" s="1">
         <v>750</v>
       </c>
-      <c r="F24" s="2"/>
+      <c r="F24" s="2" t="s">
+        <v>246</v>
+      </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
@@ -2090,7 +2128,7 @@
         <v>580</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -2127,7 +2165,9 @@
       <c r="E28" s="1">
         <v>450</v>
       </c>
-      <c r="F28" s="2"/>
+      <c r="F28" s="2" t="s">
+        <v>245</v>
+      </c>
     </row>
     <row r="29" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
@@ -2146,7 +2186,7 @@
         <v>360</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="45" x14ac:dyDescent="0.25">
@@ -2166,7 +2206,7 @@
         <v>320</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="60" x14ac:dyDescent="0.25">
@@ -2186,7 +2226,7 @@
         <v>240</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -2224,7 +2264,7 @@
         <v>90</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -2327,7 +2367,7 @@
         <v>101</v>
       </c>
       <c r="B2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C2">
         <v>462</v>
@@ -2341,7 +2381,7 @@
         <v>102</v>
       </c>
       <c r="B3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C3">
         <v>119</v>
@@ -2367,7 +2407,7 @@
         <v>103</v>
       </c>
       <c r="B4" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C4">
         <v>83</v>
@@ -2393,7 +2433,7 @@
         <v>104</v>
       </c>
       <c r="B5" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C5">
         <v>130</v>
@@ -2419,7 +2459,7 @@
         <v>105</v>
       </c>
       <c r="B6" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C6">
         <v>123</v>
@@ -2445,7 +2485,7 @@
         <v>106</v>
       </c>
       <c r="B7" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C7">
         <v>122</v>
@@ -2471,7 +2511,7 @@
         <v>107</v>
       </c>
       <c r="B8" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C8">
         <v>55</v>
@@ -2497,7 +2537,7 @@
         <v>108</v>
       </c>
       <c r="B9" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C9">
         <v>96</v>
@@ -2523,7 +2563,7 @@
         <v>109</v>
       </c>
       <c r="B10" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C10">
         <v>123</v>
@@ -2549,7 +2589,7 @@
         <v>110</v>
       </c>
       <c r="B11" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C11">
         <v>129</v>
@@ -2575,7 +2615,7 @@
         <v>111</v>
       </c>
       <c r="B12" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C12">
         <v>58</v>
@@ -2601,7 +2641,7 @@
         <v>112</v>
       </c>
       <c r="B13" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C13">
         <v>91</v>
@@ -2627,7 +2667,7 @@
         <v>113</v>
       </c>
       <c r="B14" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C14" s="8">
         <v>86</v>
@@ -6493,7 +6533,7 @@
         <v>138</v>
       </c>
       <c r="I1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="45" x14ac:dyDescent="0.25">
@@ -6910,7 +6950,7 @@
         <v>93</v>
       </c>
       <c r="I17" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -6940,7 +6980,7 @@
         <v>102</v>
       </c>
       <c r="I18" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
@@ -7158,7 +7198,7 @@
         <v>105</v>
       </c>
       <c r="I26" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="60" x14ac:dyDescent="0.25">
@@ -7247,13 +7287,13 @@
         <v>18</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C30" t="s">
         <v>75</v>
       </c>
       <c r="D30" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E30" s="4">
         <v>434.5</v>
@@ -7266,10 +7306,10 @@
         <v>434.5</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
@@ -7299,7 +7339,7 @@
         <v>135</v>
       </c>
       <c r="I31" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
@@ -7329,7 +7369,7 @@
         <v>135</v>
       </c>
       <c r="I32" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
@@ -7359,7 +7399,7 @@
         <v>135</v>
       </c>
       <c r="I33" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
@@ -7389,7 +7429,7 @@
         <v>136</v>
       </c>
       <c r="I34" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
@@ -7745,7 +7785,7 @@
         <v>101</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
   </sheetData>
@@ -7842,17 +7882,17 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>215</v>
+        <v>243</v>
       </c>
       <c r="B2" s="11" t="s">
         <v>72</v>
       </c>
       <c r="C2" s="1">
-        <f>310*1.2/4600</f>
-        <v>8.0869565217391304E-2</v>
+        <f>500*1.2/4600</f>
+        <v>0.13043478260869565</v>
       </c>
       <c r="D2">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -7878,7 +7918,7 @@
         <v>2</v>
       </c>
       <c r="F3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
   </sheetData>

--- a/input.xlsx
+++ b/input.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/25a393584c41f6f2/Documents/Mon Patrimoine/Projet Immobilier/2023 Terrasses de Galieni/09 - Copropriété/Site de calcul des charges de copropriété/streamlit-copro-charges/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="708" documentId="13_ncr:1_{471232EB-3AAB-4D08-BC1C-7B7CD1C1D853}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6A140CCE-984B-4FAC-939A-1C0CB3B44D57}"/>
+  <xr:revisionPtr revIDLastSave="1276" documentId="13_ncr:1_{471232EB-3AAB-4D08-BC1C-7B7CD1C1D853}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D5BCE6EF-3B86-4285-8B2D-14A1ABACB257}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Provisions" sheetId="9" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="484" uniqueCount="251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="634" uniqueCount="410">
   <si>
     <t>Taxes</t>
   </si>
@@ -129,9 +129,6 @@
     <t>Assistance technique d'urgence en cas de sinistres sur les parties communes 24/7</t>
   </si>
   <si>
-    <t>ça coute combien ?</t>
-  </si>
-  <si>
     <t>Eau froide</t>
   </si>
   <si>
@@ -205,9 +202,6 @@
   </si>
   <si>
     <t>Entretien et petites réparations portes et serrures</t>
-  </si>
-  <si>
-    <t>EAUFR</t>
   </si>
   <si>
     <t>ELECCOMM</t>
@@ -557,30 +551,6 @@
     <t>Electricité du batiment 3</t>
   </si>
   <si>
-    <t>Consommation d'eau</t>
-  </si>
-  <si>
-    <t>Eau publique (Est Ensemble)</t>
-  </si>
-  <si>
-    <t>Consommation sobre, sur la base qu'un T2 de 50m2 paie 160€ à l'année</t>
-  </si>
-  <si>
-    <t>Consommation sobre, sur la base qu'un T2 de 50m2 paie 240€ à l'année</t>
-  </si>
-  <si>
-    <t>Consommation sobre, sur la base qu'un T2 de 50m2 paie 370€ à l'année</t>
-  </si>
-  <si>
-    <t>1 - Consommation d'eau sobre</t>
-  </si>
-  <si>
-    <t>2 - Consommation d'eau rationnelle</t>
-  </si>
-  <si>
-    <t>3 - Consommation d'eau confortable</t>
-  </si>
-  <si>
     <t>Fourniture de granulé de bois</t>
   </si>
   <si>
@@ -620,9 +590,6 @@
     <t>Syndic fourcette moyenne</t>
   </si>
   <si>
-    <t>Lot 225 - T4 7eme étage Batiment 2 exposé ouest</t>
-  </si>
-  <si>
     <t>2 - Consommation pour un hiver doux</t>
   </si>
   <si>
@@ -635,9 +602,6 @@
     <t>4 - Consommation pour un hiver rude</t>
   </si>
   <si>
-    <t>Lot 308 - T2 2ème étage Batiment 3 exposé ouest</t>
-  </si>
-  <si>
     <t>Tantièmes Stationnement</t>
   </si>
   <si>
@@ -684,12 +648,6 @@
   </si>
   <si>
     <t>Option adoucissant eau CRAM</t>
-  </si>
-  <si>
-    <t>Prix du granulé: Gruchy = 310€/t, CRAM = 392€/t et Prochalor 500€/t</t>
-  </si>
-  <si>
-    <t>Chaudière d'appoint au gaz</t>
   </si>
   <si>
     <t>X</t>
@@ -745,45 +703,6 @@
     <t>Description longue</t>
   </si>
   <si>
-    <t>Lot 101</t>
-  </si>
-  <si>
-    <t>Lot 102</t>
-  </si>
-  <si>
-    <t>Lot 103</t>
-  </si>
-  <si>
-    <t>Lot 104</t>
-  </si>
-  <si>
-    <t>Lot 105</t>
-  </si>
-  <si>
-    <t>Lot 106</t>
-  </si>
-  <si>
-    <t>Lot 107</t>
-  </si>
-  <si>
-    <t>Lot 108</t>
-  </si>
-  <si>
-    <t>Lot 109</t>
-  </si>
-  <si>
-    <t>Lot 110</t>
-  </si>
-  <si>
-    <t>Lot 111</t>
-  </si>
-  <si>
-    <t>Lot 112</t>
-  </si>
-  <si>
-    <t>Lot 113 - T2 45m2 3ème étage Batiment 1.1 exposé nord/est</t>
-  </si>
-  <si>
     <t>Herz Firematic 130</t>
   </si>
   <si>
@@ -805,8 +724,565 @@
     <t>Electricité du bâtiment 3: éclairages couloirs, éclairages hall, interphones. Relié aux panneaux solaires, avec revente du surplus d'électricité.</t>
   </si>
   <si>
-    <t>La facturation par Est Ensemble est progressive, gratuit jusqu'à 10m3, puis de 10 à 28 m³ = 1,1988 € HT / m³, de 28 à 86 m³ = 1,3320 € HT / m³, de 86 à 101 m³ = 1,3720 € HT / m³, de 101 à 131 m³ = 1,4200 € HT / m³, de 131 à 140 m³ = 1,4919 € HT / m³ et Plus de 140 m³ = 1,5366 € HT / m³
-On rajoute la redevance (3,3€/m3) et la TVA (8%)</t>
+    <t>EAU</t>
+  </si>
+  <si>
+    <t>Fonds travaux ALUR</t>
+  </si>
+  <si>
+    <t>FONDTRVX</t>
+  </si>
+  <si>
+    <t>Fonds Travaux ALUR</t>
+  </si>
+  <si>
+    <t>Le fonds travaux ALUR doit représenter 5% du budget provisionnel, mais les copropritété de résidence de moins de 5 ans en sont exemptés</t>
+  </si>
+  <si>
+    <t>Chaudière d'appoint au gaz 0,1256€ le kWh</t>
+  </si>
+  <si>
+    <t>La facturation par Est Ensemble est progressive, gratuit jusqu'à 10m3, puis de 10 à 28 m³ = 1,1988 € HT / m³, de 28 à 86 m³ = 1,3320 € HT / m³, de 86 à 101 m³ = 1,3720 € HT / m³, de 101 à 131 m³ = 1,4200 € HT / m³, de 131 à 140 m³ = 1,4919 € HT / m³ et Plus de 140 m³ = 1,5366 € HT / m³. On rajoute la redevance (3,3€/m3) et la TVA (8%). Pour référence la consommation moyenne d'eau d'un adulte sur 1 an est de 55 m3.</t>
+  </si>
+  <si>
+    <t>Lot 102 - 1er étage Batiment 1.1 (1111)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lot 103 - 1er étage Batiment 1.1 (1112) </t>
+  </si>
+  <si>
+    <t>Lot 104 - 1er étage Batiment 1.1 (1113)</t>
+  </si>
+  <si>
+    <t>Lot 105 - 1er étage Batiment 1.1 (1114)</t>
+  </si>
+  <si>
+    <t>Lot 106 - 2er étage Batiment 1.1 (1121)</t>
+  </si>
+  <si>
+    <t>Lot 107 - Studio 2eme étage Batiment 1.1 (1122)</t>
+  </si>
+  <si>
+    <t>Lot 110 - 3eme étage Batiment 1.1 (1131)</t>
+  </si>
+  <si>
+    <t>Lot 109 - 2eme étage Batiment 1.1 (1124)</t>
+  </si>
+  <si>
+    <t>Lot 108 - 2eme étage Batiment 1.1 (1123)</t>
+  </si>
+  <si>
+    <t>Lot 111 - Studio 3eme étage Batiment 1.1 (1132)</t>
+  </si>
+  <si>
+    <t>Lot 113 - T2 3ème étage Batiment 1.1 (1134)</t>
+  </si>
+  <si>
+    <t>Lot 112 - 3eme étage Batiment 1.1 (1133)</t>
+  </si>
+  <si>
+    <t>Lot 114 - 4eme étage Batiment 1.1 (1141)</t>
+  </si>
+  <si>
+    <t>Lot 115 - Studio 4eme étage Batiment 1.1 (1142)</t>
+  </si>
+  <si>
+    <t>Lot 116 - 4eme étage Batiment 1.1 (1143)</t>
+  </si>
+  <si>
+    <t>Lot 117 - T5 5eme étage Batiment 1.1 (1151)</t>
+  </si>
+  <si>
+    <t>Lot 118 - Penthouse 6-7eme étage Batiment 1.1 (1161)</t>
+  </si>
+  <si>
+    <t>Lot 119 - 1er étage Batiment 1.2 (1211)</t>
+  </si>
+  <si>
+    <t>Lot 133 - Penthouse 6-7eme étage Batiment 1.2 (1261)</t>
+  </si>
+  <si>
+    <t>Lot 134 - T2 5eme étage Batiment 1.2 (1251)</t>
+  </si>
+  <si>
+    <t>Lot 135 - T2 5eme étage Batiment 1.2 (1252)</t>
+  </si>
+  <si>
+    <t>Lot 313 - T2 RDC Batiment 3 (304)</t>
+  </si>
+  <si>
+    <t>Lot 314 - T2 RDC Batiment 3 (305)</t>
+  </si>
+  <si>
+    <t>Lot 315 - T2 2eme étage Batiment 3 (323)</t>
+  </si>
+  <si>
+    <t>Lot 316 - T2 2eme étage Batiment 3 (324)</t>
+  </si>
+  <si>
+    <t>Lot 201 - Local commercial RDC Batiment 2 (2)</t>
+  </si>
+  <si>
+    <t>Lot 101 - Local commercial RDC Batiment 1 (1)</t>
+  </si>
+  <si>
+    <t>Lot 312 - 3eme étage Batiment 3 (333)</t>
+  </si>
+  <si>
+    <t>Lot 311 - Penthouse 3-4eme étage Batiment 3 (332)</t>
+  </si>
+  <si>
+    <t>Lot 310 - Studio 3eme étage Batiment 3 (331)</t>
+  </si>
+  <si>
+    <t>Lot 308 - Studio 2eme étage Batiment 3 (322)</t>
+  </si>
+  <si>
+    <t>Lot 307 - 2eme étage Batiment 3 (321)</t>
+  </si>
+  <si>
+    <t>Lot 306 - 1er étage Batiment 3 (312)</t>
+  </si>
+  <si>
+    <t>Lot 305 - 1er étage Batiment 3 (311)</t>
+  </si>
+  <si>
+    <t>Lot 303 - Studio RDC Batiment 3 (304)</t>
+  </si>
+  <si>
+    <t>Lot 301 - Duplex RDC-1er étage Batiment 3 (301)</t>
+  </si>
+  <si>
+    <t>Lot 302 - Duplex RDC-1er étage Batiment 3 (302)</t>
+  </si>
+  <si>
+    <t>Lot 222 - Studio 6eme étage Batiment 2 (262)</t>
+  </si>
+  <si>
+    <t>Lot 223 - 6eme étage Batiment 2 (263)</t>
+  </si>
+  <si>
+    <t>Lot 224 - 7eme étage Batiment 2 (271)</t>
+  </si>
+  <si>
+    <t>Lot 225 - 7eme étage Batiment 2 (272)</t>
+  </si>
+  <si>
+    <t>Lot 202 - 1er étage Batiment 2 (211)</t>
+  </si>
+  <si>
+    <t>Lot 203 - 1er étage Batiment 2 (212)</t>
+  </si>
+  <si>
+    <t>Lot 204 - 1er étage Batiment 2 (213)</t>
+  </si>
+  <si>
+    <t>Lot 205 - 1er étage Batiment 2 (214)</t>
+  </si>
+  <si>
+    <t>Lot 206 - 2eme étage Batiment 2 (221)</t>
+  </si>
+  <si>
+    <t>Lot 207 - 2eme étage Batiment 2 (222)</t>
+  </si>
+  <si>
+    <t>Lot 208 - 2eme étage Batiment 2 (223)</t>
+  </si>
+  <si>
+    <t>Lot 209 - 2eme étage Batiment 2 (224)</t>
+  </si>
+  <si>
+    <t>Lot 210 - 3eme étage Batiment 2 (231)</t>
+  </si>
+  <si>
+    <t>Lot 211 - 3eme étage Batiment 2 (232)</t>
+  </si>
+  <si>
+    <t>Lot 213 - 3eme étage Batiment 2 (234)</t>
+  </si>
+  <si>
+    <t>Lot 212 - 3eme étage Batiment 2 (233)</t>
+  </si>
+  <si>
+    <t>Lot 214 - 4eme étage Batiment 2 (241)</t>
+  </si>
+  <si>
+    <t>Lot 215 - 4eme étage Batiment 2 (242)</t>
+  </si>
+  <si>
+    <t>Lot 216 - Studio 4eme étage Batiment 2 (243)</t>
+  </si>
+  <si>
+    <t>Lot 217 - 4eme étage Batiment 2 (244)</t>
+  </si>
+  <si>
+    <t>Lot 218 - 5eme étage Batiment 2 (251)</t>
+  </si>
+  <si>
+    <t>Lot 219 - Studio 5eme étage Batiment 2 (252)</t>
+  </si>
+  <si>
+    <t>Lot 220 - 5eme étage Batiment 2 (253)</t>
+  </si>
+  <si>
+    <t>Lot 221 - 6eme étage Batiment 2 (261)</t>
+  </si>
+  <si>
+    <t>Lot 412 - Parking 1er sous sol Batiment 1.2 (12)</t>
+  </si>
+  <si>
+    <t>Lot 453 - Parking 2eme sous sol Batiment 1.1 (55)</t>
+  </si>
+  <si>
+    <t>Lot 454 - Parking 2eme sous sol Batiment 1.1 (56)</t>
+  </si>
+  <si>
+    <t>Lot 455 - Parking 2eme sous sol Batiment 1.1 (57)</t>
+  </si>
+  <si>
+    <t>Lot 456 - Parking 2eme sous sol Batiment 1.1 (58)</t>
+  </si>
+  <si>
+    <t>Lot 457 - Parking 2eme sous sol Batiment 1.2 (59)</t>
+  </si>
+  <si>
+    <t>Lot 458 - Parking 2eme sous sol Batiment 1.1 (60)</t>
+  </si>
+  <si>
+    <t>Lot 459 - Parking 2eme sous sol Batiment 1.1 (61)</t>
+  </si>
+  <si>
+    <t>Lot 462 - Parking 2eme sous sol Batiment 1.1 (64)</t>
+  </si>
+  <si>
+    <t>Lot 460 - Parking 2eme sous sol Batiment 1.1 (62)</t>
+  </si>
+  <si>
+    <t>Lot 461 - Parking 2eme sous sol Batiment 1.1 (63)</t>
+  </si>
+  <si>
+    <t>Lot 463 - Parking 2eme sous sol Batiment 1.2 (65)</t>
+  </si>
+  <si>
+    <t>Lot 401 - Parking 1er sous sol Batiment 1.2 (1)</t>
+  </si>
+  <si>
+    <t>Lot 402 - Parking 1er sous sol Batiment 1.2 (2)</t>
+  </si>
+  <si>
+    <t>Lot 403 - Parking 1er sous sol Batiment 1.1 (3)</t>
+  </si>
+  <si>
+    <t>Lot 404 - Parking 1er sous sol Batiment 1.1 (4)</t>
+  </si>
+  <si>
+    <t>Lot 405 - Parking 1er sous sol Batiment 1.1 (5)</t>
+  </si>
+  <si>
+    <t>Lot 406 - Parking 1er sous sol Batiment 1.1 (6)</t>
+  </si>
+  <si>
+    <t>Lot 407 - Parking 1er sous sol Batiment 1.2 (7)</t>
+  </si>
+  <si>
+    <t>Lot 408 - Parking 1er sous sol Batiment 1.1 (8)</t>
+  </si>
+  <si>
+    <t>Lot 409 - Parking 1er sous sol Batiment 1.2 (9)</t>
+  </si>
+  <si>
+    <t>Lot 410 - Parking 1er sous sol Batiment 1.2 (10)</t>
+  </si>
+  <si>
+    <t>Lot 411 - Parking 1er sous sol Batiment 1.2 (11)</t>
+  </si>
+  <si>
+    <t>Lot 413 - Parking 1er sous sol Batiment 1.2 (13)</t>
+  </si>
+  <si>
+    <t>Lot 414 - Parking 1er sous sol Batiment 1.2 (14)</t>
+  </si>
+  <si>
+    <t>Lot 415 - Parking 1er sous sol Batiment 1.2 (15)</t>
+  </si>
+  <si>
+    <t>Lot 416 - Parking 1er sous sol Batiment 1.2 (16)</t>
+  </si>
+  <si>
+    <t>Lot 417 - Parking 1er sous sol Batiment 1.2 (17)</t>
+  </si>
+  <si>
+    <t>Lot 418 - Parking 1er sous sol Batiment 1.2 (18)</t>
+  </si>
+  <si>
+    <t>Lot 419 - Parking 1er sous sol Batiment 2 (19)</t>
+  </si>
+  <si>
+    <t>Lot 420 - Parking 1er sous sol Batiment 2 (20)</t>
+  </si>
+  <si>
+    <t>Lot 421 - Parking 1er sous sol Batiment 2 (21)</t>
+  </si>
+  <si>
+    <t>Lot 422 - Parking 1er sous sol Batiment 2 (22)</t>
+  </si>
+  <si>
+    <t>Lot 423 - Parking 1er sous sol Batiment 2 (23)</t>
+  </si>
+  <si>
+    <t>Lot 424 - Parking 1er sous sol Batiment 2 (24)</t>
+  </si>
+  <si>
+    <t>Lot 425 - Parking 1er sous sol Batiment 2 (25)</t>
+  </si>
+  <si>
+    <t>Lot 426 - Parking 1er sous sol Batiment 2 (26)</t>
+  </si>
+  <si>
+    <t>Lot 427 - Parking 1er sous sol Batiment 2 (27)</t>
+  </si>
+  <si>
+    <t>Lot 428 - Parking 1er sous sol Batiment 2 (28)</t>
+  </si>
+  <si>
+    <t>Lot 429 - Parking 1er sous sol Batiment 2 (29)</t>
+  </si>
+  <si>
+    <t>Lot 430 - Parking 1er sous sol Batiment 2 (30)</t>
+  </si>
+  <si>
+    <t>Lot 431 - Parking 1er sous sol Batiment 2 (31)</t>
+  </si>
+  <si>
+    <t>Lot 432 - Parking 1er sous sol Batiment 2 (32)</t>
+  </si>
+  <si>
+    <t>Lot 433 - Parking 1er sous sol Batiment 3 (34)</t>
+  </si>
+  <si>
+    <t>Lot 434 - Parking 1er sous sol Batiment 3 (35)</t>
+  </si>
+  <si>
+    <t>Lot 435 - Parking 1er sous sol Batiment 3 (36)</t>
+  </si>
+  <si>
+    <t>Lot 436 - Parking 1er sous sol Batiment 3 (37)</t>
+  </si>
+  <si>
+    <t>Lot 437 - Parking 1er sous sol Batiment 3 (38)</t>
+  </si>
+  <si>
+    <t>Lot 438 - Parking 1er sous sol Batiment 3 (39)</t>
+  </si>
+  <si>
+    <t>Lot 439 - Parking 1er sous sol Batiment 3 (40)</t>
+  </si>
+  <si>
+    <t>Lot 440 - Parking 1er sous sol Batiment 3 (41)</t>
+  </si>
+  <si>
+    <t>Lot 441 - Parking 1er sous sol Batiment 3 (42)</t>
+  </si>
+  <si>
+    <t>Lot 442 - Parking 1er sous sol Batiment 3 (43)</t>
+  </si>
+  <si>
+    <t>Lot 443 - Parking 1er sous sol Batiment 3 (44)</t>
+  </si>
+  <si>
+    <t>Lot 444 - Parking 1er sous sol Batiment 3 (45)</t>
+  </si>
+  <si>
+    <t>Lot 445 - Parking 1er sous sol Batiment 3 (46)</t>
+  </si>
+  <si>
+    <t>Lot 446 - Parking 1er sous sol Batiment 2 (47)</t>
+  </si>
+  <si>
+    <t>Lot 447 - Parking 1er sous sol Batiment 2 (49)</t>
+  </si>
+  <si>
+    <t>Lot 448 - Parking 1er sous sol Batiment 2 (50)</t>
+  </si>
+  <si>
+    <t>Lot 449 - Parking 1er sous sol Batiment 2 (51)</t>
+  </si>
+  <si>
+    <t>Lot 450 - Parking 1er sous sol Batiment 2 (52)</t>
+  </si>
+  <si>
+    <t>Lot 451 - Parking 1er sous sol Batiment 1.2 (53)</t>
+  </si>
+  <si>
+    <t>Lot 452 - Parking 1er sous sol Batiment 2 (54)</t>
+  </si>
+  <si>
+    <t>Lot 464 - Parking 2eme sous sol Batiment 1.1 (66)</t>
+  </si>
+  <si>
+    <t>Lot 465 - Parking 2eme sous sol Batiment 1.1 (67)</t>
+  </si>
+  <si>
+    <t>Lot 466 - Parking 2eme sous sol Batiment 2 (68)</t>
+  </si>
+  <si>
+    <t>Lot 467 - Parking 2eme sous sol Batiment 2 (69)</t>
+  </si>
+  <si>
+    <t>Lot 468 - Parking 2eme sous sol Batiment 2 (70)</t>
+  </si>
+  <si>
+    <t>Lot 469 - Parking 2eme sous sol Batiment 2 (71)</t>
+  </si>
+  <si>
+    <t>Lot 470 - Parking 2eme sous sol Batiment 1.1 (72)</t>
+  </si>
+  <si>
+    <t>Lot 471 - Parking 2eme sous sol Batiment 1.1 (73)</t>
+  </si>
+  <si>
+    <t>Lot 472 - Parking 2eme sous sol Batiment 1.1 (74)</t>
+  </si>
+  <si>
+    <t>Lot 473 - Parking 2eme sous sol Batiment 1.1 (75)</t>
+  </si>
+  <si>
+    <t>Lot 474 - Parking 2eme sous sol Batiment 1.1 (76)</t>
+  </si>
+  <si>
+    <t>Lot 475 - Parking 2eme sous sol Batiment 1.1 (77)</t>
+  </si>
+  <si>
+    <t>Lot 476 - Parking 2eme sous sol Batiment 1.1 (78)</t>
+  </si>
+  <si>
+    <t>Lot 477 - Parking 2eme sous sol Batiment 1.1 (79)</t>
+  </si>
+  <si>
+    <t>Lot 478 - Parking 2eme sous sol Batiment 1.1 (80)</t>
+  </si>
+  <si>
+    <t>Lot 479 - Parking 2eme sous sol Batiment 1.1 (81)</t>
+  </si>
+  <si>
+    <t>Lot 480 - Parking 2eme sous sol Batiment 1.1 (82)</t>
+  </si>
+  <si>
+    <t>Lot 481 - Parking 2eme sous sol Batiment 1.1 (83)</t>
+  </si>
+  <si>
+    <t>Lot 482 - Parking 2eme sous sol Batiment 1.1 (84)</t>
+  </si>
+  <si>
+    <t>Lot 483 - Parking 2eme sous sol Batiment 1.1 (85)</t>
+  </si>
+  <si>
+    <t>Lot 484 - Parking 2eme sous sol Batiment 1.1 (86)</t>
+  </si>
+  <si>
+    <t>Lot 485 - Parking 2eme sous sol Batiment 1.1 (87)</t>
+  </si>
+  <si>
+    <t>Lot 486 - Parking 2eme sous sol Batiment 1.1 (88)</t>
+  </si>
+  <si>
+    <t>Lot 487 - Parking 2eme sous sol Batiment 1.1 (89)</t>
+  </si>
+  <si>
+    <t>Lot 488 - Parking 2eme sous sol Batiment 1.1 (90)</t>
+  </si>
+  <si>
+    <t>Lot 489 - Parking 2eme sous sol Batiment 1.1 (91)</t>
+  </si>
+  <si>
+    <t>Lot 490 - Parking 2eme sous sol Batiment 1.1 (92)</t>
+  </si>
+  <si>
+    <t>Lot 491 - Parking 2eme sous sol Batiment 1.1 (93)</t>
+  </si>
+  <si>
+    <t>Lot 492 - Parking 2eme sous sol Batiment 1.1 (94)</t>
+  </si>
+  <si>
+    <t>Lot 493 - Parking 2eme sous sol Batiment 1.1 (95)</t>
+  </si>
+  <si>
+    <t>Lot 494 - Parking 2eme sous sol Batiment 1.1 (96)</t>
+  </si>
+  <si>
+    <t>Lot 495 - Parking 2eme sous sol Batiment 1.1 (97)</t>
+  </si>
+  <si>
+    <t>Lot 496 - Parking 2eme sous sol Batiment 1.1 (98)</t>
+  </si>
+  <si>
+    <t>Lot 497 - Parking 2eme sous sol Batiment 1.1 (99)</t>
+  </si>
+  <si>
+    <t>Lot 498 - Parking 2eme sous sol Batiment 1.1 (100)</t>
+  </si>
+  <si>
+    <t>Lot 506 - Parking 1er sous sol Batiment 3 (33)</t>
+  </si>
+  <si>
+    <t>Lot 499 - Parking 2eme sous sol Batiment 1.1 (101)</t>
+  </si>
+  <si>
+    <t>Lot 500 - Parking 2eme sous sol Batiment 1.1 (102)</t>
+  </si>
+  <si>
+    <t>Lot 501 - Parking 2eme sous sol Batiment 1.1 (103)</t>
+  </si>
+  <si>
+    <t>Lot 502 - Cave 2eme sous sol (1)</t>
+  </si>
+  <si>
+    <t>Lot 503 - Cave 2eme sous sol (2)</t>
+  </si>
+  <si>
+    <t>Lot 504 - Cave 2eme sous sol (3)</t>
+  </si>
+  <si>
+    <t>Lot 505 - Cave 2eme sous sol (4)</t>
+  </si>
+  <si>
+    <t>Lot 120 - 1er étage Batiment 1.2 (1212)</t>
+  </si>
+  <si>
+    <t>Lot 121 - 1er étage Batiment 1.2 (1213)</t>
+  </si>
+  <si>
+    <t>Lot 122 - 2eme étage Batiment 1.2 (1221)</t>
+  </si>
+  <si>
+    <t>Lot 123 - 2eme étage Batiment 1.2 (1222)</t>
+  </si>
+  <si>
+    <t>Lot 124 - 2eme étage Batiment 1.2 (1223)</t>
+  </si>
+  <si>
+    <t>Lot 125 - 3eme étage Batiment 1.2 (1231)</t>
+  </si>
+  <si>
+    <t>Lot 126 - 3eme étage Batiment 1.2 (1232)</t>
+  </si>
+  <si>
+    <t>Lot 127 - 3eme etage Batiment 1.2 (1233)</t>
+  </si>
+  <si>
+    <t>Lot 128 - 4eme étage Batiment 1.2 (1241)</t>
+  </si>
+  <si>
+    <t>Lot 130 - 4eme étage Batiment 1.2 (1243)</t>
+  </si>
+  <si>
+    <t>Lot 129 - 4eme étage Batiment 1.2 (1242)</t>
+  </si>
+  <si>
+    <t>Lot 132 - 5eme étage Batiment 1.2 (1253)</t>
+  </si>
+  <si>
+    <t>Prix de la tonne de granulés: Gruchy = 310€/t, CRAM = 392€/t (dans le simulateur) et Prochalor 500€/t - 1 tonne de granulés de bois = 4800-5000kWh</t>
   </si>
 </sst>
 </file>
@@ -955,6 +1431,30 @@
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_-* #,##0.00\ &quot;€&quot;_-;\-* #,##0.00\ &quot;€&quot;_-;_-* &quot;-&quot;??\ &quot;€&quot;_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -1225,30 +1725,6 @@
       </font>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="34" formatCode="_-* #,##0.00\ &quot;€&quot;_-;\-* #,##0.00\ &quot;€&quot;_-;_-* &quot;-&quot;??\ &quot;€&quot;_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1267,8 +1743,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{13C2BCD2-5CEA-4301-A571-688E40226767}" name="Provisions" displayName="Provisions" ref="A1:F34">
-  <autoFilter ref="A1:F34" xr:uid="{13C2BCD2-5CEA-4301-A571-688E40226767}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{13C2BCD2-5CEA-4301-A571-688E40226767}" name="Provisions" displayName="Provisions" ref="A1:F35">
+  <autoFilter ref="A1:F35" xr:uid="{13C2BCD2-5CEA-4301-A571-688E40226767}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F34">
     <sortCondition descending="1" ref="E1:E34"/>
   </sortState>
@@ -1277,8 +1753,8 @@
     <tableColumn id="4" xr3:uid="{84F1F30D-4827-43F2-8865-B7957E3E712D}" name="ID"/>
     <tableColumn id="7" xr3:uid="{512EABBD-B863-4251-833D-8B8D1F1626EF}" name="Description"/>
     <tableColumn id="2" xr3:uid="{D09C4BB0-FEBD-4A72-9E87-B5258D8B62D7}" name="Label de la provision"/>
-    <tableColumn id="3" xr3:uid="{347751FB-EF14-4BD7-9D47-427E04136B77}" name="Provision" totalsRowFunction="sum" dataDxfId="26" totalsRowDxfId="25"/>
-    <tableColumn id="5" xr3:uid="{CA26B6F8-88AD-418A-B213-749ABA66E926}" name="Description longue" dataDxfId="24"/>
+    <tableColumn id="3" xr3:uid="{347751FB-EF14-4BD7-9D47-427E04136B77}" name="Provision" totalsRowFunction="sum" dataDxfId="11" totalsRowDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{CA26B6F8-88AD-418A-B213-749ABA66E926}" name="Description longue" dataDxfId="9"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1288,37 +1764,37 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{74E83642-0ED6-4017-A369-70F6DD3FC748}" name="Lots" displayName="Lots" ref="A1:P180" totalsRowShown="0">
   <autoFilter ref="A1:P180" xr:uid="{74E83642-0ED6-4017-A369-70F6DD3FC748}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:P180">
-    <sortCondition ref="B1:B180"/>
+    <sortCondition ref="A1:A180"/>
   </sortState>
   <tableColumns count="16">
-    <tableColumn id="3" xr3:uid="{1687C042-C916-4161-82C2-2A915364FCD2}" name="Numéro de lot" dataDxfId="23"/>
+    <tableColumn id="3" xr3:uid="{1687C042-C916-4161-82C2-2A915364FCD2}" name="Numéro de lot" dataDxfId="26"/>
     <tableColumn id="1" xr3:uid="{788DBA8C-5B77-4079-8161-FA45C58518AE}" name="Description"/>
-    <tableColumn id="2" xr3:uid="{BE5ACA99-AEAF-4E51-BE0A-B3FB8FCCF08B}" name="Tantièmes copropriété" dataDxfId="22">
+    <tableColumn id="2" xr3:uid="{BE5ACA99-AEAF-4E51-BE0A-B3FB8FCCF08B}" name="Tantièmes copropriété" dataDxfId="25">
       <calculatedColumnFormula>7/10000</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{D62FAA89-C46E-4AF6-A14F-7FD6F46E7F00}" name="Tantièmes ascenseur 1-1" dataDxfId="21"/>
-    <tableColumn id="9" xr3:uid="{C3B9BDED-CB2A-4305-9CBF-418F5971AC1E}" name="Tantièmes ascenseur 1-2" dataDxfId="20"/>
-    <tableColumn id="10" xr3:uid="{C2291DE1-C707-4F83-846E-F914B4B42E52}" name="Tantièmes ascenseur 2" dataDxfId="19"/>
-    <tableColumn id="11" xr3:uid="{4F70F08A-4C2F-41B0-88EB-711B1A0760CD}" name="Tantièmes ascenseur 3" dataDxfId="18"/>
-    <tableColumn id="14" xr3:uid="{80D23396-716C-46AC-9B55-BCBC6C981351}" name="Tantièmes chauffage" dataDxfId="17"/>
-    <tableColumn id="15" xr3:uid="{E3955139-B619-4DD0-8FC1-ECA97048DFE4}" name="Tantièmes Batiment 1" dataDxfId="16"/>
-    <tableColumn id="16" xr3:uid="{C73E9407-A858-4EF7-81C2-6C70C4B157A2}" name="Tantièmes Batiment 2" dataDxfId="15"/>
-    <tableColumn id="17" xr3:uid="{A07338CA-0096-4091-89B2-A46FF2D323C2}" name="Tantièmes Batiment 3" dataDxfId="14"/>
-    <tableColumn id="18" xr3:uid="{7A3012D8-2375-4F10-9E84-F2F5060C6A99}" name="Tantièmes Hall 1-1" dataDxfId="13"/>
-    <tableColumn id="19" xr3:uid="{67961B6E-B577-4A49-B099-623FB85519B4}" name="Tantièmes Hall 1-2" dataDxfId="12"/>
-    <tableColumn id="20" xr3:uid="{03C201C1-F8AA-4D3C-AEBC-425B180BC2D7}" name="Tantièmes Hall 2" dataDxfId="11"/>
-    <tableColumn id="21" xr3:uid="{4826FC05-81A9-4020-8D1D-83D3D5C5A05A}" name="Tantièmes Logement/Stationnements" dataDxfId="10"/>
-    <tableColumn id="6" xr3:uid="{7B87787E-3595-42D5-B815-AF76B67432D8}" name="Tantièmes Stationnement" dataDxfId="9"/>
+    <tableColumn id="8" xr3:uid="{D62FAA89-C46E-4AF6-A14F-7FD6F46E7F00}" name="Tantièmes ascenseur 1-1" dataDxfId="24"/>
+    <tableColumn id="9" xr3:uid="{C3B9BDED-CB2A-4305-9CBF-418F5971AC1E}" name="Tantièmes ascenseur 1-2" dataDxfId="23"/>
+    <tableColumn id="10" xr3:uid="{C2291DE1-C707-4F83-846E-F914B4B42E52}" name="Tantièmes ascenseur 2" dataDxfId="22"/>
+    <tableColumn id="11" xr3:uid="{4F70F08A-4C2F-41B0-88EB-711B1A0760CD}" name="Tantièmes ascenseur 3" dataDxfId="21"/>
+    <tableColumn id="14" xr3:uid="{80D23396-716C-46AC-9B55-BCBC6C981351}" name="Tantièmes chauffage" dataDxfId="20"/>
+    <tableColumn id="15" xr3:uid="{E3955139-B619-4DD0-8FC1-ECA97048DFE4}" name="Tantièmes Batiment 1" dataDxfId="19"/>
+    <tableColumn id="16" xr3:uid="{C73E9407-A858-4EF7-81C2-6C70C4B157A2}" name="Tantièmes Batiment 2" dataDxfId="18"/>
+    <tableColumn id="17" xr3:uid="{A07338CA-0096-4091-89B2-A46FF2D323C2}" name="Tantièmes Batiment 3" dataDxfId="17"/>
+    <tableColumn id="18" xr3:uid="{7A3012D8-2375-4F10-9E84-F2F5060C6A99}" name="Tantièmes Hall 1-1" dataDxfId="16"/>
+    <tableColumn id="19" xr3:uid="{67961B6E-B577-4A49-B099-623FB85519B4}" name="Tantièmes Hall 1-2" dataDxfId="15"/>
+    <tableColumn id="20" xr3:uid="{03C201C1-F8AA-4D3C-AEBC-425B180BC2D7}" name="Tantièmes Hall 2" dataDxfId="14"/>
+    <tableColumn id="21" xr3:uid="{4826FC05-81A9-4020-8D1D-83D3D5C5A05A}" name="Tantièmes Logement/Stationnements" dataDxfId="13"/>
+    <tableColumn id="6" xr3:uid="{7B87787E-3595-42D5-B815-AF76B67432D8}" name="Tantièmes Stationnement" dataDxfId="12"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{AFF80A4D-E18B-42B5-9271-DD654E188D32}" name="Prestations" displayName="Prestations" ref="A1:I48" totalsRowShown="0">
-  <autoFilter ref="A1:I48" xr:uid="{AFF80A4D-E18B-42B5-9271-DD654E188D32}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H48">
-    <sortCondition ref="B1:B48"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{AFF80A4D-E18B-42B5-9271-DD654E188D32}" name="Prestations" displayName="Prestations" ref="A1:I45" totalsRowShown="0">
+  <autoFilter ref="A1:I45" xr:uid="{AFF80A4D-E18B-42B5-9271-DD654E188D32}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H45">
+    <sortCondition ref="B1:B45"/>
   </sortState>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{7753A616-C6B5-4B02-AE3F-2A95253630B8}" name="Type de prestation" dataDxfId="8"/>
@@ -1342,7 +1818,9 @@
   <autoFilter ref="A1:C2" xr:uid="{0628909A-75FF-41C1-9EE4-F3C649717216}"/>
   <tableColumns count="3">
     <tableColumn id="4" xr3:uid="{B1EE509D-2894-4393-AA6B-5D042BB6CCBA}" name="Label"/>
-    <tableColumn id="2" xr3:uid="{0EB0E801-9DD6-4459-8AAC-AA0D5AC1F393}" name="Volume à chauffer en m3"/>
+    <tableColumn id="2" xr3:uid="{0EB0E801-9DD6-4459-8AAC-AA0D5AC1F393}" name="Volume à chauffer en m3">
+      <calculatedColumnFormula>5735*2.5</calculatedColumnFormula>
+    </tableColumn>
     <tableColumn id="3" xr3:uid="{194ABB34-607A-43C7-8DED-8E1BDC9DD34E}" name="Coefficient d'isolation"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1630,7 +2108,7 @@
   <sheetPr>
     <tabColor theme="9" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32.42578125" bestFit="1" customWidth="1"/>
@@ -1643,76 +2121,76 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>201</v>
+        <v>189</v>
       </c>
       <c r="B1" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="C1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F1" t="s">
-        <v>229</v>
+        <v>215</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B2" t="s">
-        <v>55</v>
+        <v>223</v>
       </c>
       <c r="C2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E2" s="1">
         <v>35000</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>250</v>
+        <v>229</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E3" s="1">
         <v>27000</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>244</v>
+        <v>217</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E4" s="1">
         <v>23100</v>
@@ -1721,16 +2199,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E5" s="1">
         <v>18000</v>
@@ -1739,16 +2217,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B6" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E6" s="1">
         <v>17650</v>
@@ -1757,16 +2235,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B7" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E7" s="1">
         <v>16800</v>
@@ -1775,16 +2253,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B8" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E8" s="1">
         <v>6200</v>
@@ -1793,16 +2271,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B9" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C9" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D9" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E9" s="1">
         <v>4000</v>
@@ -1811,16 +2289,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B10" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E10" s="1">
         <v>3500</v>
@@ -1829,16 +2307,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B11" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C11" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D11" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E11" s="1">
         <v>3000</v>
@@ -1847,16 +2325,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B12" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C12" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D12" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E12" s="1">
         <v>2900</v>
@@ -1865,16 +2343,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B13" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C13" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D13" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E13" s="1">
         <v>2900</v>
@@ -1883,16 +2361,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="B14" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C14" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D14" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E14" s="1">
         <v>2700</v>
@@ -1901,36 +2379,36 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B15" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C15" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D15" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E15" s="1">
         <v>2000</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>247</v>
+        <v>220</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B16" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C16" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D16" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E16" s="1">
         <v>1500</v>
@@ -1939,16 +2417,16 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="B17" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C17" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D17" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E17" s="1">
         <v>1500</v>
@@ -1957,116 +2435,116 @@
     </row>
     <row r="18" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B18" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C18" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D18" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E18" s="1">
         <v>1050</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>228</v>
+        <v>214</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B19" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C19" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D19" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E19" s="1">
         <v>1000</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>248</v>
+        <v>221</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B20" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C20" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D20" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E20" s="1">
         <v>1000</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>249</v>
+        <v>222</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B21" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C21" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D21" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E21" s="1">
         <v>920</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>227</v>
+        <v>213</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="135" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B22" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C22" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D22" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E22" s="1">
         <v>900</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>226</v>
+        <v>212</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B23" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C23" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D23" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E23" s="1">
         <v>850</v>
@@ -2075,36 +2553,36 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B24" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C24" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D24" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E24" s="1">
         <v>750</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>246</v>
+        <v>219</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B25" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C25" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D25" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E25" s="1">
         <v>650</v>
@@ -2113,36 +2591,36 @@
     </row>
     <row r="26" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B26" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C26" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D26" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E26" s="1">
         <v>580</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B27" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C27" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D27" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E27" s="1">
         <v>570</v>
@@ -2151,96 +2629,96 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="B28" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C28" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D28" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E28" s="1">
         <v>450</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>245</v>
+        <v>218</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="B29" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C29" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D29" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E29" s="1">
         <v>360</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="B30" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C30" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D30" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E30" s="1">
         <v>320</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B31" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C31" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D31" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E31" s="1">
         <v>240</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>223</v>
+        <v>209</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B32" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C32" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D32" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E32" s="1">
         <v>220</v>
@@ -2249,39 +2727,56 @@
     </row>
     <row r="33" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="B33" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C33" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D33" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E33" s="1">
         <v>90</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B34" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C34" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D34" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E34" s="1"/>
       <c r="F34" s="2"/>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>145</v>
+      </c>
+      <c r="B35" t="s">
+        <v>225</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="D35" t="s">
+        <v>226</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>227</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2314,52 +2809,52 @@
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C1" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="E1" s="8" t="s">
         <v>147</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="F1" s="8" t="s">
         <v>148</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="G1" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="H1" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="I1" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="G1" s="8" t="s">
-        <v>187</v>
-      </c>
-      <c r="H1" s="8" t="s">
+      <c r="J1" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="K1" s="8" t="s">
         <v>152</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="L1" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="M1" s="8" t="s">
         <v>154</v>
       </c>
-      <c r="L1" s="8" t="s">
+      <c r="N1" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="M1" s="8" t="s">
+      <c r="O1" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="N1" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="O1" s="8" t="s">
-        <v>158</v>
-      </c>
       <c r="P1" s="8" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
@@ -2367,7 +2862,7 @@
         <v>101</v>
       </c>
       <c r="B2" t="s">
-        <v>230</v>
+        <v>256</v>
       </c>
       <c r="C2">
         <v>462</v>
@@ -2381,7 +2876,7 @@
         <v>102</v>
       </c>
       <c r="B3" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C3">
         <v>119</v>
@@ -2407,7 +2902,7 @@
         <v>103</v>
       </c>
       <c r="B4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C4">
         <v>83</v>
@@ -2433,7 +2928,7 @@
         <v>104</v>
       </c>
       <c r="B5" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C5">
         <v>130</v>
@@ -2459,7 +2954,7 @@
         <v>105</v>
       </c>
       <c r="B6" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C6">
         <v>123</v>
@@ -2485,7 +2980,7 @@
         <v>106</v>
       </c>
       <c r="B7" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C7">
         <v>122</v>
@@ -2511,7 +3006,7 @@
         <v>107</v>
       </c>
       <c r="B8" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C8">
         <v>55</v>
@@ -2537,7 +3032,7 @@
         <v>108</v>
       </c>
       <c r="B9" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C9">
         <v>96</v>
@@ -2563,7 +3058,7 @@
         <v>109</v>
       </c>
       <c r="B10" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C10">
         <v>123</v>
@@ -2589,7 +3084,7 @@
         <v>110</v>
       </c>
       <c r="B11" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="C11">
         <v>129</v>
@@ -2615,7 +3110,7 @@
         <v>111</v>
       </c>
       <c r="B12" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C12">
         <v>58</v>
@@ -2667,7 +3162,7 @@
         <v>113</v>
       </c>
       <c r="B14" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C14" s="8">
         <v>86</v>
@@ -2700,9 +3195,8 @@
       <c r="A15" s="8">
         <v>114</v>
       </c>
-      <c r="B15" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 114</v>
+      <c r="B15" t="s">
+        <v>242</v>
       </c>
       <c r="C15">
         <v>94</v>
@@ -2727,9 +3221,8 @@
       <c r="A16" s="8">
         <v>115</v>
       </c>
-      <c r="B16" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 115</v>
+      <c r="B16" t="s">
+        <v>243</v>
       </c>
       <c r="C16">
         <v>60</v>
@@ -2754,9 +3247,8 @@
       <c r="A17" s="8">
         <v>116</v>
       </c>
-      <c r="B17" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 116</v>
+      <c r="B17" t="s">
+        <v>244</v>
       </c>
       <c r="C17">
         <v>162</v>
@@ -2781,9 +3273,8 @@
       <c r="A18" s="8">
         <v>117</v>
       </c>
-      <c r="B18" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 117</v>
+      <c r="B18" t="s">
+        <v>245</v>
       </c>
       <c r="C18">
         <v>202</v>
@@ -2808,9 +3299,8 @@
       <c r="A19" s="8">
         <v>118</v>
       </c>
-      <c r="B19" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 118</v>
+      <c r="B19" t="s">
+        <v>246</v>
       </c>
       <c r="C19">
         <v>294</v>
@@ -2835,9 +3325,8 @@
       <c r="A20" s="8">
         <v>119</v>
       </c>
-      <c r="B20" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 119</v>
+      <c r="B20" t="s">
+        <v>247</v>
       </c>
       <c r="C20">
         <v>81</v>
@@ -2862,9 +3351,8 @@
       <c r="A21" s="8">
         <v>120</v>
       </c>
-      <c r="B21" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 120</v>
+      <c r="B21" t="s">
+        <v>397</v>
       </c>
       <c r="C21">
         <v>115</v>
@@ -2889,9 +3377,8 @@
       <c r="A22" s="8">
         <v>121</v>
       </c>
-      <c r="B22" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 121</v>
+      <c r="B22" t="s">
+        <v>398</v>
       </c>
       <c r="C22">
         <v>112</v>
@@ -2916,9 +3403,8 @@
       <c r="A23" s="8">
         <v>122</v>
       </c>
-      <c r="B23" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 122</v>
+      <c r="B23" t="s">
+        <v>399</v>
       </c>
       <c r="C23">
         <v>83</v>
@@ -2943,9 +3429,8 @@
       <c r="A24" s="8">
         <v>123</v>
       </c>
-      <c r="B24" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 123</v>
+      <c r="B24" t="s">
+        <v>400</v>
       </c>
       <c r="C24">
         <v>118</v>
@@ -2970,9 +3455,8 @@
       <c r="A25" s="8">
         <v>124</v>
       </c>
-      <c r="B25" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 124</v>
+      <c r="B25" t="s">
+        <v>401</v>
       </c>
       <c r="C25">
         <v>117</v>
@@ -2997,9 +3481,8 @@
       <c r="A26" s="8">
         <v>125</v>
       </c>
-      <c r="B26" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 125</v>
+      <c r="B26" t="s">
+        <v>402</v>
       </c>
       <c r="C26">
         <v>87</v>
@@ -3024,9 +3507,8 @@
       <c r="A27" s="8">
         <v>126</v>
       </c>
-      <c r="B27" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 126</v>
+      <c r="B27" t="s">
+        <v>403</v>
       </c>
       <c r="C27">
         <v>125</v>
@@ -3051,9 +3533,8 @@
       <c r="A28" s="8">
         <v>127</v>
       </c>
-      <c r="B28" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 127</v>
+      <c r="B28" t="s">
+        <v>404</v>
       </c>
       <c r="C28">
         <v>123</v>
@@ -3078,9 +3559,8 @@
       <c r="A29" s="8">
         <v>128</v>
       </c>
-      <c r="B29" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 128</v>
+      <c r="B29" t="s">
+        <v>405</v>
       </c>
       <c r="C29">
         <v>88</v>
@@ -3105,9 +3585,8 @@
       <c r="A30" s="8">
         <v>129</v>
       </c>
-      <c r="B30" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 129</v>
+      <c r="B30" t="s">
+        <v>407</v>
       </c>
       <c r="C30">
         <v>127</v>
@@ -3132,9 +3611,8 @@
       <c r="A31" s="8">
         <v>130</v>
       </c>
-      <c r="B31" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 130</v>
+      <c r="B31" t="s">
+        <v>406</v>
       </c>
       <c r="C31">
         <v>127</v>
@@ -3159,9 +3637,8 @@
       <c r="A32" s="8">
         <v>132</v>
       </c>
-      <c r="B32" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 132</v>
+      <c r="B32" t="s">
+        <v>408</v>
       </c>
       <c r="C32">
         <v>172</v>
@@ -3186,9 +3663,8 @@
       <c r="A33" s="8">
         <v>133</v>
       </c>
-      <c r="B33" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 133</v>
+      <c r="B33" t="s">
+        <v>248</v>
       </c>
       <c r="C33">
         <v>218</v>
@@ -3213,9 +3689,8 @@
       <c r="A34" s="8">
         <v>134</v>
       </c>
-      <c r="B34" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 134</v>
+      <c r="B34" t="s">
+        <v>249</v>
       </c>
       <c r="C34">
         <v>102</v>
@@ -3240,9 +3715,8 @@
       <c r="A35" s="8">
         <v>135</v>
       </c>
-      <c r="B35" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 135</v>
+      <c r="B35" t="s">
+        <v>250</v>
       </c>
       <c r="C35">
         <v>83</v>
@@ -3267,9 +3741,8 @@
       <c r="A36" s="8">
         <v>201</v>
       </c>
-      <c r="B36" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 201</v>
+      <c r="B36" t="s">
+        <v>255</v>
       </c>
       <c r="C36">
         <v>401</v>
@@ -3282,9 +3755,8 @@
       <c r="A37" s="8">
         <v>202</v>
       </c>
-      <c r="B37" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 202</v>
+      <c r="B37" t="s">
+        <v>271</v>
       </c>
       <c r="C37">
         <v>114</v>
@@ -3309,9 +3781,8 @@
       <c r="A38" s="8">
         <v>203</v>
       </c>
-      <c r="B38" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 203</v>
+      <c r="B38" t="s">
+        <v>272</v>
       </c>
       <c r="C38">
         <v>84</v>
@@ -3336,9 +3807,8 @@
       <c r="A39" s="8">
         <v>204</v>
       </c>
-      <c r="B39" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 204</v>
+      <c r="B39" t="s">
+        <v>273</v>
       </c>
       <c r="C39">
         <v>81</v>
@@ -3363,9 +3833,8 @@
       <c r="A40" s="8">
         <v>205</v>
       </c>
-      <c r="B40" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 205</v>
+      <c r="B40" t="s">
+        <v>274</v>
       </c>
       <c r="C40">
         <v>118</v>
@@ -3390,9 +3859,8 @@
       <c r="A41" s="8">
         <v>206</v>
       </c>
-      <c r="B41" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 206</v>
+      <c r="B41" t="s">
+        <v>275</v>
       </c>
       <c r="C41">
         <v>120</v>
@@ -3417,9 +3885,8 @@
       <c r="A42" s="8">
         <v>207</v>
       </c>
-      <c r="B42" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 207</v>
+      <c r="B42" t="s">
+        <v>276</v>
       </c>
       <c r="C42">
         <v>89</v>
@@ -3444,9 +3911,8 @@
       <c r="A43" s="8">
         <v>208</v>
       </c>
-      <c r="B43" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 208</v>
+      <c r="B43" t="s">
+        <v>277</v>
       </c>
       <c r="C43">
         <v>84</v>
@@ -3471,9 +3937,8 @@
       <c r="A44" s="8">
         <v>209</v>
       </c>
-      <c r="B44" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 209</v>
+      <c r="B44" t="s">
+        <v>278</v>
       </c>
       <c r="C44">
         <v>124</v>
@@ -3498,9 +3963,8 @@
       <c r="A45" s="8">
         <v>210</v>
       </c>
-      <c r="B45" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 210</v>
+      <c r="B45" t="s">
+        <v>279</v>
       </c>
       <c r="C45">
         <v>126</v>
@@ -3525,9 +3989,8 @@
       <c r="A46" s="8">
         <v>211</v>
       </c>
-      <c r="B46" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 211</v>
+      <c r="B46" t="s">
+        <v>280</v>
       </c>
       <c r="C46">
         <v>91</v>
@@ -3552,9 +4015,8 @@
       <c r="A47" s="8">
         <v>212</v>
       </c>
-      <c r="B47" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 212</v>
+      <c r="B47" t="s">
+        <v>282</v>
       </c>
       <c r="C47">
         <v>88</v>
@@ -3579,9 +4041,8 @@
       <c r="A48" s="8">
         <v>213</v>
       </c>
-      <c r="B48" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 213</v>
+      <c r="B48" t="s">
+        <v>281</v>
       </c>
       <c r="C48">
         <v>131</v>
@@ -3606,9 +4067,8 @@
       <c r="A49" s="8">
         <v>214</v>
       </c>
-      <c r="B49" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 214</v>
+      <c r="B49" t="s">
+        <v>283</v>
       </c>
       <c r="C49">
         <v>130</v>
@@ -3633,9 +4093,8 @@
       <c r="A50" s="8">
         <v>215</v>
       </c>
-      <c r="B50" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 215</v>
+      <c r="B50" t="s">
+        <v>284</v>
       </c>
       <c r="C50">
         <v>93</v>
@@ -3660,9 +4119,8 @@
       <c r="A51" s="8">
         <v>216</v>
       </c>
-      <c r="B51" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 216</v>
+      <c r="B51" t="s">
+        <v>285</v>
       </c>
       <c r="C51">
         <v>59</v>
@@ -3687,9 +4145,8 @@
       <c r="A52" s="8">
         <v>217</v>
       </c>
-      <c r="B52" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 217</v>
+      <c r="B52" t="s">
+        <v>286</v>
       </c>
       <c r="C52">
         <v>166</v>
@@ -3714,9 +4171,8 @@
       <c r="A53" s="8">
         <v>218</v>
       </c>
-      <c r="B53" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 218</v>
+      <c r="B53" t="s">
+        <v>287</v>
       </c>
       <c r="C53">
         <v>186</v>
@@ -3741,9 +4197,8 @@
       <c r="A54" s="8">
         <v>219</v>
       </c>
-      <c r="B54" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 219</v>
+      <c r="B54" t="s">
+        <v>288</v>
       </c>
       <c r="C54">
         <v>61</v>
@@ -3768,9 +4223,8 @@
       <c r="A55" s="8">
         <v>220</v>
       </c>
-      <c r="B55" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 220</v>
+      <c r="B55" t="s">
+        <v>289</v>
       </c>
       <c r="C55">
         <v>171</v>
@@ -3795,9 +4249,8 @@
       <c r="A56" s="8">
         <v>221</v>
       </c>
-      <c r="B56" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 221</v>
+      <c r="B56" t="s">
+        <v>290</v>
       </c>
       <c r="C56">
         <v>178</v>
@@ -3822,9 +4275,8 @@
       <c r="A57" s="8">
         <v>222</v>
       </c>
-      <c r="B57" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 222</v>
+      <c r="B57" t="s">
+        <v>267</v>
       </c>
       <c r="C57">
         <v>62</v>
@@ -3849,9 +4301,8 @@
       <c r="A58" s="8">
         <v>223</v>
       </c>
-      <c r="B58" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 223</v>
+      <c r="B58" t="s">
+        <v>268</v>
       </c>
       <c r="C58">
         <v>174</v>
@@ -3876,9 +4327,8 @@
       <c r="A59" s="8">
         <v>224</v>
       </c>
-      <c r="B59" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 224</v>
+      <c r="B59" t="s">
+        <v>269</v>
       </c>
       <c r="C59">
         <v>181</v>
@@ -3904,7 +4354,7 @@
         <v>225</v>
       </c>
       <c r="B60" t="s">
-        <v>192</v>
+        <v>270</v>
       </c>
       <c r="C60" s="8">
         <v>197</v>
@@ -3937,9 +4387,8 @@
       <c r="A61" s="8">
         <v>301</v>
       </c>
-      <c r="B61" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 301</v>
+      <c r="B61" t="s">
+        <v>265</v>
       </c>
       <c r="C61">
         <v>169</v>
@@ -3958,9 +4407,8 @@
       <c r="A62" s="8">
         <v>302</v>
       </c>
-      <c r="B62" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 302</v>
+      <c r="B62" t="s">
+        <v>266</v>
       </c>
       <c r="C62">
         <v>158</v>
@@ -3979,9 +4427,8 @@
       <c r="A63" s="8">
         <v>303</v>
       </c>
-      <c r="B63" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 303</v>
+      <c r="B63" t="s">
+        <v>264</v>
       </c>
       <c r="C63">
         <v>71</v>
@@ -4000,9 +4447,8 @@
       <c r="A64" s="8">
         <v>305</v>
       </c>
-      <c r="B64" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 305</v>
+      <c r="B64" t="s">
+        <v>263</v>
       </c>
       <c r="C64">
         <v>134</v>
@@ -4024,9 +4470,8 @@
       <c r="A65" s="8">
         <v>306</v>
       </c>
-      <c r="B65" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 306</v>
+      <c r="B65" t="s">
+        <v>262</v>
       </c>
       <c r="C65">
         <v>147</v>
@@ -4048,9 +4493,8 @@
       <c r="A66" s="8">
         <v>307</v>
       </c>
-      <c r="B66" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 307</v>
+      <c r="B66" t="s">
+        <v>261</v>
       </c>
       <c r="C66">
         <v>155</v>
@@ -4073,7 +4517,7 @@
         <v>308</v>
       </c>
       <c r="B67" t="s">
-        <v>197</v>
+        <v>260</v>
       </c>
       <c r="C67" s="8">
         <v>75</v>
@@ -4104,9 +4548,8 @@
       <c r="A68" s="8">
         <v>310</v>
       </c>
-      <c r="B68" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 310</v>
+      <c r="B68" t="s">
+        <v>259</v>
       </c>
       <c r="C68">
         <v>52</v>
@@ -4128,9 +4571,8 @@
       <c r="A69" s="8">
         <v>311</v>
       </c>
-      <c r="B69" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 311</v>
+      <c r="B69" t="s">
+        <v>258</v>
       </c>
       <c r="C69">
         <v>193</v>
@@ -4152,9 +4594,8 @@
       <c r="A70" s="8">
         <v>312</v>
       </c>
-      <c r="B70" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 312</v>
+      <c r="B70" t="s">
+        <v>257</v>
       </c>
       <c r="C70">
         <v>133</v>
@@ -4176,9 +4617,8 @@
       <c r="A71" s="8">
         <v>313</v>
       </c>
-      <c r="B71" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 313</v>
+      <c r="B71" t="s">
+        <v>251</v>
       </c>
       <c r="C71">
         <v>72</v>
@@ -4197,9 +4637,8 @@
       <c r="A72" s="8">
         <v>314</v>
       </c>
-      <c r="B72" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 314</v>
+      <c r="B72" t="s">
+        <v>252</v>
       </c>
       <c r="C72">
         <v>79</v>
@@ -4218,9 +4657,8 @@
       <c r="A73" s="8">
         <v>315</v>
       </c>
-      <c r="B73" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 315</v>
+      <c r="B73" t="s">
+        <v>253</v>
       </c>
       <c r="C73">
         <v>85</v>
@@ -4242,9 +4680,8 @@
       <c r="A74" s="8">
         <v>316</v>
       </c>
-      <c r="B74" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 316</v>
+      <c r="B74" t="s">
+        <v>254</v>
       </c>
       <c r="C74">
         <v>90</v>
@@ -4266,9 +4703,8 @@
       <c r="A75" s="8">
         <v>401</v>
       </c>
-      <c r="B75" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 401</v>
+      <c r="B75" t="s">
+        <v>303</v>
       </c>
       <c r="C75">
         <v>7</v>
@@ -4287,9 +4723,8 @@
       <c r="A76" s="8">
         <v>402</v>
       </c>
-      <c r="B76" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 402</v>
+      <c r="B76" t="s">
+        <v>304</v>
       </c>
       <c r="C76">
         <v>7</v>
@@ -4308,9 +4743,8 @@
       <c r="A77" s="8">
         <v>403</v>
       </c>
-      <c r="B77" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 403</v>
+      <c r="B77" t="s">
+        <v>305</v>
       </c>
       <c r="C77">
         <v>7</v>
@@ -4329,9 +4763,8 @@
       <c r="A78" s="8">
         <v>404</v>
       </c>
-      <c r="B78" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 404</v>
+      <c r="B78" t="s">
+        <v>306</v>
       </c>
       <c r="C78">
         <v>7</v>
@@ -4350,9 +4783,8 @@
       <c r="A79" s="8">
         <v>405</v>
       </c>
-      <c r="B79" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 405</v>
+      <c r="B79" t="s">
+        <v>307</v>
       </c>
       <c r="C79">
         <v>7</v>
@@ -4371,9 +4803,8 @@
       <c r="A80" s="8">
         <v>406</v>
       </c>
-      <c r="B80" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 406</v>
+      <c r="B80" t="s">
+        <v>308</v>
       </c>
       <c r="C80">
         <v>7</v>
@@ -4392,9 +4823,8 @@
       <c r="A81" s="8">
         <v>407</v>
       </c>
-      <c r="B81" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 407</v>
+      <c r="B81" t="s">
+        <v>309</v>
       </c>
       <c r="C81">
         <v>7</v>
@@ -4413,9 +4843,8 @@
       <c r="A82" s="8">
         <v>408</v>
       </c>
-      <c r="B82" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 408</v>
+      <c r="B82" t="s">
+        <v>310</v>
       </c>
       <c r="C82">
         <v>7</v>
@@ -4434,9 +4863,8 @@
       <c r="A83" s="8">
         <v>409</v>
       </c>
-      <c r="B83" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 409</v>
+      <c r="B83" t="s">
+        <v>311</v>
       </c>
       <c r="C83">
         <v>7</v>
@@ -4455,9 +4883,8 @@
       <c r="A84" s="8">
         <v>410</v>
       </c>
-      <c r="B84" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 410</v>
+      <c r="B84" t="s">
+        <v>312</v>
       </c>
       <c r="C84">
         <v>7</v>
@@ -4476,9 +4903,8 @@
       <c r="A85" s="8">
         <v>411</v>
       </c>
-      <c r="B85" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 411</v>
+      <c r="B85" t="s">
+        <v>313</v>
       </c>
       <c r="C85">
         <v>7</v>
@@ -4497,9 +4923,8 @@
       <c r="A86" s="8">
         <v>412</v>
       </c>
-      <c r="B86" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 412</v>
+      <c r="B86" t="s">
+        <v>291</v>
       </c>
       <c r="C86">
         <v>7</v>
@@ -4518,9 +4943,8 @@
       <c r="A87" s="8">
         <v>413</v>
       </c>
-      <c r="B87" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 413</v>
+      <c r="B87" t="s">
+        <v>314</v>
       </c>
       <c r="C87">
         <v>7</v>
@@ -4539,9 +4963,8 @@
       <c r="A88" s="8">
         <v>414</v>
       </c>
-      <c r="B88" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 414</v>
+      <c r="B88" t="s">
+        <v>315</v>
       </c>
       <c r="C88">
         <v>7</v>
@@ -4560,9 +4983,8 @@
       <c r="A89" s="8">
         <v>415</v>
       </c>
-      <c r="B89" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 415</v>
+      <c r="B89" t="s">
+        <v>316</v>
       </c>
       <c r="C89">
         <v>7</v>
@@ -4581,9 +5003,8 @@
       <c r="A90" s="8">
         <v>416</v>
       </c>
-      <c r="B90" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 416</v>
+      <c r="B90" t="s">
+        <v>317</v>
       </c>
       <c r="C90">
         <v>7</v>
@@ -4602,9 +5023,8 @@
       <c r="A91" s="8">
         <v>417</v>
       </c>
-      <c r="B91" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 417</v>
+      <c r="B91" t="s">
+        <v>318</v>
       </c>
       <c r="C91">
         <v>7</v>
@@ -4623,9 +5043,8 @@
       <c r="A92" s="8">
         <v>418</v>
       </c>
-      <c r="B92" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 418</v>
+      <c r="B92" t="s">
+        <v>319</v>
       </c>
       <c r="C92">
         <v>7</v>
@@ -4644,9 +5063,8 @@
       <c r="A93" s="8">
         <v>419</v>
       </c>
-      <c r="B93" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 419</v>
+      <c r="B93" t="s">
+        <v>320</v>
       </c>
       <c r="C93">
         <v>7</v>
@@ -4665,9 +5083,8 @@
       <c r="A94" s="8">
         <v>420</v>
       </c>
-      <c r="B94" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 420</v>
+      <c r="B94" t="s">
+        <v>321</v>
       </c>
       <c r="C94">
         <v>7</v>
@@ -4686,9 +5103,8 @@
       <c r="A95" s="8">
         <v>421</v>
       </c>
-      <c r="B95" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 421</v>
+      <c r="B95" t="s">
+        <v>322</v>
       </c>
       <c r="C95">
         <v>7</v>
@@ -4707,9 +5123,8 @@
       <c r="A96" s="8">
         <v>422</v>
       </c>
-      <c r="B96" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 422</v>
+      <c r="B96" t="s">
+        <v>323</v>
       </c>
       <c r="C96">
         <v>7</v>
@@ -4728,9 +5143,8 @@
       <c r="A97" s="8">
         <v>423</v>
       </c>
-      <c r="B97" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 423</v>
+      <c r="B97" t="s">
+        <v>324</v>
       </c>
       <c r="C97">
         <v>7</v>
@@ -4749,9 +5163,8 @@
       <c r="A98" s="8">
         <v>424</v>
       </c>
-      <c r="B98" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 424</v>
+      <c r="B98" t="s">
+        <v>325</v>
       </c>
       <c r="C98">
         <v>7</v>
@@ -4770,9 +5183,8 @@
       <c r="A99" s="8">
         <v>425</v>
       </c>
-      <c r="B99" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 425</v>
+      <c r="B99" t="s">
+        <v>326</v>
       </c>
       <c r="C99">
         <v>7</v>
@@ -4791,9 +5203,8 @@
       <c r="A100" s="8">
         <v>426</v>
       </c>
-      <c r="B100" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 426</v>
+      <c r="B100" t="s">
+        <v>327</v>
       </c>
       <c r="C100">
         <v>7</v>
@@ -4812,9 +5223,8 @@
       <c r="A101" s="8">
         <v>427</v>
       </c>
-      <c r="B101" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 427</v>
+      <c r="B101" t="s">
+        <v>328</v>
       </c>
       <c r="C101">
         <v>7</v>
@@ -4833,9 +5243,8 @@
       <c r="A102" s="8">
         <v>428</v>
       </c>
-      <c r="B102" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 428</v>
+      <c r="B102" t="s">
+        <v>329</v>
       </c>
       <c r="C102">
         <v>7</v>
@@ -4854,9 +5263,8 @@
       <c r="A103" s="8">
         <v>429</v>
       </c>
-      <c r="B103" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 429</v>
+      <c r="B103" t="s">
+        <v>330</v>
       </c>
       <c r="C103">
         <v>7</v>
@@ -4875,9 +5283,8 @@
       <c r="A104" s="8">
         <v>430</v>
       </c>
-      <c r="B104" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 430</v>
+      <c r="B104" t="s">
+        <v>331</v>
       </c>
       <c r="C104">
         <v>7</v>
@@ -4896,9 +5303,8 @@
       <c r="A105" s="8">
         <v>431</v>
       </c>
-      <c r="B105" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 431</v>
+      <c r="B105" t="s">
+        <v>332</v>
       </c>
       <c r="C105">
         <v>7</v>
@@ -4917,9 +5323,8 @@
       <c r="A106" s="8">
         <v>432</v>
       </c>
-      <c r="B106" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 432</v>
+      <c r="B106" t="s">
+        <v>333</v>
       </c>
       <c r="C106">
         <v>7</v>
@@ -4938,9 +5343,8 @@
       <c r="A107" s="8">
         <v>433</v>
       </c>
-      <c r="B107" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 433</v>
+      <c r="B107" t="s">
+        <v>334</v>
       </c>
       <c r="C107">
         <v>7</v>
@@ -4959,9 +5363,8 @@
       <c r="A108" s="8">
         <v>434</v>
       </c>
-      <c r="B108" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 434</v>
+      <c r="B108" t="s">
+        <v>335</v>
       </c>
       <c r="C108">
         <v>7</v>
@@ -4980,9 +5383,8 @@
       <c r="A109" s="8">
         <v>435</v>
       </c>
-      <c r="B109" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 435</v>
+      <c r="B109" t="s">
+        <v>336</v>
       </c>
       <c r="C109">
         <v>7</v>
@@ -5001,9 +5403,8 @@
       <c r="A110" s="8">
         <v>436</v>
       </c>
-      <c r="B110" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 436</v>
+      <c r="B110" t="s">
+        <v>337</v>
       </c>
       <c r="C110">
         <v>7</v>
@@ -5022,9 +5423,8 @@
       <c r="A111" s="8">
         <v>437</v>
       </c>
-      <c r="B111" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 437</v>
+      <c r="B111" t="s">
+        <v>338</v>
       </c>
       <c r="C111">
         <v>7</v>
@@ -5043,9 +5443,8 @@
       <c r="A112" s="8">
         <v>438</v>
       </c>
-      <c r="B112" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 438</v>
+      <c r="B112" t="s">
+        <v>339</v>
       </c>
       <c r="C112">
         <v>7</v>
@@ -5064,9 +5463,8 @@
       <c r="A113" s="8">
         <v>439</v>
       </c>
-      <c r="B113" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 439</v>
+      <c r="B113" t="s">
+        <v>340</v>
       </c>
       <c r="C113">
         <v>7</v>
@@ -5085,9 +5483,8 @@
       <c r="A114" s="8">
         <v>440</v>
       </c>
-      <c r="B114" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 440</v>
+      <c r="B114" t="s">
+        <v>341</v>
       </c>
       <c r="C114">
         <v>7</v>
@@ -5106,9 +5503,8 @@
       <c r="A115" s="8">
         <v>441</v>
       </c>
-      <c r="B115" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 441</v>
+      <c r="B115" t="s">
+        <v>342</v>
       </c>
       <c r="C115">
         <v>7</v>
@@ -5127,9 +5523,8 @@
       <c r="A116" s="8">
         <v>442</v>
       </c>
-      <c r="B116" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 442</v>
+      <c r="B116" t="s">
+        <v>343</v>
       </c>
       <c r="C116">
         <v>7</v>
@@ -5148,9 +5543,8 @@
       <c r="A117" s="8">
         <v>443</v>
       </c>
-      <c r="B117" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 443</v>
+      <c r="B117" t="s">
+        <v>344</v>
       </c>
       <c r="C117">
         <v>7</v>
@@ -5169,9 +5563,8 @@
       <c r="A118" s="8">
         <v>444</v>
       </c>
-      <c r="B118" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 444</v>
+      <c r="B118" t="s">
+        <v>345</v>
       </c>
       <c r="C118">
         <v>7</v>
@@ -5190,9 +5583,8 @@
       <c r="A119" s="8">
         <v>445</v>
       </c>
-      <c r="B119" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 445</v>
+      <c r="B119" t="s">
+        <v>346</v>
       </c>
       <c r="C119">
         <v>7</v>
@@ -5211,9 +5603,8 @@
       <c r="A120" s="8">
         <v>446</v>
       </c>
-      <c r="B120" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 446</v>
+      <c r="B120" t="s">
+        <v>347</v>
       </c>
       <c r="C120">
         <v>7</v>
@@ -5232,9 +5623,8 @@
       <c r="A121" s="8">
         <v>447</v>
       </c>
-      <c r="B121" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 447</v>
+      <c r="B121" t="s">
+        <v>348</v>
       </c>
       <c r="C121">
         <v>7</v>
@@ -5253,9 +5643,8 @@
       <c r="A122" s="8">
         <v>448</v>
       </c>
-      <c r="B122" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 448</v>
+      <c r="B122" t="s">
+        <v>349</v>
       </c>
       <c r="C122">
         <v>7</v>
@@ -5274,9 +5663,8 @@
       <c r="A123" s="8">
         <v>449</v>
       </c>
-      <c r="B123" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 449</v>
+      <c r="B123" t="s">
+        <v>350</v>
       </c>
       <c r="C123">
         <v>7</v>
@@ -5295,9 +5683,8 @@
       <c r="A124" s="8">
         <v>450</v>
       </c>
-      <c r="B124" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 450</v>
+      <c r="B124" t="s">
+        <v>351</v>
       </c>
       <c r="C124">
         <v>7</v>
@@ -5316,9 +5703,8 @@
       <c r="A125" s="8">
         <v>451</v>
       </c>
-      <c r="B125" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 451</v>
+      <c r="B125" t="s">
+        <v>352</v>
       </c>
       <c r="C125">
         <v>7</v>
@@ -5337,9 +5723,8 @@
       <c r="A126" s="8">
         <v>452</v>
       </c>
-      <c r="B126" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 452</v>
+      <c r="B126" t="s">
+        <v>353</v>
       </c>
       <c r="C126">
         <v>7</v>
@@ -5358,9 +5743,8 @@
       <c r="A127" s="8">
         <v>453</v>
       </c>
-      <c r="B127" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 453</v>
+      <c r="B127" t="s">
+        <v>292</v>
       </c>
       <c r="C127">
         <v>7</v>
@@ -5379,9 +5763,8 @@
       <c r="A128" s="8">
         <v>454</v>
       </c>
-      <c r="B128" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 454</v>
+      <c r="B128" t="s">
+        <v>293</v>
       </c>
       <c r="C128">
         <v>7</v>
@@ -5400,9 +5783,8 @@
       <c r="A129" s="8">
         <v>455</v>
       </c>
-      <c r="B129" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 455</v>
+      <c r="B129" t="s">
+        <v>294</v>
       </c>
       <c r="C129">
         <v>7</v>
@@ -5421,9 +5803,8 @@
       <c r="A130" s="8">
         <v>456</v>
       </c>
-      <c r="B130" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 456</v>
+      <c r="B130" t="s">
+        <v>295</v>
       </c>
       <c r="C130">
         <v>7</v>
@@ -5442,9 +5823,8 @@
       <c r="A131" s="8">
         <v>457</v>
       </c>
-      <c r="B131" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 457</v>
+      <c r="B131" t="s">
+        <v>296</v>
       </c>
       <c r="C131">
         <v>7</v>
@@ -5463,9 +5843,8 @@
       <c r="A132" s="8">
         <v>458</v>
       </c>
-      <c r="B132" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 458</v>
+      <c r="B132" t="s">
+        <v>297</v>
       </c>
       <c r="C132">
         <v>7</v>
@@ -5484,9 +5863,8 @@
       <c r="A133" s="8">
         <v>459</v>
       </c>
-      <c r="B133" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 459</v>
+      <c r="B133" t="s">
+        <v>298</v>
       </c>
       <c r="C133">
         <v>7</v>
@@ -5505,9 +5883,8 @@
       <c r="A134" s="8">
         <v>460</v>
       </c>
-      <c r="B134" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 460</v>
+      <c r="B134" t="s">
+        <v>300</v>
       </c>
       <c r="C134">
         <v>7</v>
@@ -5526,9 +5903,8 @@
       <c r="A135" s="8">
         <v>461</v>
       </c>
-      <c r="B135" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 461</v>
+      <c r="B135" t="s">
+        <v>301</v>
       </c>
       <c r="C135">
         <v>7</v>
@@ -5547,9 +5923,8 @@
       <c r="A136" s="8">
         <v>462</v>
       </c>
-      <c r="B136" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 462</v>
+      <c r="B136" t="s">
+        <v>299</v>
       </c>
       <c r="C136">
         <v>7</v>
@@ -5568,9 +5943,8 @@
       <c r="A137" s="8">
         <v>463</v>
       </c>
-      <c r="B137" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 463</v>
+      <c r="B137" t="s">
+        <v>302</v>
       </c>
       <c r="C137">
         <v>7</v>
@@ -5589,9 +5963,8 @@
       <c r="A138" s="8">
         <v>464</v>
       </c>
-      <c r="B138" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 464</v>
+      <c r="B138" t="s">
+        <v>354</v>
       </c>
       <c r="C138">
         <v>7</v>
@@ -5610,9 +5983,8 @@
       <c r="A139" s="8">
         <v>465</v>
       </c>
-      <c r="B139" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 465</v>
+      <c r="B139" t="s">
+        <v>355</v>
       </c>
       <c r="C139">
         <v>7</v>
@@ -5631,9 +6003,8 @@
       <c r="A140" s="8">
         <v>466</v>
       </c>
-      <c r="B140" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 466</v>
+      <c r="B140" t="s">
+        <v>356</v>
       </c>
       <c r="C140">
         <v>7</v>
@@ -5652,9 +6023,8 @@
       <c r="A141" s="8">
         <v>467</v>
       </c>
-      <c r="B141" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 467</v>
+      <c r="B141" t="s">
+        <v>357</v>
       </c>
       <c r="C141">
         <v>7</v>
@@ -5673,9 +6043,8 @@
       <c r="A142" s="8">
         <v>468</v>
       </c>
-      <c r="B142" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 468</v>
+      <c r="B142" t="s">
+        <v>358</v>
       </c>
       <c r="C142">
         <v>7</v>
@@ -5694,9 +6063,8 @@
       <c r="A143" s="8">
         <v>469</v>
       </c>
-      <c r="B143" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 469</v>
+      <c r="B143" t="s">
+        <v>359</v>
       </c>
       <c r="C143">
         <v>7</v>
@@ -5715,9 +6083,8 @@
       <c r="A144" s="8">
         <v>470</v>
       </c>
-      <c r="B144" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 470</v>
+      <c r="B144" t="s">
+        <v>360</v>
       </c>
       <c r="C144">
         <v>7</v>
@@ -5736,9 +6103,8 @@
       <c r="A145" s="8">
         <v>471</v>
       </c>
-      <c r="B145" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 471</v>
+      <c r="B145" t="s">
+        <v>361</v>
       </c>
       <c r="C145">
         <v>7</v>
@@ -5757,9 +6123,8 @@
       <c r="A146" s="8">
         <v>472</v>
       </c>
-      <c r="B146" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 472</v>
+      <c r="B146" t="s">
+        <v>362</v>
       </c>
       <c r="C146">
         <v>7</v>
@@ -5778,9 +6143,8 @@
       <c r="A147" s="8">
         <v>473</v>
       </c>
-      <c r="B147" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 473</v>
+      <c r="B147" t="s">
+        <v>363</v>
       </c>
       <c r="C147">
         <v>7</v>
@@ -5799,9 +6163,8 @@
       <c r="A148" s="8">
         <v>474</v>
       </c>
-      <c r="B148" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 474</v>
+      <c r="B148" t="s">
+        <v>364</v>
       </c>
       <c r="C148">
         <v>7</v>
@@ -5820,9 +6183,8 @@
       <c r="A149" s="8">
         <v>475</v>
       </c>
-      <c r="B149" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 475</v>
+      <c r="B149" t="s">
+        <v>365</v>
       </c>
       <c r="C149">
         <v>7</v>
@@ -5841,9 +6203,8 @@
       <c r="A150" s="8">
         <v>476</v>
       </c>
-      <c r="B150" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 476</v>
+      <c r="B150" t="s">
+        <v>366</v>
       </c>
       <c r="C150">
         <v>7</v>
@@ -5862,9 +6223,8 @@
       <c r="A151" s="8">
         <v>477</v>
       </c>
-      <c r="B151" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 477</v>
+      <c r="B151" t="s">
+        <v>367</v>
       </c>
       <c r="C151">
         <v>7</v>
@@ -5883,9 +6243,8 @@
       <c r="A152" s="8">
         <v>478</v>
       </c>
-      <c r="B152" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 478</v>
+      <c r="B152" t="s">
+        <v>368</v>
       </c>
       <c r="C152">
         <v>7</v>
@@ -5904,9 +6263,8 @@
       <c r="A153" s="8">
         <v>479</v>
       </c>
-      <c r="B153" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 479</v>
+      <c r="B153" t="s">
+        <v>369</v>
       </c>
       <c r="C153">
         <v>7</v>
@@ -5925,9 +6283,8 @@
       <c r="A154" s="8">
         <v>480</v>
       </c>
-      <c r="B154" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 480</v>
+      <c r="B154" t="s">
+        <v>370</v>
       </c>
       <c r="C154">
         <v>7</v>
@@ -5946,9 +6303,8 @@
       <c r="A155" s="8">
         <v>481</v>
       </c>
-      <c r="B155" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 481</v>
+      <c r="B155" t="s">
+        <v>371</v>
       </c>
       <c r="C155">
         <v>7</v>
@@ -5967,9 +6323,8 @@
       <c r="A156" s="8">
         <v>482</v>
       </c>
-      <c r="B156" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 482</v>
+      <c r="B156" t="s">
+        <v>372</v>
       </c>
       <c r="C156">
         <v>7</v>
@@ -5988,9 +6343,8 @@
       <c r="A157" s="8">
         <v>483</v>
       </c>
-      <c r="B157" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 483</v>
+      <c r="B157" t="s">
+        <v>373</v>
       </c>
       <c r="C157">
         <v>7</v>
@@ -6009,9 +6363,8 @@
       <c r="A158" s="8">
         <v>484</v>
       </c>
-      <c r="B158" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 484</v>
+      <c r="B158" t="s">
+        <v>374</v>
       </c>
       <c r="C158">
         <v>7</v>
@@ -6030,9 +6383,8 @@
       <c r="A159" s="8">
         <v>485</v>
       </c>
-      <c r="B159" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 485</v>
+      <c r="B159" t="s">
+        <v>375</v>
       </c>
       <c r="C159">
         <v>7</v>
@@ -6051,9 +6403,8 @@
       <c r="A160" s="8">
         <v>486</v>
       </c>
-      <c r="B160" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 486</v>
+      <c r="B160" t="s">
+        <v>376</v>
       </c>
       <c r="C160">
         <v>7</v>
@@ -6072,9 +6423,8 @@
       <c r="A161" s="8">
         <v>487</v>
       </c>
-      <c r="B161" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 487</v>
+      <c r="B161" t="s">
+        <v>377</v>
       </c>
       <c r="C161">
         <v>7</v>
@@ -6093,9 +6443,8 @@
       <c r="A162" s="8">
         <v>488</v>
       </c>
-      <c r="B162" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 488</v>
+      <c r="B162" t="s">
+        <v>378</v>
       </c>
       <c r="C162">
         <v>7</v>
@@ -6114,9 +6463,8 @@
       <c r="A163" s="8">
         <v>489</v>
       </c>
-      <c r="B163" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 489</v>
+      <c r="B163" t="s">
+        <v>379</v>
       </c>
       <c r="C163">
         <v>7</v>
@@ -6135,9 +6483,8 @@
       <c r="A164" s="8">
         <v>490</v>
       </c>
-      <c r="B164" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 490</v>
+      <c r="B164" t="s">
+        <v>380</v>
       </c>
       <c r="C164">
         <v>7</v>
@@ -6156,9 +6503,8 @@
       <c r="A165" s="8">
         <v>491</v>
       </c>
-      <c r="B165" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 491</v>
+      <c r="B165" t="s">
+        <v>381</v>
       </c>
       <c r="C165">
         <v>7</v>
@@ -6177,9 +6523,8 @@
       <c r="A166" s="8">
         <v>492</v>
       </c>
-      <c r="B166" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 492</v>
+      <c r="B166" t="s">
+        <v>382</v>
       </c>
       <c r="C166">
         <v>7</v>
@@ -6198,9 +6543,8 @@
       <c r="A167" s="8">
         <v>493</v>
       </c>
-      <c r="B167" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 493</v>
+      <c r="B167" t="s">
+        <v>383</v>
       </c>
       <c r="C167">
         <v>7</v>
@@ -6219,9 +6563,8 @@
       <c r="A168" s="8">
         <v>494</v>
       </c>
-      <c r="B168" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 494</v>
+      <c r="B168" t="s">
+        <v>384</v>
       </c>
       <c r="C168">
         <v>7</v>
@@ -6240,9 +6583,8 @@
       <c r="A169" s="8">
         <v>495</v>
       </c>
-      <c r="B169" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 495</v>
+      <c r="B169" t="s">
+        <v>385</v>
       </c>
       <c r="C169">
         <v>7</v>
@@ -6261,9 +6603,8 @@
       <c r="A170" s="8">
         <v>496</v>
       </c>
-      <c r="B170" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 496</v>
+      <c r="B170" t="s">
+        <v>386</v>
       </c>
       <c r="C170">
         <v>7</v>
@@ -6282,9 +6623,8 @@
       <c r="A171" s="8">
         <v>497</v>
       </c>
-      <c r="B171" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 497</v>
+      <c r="B171" t="s">
+        <v>387</v>
       </c>
       <c r="C171">
         <v>7</v>
@@ -6303,9 +6643,8 @@
       <c r="A172" s="8">
         <v>498</v>
       </c>
-      <c r="B172" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 498</v>
+      <c r="B172" t="s">
+        <v>388</v>
       </c>
       <c r="C172">
         <v>7</v>
@@ -6324,9 +6663,8 @@
       <c r="A173" s="8">
         <v>499</v>
       </c>
-      <c r="B173" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 499</v>
+      <c r="B173" t="s">
+        <v>390</v>
       </c>
       <c r="C173">
         <v>7</v>
@@ -6345,9 +6683,8 @@
       <c r="A174" s="8">
         <v>500</v>
       </c>
-      <c r="B174" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 500</v>
+      <c r="B174" t="s">
+        <v>391</v>
       </c>
       <c r="C174">
         <v>7</v>
@@ -6366,9 +6703,8 @@
       <c r="A175" s="8">
         <v>501</v>
       </c>
-      <c r="B175" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 501</v>
+      <c r="B175" t="s">
+        <v>392</v>
       </c>
       <c r="C175">
         <v>7</v>
@@ -6387,9 +6723,8 @@
       <c r="A176" s="8">
         <v>502</v>
       </c>
-      <c r="B176" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 502</v>
+      <c r="B176" t="s">
+        <v>393</v>
       </c>
       <c r="C176">
         <v>1</v>
@@ -6406,9 +6741,8 @@
       <c r="A177" s="8">
         <v>503</v>
       </c>
-      <c r="B177" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 503</v>
+      <c r="B177" t="s">
+        <v>394</v>
       </c>
       <c r="C177">
         <v>1</v>
@@ -6425,9 +6759,8 @@
       <c r="A178" s="8">
         <v>504</v>
       </c>
-      <c r="B178" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 504</v>
+      <c r="B178" t="s">
+        <v>395</v>
       </c>
       <c r="C178">
         <v>1</v>
@@ -6444,9 +6777,8 @@
       <c r="A179" s="8">
         <v>505</v>
       </c>
-      <c r="B179" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 505</v>
+      <c r="B179" t="s">
+        <v>396</v>
       </c>
       <c r="C179">
         <v>1</v>
@@ -6463,9 +6795,8 @@
       <c r="A180" s="8">
         <v>506</v>
       </c>
-      <c r="B180" t="str">
-        <f>"Lot "&amp;Lots[[#This Row],[Numéro de lot]]</f>
-        <v>Lot 506</v>
+      <c r="B180" t="s">
+        <v>389</v>
       </c>
       <c r="C180">
         <v>7</v>
@@ -6493,7 +6824,7 @@
   <sheetPr>
     <tabColor theme="9" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:I48"/>
+  <dimension ref="A1:I45"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="48.140625" customWidth="1"/>
@@ -6509,16 +6840,16 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="D1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E1" s="10" t="s">
         <v>4</v>
@@ -6530,10 +6861,10 @@
         <v>3</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="I1" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="45" x14ac:dyDescent="0.25">
@@ -6553,22 +6884,19 @@
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
         <v>0</v>
       </c>
-      <c r="H2" s="2" t="s">
-        <v>29</v>
-      </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D3" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="E3" s="4">
         <v>0</v>
@@ -6581,21 +6909,21 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D4" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="E4" s="4">
         <v>10000</v>
@@ -6608,406 +6936,405 @@
         <v>10000</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="D5" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="E5" s="4">
-        <v>16000</v>
+        <v>1940</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>2</v>
       </c>
       <c r="G5" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>16000</v>
+        <v>1940</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>180</v>
+        <v>169</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D6" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="E6" s="4">
-        <v>1940</v>
+        <v>18000</v>
       </c>
       <c r="F6" s="6" t="s">
         <v>2</v>
       </c>
       <c r="G6" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>1940</v>
+        <v>18000</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D7" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="E7" s="4">
-        <v>18000</v>
+        <v>5710</v>
       </c>
       <c r="F7" s="6" t="s">
         <v>2</v>
       </c>
       <c r="G7" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>18000</v>
+        <v>5710</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="D8" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="E8" s="4">
-        <v>24000</v>
+        <v>20000</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>2</v>
       </c>
       <c r="G8" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>24000</v>
+        <v>20000</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D9" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="E9" s="4">
-        <v>5710</v>
+        <v>10770</v>
       </c>
       <c r="F9" s="6" t="s">
         <v>2</v>
       </c>
       <c r="G9" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>5710</v>
+        <v>10770</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D10" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="E10" s="4">
-        <v>20000</v>
+        <v>25000</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>2</v>
       </c>
       <c r="G10" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>20000</v>
+        <v>25000</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>171</v>
+        <v>9</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>55</v>
+        <v>113</v>
       </c>
       <c r="D11" t="s">
-        <v>172</v>
+        <v>10</v>
       </c>
       <c r="E11" s="4">
-        <v>37000</v>
+        <v>3000</v>
       </c>
       <c r="F11" s="6" t="s">
         <v>2</v>
       </c>
       <c r="G11" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>37000</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>180</v>
+        <v>9</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>73</v>
+        <v>112</v>
       </c>
       <c r="D12" t="s">
-        <v>188</v>
+        <v>11</v>
       </c>
       <c r="E12" s="4">
-        <v>10770</v>
+        <v>2460</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>2</v>
       </c>
       <c r="G12" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>10770</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+        <v>2460</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>179</v>
+        <v>28</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>196</v>
+        <v>28</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="D13" t="s">
-        <v>188</v>
+        <v>27</v>
       </c>
       <c r="E13" s="4">
-        <v>25000</v>
+        <v>1051.2</v>
       </c>
       <c r="F13" s="6" t="s">
         <v>2</v>
       </c>
       <c r="G13" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>25000</v>
+        <v>1051.2</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
+      </c>
+      <c r="C14" t="s">
+        <v>66</v>
       </c>
       <c r="D14" t="s">
-        <v>10</v>
+        <v>90</v>
       </c>
       <c r="E14" s="4">
-        <v>3000</v>
+        <v>748.15</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>2</v>
       </c>
       <c r="G14" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>3000</v>
+        <v>748.15</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="I14" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
+      </c>
+      <c r="C15" t="s">
+        <v>65</v>
       </c>
       <c r="D15" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E15" s="4">
-        <v>2460</v>
+        <v>6096.65</v>
       </c>
       <c r="F15" s="6" t="s">
         <v>2</v>
       </c>
       <c r="G15" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>2460</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+        <v>6096.65</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="I15" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>69</v>
+        <v>114</v>
+      </c>
+      <c r="C16" t="s">
+        <v>65</v>
       </c>
       <c r="D16" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="E16" s="4">
-        <v>1051.2</v>
+        <v>7502.9</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>2</v>
       </c>
       <c r="G16" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>1051.2</v>
+        <v>7502.9</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="C17" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D17" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="E17" s="4">
-        <v>748.15</v>
+        <f>16750</f>
+        <v>16750</v>
       </c>
       <c r="F17" s="6" t="s">
         <v>2</v>
       </c>
       <c r="G17" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>748.15</v>
+        <v>16750</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="I17" t="s">
-        <v>216</v>
+        <v>199</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>117</v>
+        <v>201</v>
       </c>
       <c r="C18" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="D18" t="s">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c r="E18" s="4">
-        <v>6096.65</v>
+        <f>887</f>
+        <v>887</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>2</v>
       </c>
       <c r="G18" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>6096.65</v>
+        <v>887</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="I18" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="C19" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="D19" t="s">
-        <v>7</v>
-      </c>
-      <c r="E19" s="4">
-        <v>7502.9</v>
+        <v>22</v>
       </c>
       <c r="F19" s="6" t="s">
         <v>2</v>
       </c>
       <c r="G19" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>7502.9</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>103</v>
+        <v>0</v>
+      </c>
+      <c r="H19" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -7015,301 +7342,311 @@
         <v>20</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C20" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D20" t="s">
-        <v>82</v>
-      </c>
-      <c r="E20" s="4">
-        <f>16750</f>
-        <v>16750</v>
+        <v>21</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>2</v>
       </c>
       <c r="G20" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>16750</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="H20" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>213</v>
+        <v>119</v>
       </c>
       <c r="C21" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="D21" t="s">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="E21" s="4">
-        <f>887</f>
-        <v>887</v>
+        <f>1140*12</f>
+        <v>13680</v>
       </c>
       <c r="F21" s="6" t="s">
         <v>2</v>
       </c>
       <c r="G21" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>887</v>
+        <v>13680</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>130</v>
+        <v>117</v>
       </c>
       <c r="C22" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="D22" t="s">
-        <v>22</v>
+        <v>108</v>
+      </c>
+      <c r="E22" s="4">
+        <f>2836.8*12</f>
+        <v>34041.600000000006</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>2</v>
       </c>
       <c r="G22" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>0</v>
-      </c>
-      <c r="H22" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+        <v>34041.600000000006</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="C23" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="D23" t="s">
-        <v>21</v>
+        <v>105</v>
+      </c>
+      <c r="E23" s="4">
+        <f>1518*12</f>
+        <v>18216</v>
       </c>
       <c r="F23" s="6" t="s">
         <v>2</v>
       </c>
       <c r="G23" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>0</v>
-      </c>
-      <c r="H23" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+        <v>18216</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="I23" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C24" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="D24" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E24" s="4">
-        <f>1140*12</f>
-        <v>13680</v>
+        <v>516</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>2</v>
       </c>
       <c r="G24" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>13680</v>
+        <v>516</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="C25" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="D25" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E25" s="4">
-        <f>2836.8*12</f>
-        <v>34041.600000000006</v>
+        <v>456</v>
       </c>
       <c r="F25" s="6" t="s">
         <v>2</v>
       </c>
       <c r="G25" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>34041.600000000006</v>
+        <v>456</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="225" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="C26" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="D26" t="s">
-        <v>107</v>
+        <v>19</v>
       </c>
       <c r="E26" s="4">
-        <f>1518*12</f>
-        <v>18216</v>
+        <v>660</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>2</v>
       </c>
       <c r="G26" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>18216</v>
+        <v>660</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="I26" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>18</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>125</v>
+        <v>203</v>
       </c>
       <c r="C27" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D27" t="s">
-        <v>111</v>
+        <v>204</v>
       </c>
       <c r="E27" s="4">
-        <v>516</v>
+        <v>434.5</v>
       </c>
       <c r="F27" s="6" t="s">
         <v>2</v>
       </c>
       <c r="G27" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>516</v>
+        <v>434.5</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+        <v>205</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="C28" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="D28" t="s">
-        <v>111</v>
+        <v>79</v>
       </c>
       <c r="E28" s="4">
-        <v>456</v>
+        <v>2400</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G28" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>456</v>
+        <v>2880</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" ht="225" x14ac:dyDescent="0.25">
+        <v>133</v>
+      </c>
+      <c r="I28" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="C29" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="D29" t="s">
-        <v>19</v>
+        <v>79</v>
       </c>
       <c r="E29" s="4">
-        <v>660</v>
+        <v>2400</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G29" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>660</v>
+        <v>2880</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>133</v>
       </c>
+      <c r="I29" t="s">
+        <v>202</v>
+      </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>217</v>
+        <v>142</v>
       </c>
       <c r="C30" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="D30" t="s">
-        <v>218</v>
+        <v>79</v>
       </c>
       <c r="E30" s="4">
-        <v>434.5</v>
+        <v>2450</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G30" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>434.5</v>
+        <v>2940</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>216</v>
+        <v>133</v>
+      </c>
+      <c r="I30" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
@@ -7317,259 +7654,250 @@
         <v>13</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="C31" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D31" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E31" s="4">
-        <v>2400</v>
+        <v>2200</v>
       </c>
       <c r="F31" s="6" t="s">
         <v>1</v>
       </c>
       <c r="G31" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>2880</v>
+        <v>2640</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I31" t="s">
-        <v>216</v>
+        <v>202</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="C32" t="s">
-        <v>88</v>
+        <v>25</v>
       </c>
       <c r="D32" t="s">
-        <v>81</v>
+        <v>26</v>
       </c>
       <c r="E32" s="4">
-        <v>2400</v>
+        <v>160</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G32" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>2880</v>
-      </c>
-      <c r="H32" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="I32" t="s">
-        <v>216</v>
+        <v>160</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>144</v>
+        <v>111</v>
       </c>
       <c r="C33" t="s">
-        <v>89</v>
+        <v>55</v>
       </c>
       <c r="D33" t="s">
-        <v>81</v>
+        <v>108</v>
       </c>
       <c r="E33" s="4">
-        <v>2450</v>
+        <f>2400*12</f>
+        <v>28800</v>
       </c>
       <c r="F33" s="6" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G33" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>2940</v>
+        <v>28800</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="I33" t="s">
-        <v>216</v>
+        <v>107</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>146</v>
+        <v>110</v>
       </c>
       <c r="C34" t="s">
-        <v>90</v>
+        <v>55</v>
       </c>
       <c r="D34" t="s">
-        <v>81</v>
+        <v>108</v>
       </c>
       <c r="E34" s="4">
-        <v>2200</v>
+        <f>1320*12</f>
+        <v>15840</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G34" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>2640</v>
+        <v>15840</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="I34" t="s">
-        <v>216</v>
+        <v>106</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>25</v>
+        <v>122</v>
       </c>
       <c r="D35" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="E35" s="4">
-        <v>160</v>
+        <v>3198.13</v>
       </c>
       <c r="F35" s="6" t="s">
         <v>2</v>
       </c>
       <c r="G35" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>160</v>
+        <v>3198.13</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="C36" t="s">
-        <v>57</v>
+        <v>121</v>
       </c>
       <c r="D36" t="s">
-        <v>110</v>
+        <v>16</v>
       </c>
       <c r="E36" s="4">
-        <f>2400*12</f>
-        <v>28800</v>
+        <v>3322.8</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>2</v>
       </c>
       <c r="G36" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>28800</v>
-      </c>
-      <c r="H36" s="2" t="s">
-        <v>109</v>
+        <v>3322.8</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="C37" t="s">
-        <v>57</v>
+        <v>120</v>
       </c>
       <c r="D37" t="s">
-        <v>110</v>
+        <v>15</v>
       </c>
       <c r="E37" s="4">
-        <f>1320*12</f>
-        <v>15840</v>
+        <v>3138.27</v>
       </c>
       <c r="F37" s="6" t="s">
         <v>2</v>
       </c>
       <c r="G37" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>15840</v>
-      </c>
-      <c r="H37" s="2" t="s">
-        <v>108</v>
+        <v>3138.27</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>124</v>
+        <v>138</v>
+      </c>
+      <c r="C38" t="s">
+        <v>85</v>
       </c>
       <c r="D38" t="s">
-        <v>17</v>
+        <v>79</v>
       </c>
       <c r="E38" s="4">
-        <v>3198.13</v>
+        <v>240</v>
       </c>
       <c r="F38" s="6" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G38" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>3198.13</v>
+        <v>288</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>123</v>
+        <v>139</v>
+      </c>
+      <c r="C39" t="s">
+        <v>86</v>
       </c>
       <c r="D39" t="s">
-        <v>16</v>
+        <v>79</v>
       </c>
       <c r="E39" s="4">
-        <v>3322.8</v>
+        <v>240</v>
       </c>
       <c r="F39" s="6" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G39" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>3322.8</v>
+        <v>288</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>122</v>
+        <v>141</v>
+      </c>
+      <c r="C40" t="s">
+        <v>87</v>
       </c>
       <c r="D40" t="s">
-        <v>15</v>
+        <v>79</v>
       </c>
       <c r="E40" s="4">
-        <v>3138.27</v>
+        <v>240</v>
       </c>
       <c r="F40" s="6" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G40" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>3138.27</v>
+        <v>288</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
@@ -7577,13 +7905,13 @@
         <v>13</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="C41" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D41" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E41" s="4">
         <v>240</v>
@@ -7596,208 +7924,134 @@
         <v>288</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>13</v>
+        <v>98</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="C42" t="s">
-        <v>88</v>
+        <v>179</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>67</v>
       </c>
       <c r="D42" t="s">
-        <v>81</v>
-      </c>
-      <c r="E42" s="4">
-        <v>240</v>
-      </c>
-      <c r="F42" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="G42" s="4">
+        <v>178</v>
+      </c>
+      <c r="E42" s="5">
+        <v>10000</v>
+      </c>
+      <c r="F42" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="G42" s="5">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>288</v>
-      </c>
-      <c r="H42" s="2" t="s">
-        <v>135</v>
-      </c>
+        <v>10000</v>
+      </c>
+      <c r="H42" s="3"/>
+      <c r="I42" s="2"/>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>13</v>
+        <v>98</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="C43" t="s">
-        <v>89</v>
+        <v>181</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>67</v>
       </c>
       <c r="D43" t="s">
-        <v>81</v>
-      </c>
-      <c r="E43" s="4">
-        <v>240</v>
-      </c>
-      <c r="F43" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="G43" s="4">
+        <v>178</v>
+      </c>
+      <c r="E43" s="5">
+        <v>12500</v>
+      </c>
+      <c r="F43" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="G43" s="5">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>288</v>
-      </c>
-      <c r="H43" s="2" t="s">
-        <v>135</v>
-      </c>
+        <v>12500</v>
+      </c>
+      <c r="H43" s="3"/>
+      <c r="I43" s="2"/>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>13</v>
+        <v>98</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="C44" t="s">
-        <v>90</v>
+        <v>180</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>67</v>
       </c>
       <c r="D44" t="s">
-        <v>81</v>
-      </c>
-      <c r="E44" s="4">
-        <v>240</v>
-      </c>
-      <c r="F44" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="G44" s="4">
+        <v>178</v>
+      </c>
+      <c r="E44" s="5">
+        <v>15000</v>
+      </c>
+      <c r="F44" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="G44" s="5">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>288</v>
-      </c>
-      <c r="H44" s="2" t="s">
-        <v>135</v>
-      </c>
+        <v>15000</v>
+      </c>
+      <c r="H44" s="3"/>
+      <c r="I44" s="2"/>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>189</v>
+        <v>98</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D45" t="s">
-        <v>188</v>
+        <v>27</v>
       </c>
       <c r="E45" s="5">
-        <v>10000</v>
+        <v>16800</v>
       </c>
       <c r="F45" s="7" t="s">
         <v>2</v>
       </c>
       <c r="G45" s="5">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>10000</v>
-      </c>
-      <c r="H45" s="3"/>
-      <c r="I45" s="2"/>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A46" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D46" t="s">
-        <v>188</v>
-      </c>
-      <c r="E46" s="5">
-        <v>12500</v>
-      </c>
-      <c r="F46" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="G46" s="5">
-        <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>12500</v>
-      </c>
-      <c r="H46" s="3"/>
-      <c r="I46" s="2"/>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A47" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D47" t="s">
-        <v>188</v>
-      </c>
-      <c r="E47" s="5">
-        <v>15000</v>
-      </c>
-      <c r="F47" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="G47" s="5">
-        <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>15000</v>
-      </c>
-      <c r="H47" s="3"/>
-      <c r="I47" s="2"/>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A48" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D48" t="s">
-        <v>27</v>
-      </c>
-      <c r="E48" s="5">
         <v>16800</v>
       </c>
-      <c r="F48" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="G48" s="5">
-        <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>16800</v>
-      </c>
-      <c r="H48" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="I48" s="2" t="s">
-        <v>216</v>
+      <c r="H45" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="I45" s="2" t="s">
+        <v>202</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C48" xr:uid="{10A37FDE-E67C-425C-BC79-E21761381591}">
-      <formula1>#REF!</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{071BD1E1-9B70-433B-ADD3-203A568DABB9}">
+          <x14:formula1>
+            <xm:f>Provisions!$B:$B</xm:f>
+          </x14:formula1>
+          <xm:sqref>C1:C1048576</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
@@ -7816,21 +8070,22 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>208</v>
+        <v>196</v>
       </c>
       <c r="B1" t="s">
-        <v>207</v>
+        <v>195</v>
       </c>
       <c r="C1" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>209</v>
+        <v>197</v>
       </c>
       <c r="B2">
-        <v>10142</v>
+        <f>5735*2.5</f>
+        <v>14337.5</v>
       </c>
       <c r="C2">
         <v>0.5</v>
@@ -7857,39 +8112,39 @@
     <col min="3" max="3" width="21.28515625" style="1" customWidth="1"/>
     <col min="4" max="4" width="30.140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="24.7109375" customWidth="1"/>
-    <col min="6" max="6" width="61.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="133.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>203</v>
+        <v>191</v>
       </c>
       <c r="B1" t="s">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
       <c r="D1" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="E1" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="F1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>243</v>
+        <v>216</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C2" s="1">
-        <f>500*1.2/4600</f>
-        <v>0.13043478260869565</v>
+        <f>392*1.2/4900</f>
+        <v>9.6000000000000002E-2</v>
       </c>
       <c r="D2">
         <v>130</v>
@@ -7898,18 +8153,18 @@
         <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>214</v>
+        <v>409</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="B3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C3" s="1">
-        <v>0.12770000000000001</v>
+        <v>0.12559999999999999</v>
       </c>
       <c r="D3">
         <v>225</v>
@@ -7918,7 +8173,7 @@
         <v>2</v>
       </c>
       <c r="F3" t="s">
-        <v>215</v>
+        <v>228</v>
       </c>
     </row>
   </sheetData>

--- a/input.xlsx
+++ b/input.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/25a393584c41f6f2/Documents/Mon Patrimoine/Projet Immobilier/2023 Terrasses de Galieni/09 - Copropriété/Site de calcul des charges de copropriété/streamlit-copro-charges/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1276" documentId="13_ncr:1_{471232EB-3AAB-4D08-BC1C-7B7CD1C1D853}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D5BCE6EF-3B86-4285-8B2D-14A1ABACB257}"/>
+  <xr:revisionPtr revIDLastSave="1297" documentId="13_ncr:1_{471232EB-3AAB-4D08-BC1C-7B7CD1C1D853}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6C1FEAFF-C718-4A32-9732-4AE22D2C289D}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Provisions" sheetId="9" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="634" uniqueCount="410">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="639" uniqueCount="415">
   <si>
     <t>Taxes</t>
   </si>
@@ -624,9 +624,6 @@
   </si>
   <si>
     <t>Prix unitaire du kWh</t>
-  </si>
-  <si>
-    <t>Atlantic Varmax 2 225</t>
   </si>
   <si>
     <t>Volume à chauffer en m3</t>
@@ -703,9 +700,6 @@
     <t>Description longue</t>
   </si>
   <si>
-    <t>Herz Firematic 130</t>
-  </si>
-  <si>
     <t>De 310€/t pour Gruchy à 500€/t pour Prochalor</t>
   </si>
   <si>
@@ -1283,6 +1277,27 @@
   </si>
   <si>
     <t>Prix de la tonne de granulés: Gruchy = 310€/t, CRAM = 392€/t (dans le simulateur) et Prochalor 500€/t - 1 tonne de granulés de bois = 4800-5000kWh</t>
+  </si>
+  <si>
+    <t>Herz Firematic 120</t>
+  </si>
+  <si>
+    <t>Atlantic Varmax 2 140</t>
+  </si>
+  <si>
+    <t>Unité</t>
+  </si>
+  <si>
+    <t>tonne de granulé</t>
+  </si>
+  <si>
+    <t>kWh</t>
+  </si>
+  <si>
+    <t>Prix de l'unité</t>
+  </si>
+  <si>
+    <t>kWh par unité</t>
   </si>
 </sst>
 </file>
@@ -1293,7 +1308,7 @@
     <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;€&quot;_-;\-* #,##0.00\ &quot;€&quot;_-;_-* &quot;-&quot;??\ &quot;€&quot;_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$€-40C]_-;\-* #,##0.00\ [$€-40C]_-;_-* &quot;-&quot;??\ [$€-40C]_-;_-@_-"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1304,6 +1319,12 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1348,7 +1369,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1367,13 +1388,52 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="27">
+  <dxfs count="30">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -1431,30 +1491,6 @@
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="34" formatCode="_-* #,##0.00\ &quot;€&quot;_-;\-* #,##0.00\ &quot;€&quot;_-;_-* &quot;-&quot;??\ &quot;€&quot;_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
     </dxf>
     <dxf>
       <font>
@@ -1725,6 +1761,48 @@
       </font>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_-* #,##0.00\ &quot;€&quot;_-;\-* #,##0.00\ &quot;€&quot;_-;_-* &quot;-&quot;??\ &quot;€&quot;_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1753,8 +1831,8 @@
     <tableColumn id="4" xr3:uid="{84F1F30D-4827-43F2-8865-B7957E3E712D}" name="ID"/>
     <tableColumn id="7" xr3:uid="{512EABBD-B863-4251-833D-8B8D1F1626EF}" name="Description"/>
     <tableColumn id="2" xr3:uid="{D09C4BB0-FEBD-4A72-9E87-B5258D8B62D7}" name="Label de la provision"/>
-    <tableColumn id="3" xr3:uid="{347751FB-EF14-4BD7-9D47-427E04136B77}" name="Provision" totalsRowFunction="sum" dataDxfId="11" totalsRowDxfId="10"/>
-    <tableColumn id="5" xr3:uid="{CA26B6F8-88AD-418A-B213-749ABA66E926}" name="Description longue" dataDxfId="9"/>
+    <tableColumn id="3" xr3:uid="{347751FB-EF14-4BD7-9D47-427E04136B77}" name="Provision" totalsRowFunction="sum" dataDxfId="28" totalsRowDxfId="27"/>
+    <tableColumn id="5" xr3:uid="{CA26B6F8-88AD-418A-B213-749ABA66E926}" name="Description longue" dataDxfId="26"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1767,24 +1845,24 @@
     <sortCondition ref="A1:A180"/>
   </sortState>
   <tableColumns count="16">
-    <tableColumn id="3" xr3:uid="{1687C042-C916-4161-82C2-2A915364FCD2}" name="Numéro de lot" dataDxfId="26"/>
+    <tableColumn id="3" xr3:uid="{1687C042-C916-4161-82C2-2A915364FCD2}" name="Numéro de lot" dataDxfId="25"/>
     <tableColumn id="1" xr3:uid="{788DBA8C-5B77-4079-8161-FA45C58518AE}" name="Description"/>
-    <tableColumn id="2" xr3:uid="{BE5ACA99-AEAF-4E51-BE0A-B3FB8FCCF08B}" name="Tantièmes copropriété" dataDxfId="25">
+    <tableColumn id="2" xr3:uid="{BE5ACA99-AEAF-4E51-BE0A-B3FB8FCCF08B}" name="Tantièmes copropriété" dataDxfId="24">
       <calculatedColumnFormula>7/10000</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{D62FAA89-C46E-4AF6-A14F-7FD6F46E7F00}" name="Tantièmes ascenseur 1-1" dataDxfId="24"/>
-    <tableColumn id="9" xr3:uid="{C3B9BDED-CB2A-4305-9CBF-418F5971AC1E}" name="Tantièmes ascenseur 1-2" dataDxfId="23"/>
-    <tableColumn id="10" xr3:uid="{C2291DE1-C707-4F83-846E-F914B4B42E52}" name="Tantièmes ascenseur 2" dataDxfId="22"/>
-    <tableColumn id="11" xr3:uid="{4F70F08A-4C2F-41B0-88EB-711B1A0760CD}" name="Tantièmes ascenseur 3" dataDxfId="21"/>
-    <tableColumn id="14" xr3:uid="{80D23396-716C-46AC-9B55-BCBC6C981351}" name="Tantièmes chauffage" dataDxfId="20"/>
-    <tableColumn id="15" xr3:uid="{E3955139-B619-4DD0-8FC1-ECA97048DFE4}" name="Tantièmes Batiment 1" dataDxfId="19"/>
-    <tableColumn id="16" xr3:uid="{C73E9407-A858-4EF7-81C2-6C70C4B157A2}" name="Tantièmes Batiment 2" dataDxfId="18"/>
-    <tableColumn id="17" xr3:uid="{A07338CA-0096-4091-89B2-A46FF2D323C2}" name="Tantièmes Batiment 3" dataDxfId="17"/>
-    <tableColumn id="18" xr3:uid="{7A3012D8-2375-4F10-9E84-F2F5060C6A99}" name="Tantièmes Hall 1-1" dataDxfId="16"/>
-    <tableColumn id="19" xr3:uid="{67961B6E-B577-4A49-B099-623FB85519B4}" name="Tantièmes Hall 1-2" dataDxfId="15"/>
-    <tableColumn id="20" xr3:uid="{03C201C1-F8AA-4D3C-AEBC-425B180BC2D7}" name="Tantièmes Hall 2" dataDxfId="14"/>
-    <tableColumn id="21" xr3:uid="{4826FC05-81A9-4020-8D1D-83D3D5C5A05A}" name="Tantièmes Logement/Stationnements" dataDxfId="13"/>
-    <tableColumn id="6" xr3:uid="{7B87787E-3595-42D5-B815-AF76B67432D8}" name="Tantièmes Stationnement" dataDxfId="12"/>
+    <tableColumn id="8" xr3:uid="{D62FAA89-C46E-4AF6-A14F-7FD6F46E7F00}" name="Tantièmes ascenseur 1-1" dataDxfId="23"/>
+    <tableColumn id="9" xr3:uid="{C3B9BDED-CB2A-4305-9CBF-418F5971AC1E}" name="Tantièmes ascenseur 1-2" dataDxfId="22"/>
+    <tableColumn id="10" xr3:uid="{C2291DE1-C707-4F83-846E-F914B4B42E52}" name="Tantièmes ascenseur 2" dataDxfId="21"/>
+    <tableColumn id="11" xr3:uid="{4F70F08A-4C2F-41B0-88EB-711B1A0760CD}" name="Tantièmes ascenseur 3" dataDxfId="20"/>
+    <tableColumn id="14" xr3:uid="{80D23396-716C-46AC-9B55-BCBC6C981351}" name="Tantièmes chauffage" dataDxfId="19"/>
+    <tableColumn id="15" xr3:uid="{E3955139-B619-4DD0-8FC1-ECA97048DFE4}" name="Tantièmes Batiment 1" dataDxfId="18"/>
+    <tableColumn id="16" xr3:uid="{C73E9407-A858-4EF7-81C2-6C70C4B157A2}" name="Tantièmes Batiment 2" dataDxfId="17"/>
+    <tableColumn id="17" xr3:uid="{A07338CA-0096-4091-89B2-A46FF2D323C2}" name="Tantièmes Batiment 3" dataDxfId="16"/>
+    <tableColumn id="18" xr3:uid="{7A3012D8-2375-4F10-9E84-F2F5060C6A99}" name="Tantièmes Hall 1-1" dataDxfId="15"/>
+    <tableColumn id="19" xr3:uid="{67961B6E-B577-4A49-B099-623FB85519B4}" name="Tantièmes Hall 1-2" dataDxfId="14"/>
+    <tableColumn id="20" xr3:uid="{03C201C1-F8AA-4D3C-AEBC-425B180BC2D7}" name="Tantièmes Hall 2" dataDxfId="13"/>
+    <tableColumn id="21" xr3:uid="{4826FC05-81A9-4020-8D1D-83D3D5C5A05A}" name="Tantièmes Logement/Stationnements" dataDxfId="12"/>
+    <tableColumn id="6" xr3:uid="{7B87787E-3595-42D5-B815-AF76B67432D8}" name="Tantièmes Stationnement" dataDxfId="11"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1797,17 +1875,17 @@
     <sortCondition ref="B1:B45"/>
   </sortState>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{7753A616-C6B5-4B02-AE3F-2A95253630B8}" name="Type de prestation" dataDxfId="8"/>
-    <tableColumn id="2" xr3:uid="{D7B6EA29-CA0A-4C24-9A81-3DF01785BD0C}" name="Label de la prestation" dataDxfId="7"/>
-    <tableColumn id="8" xr3:uid="{91FE62B8-BF79-4277-91C2-4B3C13901105}" name="ID prestation" dataDxfId="6"/>
+    <tableColumn id="1" xr3:uid="{7753A616-C6B5-4B02-AE3F-2A95253630B8}" name="Type de prestation" dataDxfId="10"/>
+    <tableColumn id="2" xr3:uid="{D7B6EA29-CA0A-4C24-9A81-3DF01785BD0C}" name="Label de la prestation" dataDxfId="9"/>
+    <tableColumn id="8" xr3:uid="{91FE62B8-BF79-4277-91C2-4B3C13901105}" name="ID prestation" dataDxfId="8"/>
     <tableColumn id="3" xr3:uid="{2ADF6FF1-1416-43FA-A9BF-E696654CC8CD}" name="Prestataire"/>
-    <tableColumn id="4" xr3:uid="{1C295B62-0191-41FA-9660-5BADE532BEE7}" name="Cout" dataDxfId="5"/>
-    <tableColumn id="5" xr3:uid="{1E3C456B-12BB-4B06-B366-57CE3DA87819}" name="Taxes" dataDxfId="4"/>
-    <tableColumn id="6" xr3:uid="{20997A37-E6E3-4308-9ACD-8D77B289D813}" name="Total TTC" dataDxfId="3">
+    <tableColumn id="4" xr3:uid="{1C295B62-0191-41FA-9660-5BADE532BEE7}" name="Cout" dataDxfId="7"/>
+    <tableColumn id="5" xr3:uid="{1E3C456B-12BB-4B06-B366-57CE3DA87819}" name="Taxes" dataDxfId="6"/>
+    <tableColumn id="6" xr3:uid="{20997A37-E6E3-4308-9ACD-8D77B289D813}" name="Total TTC" dataDxfId="5">
       <calculatedColumnFormula>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{6BDB0ED6-23A7-4E1A-A654-9E18B0DA38B5}" name="Description" dataDxfId="2"/>
-    <tableColumn id="9" xr3:uid="{C919E254-DE7F-4D3B-8CF6-79E643BBF97F}" name="Prestation choisie actuellement" dataDxfId="1"/>
+    <tableColumn id="7" xr3:uid="{6BDB0ED6-23A7-4E1A-A654-9E18B0DA38B5}" name="Description" dataDxfId="4"/>
+    <tableColumn id="9" xr3:uid="{C919E254-DE7F-4D3B-8CF6-79E643BBF97F}" name="Prestation choisie actuellement" dataDxfId="3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1828,12 +1906,15 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{587622F4-20CE-4A1D-A4F7-C9DCD51AF751}" name="Chauffage" displayName="Chauffage" ref="A1:F3" totalsRowShown="0">
-  <autoFilter ref="A1:F3" xr:uid="{587622F4-20CE-4A1D-A4F7-C9DCD51AF751}"/>
-  <tableColumns count="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{587622F4-20CE-4A1D-A4F7-C9DCD51AF751}" name="Chauffage" displayName="Chauffage" ref="A1:I3" totalsRowShown="0">
+  <autoFilter ref="A1:I3" xr:uid="{587622F4-20CE-4A1D-A4F7-C9DCD51AF751}"/>
+  <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{455C30A6-2C19-4BD7-B8A4-D1C6252917DD}" name="Type de chaudière"/>
     <tableColumn id="2" xr3:uid="{FAAC8507-DC80-422C-8508-496178C23374}" name="ID poste de provision"/>
-    <tableColumn id="3" xr3:uid="{17764D71-05D7-4B37-8536-4004CBBE2CD4}" name="Prix unitaire du kWh" dataDxfId="0" dataCellStyle="Currency"/>
+    <tableColumn id="3" xr3:uid="{17764D71-05D7-4B37-8536-4004CBBE2CD4}" name="Prix unitaire du kWh" dataDxfId="29" dataCellStyle="Currency"/>
+    <tableColumn id="7" xr3:uid="{39B6FB9A-9DCB-412D-8CBD-94E321E39A50}" name="Unité" dataDxfId="2" dataCellStyle="Currency"/>
+    <tableColumn id="8" xr3:uid="{C769AD0E-5A43-462D-8737-CE59FA9E9F57}" name="Prix de l'unité" dataDxfId="1" dataCellStyle="Currency"/>
+    <tableColumn id="9" xr3:uid="{C32F2A17-C994-4DCC-A33C-2604586EDB4F}" name="kWh par unité" dataDxfId="0" dataCellStyle="Currency"/>
     <tableColumn id="4" xr3:uid="{FECEDA0B-3F17-4D04-AB3F-B1B848AA5DB2}" name="Production maximum en kW"/>
     <tableColumn id="5" xr3:uid="{ED1B8FB3-6899-430D-BDC7-A9BDBA679526}" name="Ordre d'utilisation"/>
     <tableColumn id="6" xr3:uid="{F8EB0843-7F05-427F-9B41-0852730F32C9}" name="Description"/>
@@ -2136,7 +2217,7 @@
         <v>95</v>
       </c>
       <c r="F1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="45" x14ac:dyDescent="0.25">
@@ -2144,7 +2225,7 @@
         <v>145</v>
       </c>
       <c r="B2" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C2" t="s">
         <v>29</v>
@@ -2156,7 +2237,7 @@
         <v>35000</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -2176,7 +2257,7 @@
         <v>27000</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -2394,7 +2475,7 @@
         <v>2000</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -2450,7 +2531,7 @@
         <v>1050</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -2470,7 +2551,7 @@
         <v>1000</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -2490,7 +2571,7 @@
         <v>1000</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="75" x14ac:dyDescent="0.25">
@@ -2510,7 +2591,7 @@
         <v>920</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="135" x14ac:dyDescent="0.25">
@@ -2530,7 +2611,7 @@
         <v>900</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -2568,7 +2649,7 @@
         <v>750</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -2606,7 +2687,7 @@
         <v>580</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -2644,7 +2725,7 @@
         <v>450</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="60" x14ac:dyDescent="0.25">
@@ -2664,7 +2745,7 @@
         <v>360</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="45" x14ac:dyDescent="0.25">
@@ -2684,7 +2765,7 @@
         <v>320</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="60" x14ac:dyDescent="0.25">
@@ -2704,7 +2785,7 @@
         <v>240</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -2742,7 +2823,7 @@
         <v>90</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -2766,16 +2847,16 @@
         <v>145</v>
       </c>
       <c r="B35" t="s">
+        <v>223</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="D35" t="s">
+        <v>224</v>
+      </c>
+      <c r="F35" s="2" t="s">
         <v>225</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="D35" t="s">
-        <v>226</v>
-      </c>
-      <c r="F35" s="2" t="s">
-        <v>227</v>
       </c>
     </row>
   </sheetData>
@@ -2862,7 +2943,7 @@
         <v>101</v>
       </c>
       <c r="B2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C2">
         <v>462</v>
@@ -2876,7 +2957,7 @@
         <v>102</v>
       </c>
       <c r="B3" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C3">
         <v>119</v>
@@ -2902,7 +2983,7 @@
         <v>103</v>
       </c>
       <c r="B4" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C4">
         <v>83</v>
@@ -2928,7 +3009,7 @@
         <v>104</v>
       </c>
       <c r="B5" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C5">
         <v>130</v>
@@ -2954,7 +3035,7 @@
         <v>105</v>
       </c>
       <c r="B6" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C6">
         <v>123</v>
@@ -2980,7 +3061,7 @@
         <v>106</v>
       </c>
       <c r="B7" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C7">
         <v>122</v>
@@ -3006,7 +3087,7 @@
         <v>107</v>
       </c>
       <c r="B8" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C8">
         <v>55</v>
@@ -3032,7 +3113,7 @@
         <v>108</v>
       </c>
       <c r="B9" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C9">
         <v>96</v>
@@ -3058,7 +3139,7 @@
         <v>109</v>
       </c>
       <c r="B10" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C10">
         <v>123</v>
@@ -3084,7 +3165,7 @@
         <v>110</v>
       </c>
       <c r="B11" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C11">
         <v>129</v>
@@ -3110,7 +3191,7 @@
         <v>111</v>
       </c>
       <c r="B12" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C12">
         <v>58</v>
@@ -3136,7 +3217,7 @@
         <v>112</v>
       </c>
       <c r="B13" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C13">
         <v>91</v>
@@ -3162,7 +3243,7 @@
         <v>113</v>
       </c>
       <c r="B14" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C14" s="8">
         <v>86</v>
@@ -3196,7 +3277,7 @@
         <v>114</v>
       </c>
       <c r="B15" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C15">
         <v>94</v>
@@ -3222,7 +3303,7 @@
         <v>115</v>
       </c>
       <c r="B16" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C16">
         <v>60</v>
@@ -3248,7 +3329,7 @@
         <v>116</v>
       </c>
       <c r="B17" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C17">
         <v>162</v>
@@ -3274,7 +3355,7 @@
         <v>117</v>
       </c>
       <c r="B18" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C18">
         <v>202</v>
@@ -3300,7 +3381,7 @@
         <v>118</v>
       </c>
       <c r="B19" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C19">
         <v>294</v>
@@ -3326,7 +3407,7 @@
         <v>119</v>
       </c>
       <c r="B20" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C20">
         <v>81</v>
@@ -3352,7 +3433,7 @@
         <v>120</v>
       </c>
       <c r="B21" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C21">
         <v>115</v>
@@ -3378,7 +3459,7 @@
         <v>121</v>
       </c>
       <c r="B22" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C22">
         <v>112</v>
@@ -3404,7 +3485,7 @@
         <v>122</v>
       </c>
       <c r="B23" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="C23">
         <v>83</v>
@@ -3430,7 +3511,7 @@
         <v>123</v>
       </c>
       <c r="B24" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C24">
         <v>118</v>
@@ -3456,7 +3537,7 @@
         <v>124</v>
       </c>
       <c r="B25" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C25">
         <v>117</v>
@@ -3482,7 +3563,7 @@
         <v>125</v>
       </c>
       <c r="B26" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C26">
         <v>87</v>
@@ -3508,7 +3589,7 @@
         <v>126</v>
       </c>
       <c r="B27" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="C27">
         <v>125</v>
@@ -3534,7 +3615,7 @@
         <v>127</v>
       </c>
       <c r="B28" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C28">
         <v>123</v>
@@ -3560,7 +3641,7 @@
         <v>128</v>
       </c>
       <c r="B29" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="C29">
         <v>88</v>
@@ -3586,7 +3667,7 @@
         <v>129</v>
       </c>
       <c r="B30" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="C30">
         <v>127</v>
@@ -3612,7 +3693,7 @@
         <v>130</v>
       </c>
       <c r="B31" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C31">
         <v>127</v>
@@ -3638,7 +3719,7 @@
         <v>132</v>
       </c>
       <c r="B32" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C32">
         <v>172</v>
@@ -3664,7 +3745,7 @@
         <v>133</v>
       </c>
       <c r="B33" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C33">
         <v>218</v>
@@ -3690,7 +3771,7 @@
         <v>134</v>
       </c>
       <c r="B34" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C34">
         <v>102</v>
@@ -3716,7 +3797,7 @@
         <v>135</v>
       </c>
       <c r="B35" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C35">
         <v>83</v>
@@ -3742,7 +3823,7 @@
         <v>201</v>
       </c>
       <c r="B36" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C36">
         <v>401</v>
@@ -3756,7 +3837,7 @@
         <v>202</v>
       </c>
       <c r="B37" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C37">
         <v>114</v>
@@ -3782,7 +3863,7 @@
         <v>203</v>
       </c>
       <c r="B38" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C38">
         <v>84</v>
@@ -3808,7 +3889,7 @@
         <v>204</v>
       </c>
       <c r="B39" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C39">
         <v>81</v>
@@ -3834,7 +3915,7 @@
         <v>205</v>
       </c>
       <c r="B40" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C40">
         <v>118</v>
@@ -3860,7 +3941,7 @@
         <v>206</v>
       </c>
       <c r="B41" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C41">
         <v>120</v>
@@ -3886,7 +3967,7 @@
         <v>207</v>
       </c>
       <c r="B42" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C42">
         <v>89</v>
@@ -3912,7 +3993,7 @@
         <v>208</v>
       </c>
       <c r="B43" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C43">
         <v>84</v>
@@ -3938,7 +4019,7 @@
         <v>209</v>
       </c>
       <c r="B44" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C44">
         <v>124</v>
@@ -3964,7 +4045,7 @@
         <v>210</v>
       </c>
       <c r="B45" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C45">
         <v>126</v>
@@ -3990,7 +4071,7 @@
         <v>211</v>
       </c>
       <c r="B46" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C46">
         <v>91</v>
@@ -4016,7 +4097,7 @@
         <v>212</v>
       </c>
       <c r="B47" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C47">
         <v>88</v>
@@ -4042,7 +4123,7 @@
         <v>213</v>
       </c>
       <c r="B48" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C48">
         <v>131</v>
@@ -4068,7 +4149,7 @@
         <v>214</v>
       </c>
       <c r="B49" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C49">
         <v>130</v>
@@ -4094,7 +4175,7 @@
         <v>215</v>
       </c>
       <c r="B50" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C50">
         <v>93</v>
@@ -4120,7 +4201,7 @@
         <v>216</v>
       </c>
       <c r="B51" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C51">
         <v>59</v>
@@ -4146,7 +4227,7 @@
         <v>217</v>
       </c>
       <c r="B52" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C52">
         <v>166</v>
@@ -4172,7 +4253,7 @@
         <v>218</v>
       </c>
       <c r="B53" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C53">
         <v>186</v>
@@ -4198,7 +4279,7 @@
         <v>219</v>
       </c>
       <c r="B54" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C54">
         <v>61</v>
@@ -4224,7 +4305,7 @@
         <v>220</v>
       </c>
       <c r="B55" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C55">
         <v>171</v>
@@ -4250,7 +4331,7 @@
         <v>221</v>
       </c>
       <c r="B56" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C56">
         <v>178</v>
@@ -4276,7 +4357,7 @@
         <v>222</v>
       </c>
       <c r="B57" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C57">
         <v>62</v>
@@ -4302,7 +4383,7 @@
         <v>223</v>
       </c>
       <c r="B58" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C58">
         <v>174</v>
@@ -4328,7 +4409,7 @@
         <v>224</v>
       </c>
       <c r="B59" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C59">
         <v>181</v>
@@ -4354,7 +4435,7 @@
         <v>225</v>
       </c>
       <c r="B60" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C60" s="8">
         <v>197</v>
@@ -4388,7 +4469,7 @@
         <v>301</v>
       </c>
       <c r="B61" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C61">
         <v>169</v>
@@ -4408,7 +4489,7 @@
         <v>302</v>
       </c>
       <c r="B62" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C62">
         <v>158</v>
@@ -4428,7 +4509,7 @@
         <v>303</v>
       </c>
       <c r="B63" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C63">
         <v>71</v>
@@ -4448,7 +4529,7 @@
         <v>305</v>
       </c>
       <c r="B64" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C64">
         <v>134</v>
@@ -4471,7 +4552,7 @@
         <v>306</v>
       </c>
       <c r="B65" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C65">
         <v>147</v>
@@ -4494,7 +4575,7 @@
         <v>307</v>
       </c>
       <c r="B66" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C66">
         <v>155</v>
@@ -4517,7 +4598,7 @@
         <v>308</v>
       </c>
       <c r="B67" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C67" s="8">
         <v>75</v>
@@ -4549,7 +4630,7 @@
         <v>310</v>
       </c>
       <c r="B68" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C68">
         <v>52</v>
@@ -4572,7 +4653,7 @@
         <v>311</v>
       </c>
       <c r="B69" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C69">
         <v>193</v>
@@ -4595,7 +4676,7 @@
         <v>312</v>
       </c>
       <c r="B70" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C70">
         <v>133</v>
@@ -4618,7 +4699,7 @@
         <v>313</v>
       </c>
       <c r="B71" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C71">
         <v>72</v>
@@ -4638,7 +4719,7 @@
         <v>314</v>
       </c>
       <c r="B72" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C72">
         <v>79</v>
@@ -4658,7 +4739,7 @@
         <v>315</v>
       </c>
       <c r="B73" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C73">
         <v>85</v>
@@ -4681,7 +4762,7 @@
         <v>316</v>
       </c>
       <c r="B74" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C74">
         <v>90</v>
@@ -4704,7 +4785,7 @@
         <v>401</v>
       </c>
       <c r="B75" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C75">
         <v>7</v>
@@ -4724,7 +4805,7 @@
         <v>402</v>
       </c>
       <c r="B76" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C76">
         <v>7</v>
@@ -4744,7 +4825,7 @@
         <v>403</v>
       </c>
       <c r="B77" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C77">
         <v>7</v>
@@ -4764,7 +4845,7 @@
         <v>404</v>
       </c>
       <c r="B78" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C78">
         <v>7</v>
@@ -4784,7 +4865,7 @@
         <v>405</v>
       </c>
       <c r="B79" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C79">
         <v>7</v>
@@ -4804,7 +4885,7 @@
         <v>406</v>
       </c>
       <c r="B80" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C80">
         <v>7</v>
@@ -4824,7 +4905,7 @@
         <v>407</v>
       </c>
       <c r="B81" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C81">
         <v>7</v>
@@ -4844,7 +4925,7 @@
         <v>408</v>
       </c>
       <c r="B82" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C82">
         <v>7</v>
@@ -4864,7 +4945,7 @@
         <v>409</v>
       </c>
       <c r="B83" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C83">
         <v>7</v>
@@ -4884,7 +4965,7 @@
         <v>410</v>
       </c>
       <c r="B84" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C84">
         <v>7</v>
@@ -4904,7 +4985,7 @@
         <v>411</v>
       </c>
       <c r="B85" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C85">
         <v>7</v>
@@ -4924,7 +5005,7 @@
         <v>412</v>
       </c>
       <c r="B86" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C86">
         <v>7</v>
@@ -4944,7 +5025,7 @@
         <v>413</v>
       </c>
       <c r="B87" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C87">
         <v>7</v>
@@ -4964,7 +5045,7 @@
         <v>414</v>
       </c>
       <c r="B88" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C88">
         <v>7</v>
@@ -4984,7 +5065,7 @@
         <v>415</v>
       </c>
       <c r="B89" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C89">
         <v>7</v>
@@ -5004,7 +5085,7 @@
         <v>416</v>
       </c>
       <c r="B90" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C90">
         <v>7</v>
@@ -5024,7 +5105,7 @@
         <v>417</v>
       </c>
       <c r="B91" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C91">
         <v>7</v>
@@ -5044,7 +5125,7 @@
         <v>418</v>
       </c>
       <c r="B92" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C92">
         <v>7</v>
@@ -5064,7 +5145,7 @@
         <v>419</v>
       </c>
       <c r="B93" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C93">
         <v>7</v>
@@ -5084,7 +5165,7 @@
         <v>420</v>
       </c>
       <c r="B94" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C94">
         <v>7</v>
@@ -5104,7 +5185,7 @@
         <v>421</v>
       </c>
       <c r="B95" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C95">
         <v>7</v>
@@ -5124,7 +5205,7 @@
         <v>422</v>
       </c>
       <c r="B96" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C96">
         <v>7</v>
@@ -5144,7 +5225,7 @@
         <v>423</v>
       </c>
       <c r="B97" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C97">
         <v>7</v>
@@ -5164,7 +5245,7 @@
         <v>424</v>
       </c>
       <c r="B98" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C98">
         <v>7</v>
@@ -5184,7 +5265,7 @@
         <v>425</v>
       </c>
       <c r="B99" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C99">
         <v>7</v>
@@ -5204,7 +5285,7 @@
         <v>426</v>
       </c>
       <c r="B100" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C100">
         <v>7</v>
@@ -5224,7 +5305,7 @@
         <v>427</v>
       </c>
       <c r="B101" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C101">
         <v>7</v>
@@ -5244,7 +5325,7 @@
         <v>428</v>
       </c>
       <c r="B102" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C102">
         <v>7</v>
@@ -5264,7 +5345,7 @@
         <v>429</v>
       </c>
       <c r="B103" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C103">
         <v>7</v>
@@ -5284,7 +5365,7 @@
         <v>430</v>
       </c>
       <c r="B104" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C104">
         <v>7</v>
@@ -5304,7 +5385,7 @@
         <v>431</v>
       </c>
       <c r="B105" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C105">
         <v>7</v>
@@ -5324,7 +5405,7 @@
         <v>432</v>
       </c>
       <c r="B106" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C106">
         <v>7</v>
@@ -5344,7 +5425,7 @@
         <v>433</v>
       </c>
       <c r="B107" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C107">
         <v>7</v>
@@ -5364,7 +5445,7 @@
         <v>434</v>
       </c>
       <c r="B108" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C108">
         <v>7</v>
@@ -5384,7 +5465,7 @@
         <v>435</v>
       </c>
       <c r="B109" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C109">
         <v>7</v>
@@ -5404,7 +5485,7 @@
         <v>436</v>
       </c>
       <c r="B110" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C110">
         <v>7</v>
@@ -5424,7 +5505,7 @@
         <v>437</v>
       </c>
       <c r="B111" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C111">
         <v>7</v>
@@ -5444,7 +5525,7 @@
         <v>438</v>
       </c>
       <c r="B112" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C112">
         <v>7</v>
@@ -5464,7 +5545,7 @@
         <v>439</v>
       </c>
       <c r="B113" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C113">
         <v>7</v>
@@ -5484,7 +5565,7 @@
         <v>440</v>
       </c>
       <c r="B114" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C114">
         <v>7</v>
@@ -5504,7 +5585,7 @@
         <v>441</v>
       </c>
       <c r="B115" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C115">
         <v>7</v>
@@ -5524,7 +5605,7 @@
         <v>442</v>
       </c>
       <c r="B116" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C116">
         <v>7</v>
@@ -5544,7 +5625,7 @@
         <v>443</v>
       </c>
       <c r="B117" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C117">
         <v>7</v>
@@ -5564,7 +5645,7 @@
         <v>444</v>
       </c>
       <c r="B118" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C118">
         <v>7</v>
@@ -5584,7 +5665,7 @@
         <v>445</v>
       </c>
       <c r="B119" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C119">
         <v>7</v>
@@ -5604,7 +5685,7 @@
         <v>446</v>
       </c>
       <c r="B120" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C120">
         <v>7</v>
@@ -5624,7 +5705,7 @@
         <v>447</v>
       </c>
       <c r="B121" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C121">
         <v>7</v>
@@ -5644,7 +5725,7 @@
         <v>448</v>
       </c>
       <c r="B122" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C122">
         <v>7</v>
@@ -5664,7 +5745,7 @@
         <v>449</v>
       </c>
       <c r="B123" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C123">
         <v>7</v>
@@ -5684,7 +5765,7 @@
         <v>450</v>
       </c>
       <c r="B124" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C124">
         <v>7</v>
@@ -5704,7 +5785,7 @@
         <v>451</v>
       </c>
       <c r="B125" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C125">
         <v>7</v>
@@ -5724,7 +5805,7 @@
         <v>452</v>
       </c>
       <c r="B126" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C126">
         <v>7</v>
@@ -5744,7 +5825,7 @@
         <v>453</v>
       </c>
       <c r="B127" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C127">
         <v>7</v>
@@ -5764,7 +5845,7 @@
         <v>454</v>
       </c>
       <c r="B128" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C128">
         <v>7</v>
@@ -5784,7 +5865,7 @@
         <v>455</v>
       </c>
       <c r="B129" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C129">
         <v>7</v>
@@ -5804,7 +5885,7 @@
         <v>456</v>
       </c>
       <c r="B130" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C130">
         <v>7</v>
@@ -5824,7 +5905,7 @@
         <v>457</v>
       </c>
       <c r="B131" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C131">
         <v>7</v>
@@ -5844,7 +5925,7 @@
         <v>458</v>
       </c>
       <c r="B132" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C132">
         <v>7</v>
@@ -5864,7 +5945,7 @@
         <v>459</v>
       </c>
       <c r="B133" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C133">
         <v>7</v>
@@ -5884,7 +5965,7 @@
         <v>460</v>
       </c>
       <c r="B134" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C134">
         <v>7</v>
@@ -5904,7 +5985,7 @@
         <v>461</v>
       </c>
       <c r="B135" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C135">
         <v>7</v>
@@ -5924,7 +6005,7 @@
         <v>462</v>
       </c>
       <c r="B136" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C136">
         <v>7</v>
@@ -5944,7 +6025,7 @@
         <v>463</v>
       </c>
       <c r="B137" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C137">
         <v>7</v>
@@ -5964,7 +6045,7 @@
         <v>464</v>
       </c>
       <c r="B138" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C138">
         <v>7</v>
@@ -5984,7 +6065,7 @@
         <v>465</v>
       </c>
       <c r="B139" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C139">
         <v>7</v>
@@ -6004,7 +6085,7 @@
         <v>466</v>
       </c>
       <c r="B140" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C140">
         <v>7</v>
@@ -6024,7 +6105,7 @@
         <v>467</v>
       </c>
       <c r="B141" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C141">
         <v>7</v>
@@ -6044,7 +6125,7 @@
         <v>468</v>
       </c>
       <c r="B142" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C142">
         <v>7</v>
@@ -6064,7 +6145,7 @@
         <v>469</v>
       </c>
       <c r="B143" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C143">
         <v>7</v>
@@ -6084,7 +6165,7 @@
         <v>470</v>
       </c>
       <c r="B144" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C144">
         <v>7</v>
@@ -6104,7 +6185,7 @@
         <v>471</v>
       </c>
       <c r="B145" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C145">
         <v>7</v>
@@ -6124,7 +6205,7 @@
         <v>472</v>
       </c>
       <c r="B146" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C146">
         <v>7</v>
@@ -6144,7 +6225,7 @@
         <v>473</v>
       </c>
       <c r="B147" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C147">
         <v>7</v>
@@ -6164,7 +6245,7 @@
         <v>474</v>
       </c>
       <c r="B148" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C148">
         <v>7</v>
@@ -6184,7 +6265,7 @@
         <v>475</v>
       </c>
       <c r="B149" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C149">
         <v>7</v>
@@ -6204,7 +6285,7 @@
         <v>476</v>
       </c>
       <c r="B150" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C150">
         <v>7</v>
@@ -6224,7 +6305,7 @@
         <v>477</v>
       </c>
       <c r="B151" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C151">
         <v>7</v>
@@ -6244,7 +6325,7 @@
         <v>478</v>
       </c>
       <c r="B152" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C152">
         <v>7</v>
@@ -6264,7 +6345,7 @@
         <v>479</v>
       </c>
       <c r="B153" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C153">
         <v>7</v>
@@ -6284,7 +6365,7 @@
         <v>480</v>
       </c>
       <c r="B154" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C154">
         <v>7</v>
@@ -6304,7 +6385,7 @@
         <v>481</v>
       </c>
       <c r="B155" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C155">
         <v>7</v>
@@ -6324,7 +6405,7 @@
         <v>482</v>
       </c>
       <c r="B156" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C156">
         <v>7</v>
@@ -6344,7 +6425,7 @@
         <v>483</v>
       </c>
       <c r="B157" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C157">
         <v>7</v>
@@ -6364,7 +6445,7 @@
         <v>484</v>
       </c>
       <c r="B158" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C158">
         <v>7</v>
@@ -6384,7 +6465,7 @@
         <v>485</v>
       </c>
       <c r="B159" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C159">
         <v>7</v>
@@ -6404,7 +6485,7 @@
         <v>486</v>
       </c>
       <c r="B160" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C160">
         <v>7</v>
@@ -6424,7 +6505,7 @@
         <v>487</v>
       </c>
       <c r="B161" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C161">
         <v>7</v>
@@ -6444,7 +6525,7 @@
         <v>488</v>
       </c>
       <c r="B162" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C162">
         <v>7</v>
@@ -6464,7 +6545,7 @@
         <v>489</v>
       </c>
       <c r="B163" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C163">
         <v>7</v>
@@ -6484,7 +6565,7 @@
         <v>490</v>
       </c>
       <c r="B164" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C164">
         <v>7</v>
@@ -6504,7 +6585,7 @@
         <v>491</v>
       </c>
       <c r="B165" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C165">
         <v>7</v>
@@ -6524,7 +6605,7 @@
         <v>492</v>
       </c>
       <c r="B166" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C166">
         <v>7</v>
@@ -6544,7 +6625,7 @@
         <v>493</v>
       </c>
       <c r="B167" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C167">
         <v>7</v>
@@ -6564,7 +6645,7 @@
         <v>494</v>
       </c>
       <c r="B168" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C168">
         <v>7</v>
@@ -6584,7 +6665,7 @@
         <v>495</v>
       </c>
       <c r="B169" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="C169">
         <v>7</v>
@@ -6604,7 +6685,7 @@
         <v>496</v>
       </c>
       <c r="B170" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C170">
         <v>7</v>
@@ -6624,7 +6705,7 @@
         <v>497</v>
       </c>
       <c r="B171" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C171">
         <v>7</v>
@@ -6644,7 +6725,7 @@
         <v>498</v>
       </c>
       <c r="B172" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C172">
         <v>7</v>
@@ -6664,7 +6745,7 @@
         <v>499</v>
       </c>
       <c r="B173" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C173">
         <v>7</v>
@@ -6684,7 +6765,7 @@
         <v>500</v>
       </c>
       <c r="B174" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C174">
         <v>7</v>
@@ -6704,7 +6785,7 @@
         <v>501</v>
       </c>
       <c r="B175" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C175">
         <v>7</v>
@@ -6724,7 +6805,7 @@
         <v>502</v>
       </c>
       <c r="B176" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="C176">
         <v>1</v>
@@ -6742,7 +6823,7 @@
         <v>503</v>
       </c>
       <c r="B177" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C177">
         <v>1</v>
@@ -6760,7 +6841,7 @@
         <v>504</v>
       </c>
       <c r="B178" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C178">
         <v>1</v>
@@ -6778,7 +6859,7 @@
         <v>505</v>
       </c>
       <c r="B179" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C179">
         <v>1</v>
@@ -6796,7 +6877,7 @@
         <v>506</v>
       </c>
       <c r="B180" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C180">
         <v>7</v>
@@ -6864,7 +6945,7 @@
         <v>136</v>
       </c>
       <c r="I1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="45" x14ac:dyDescent="0.25">
@@ -7197,7 +7278,7 @@
         <v>91</v>
       </c>
       <c r="I14" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -7227,7 +7308,7 @@
         <v>100</v>
       </c>
       <c r="I15" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
@@ -7282,7 +7363,7 @@
         <v>16750</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -7290,7 +7371,7 @@
         <v>20</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C18" t="s">
         <v>72</v>
@@ -7445,7 +7526,7 @@
         <v>103</v>
       </c>
       <c r="I23" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="60" x14ac:dyDescent="0.25">
@@ -7534,13 +7615,13 @@
         <v>18</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C27" t="s">
         <v>73</v>
       </c>
       <c r="D27" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E27" s="4">
         <v>434.5</v>
@@ -7553,10 +7634,10 @@
         <v>434.5</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
@@ -7586,7 +7667,7 @@
         <v>133</v>
       </c>
       <c r="I28" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
@@ -7616,7 +7697,7 @@
         <v>133</v>
       </c>
       <c r="I29" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
@@ -7646,7 +7727,7 @@
         <v>133</v>
       </c>
       <c r="I30" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
@@ -7676,7 +7757,7 @@
         <v>134</v>
       </c>
       <c r="I31" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
@@ -8032,7 +8113,7 @@
         <v>99</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
   </sheetData>
@@ -8070,10 +8151,10 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C1" t="s">
         <v>190</v>
@@ -8081,7 +8162,7 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B2">
         <f>5735*2.5</f>
@@ -8104,7 +8185,7 @@
   <sheetPr>
     <tabColor theme="9" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.140625" bestFit="1" customWidth="1"/>
@@ -8112,10 +8193,13 @@
     <col min="3" max="3" width="21.28515625" style="1" customWidth="1"/>
     <col min="4" max="4" width="30.140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="24.7109375" customWidth="1"/>
-    <col min="6" max="6" width="133.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.42578125" style="13" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="29" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="133.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>191</v>
       </c>
@@ -8125,19 +8209,28 @@
       <c r="C1" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="D1" t="s">
-        <v>200</v>
-      </c>
-      <c r="E1" t="s">
-        <v>198</v>
-      </c>
-      <c r="F1" t="s">
+      <c r="D1" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="F1" s="12" t="s">
+        <v>414</v>
+      </c>
+      <c r="G1" t="s">
+        <v>199</v>
+      </c>
+      <c r="H1" t="s">
+        <v>197</v>
+      </c>
+      <c r="I1" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>216</v>
+        <v>408</v>
       </c>
       <c r="B2" s="11" t="s">
         <v>70</v>
@@ -8146,19 +8239,28 @@
         <f>392*1.2/4900</f>
         <v>9.6000000000000002E-2</v>
       </c>
-      <c r="D2">
-        <v>130</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="D2" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="E2" s="1">
+        <v>392</v>
+      </c>
+      <c r="F2" s="12">
+        <v>4900</v>
+      </c>
+      <c r="G2">
+        <v>120</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>409</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>194</v>
       </c>
       <c r="B3" t="s">
         <v>71</v>
@@ -8166,17 +8268,27 @@
       <c r="C3" s="1">
         <v>0.12559999999999999</v>
       </c>
-      <c r="D3">
-        <v>225</v>
-      </c>
-      <c r="E3">
+      <c r="D3" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="E3" s="1">
+        <v>0.12559999999999999</v>
+      </c>
+      <c r="F3" s="12">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>140</v>
+      </c>
+      <c r="H3">
         <v>2</v>
       </c>
-      <c r="F3" t="s">
-        <v>228</v>
+      <c r="I3" t="s">
+        <v>226</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>

--- a/input.xlsx
+++ b/input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/25a393584c41f6f2/Documents/Mon Patrimoine/Projet Immobilier/2023 Terrasses de Galieni/09 - Copropriété/Site de calcul des charges de copropriété/streamlit-copro-charges/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1297" documentId="13_ncr:1_{471232EB-3AAB-4D08-BC1C-7B7CD1C1D853}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6C1FEAFF-C718-4A32-9732-4AE22D2C289D}"/>
+  <xr:revisionPtr revIDLastSave="1309" documentId="13_ncr:1_{471232EB-3AAB-4D08-BC1C-7B7CD1C1D853}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{20F1F1F2-522E-4F69-BF13-868435BCF306}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="639" uniqueCount="415">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="640" uniqueCount="416">
   <si>
     <t>Taxes</t>
   </si>
@@ -633,9 +633,6 @@
   </si>
   <si>
     <t>Terrasses de Gallieni</t>
-  </si>
-  <si>
-    <t>Ordre d'utilisation</t>
   </si>
   <si>
     <t>Contrat  P2, engagement sur 3 ans</t>
@@ -733,9 +730,6 @@
     <t>Le fonds travaux ALUR doit représenter 5% du budget provisionnel, mais les copropritété de résidence de moins de 5 ans en sont exemptés</t>
   </si>
   <si>
-    <t>Chaudière d'appoint au gaz 0,1256€ le kWh</t>
-  </si>
-  <si>
     <t>La facturation par Est Ensemble est progressive, gratuit jusqu'à 10m3, puis de 10 à 28 m³ = 1,1988 € HT / m³, de 28 à 86 m³ = 1,3320 € HT / m³, de 86 à 101 m³ = 1,3720 € HT / m³, de 101 à 131 m³ = 1,4200 € HT / m³, de 131 à 140 m³ = 1,4919 € HT / m³ et Plus de 140 m³ = 1,5366 € HT / m³. On rajoute la redevance (3,3€/m3) et la TVA (8%). Pour référence la consommation moyenne d'eau d'un adulte sur 1 an est de 55 m3.</t>
   </si>
   <si>
@@ -1298,6 +1292,15 @@
   </si>
   <si>
     <t>kWh par unité</t>
+  </si>
+  <si>
+    <t>Chaudière d'appoint au gaz à condensation 0,1256€ le kWh</t>
+  </si>
+  <si>
+    <t>Seuil de durée d'activation (mn)</t>
+  </si>
+  <si>
+    <t>Seuil de fonctionnement (%)</t>
   </si>
 </sst>
 </file>
@@ -1389,7 +1392,7 @@
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -1397,61 +1400,6 @@
     <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
   <dxfs count="30">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -1802,6 +1750,61 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1816,10 +1819,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{13C2BCD2-5CEA-4301-A571-688E40226767}" name="Provisions" displayName="Provisions" ref="A1:F35">
   <autoFilter ref="A1:F35" xr:uid="{13C2BCD2-5CEA-4301-A571-688E40226767}"/>
@@ -1831,8 +1830,8 @@
     <tableColumn id="4" xr3:uid="{84F1F30D-4827-43F2-8865-B7957E3E712D}" name="ID"/>
     <tableColumn id="7" xr3:uid="{512EABBD-B863-4251-833D-8B8D1F1626EF}" name="Description"/>
     <tableColumn id="2" xr3:uid="{D09C4BB0-FEBD-4A72-9E87-B5258D8B62D7}" name="Label de la provision"/>
-    <tableColumn id="3" xr3:uid="{347751FB-EF14-4BD7-9D47-427E04136B77}" name="Provision" totalsRowFunction="sum" dataDxfId="28" totalsRowDxfId="27"/>
-    <tableColumn id="5" xr3:uid="{CA26B6F8-88AD-418A-B213-749ABA66E926}" name="Description longue" dataDxfId="26"/>
+    <tableColumn id="3" xr3:uid="{347751FB-EF14-4BD7-9D47-427E04136B77}" name="Provision" totalsRowFunction="sum" dataDxfId="25" totalsRowDxfId="24"/>
+    <tableColumn id="5" xr3:uid="{CA26B6F8-88AD-418A-B213-749ABA66E926}" name="Description longue" dataDxfId="23"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1845,24 +1844,24 @@
     <sortCondition ref="A1:A180"/>
   </sortState>
   <tableColumns count="16">
-    <tableColumn id="3" xr3:uid="{1687C042-C916-4161-82C2-2A915364FCD2}" name="Numéro de lot" dataDxfId="25"/>
+    <tableColumn id="3" xr3:uid="{1687C042-C916-4161-82C2-2A915364FCD2}" name="Numéro de lot" dataDxfId="22"/>
     <tableColumn id="1" xr3:uid="{788DBA8C-5B77-4079-8161-FA45C58518AE}" name="Description"/>
-    <tableColumn id="2" xr3:uid="{BE5ACA99-AEAF-4E51-BE0A-B3FB8FCCF08B}" name="Tantièmes copropriété" dataDxfId="24">
+    <tableColumn id="2" xr3:uid="{BE5ACA99-AEAF-4E51-BE0A-B3FB8FCCF08B}" name="Tantièmes copropriété" dataDxfId="21">
       <calculatedColumnFormula>7/10000</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{D62FAA89-C46E-4AF6-A14F-7FD6F46E7F00}" name="Tantièmes ascenseur 1-1" dataDxfId="23"/>
-    <tableColumn id="9" xr3:uid="{C3B9BDED-CB2A-4305-9CBF-418F5971AC1E}" name="Tantièmes ascenseur 1-2" dataDxfId="22"/>
-    <tableColumn id="10" xr3:uid="{C2291DE1-C707-4F83-846E-F914B4B42E52}" name="Tantièmes ascenseur 2" dataDxfId="21"/>
-    <tableColumn id="11" xr3:uid="{4F70F08A-4C2F-41B0-88EB-711B1A0760CD}" name="Tantièmes ascenseur 3" dataDxfId="20"/>
-    <tableColumn id="14" xr3:uid="{80D23396-716C-46AC-9B55-BCBC6C981351}" name="Tantièmes chauffage" dataDxfId="19"/>
-    <tableColumn id="15" xr3:uid="{E3955139-B619-4DD0-8FC1-ECA97048DFE4}" name="Tantièmes Batiment 1" dataDxfId="18"/>
-    <tableColumn id="16" xr3:uid="{C73E9407-A858-4EF7-81C2-6C70C4B157A2}" name="Tantièmes Batiment 2" dataDxfId="17"/>
-    <tableColumn id="17" xr3:uid="{A07338CA-0096-4091-89B2-A46FF2D323C2}" name="Tantièmes Batiment 3" dataDxfId="16"/>
-    <tableColumn id="18" xr3:uid="{7A3012D8-2375-4F10-9E84-F2F5060C6A99}" name="Tantièmes Hall 1-1" dataDxfId="15"/>
-    <tableColumn id="19" xr3:uid="{67961B6E-B577-4A49-B099-623FB85519B4}" name="Tantièmes Hall 1-2" dataDxfId="14"/>
-    <tableColumn id="20" xr3:uid="{03C201C1-F8AA-4D3C-AEBC-425B180BC2D7}" name="Tantièmes Hall 2" dataDxfId="13"/>
-    <tableColumn id="21" xr3:uid="{4826FC05-81A9-4020-8D1D-83D3D5C5A05A}" name="Tantièmes Logement/Stationnements" dataDxfId="12"/>
-    <tableColumn id="6" xr3:uid="{7B87787E-3595-42D5-B815-AF76B67432D8}" name="Tantièmes Stationnement" dataDxfId="11"/>
+    <tableColumn id="8" xr3:uid="{D62FAA89-C46E-4AF6-A14F-7FD6F46E7F00}" name="Tantièmes ascenseur 1-1" dataDxfId="20"/>
+    <tableColumn id="9" xr3:uid="{C3B9BDED-CB2A-4305-9CBF-418F5971AC1E}" name="Tantièmes ascenseur 1-2" dataDxfId="19"/>
+    <tableColumn id="10" xr3:uid="{C2291DE1-C707-4F83-846E-F914B4B42E52}" name="Tantièmes ascenseur 2" dataDxfId="18"/>
+    <tableColumn id="11" xr3:uid="{4F70F08A-4C2F-41B0-88EB-711B1A0760CD}" name="Tantièmes ascenseur 3" dataDxfId="17"/>
+    <tableColumn id="14" xr3:uid="{80D23396-716C-46AC-9B55-BCBC6C981351}" name="Tantièmes chauffage" dataDxfId="16"/>
+    <tableColumn id="15" xr3:uid="{E3955139-B619-4DD0-8FC1-ECA97048DFE4}" name="Tantièmes Batiment 1" dataDxfId="15"/>
+    <tableColumn id="16" xr3:uid="{C73E9407-A858-4EF7-81C2-6C70C4B157A2}" name="Tantièmes Batiment 2" dataDxfId="14"/>
+    <tableColumn id="17" xr3:uid="{A07338CA-0096-4091-89B2-A46FF2D323C2}" name="Tantièmes Batiment 3" dataDxfId="13"/>
+    <tableColumn id="18" xr3:uid="{7A3012D8-2375-4F10-9E84-F2F5060C6A99}" name="Tantièmes Hall 1-1" dataDxfId="12"/>
+    <tableColumn id="19" xr3:uid="{67961B6E-B577-4A49-B099-623FB85519B4}" name="Tantièmes Hall 1-2" dataDxfId="11"/>
+    <tableColumn id="20" xr3:uid="{03C201C1-F8AA-4D3C-AEBC-425B180BC2D7}" name="Tantièmes Hall 2" dataDxfId="10"/>
+    <tableColumn id="21" xr3:uid="{4826FC05-81A9-4020-8D1D-83D3D5C5A05A}" name="Tantièmes Logement/Stationnements" dataDxfId="9"/>
+    <tableColumn id="6" xr3:uid="{7B87787E-3595-42D5-B815-AF76B67432D8}" name="Tantièmes Stationnement" dataDxfId="8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1875,17 +1874,17 @@
     <sortCondition ref="B1:B45"/>
   </sortState>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{7753A616-C6B5-4B02-AE3F-2A95253630B8}" name="Type de prestation" dataDxfId="10"/>
-    <tableColumn id="2" xr3:uid="{D7B6EA29-CA0A-4C24-9A81-3DF01785BD0C}" name="Label de la prestation" dataDxfId="9"/>
-    <tableColumn id="8" xr3:uid="{91FE62B8-BF79-4277-91C2-4B3C13901105}" name="ID prestation" dataDxfId="8"/>
+    <tableColumn id="1" xr3:uid="{7753A616-C6B5-4B02-AE3F-2A95253630B8}" name="Type de prestation" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{D7B6EA29-CA0A-4C24-9A81-3DF01785BD0C}" name="Label de la prestation" dataDxfId="6"/>
+    <tableColumn id="8" xr3:uid="{91FE62B8-BF79-4277-91C2-4B3C13901105}" name="ID prestation" dataDxfId="5"/>
     <tableColumn id="3" xr3:uid="{2ADF6FF1-1416-43FA-A9BF-E696654CC8CD}" name="Prestataire"/>
-    <tableColumn id="4" xr3:uid="{1C295B62-0191-41FA-9660-5BADE532BEE7}" name="Cout" dataDxfId="7"/>
-    <tableColumn id="5" xr3:uid="{1E3C456B-12BB-4B06-B366-57CE3DA87819}" name="Taxes" dataDxfId="6"/>
-    <tableColumn id="6" xr3:uid="{20997A37-E6E3-4308-9ACD-8D77B289D813}" name="Total TTC" dataDxfId="5">
+    <tableColumn id="4" xr3:uid="{1C295B62-0191-41FA-9660-5BADE532BEE7}" name="Cout" dataDxfId="4"/>
+    <tableColumn id="5" xr3:uid="{1E3C456B-12BB-4B06-B366-57CE3DA87819}" name="Taxes" dataDxfId="3"/>
+    <tableColumn id="6" xr3:uid="{20997A37-E6E3-4308-9ACD-8D77B289D813}" name="Total TTC" dataDxfId="2">
       <calculatedColumnFormula>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{6BDB0ED6-23A7-4E1A-A654-9E18B0DA38B5}" name="Description" dataDxfId="4"/>
-    <tableColumn id="9" xr3:uid="{C919E254-DE7F-4D3B-8CF6-79E643BBF97F}" name="Prestation choisie actuellement" dataDxfId="3"/>
+    <tableColumn id="7" xr3:uid="{6BDB0ED6-23A7-4E1A-A654-9E18B0DA38B5}" name="Description" dataDxfId="1"/>
+    <tableColumn id="9" xr3:uid="{C919E254-DE7F-4D3B-8CF6-79E643BBF97F}" name="Prestation choisie actuellement" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1906,18 +1905,19 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{587622F4-20CE-4A1D-A4F7-C9DCD51AF751}" name="Chauffage" displayName="Chauffage" ref="A1:I3" totalsRowShown="0">
-  <autoFilter ref="A1:I3" xr:uid="{587622F4-20CE-4A1D-A4F7-C9DCD51AF751}"/>
-  <tableColumns count="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{587622F4-20CE-4A1D-A4F7-C9DCD51AF751}" name="Chauffage" displayName="Chauffage" ref="A1:J3" totalsRowShown="0">
+  <autoFilter ref="A1:J3" xr:uid="{587622F4-20CE-4A1D-A4F7-C9DCD51AF751}"/>
+  <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{455C30A6-2C19-4BD7-B8A4-D1C6252917DD}" name="Type de chaudière"/>
     <tableColumn id="2" xr3:uid="{FAAC8507-DC80-422C-8508-496178C23374}" name="ID poste de provision"/>
     <tableColumn id="3" xr3:uid="{17764D71-05D7-4B37-8536-4004CBBE2CD4}" name="Prix unitaire du kWh" dataDxfId="29" dataCellStyle="Currency"/>
-    <tableColumn id="7" xr3:uid="{39B6FB9A-9DCB-412D-8CBD-94E321E39A50}" name="Unité" dataDxfId="2" dataCellStyle="Currency"/>
-    <tableColumn id="8" xr3:uid="{C769AD0E-5A43-462D-8737-CE59FA9E9F57}" name="Prix de l'unité" dataDxfId="1" dataCellStyle="Currency"/>
-    <tableColumn id="9" xr3:uid="{C32F2A17-C994-4DCC-A33C-2604586EDB4F}" name="kWh par unité" dataDxfId="0" dataCellStyle="Currency"/>
+    <tableColumn id="7" xr3:uid="{39B6FB9A-9DCB-412D-8CBD-94E321E39A50}" name="Unité" dataDxfId="28" dataCellStyle="Currency"/>
+    <tableColumn id="8" xr3:uid="{C769AD0E-5A43-462D-8737-CE59FA9E9F57}" name="Prix de l'unité" dataDxfId="27" dataCellStyle="Currency"/>
+    <tableColumn id="9" xr3:uid="{C32F2A17-C994-4DCC-A33C-2604586EDB4F}" name="kWh par unité" dataDxfId="26" dataCellStyle="Currency"/>
     <tableColumn id="4" xr3:uid="{FECEDA0B-3F17-4D04-AB3F-B1B848AA5DB2}" name="Production maximum en kW"/>
-    <tableColumn id="5" xr3:uid="{ED1B8FB3-6899-430D-BDC7-A9BDBA679526}" name="Ordre d'utilisation"/>
     <tableColumn id="6" xr3:uid="{F8EB0843-7F05-427F-9B41-0852730F32C9}" name="Description"/>
+    <tableColumn id="10" xr3:uid="{9F9F9E98-6D66-4867-A354-22539BFC6A70}" name="Seuil de fonctionnement (%)"/>
+    <tableColumn id="11" xr3:uid="{D0B5F61C-1D85-4C5E-A117-B774F88FE50E}" name="Seuil de durée d'activation (mn)"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2217,7 +2217,7 @@
         <v>95</v>
       </c>
       <c r="F1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="45" x14ac:dyDescent="0.25">
@@ -2225,7 +2225,7 @@
         <v>145</v>
       </c>
       <c r="B2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C2" t="s">
         <v>29</v>
@@ -2237,7 +2237,7 @@
         <v>35000</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -2257,7 +2257,7 @@
         <v>27000</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -2475,7 +2475,7 @@
         <v>2000</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -2531,7 +2531,7 @@
         <v>1050</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -2551,7 +2551,7 @@
         <v>1000</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -2571,7 +2571,7 @@
         <v>1000</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="75" x14ac:dyDescent="0.25">
@@ -2591,7 +2591,7 @@
         <v>920</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="135" x14ac:dyDescent="0.25">
@@ -2611,7 +2611,7 @@
         <v>900</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -2649,7 +2649,7 @@
         <v>750</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -2687,7 +2687,7 @@
         <v>580</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -2725,7 +2725,7 @@
         <v>450</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="60" x14ac:dyDescent="0.25">
@@ -2745,7 +2745,7 @@
         <v>360</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="45" x14ac:dyDescent="0.25">
@@ -2765,7 +2765,7 @@
         <v>320</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="60" x14ac:dyDescent="0.25">
@@ -2785,7 +2785,7 @@
         <v>240</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -2823,7 +2823,7 @@
         <v>90</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -2847,16 +2847,16 @@
         <v>145</v>
       </c>
       <c r="B35" t="s">
+        <v>222</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="D35" t="s">
         <v>223</v>
       </c>
-      <c r="C35" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="D35" t="s">
+      <c r="F35" s="2" t="s">
         <v>224</v>
-      </c>
-      <c r="F35" s="2" t="s">
-        <v>225</v>
       </c>
     </row>
   </sheetData>
@@ -2943,7 +2943,7 @@
         <v>101</v>
       </c>
       <c r="B2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C2">
         <v>462</v>
@@ -2957,7 +2957,7 @@
         <v>102</v>
       </c>
       <c r="B3" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C3">
         <v>119</v>
@@ -2983,7 +2983,7 @@
         <v>103</v>
       </c>
       <c r="B4" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C4">
         <v>83</v>
@@ -3009,7 +3009,7 @@
         <v>104</v>
       </c>
       <c r="B5" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C5">
         <v>130</v>
@@ -3035,7 +3035,7 @@
         <v>105</v>
       </c>
       <c r="B6" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C6">
         <v>123</v>
@@ -3061,7 +3061,7 @@
         <v>106</v>
       </c>
       <c r="B7" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C7">
         <v>122</v>
@@ -3087,7 +3087,7 @@
         <v>107</v>
       </c>
       <c r="B8" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C8">
         <v>55</v>
@@ -3113,7 +3113,7 @@
         <v>108</v>
       </c>
       <c r="B9" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C9">
         <v>96</v>
@@ -3139,7 +3139,7 @@
         <v>109</v>
       </c>
       <c r="B10" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C10">
         <v>123</v>
@@ -3165,7 +3165,7 @@
         <v>110</v>
       </c>
       <c r="B11" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C11">
         <v>129</v>
@@ -3191,7 +3191,7 @@
         <v>111</v>
       </c>
       <c r="B12" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C12">
         <v>58</v>
@@ -3217,7 +3217,7 @@
         <v>112</v>
       </c>
       <c r="B13" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C13">
         <v>91</v>
@@ -3243,7 +3243,7 @@
         <v>113</v>
       </c>
       <c r="B14" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C14" s="8">
         <v>86</v>
@@ -3277,7 +3277,7 @@
         <v>114</v>
       </c>
       <c r="B15" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C15">
         <v>94</v>
@@ -3303,7 +3303,7 @@
         <v>115</v>
       </c>
       <c r="B16" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C16">
         <v>60</v>
@@ -3329,7 +3329,7 @@
         <v>116</v>
       </c>
       <c r="B17" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C17">
         <v>162</v>
@@ -3355,7 +3355,7 @@
         <v>117</v>
       </c>
       <c r="B18" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C18">
         <v>202</v>
@@ -3381,7 +3381,7 @@
         <v>118</v>
       </c>
       <c r="B19" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C19">
         <v>294</v>
@@ -3407,7 +3407,7 @@
         <v>119</v>
       </c>
       <c r="B20" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C20">
         <v>81</v>
@@ -3433,7 +3433,7 @@
         <v>120</v>
       </c>
       <c r="B21" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C21">
         <v>115</v>
@@ -3459,7 +3459,7 @@
         <v>121</v>
       </c>
       <c r="B22" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C22">
         <v>112</v>
@@ -3485,7 +3485,7 @@
         <v>122</v>
       </c>
       <c r="B23" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C23">
         <v>83</v>
@@ -3511,7 +3511,7 @@
         <v>123</v>
       </c>
       <c r="B24" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C24">
         <v>118</v>
@@ -3537,7 +3537,7 @@
         <v>124</v>
       </c>
       <c r="B25" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="C25">
         <v>117</v>
@@ -3563,7 +3563,7 @@
         <v>125</v>
       </c>
       <c r="B26" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C26">
         <v>87</v>
@@ -3589,7 +3589,7 @@
         <v>126</v>
       </c>
       <c r="B27" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C27">
         <v>125</v>
@@ -3615,7 +3615,7 @@
         <v>127</v>
       </c>
       <c r="B28" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C28">
         <v>123</v>
@@ -3641,7 +3641,7 @@
         <v>128</v>
       </c>
       <c r="B29" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="C29">
         <v>88</v>
@@ -3667,7 +3667,7 @@
         <v>129</v>
       </c>
       <c r="B30" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="C30">
         <v>127</v>
@@ -3693,7 +3693,7 @@
         <v>130</v>
       </c>
       <c r="B31" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C31">
         <v>127</v>
@@ -3719,7 +3719,7 @@
         <v>132</v>
       </c>
       <c r="B32" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C32">
         <v>172</v>
@@ -3745,7 +3745,7 @@
         <v>133</v>
       </c>
       <c r="B33" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C33">
         <v>218</v>
@@ -3771,7 +3771,7 @@
         <v>134</v>
       </c>
       <c r="B34" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C34">
         <v>102</v>
@@ -3797,7 +3797,7 @@
         <v>135</v>
       </c>
       <c r="B35" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C35">
         <v>83</v>
@@ -3823,7 +3823,7 @@
         <v>201</v>
       </c>
       <c r="B36" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C36">
         <v>401</v>
@@ -3837,7 +3837,7 @@
         <v>202</v>
       </c>
       <c r="B37" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C37">
         <v>114</v>
@@ -3863,7 +3863,7 @@
         <v>203</v>
       </c>
       <c r="B38" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C38">
         <v>84</v>
@@ -3889,7 +3889,7 @@
         <v>204</v>
       </c>
       <c r="B39" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C39">
         <v>81</v>
@@ -3915,7 +3915,7 @@
         <v>205</v>
       </c>
       <c r="B40" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C40">
         <v>118</v>
@@ -3941,7 +3941,7 @@
         <v>206</v>
       </c>
       <c r="B41" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C41">
         <v>120</v>
@@ -3967,7 +3967,7 @@
         <v>207</v>
       </c>
       <c r="B42" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C42">
         <v>89</v>
@@ -3993,7 +3993,7 @@
         <v>208</v>
       </c>
       <c r="B43" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C43">
         <v>84</v>
@@ -4019,7 +4019,7 @@
         <v>209</v>
       </c>
       <c r="B44" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C44">
         <v>124</v>
@@ -4045,7 +4045,7 @@
         <v>210</v>
       </c>
       <c r="B45" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C45">
         <v>126</v>
@@ -4071,7 +4071,7 @@
         <v>211</v>
       </c>
       <c r="B46" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C46">
         <v>91</v>
@@ -4097,7 +4097,7 @@
         <v>212</v>
       </c>
       <c r="B47" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C47">
         <v>88</v>
@@ -4123,7 +4123,7 @@
         <v>213</v>
       </c>
       <c r="B48" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C48">
         <v>131</v>
@@ -4149,7 +4149,7 @@
         <v>214</v>
       </c>
       <c r="B49" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C49">
         <v>130</v>
@@ -4175,7 +4175,7 @@
         <v>215</v>
       </c>
       <c r="B50" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C50">
         <v>93</v>
@@ -4201,7 +4201,7 @@
         <v>216</v>
       </c>
       <c r="B51" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C51">
         <v>59</v>
@@ -4227,7 +4227,7 @@
         <v>217</v>
       </c>
       <c r="B52" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C52">
         <v>166</v>
@@ -4253,7 +4253,7 @@
         <v>218</v>
       </c>
       <c r="B53" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C53">
         <v>186</v>
@@ -4279,7 +4279,7 @@
         <v>219</v>
       </c>
       <c r="B54" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C54">
         <v>61</v>
@@ -4305,7 +4305,7 @@
         <v>220</v>
       </c>
       <c r="B55" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C55">
         <v>171</v>
@@ -4331,7 +4331,7 @@
         <v>221</v>
       </c>
       <c r="B56" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C56">
         <v>178</v>
@@ -4357,7 +4357,7 @@
         <v>222</v>
       </c>
       <c r="B57" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C57">
         <v>62</v>
@@ -4383,7 +4383,7 @@
         <v>223</v>
       </c>
       <c r="B58" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C58">
         <v>174</v>
@@ -4409,7 +4409,7 @@
         <v>224</v>
       </c>
       <c r="B59" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C59">
         <v>181</v>
@@ -4435,7 +4435,7 @@
         <v>225</v>
       </c>
       <c r="B60" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C60" s="8">
         <v>197</v>
@@ -4469,7 +4469,7 @@
         <v>301</v>
       </c>
       <c r="B61" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C61">
         <v>169</v>
@@ -4489,7 +4489,7 @@
         <v>302</v>
       </c>
       <c r="B62" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C62">
         <v>158</v>
@@ -4509,7 +4509,7 @@
         <v>303</v>
       </c>
       <c r="B63" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C63">
         <v>71</v>
@@ -4529,7 +4529,7 @@
         <v>305</v>
       </c>
       <c r="B64" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C64">
         <v>134</v>
@@ -4552,7 +4552,7 @@
         <v>306</v>
       </c>
       <c r="B65" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C65">
         <v>147</v>
@@ -4575,7 +4575,7 @@
         <v>307</v>
       </c>
       <c r="B66" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C66">
         <v>155</v>
@@ -4598,7 +4598,7 @@
         <v>308</v>
       </c>
       <c r="B67" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C67" s="8">
         <v>75</v>
@@ -4630,7 +4630,7 @@
         <v>310</v>
       </c>
       <c r="B68" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C68">
         <v>52</v>
@@ -4653,7 +4653,7 @@
         <v>311</v>
       </c>
       <c r="B69" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C69">
         <v>193</v>
@@ -4676,7 +4676,7 @@
         <v>312</v>
       </c>
       <c r="B70" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C70">
         <v>133</v>
@@ -4699,7 +4699,7 @@
         <v>313</v>
       </c>
       <c r="B71" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C71">
         <v>72</v>
@@ -4719,7 +4719,7 @@
         <v>314</v>
       </c>
       <c r="B72" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C72">
         <v>79</v>
@@ -4739,7 +4739,7 @@
         <v>315</v>
       </c>
       <c r="B73" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C73">
         <v>85</v>
@@ -4762,7 +4762,7 @@
         <v>316</v>
       </c>
       <c r="B74" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C74">
         <v>90</v>
@@ -4785,7 +4785,7 @@
         <v>401</v>
       </c>
       <c r="B75" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C75">
         <v>7</v>
@@ -4805,7 +4805,7 @@
         <v>402</v>
       </c>
       <c r="B76" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C76">
         <v>7</v>
@@ -4825,7 +4825,7 @@
         <v>403</v>
       </c>
       <c r="B77" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C77">
         <v>7</v>
@@ -4845,7 +4845,7 @@
         <v>404</v>
       </c>
       <c r="B78" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C78">
         <v>7</v>
@@ -4865,7 +4865,7 @@
         <v>405</v>
       </c>
       <c r="B79" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C79">
         <v>7</v>
@@ -4885,7 +4885,7 @@
         <v>406</v>
       </c>
       <c r="B80" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C80">
         <v>7</v>
@@ -4905,7 +4905,7 @@
         <v>407</v>
       </c>
       <c r="B81" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C81">
         <v>7</v>
@@ -4925,7 +4925,7 @@
         <v>408</v>
       </c>
       <c r="B82" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C82">
         <v>7</v>
@@ -4945,7 +4945,7 @@
         <v>409</v>
       </c>
       <c r="B83" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C83">
         <v>7</v>
@@ -4965,7 +4965,7 @@
         <v>410</v>
       </c>
       <c r="B84" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C84">
         <v>7</v>
@@ -4985,7 +4985,7 @@
         <v>411</v>
       </c>
       <c r="B85" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C85">
         <v>7</v>
@@ -5005,7 +5005,7 @@
         <v>412</v>
       </c>
       <c r="B86" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C86">
         <v>7</v>
@@ -5025,7 +5025,7 @@
         <v>413</v>
       </c>
       <c r="B87" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C87">
         <v>7</v>
@@ -5045,7 +5045,7 @@
         <v>414</v>
       </c>
       <c r="B88" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C88">
         <v>7</v>
@@ -5065,7 +5065,7 @@
         <v>415</v>
       </c>
       <c r="B89" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C89">
         <v>7</v>
@@ -5085,7 +5085,7 @@
         <v>416</v>
       </c>
       <c r="B90" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C90">
         <v>7</v>
@@ -5105,7 +5105,7 @@
         <v>417</v>
       </c>
       <c r="B91" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C91">
         <v>7</v>
@@ -5125,7 +5125,7 @@
         <v>418</v>
       </c>
       <c r="B92" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C92">
         <v>7</v>
@@ -5145,7 +5145,7 @@
         <v>419</v>
       </c>
       <c r="B93" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C93">
         <v>7</v>
@@ -5165,7 +5165,7 @@
         <v>420</v>
       </c>
       <c r="B94" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C94">
         <v>7</v>
@@ -5185,7 +5185,7 @@
         <v>421</v>
       </c>
       <c r="B95" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C95">
         <v>7</v>
@@ -5205,7 +5205,7 @@
         <v>422</v>
       </c>
       <c r="B96" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C96">
         <v>7</v>
@@ -5225,7 +5225,7 @@
         <v>423</v>
       </c>
       <c r="B97" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C97">
         <v>7</v>
@@ -5245,7 +5245,7 @@
         <v>424</v>
       </c>
       <c r="B98" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C98">
         <v>7</v>
@@ -5265,7 +5265,7 @@
         <v>425</v>
       </c>
       <c r="B99" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C99">
         <v>7</v>
@@ -5285,7 +5285,7 @@
         <v>426</v>
       </c>
       <c r="B100" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C100">
         <v>7</v>
@@ -5305,7 +5305,7 @@
         <v>427</v>
       </c>
       <c r="B101" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C101">
         <v>7</v>
@@ -5325,7 +5325,7 @@
         <v>428</v>
       </c>
       <c r="B102" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C102">
         <v>7</v>
@@ -5345,7 +5345,7 @@
         <v>429</v>
       </c>
       <c r="B103" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C103">
         <v>7</v>
@@ -5365,7 +5365,7 @@
         <v>430</v>
       </c>
       <c r="B104" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C104">
         <v>7</v>
@@ -5385,7 +5385,7 @@
         <v>431</v>
       </c>
       <c r="B105" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C105">
         <v>7</v>
@@ -5405,7 +5405,7 @@
         <v>432</v>
       </c>
       <c r="B106" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C106">
         <v>7</v>
@@ -5425,7 +5425,7 @@
         <v>433</v>
       </c>
       <c r="B107" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C107">
         <v>7</v>
@@ -5445,7 +5445,7 @@
         <v>434</v>
       </c>
       <c r="B108" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C108">
         <v>7</v>
@@ -5465,7 +5465,7 @@
         <v>435</v>
       </c>
       <c r="B109" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C109">
         <v>7</v>
@@ -5485,7 +5485,7 @@
         <v>436</v>
       </c>
       <c r="B110" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C110">
         <v>7</v>
@@ -5505,7 +5505,7 @@
         <v>437</v>
       </c>
       <c r="B111" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C111">
         <v>7</v>
@@ -5525,7 +5525,7 @@
         <v>438</v>
       </c>
       <c r="B112" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C112">
         <v>7</v>
@@ -5545,7 +5545,7 @@
         <v>439</v>
       </c>
       <c r="B113" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C113">
         <v>7</v>
@@ -5565,7 +5565,7 @@
         <v>440</v>
       </c>
       <c r="B114" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C114">
         <v>7</v>
@@ -5585,7 +5585,7 @@
         <v>441</v>
       </c>
       <c r="B115" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C115">
         <v>7</v>
@@ -5605,7 +5605,7 @@
         <v>442</v>
       </c>
       <c r="B116" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C116">
         <v>7</v>
@@ -5625,7 +5625,7 @@
         <v>443</v>
       </c>
       <c r="B117" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C117">
         <v>7</v>
@@ -5645,7 +5645,7 @@
         <v>444</v>
       </c>
       <c r="B118" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C118">
         <v>7</v>
@@ -5665,7 +5665,7 @@
         <v>445</v>
       </c>
       <c r="B119" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C119">
         <v>7</v>
@@ -5685,7 +5685,7 @@
         <v>446</v>
       </c>
       <c r="B120" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C120">
         <v>7</v>
@@ -5705,7 +5705,7 @@
         <v>447</v>
       </c>
       <c r="B121" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C121">
         <v>7</v>
@@ -5725,7 +5725,7 @@
         <v>448</v>
       </c>
       <c r="B122" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C122">
         <v>7</v>
@@ -5745,7 +5745,7 @@
         <v>449</v>
       </c>
       <c r="B123" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C123">
         <v>7</v>
@@ -5765,7 +5765,7 @@
         <v>450</v>
       </c>
       <c r="B124" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C124">
         <v>7</v>
@@ -5785,7 +5785,7 @@
         <v>451</v>
       </c>
       <c r="B125" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C125">
         <v>7</v>
@@ -5805,7 +5805,7 @@
         <v>452</v>
       </c>
       <c r="B126" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C126">
         <v>7</v>
@@ -5825,7 +5825,7 @@
         <v>453</v>
       </c>
       <c r="B127" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C127">
         <v>7</v>
@@ -5845,7 +5845,7 @@
         <v>454</v>
       </c>
       <c r="B128" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C128">
         <v>7</v>
@@ -5865,7 +5865,7 @@
         <v>455</v>
       </c>
       <c r="B129" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C129">
         <v>7</v>
@@ -5885,7 +5885,7 @@
         <v>456</v>
       </c>
       <c r="B130" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C130">
         <v>7</v>
@@ -5905,7 +5905,7 @@
         <v>457</v>
       </c>
       <c r="B131" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C131">
         <v>7</v>
@@ -5925,7 +5925,7 @@
         <v>458</v>
       </c>
       <c r="B132" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C132">
         <v>7</v>
@@ -5945,7 +5945,7 @@
         <v>459</v>
       </c>
       <c r="B133" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C133">
         <v>7</v>
@@ -5965,7 +5965,7 @@
         <v>460</v>
       </c>
       <c r="B134" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C134">
         <v>7</v>
@@ -5985,7 +5985,7 @@
         <v>461</v>
       </c>
       <c r="B135" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C135">
         <v>7</v>
@@ -6005,7 +6005,7 @@
         <v>462</v>
       </c>
       <c r="B136" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C136">
         <v>7</v>
@@ -6025,7 +6025,7 @@
         <v>463</v>
       </c>
       <c r="B137" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C137">
         <v>7</v>
@@ -6045,7 +6045,7 @@
         <v>464</v>
       </c>
       <c r="B138" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C138">
         <v>7</v>
@@ -6065,7 +6065,7 @@
         <v>465</v>
       </c>
       <c r="B139" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C139">
         <v>7</v>
@@ -6085,7 +6085,7 @@
         <v>466</v>
       </c>
       <c r="B140" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C140">
         <v>7</v>
@@ -6105,7 +6105,7 @@
         <v>467</v>
       </c>
       <c r="B141" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C141">
         <v>7</v>
@@ -6125,7 +6125,7 @@
         <v>468</v>
       </c>
       <c r="B142" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C142">
         <v>7</v>
@@ -6145,7 +6145,7 @@
         <v>469</v>
       </c>
       <c r="B143" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C143">
         <v>7</v>
@@ -6165,7 +6165,7 @@
         <v>470</v>
       </c>
       <c r="B144" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C144">
         <v>7</v>
@@ -6185,7 +6185,7 @@
         <v>471</v>
       </c>
       <c r="B145" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C145">
         <v>7</v>
@@ -6205,7 +6205,7 @@
         <v>472</v>
       </c>
       <c r="B146" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C146">
         <v>7</v>
@@ -6225,7 +6225,7 @@
         <v>473</v>
       </c>
       <c r="B147" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C147">
         <v>7</v>
@@ -6245,7 +6245,7 @@
         <v>474</v>
       </c>
       <c r="B148" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C148">
         <v>7</v>
@@ -6265,7 +6265,7 @@
         <v>475</v>
       </c>
       <c r="B149" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C149">
         <v>7</v>
@@ -6285,7 +6285,7 @@
         <v>476</v>
       </c>
       <c r="B150" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C150">
         <v>7</v>
@@ -6305,7 +6305,7 @@
         <v>477</v>
       </c>
       <c r="B151" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C151">
         <v>7</v>
@@ -6325,7 +6325,7 @@
         <v>478</v>
       </c>
       <c r="B152" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C152">
         <v>7</v>
@@ -6345,7 +6345,7 @@
         <v>479</v>
       </c>
       <c r="B153" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C153">
         <v>7</v>
@@ -6365,7 +6365,7 @@
         <v>480</v>
       </c>
       <c r="B154" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C154">
         <v>7</v>
@@ -6385,7 +6385,7 @@
         <v>481</v>
       </c>
       <c r="B155" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C155">
         <v>7</v>
@@ -6405,7 +6405,7 @@
         <v>482</v>
       </c>
       <c r="B156" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C156">
         <v>7</v>
@@ -6425,7 +6425,7 @@
         <v>483</v>
       </c>
       <c r="B157" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C157">
         <v>7</v>
@@ -6445,7 +6445,7 @@
         <v>484</v>
       </c>
       <c r="B158" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C158">
         <v>7</v>
@@ -6465,7 +6465,7 @@
         <v>485</v>
       </c>
       <c r="B159" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C159">
         <v>7</v>
@@ -6485,7 +6485,7 @@
         <v>486</v>
       </c>
       <c r="B160" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C160">
         <v>7</v>
@@ -6505,7 +6505,7 @@
         <v>487</v>
       </c>
       <c r="B161" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C161">
         <v>7</v>
@@ -6525,7 +6525,7 @@
         <v>488</v>
       </c>
       <c r="B162" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C162">
         <v>7</v>
@@ -6545,7 +6545,7 @@
         <v>489</v>
       </c>
       <c r="B163" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C163">
         <v>7</v>
@@ -6565,7 +6565,7 @@
         <v>490</v>
       </c>
       <c r="B164" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C164">
         <v>7</v>
@@ -6585,7 +6585,7 @@
         <v>491</v>
       </c>
       <c r="B165" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C165">
         <v>7</v>
@@ -6605,7 +6605,7 @@
         <v>492</v>
       </c>
       <c r="B166" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C166">
         <v>7</v>
@@ -6625,7 +6625,7 @@
         <v>493</v>
       </c>
       <c r="B167" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C167">
         <v>7</v>
@@ -6645,7 +6645,7 @@
         <v>494</v>
       </c>
       <c r="B168" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C168">
         <v>7</v>
@@ -6665,7 +6665,7 @@
         <v>495</v>
       </c>
       <c r="B169" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C169">
         <v>7</v>
@@ -6685,7 +6685,7 @@
         <v>496</v>
       </c>
       <c r="B170" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C170">
         <v>7</v>
@@ -6705,7 +6705,7 @@
         <v>497</v>
       </c>
       <c r="B171" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="C171">
         <v>7</v>
@@ -6725,7 +6725,7 @@
         <v>498</v>
       </c>
       <c r="B172" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C172">
         <v>7</v>
@@ -6745,7 +6745,7 @@
         <v>499</v>
       </c>
       <c r="B173" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C173">
         <v>7</v>
@@ -6765,7 +6765,7 @@
         <v>500</v>
       </c>
       <c r="B174" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C174">
         <v>7</v>
@@ -6785,7 +6785,7 @@
         <v>501</v>
       </c>
       <c r="B175" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C175">
         <v>7</v>
@@ -6805,7 +6805,7 @@
         <v>502</v>
       </c>
       <c r="B176" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C176">
         <v>1</v>
@@ -6823,7 +6823,7 @@
         <v>503</v>
       </c>
       <c r="B177" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C177">
         <v>1</v>
@@ -6841,7 +6841,7 @@
         <v>504</v>
       </c>
       <c r="B178" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="C178">
         <v>1</v>
@@ -6859,7 +6859,7 @@
         <v>505</v>
       </c>
       <c r="B179" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C179">
         <v>1</v>
@@ -6877,7 +6877,7 @@
         <v>506</v>
       </c>
       <c r="B180" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C180">
         <v>7</v>
@@ -6945,7 +6945,7 @@
         <v>136</v>
       </c>
       <c r="I1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="45" x14ac:dyDescent="0.25">
@@ -7278,7 +7278,7 @@
         <v>91</v>
       </c>
       <c r="I14" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -7308,7 +7308,7 @@
         <v>100</v>
       </c>
       <c r="I15" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
@@ -7363,7 +7363,7 @@
         <v>16750</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -7371,7 +7371,7 @@
         <v>20</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C18" t="s">
         <v>72</v>
@@ -7526,7 +7526,7 @@
         <v>103</v>
       </c>
       <c r="I23" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="60" x14ac:dyDescent="0.25">
@@ -7615,13 +7615,13 @@
         <v>18</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C27" t="s">
         <v>73</v>
       </c>
       <c r="D27" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E27" s="4">
         <v>434.5</v>
@@ -7634,10 +7634,10 @@
         <v>434.5</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
@@ -7667,7 +7667,7 @@
         <v>133</v>
       </c>
       <c r="I28" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
@@ -7697,7 +7697,7 @@
         <v>133</v>
       </c>
       <c r="I29" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
@@ -7727,7 +7727,7 @@
         <v>133</v>
       </c>
       <c r="I30" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
@@ -7757,7 +7757,7 @@
         <v>134</v>
       </c>
       <c r="I31" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
@@ -8113,7 +8113,7 @@
         <v>99</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
   </sheetData>
@@ -8185,7 +8185,7 @@
   <sheetPr>
     <tabColor theme="9" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.140625" bestFit="1" customWidth="1"/>
@@ -8193,13 +8193,14 @@
     <col min="3" max="3" width="21.28515625" style="1" customWidth="1"/>
     <col min="4" max="4" width="30.140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="24.7109375" customWidth="1"/>
-    <col min="6" max="6" width="17.42578125" style="13" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.42578125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="29" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="133.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="133.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="36.7109375" customWidth="1"/>
+    <col min="10" max="10" width="27" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>191</v>
       </c>
@@ -8210,27 +8211,30 @@
         <v>193</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="F1" s="12" t="s">
+        <v>412</v>
+      </c>
+      <c r="G1" t="s">
+        <v>198</v>
+      </c>
+      <c r="H1" t="s">
+        <v>136</v>
+      </c>
+      <c r="I1" t="s">
+        <v>415</v>
+      </c>
+      <c r="J1" t="s">
         <v>414</v>
       </c>
-      <c r="G1" t="s">
-        <v>199</v>
-      </c>
-      <c r="H1" t="s">
-        <v>197</v>
-      </c>
-      <c r="I1" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="B2" s="11" t="s">
         <v>70</v>
@@ -8240,7 +8244,7 @@
         <v>9.6000000000000002E-2</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="E2" s="1">
         <v>392</v>
@@ -8251,16 +8255,19 @@
       <c r="G2">
         <v>120</v>
       </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="I2" t="s">
+      <c r="H2" t="s">
+        <v>405</v>
+      </c>
+      <c r="I2" s="13">
+        <v>0.3</v>
+      </c>
+      <c r="J2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>407</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>409</v>
       </c>
       <c r="B3" t="s">
         <v>71</v>
@@ -8269,7 +8276,7 @@
         <v>0.12559999999999999</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="E3" s="1">
         <v>0.12559999999999999</v>
@@ -8280,18 +8287,22 @@
       <c r="G3">
         <v>140</v>
       </c>
-      <c r="H3">
-        <v>2</v>
-      </c>
-      <c r="I3" t="s">
-        <v>226</v>
+      <c r="H3" t="s">
+        <v>413</v>
+      </c>
+      <c r="I3" s="13">
+        <v>0.08</v>
+      </c>
+      <c r="J3">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
--- a/input.xlsx
+++ b/input.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/25a393584c41f6f2/Documents/Mon Patrimoine/Projet Immobilier/2023 Terrasses de Galieni/09 - Copropriété/Site de calcul des charges de copropriété/streamlit-copro-charges/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1309" documentId="13_ncr:1_{471232EB-3AAB-4D08-BC1C-7B7CD1C1D853}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{20F1F1F2-522E-4F69-BF13-868435BCF306}"/>
+  <xr:revisionPtr revIDLastSave="1315" documentId="13_ncr:1_{471232EB-3AAB-4D08-BC1C-7B7CD1C1D853}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AD65BE4F-F1BF-4F83-BAED-91D17FA905CE}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Provisions" sheetId="9" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="640" uniqueCount="416">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="592" uniqueCount="404">
   <si>
     <t>Taxes</t>
   </si>
@@ -551,30 +551,6 @@
     <t>Electricité du batiment 3</t>
   </si>
   <si>
-    <t>Fourniture de granulé de bois</t>
-  </si>
-  <si>
-    <t>Fourniture de gaz</t>
-  </si>
-  <si>
-    <t>Chaudière biomasse à pleine capacité</t>
-  </si>
-  <si>
-    <t>Appoint au gaz léger</t>
-  </si>
-  <si>
-    <t>Appoint au gaz pour augmenter la température</t>
-  </si>
-  <si>
-    <t>Appoint au gaz pour un hiver rude</t>
-  </si>
-  <si>
-    <t>Chaudière biomasse en fonctionnement partiel</t>
-  </si>
-  <si>
-    <t>Chaudière biomasse en fonctionnement normal</t>
-  </si>
-  <si>
     <t>Tantièmes ascenseur 3</t>
   </si>
   <si>
@@ -588,18 +564,6 @@
   </si>
   <si>
     <t>Syndic fourcette moyenne</t>
-  </si>
-  <si>
-    <t>2 - Consommation pour un hiver doux</t>
-  </si>
-  <si>
-    <t>1 - Consommation pour un hiver très doux</t>
-  </si>
-  <si>
-    <t>3 - Consommation pour un hiver normal</t>
-  </si>
-  <si>
-    <t>4 - Consommation pour un hiver rude</t>
   </si>
   <si>
     <t>Tantièmes Stationnement</t>
@@ -1285,9 +1249,6 @@
     <t>tonne de granulé</t>
   </si>
   <si>
-    <t>kWh</t>
-  </si>
-  <si>
     <t>Prix de l'unité</t>
   </si>
   <si>
@@ -1301,6 +1262,9 @@
   </si>
   <si>
     <t>Seuil de fonctionnement (%)</t>
+  </si>
+  <si>
+    <t>kWh de gaz</t>
   </si>
 </sst>
 </file>
@@ -1395,9 +1359,9 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="Currency" xfId="1" builtinId="4"/>
+    <cellStyle name="Monétaire" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="2" builtinId="5"/>
+    <cellStyle name="Pourcentage" xfId="2" builtinId="5"/>
   </cellStyles>
   <dxfs count="30">
     <dxf>
@@ -1819,6 +1783,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{13C2BCD2-5CEA-4301-A571-688E40226767}" name="Provisions" displayName="Provisions" ref="A1:F35">
   <autoFilter ref="A1:F35" xr:uid="{13C2BCD2-5CEA-4301-A571-688E40226767}"/>
@@ -1868,10 +1836,10 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{AFF80A4D-E18B-42B5-9271-DD654E188D32}" name="Prestations" displayName="Prestations" ref="A1:I45" totalsRowShown="0">
-  <autoFilter ref="A1:I45" xr:uid="{AFF80A4D-E18B-42B5-9271-DD654E188D32}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H45">
-    <sortCondition ref="B1:B45"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{AFF80A4D-E18B-42B5-9271-DD654E188D32}" name="Prestations" displayName="Prestations" ref="A1:I37" totalsRowShown="0">
+  <autoFilter ref="A1:I37" xr:uid="{AFF80A4D-E18B-42B5-9271-DD654E188D32}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H37">
+    <sortCondition ref="B1:B37"/>
   </sortState>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{7753A616-C6B5-4B02-AE3F-2A95253630B8}" name="Type de prestation" dataDxfId="7"/>
@@ -1910,10 +1878,10 @@
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{455C30A6-2C19-4BD7-B8A4-D1C6252917DD}" name="Type de chaudière"/>
     <tableColumn id="2" xr3:uid="{FAAC8507-DC80-422C-8508-496178C23374}" name="ID poste de provision"/>
-    <tableColumn id="3" xr3:uid="{17764D71-05D7-4B37-8536-4004CBBE2CD4}" name="Prix unitaire du kWh" dataDxfId="29" dataCellStyle="Currency"/>
-    <tableColumn id="7" xr3:uid="{39B6FB9A-9DCB-412D-8CBD-94E321E39A50}" name="Unité" dataDxfId="28" dataCellStyle="Currency"/>
-    <tableColumn id="8" xr3:uid="{C769AD0E-5A43-462D-8737-CE59FA9E9F57}" name="Prix de l'unité" dataDxfId="27" dataCellStyle="Currency"/>
-    <tableColumn id="9" xr3:uid="{C32F2A17-C994-4DCC-A33C-2604586EDB4F}" name="kWh par unité" dataDxfId="26" dataCellStyle="Currency"/>
+    <tableColumn id="3" xr3:uid="{17764D71-05D7-4B37-8536-4004CBBE2CD4}" name="Prix unitaire du kWh" dataDxfId="29"/>
+    <tableColumn id="7" xr3:uid="{39B6FB9A-9DCB-412D-8CBD-94E321E39A50}" name="Unité" dataDxfId="28"/>
+    <tableColumn id="8" xr3:uid="{C769AD0E-5A43-462D-8737-CE59FA9E9F57}" name="Prix de l'unité" dataDxfId="27"/>
+    <tableColumn id="9" xr3:uid="{C32F2A17-C994-4DCC-A33C-2604586EDB4F}" name="kWh par unité" dataDxfId="26"/>
     <tableColumn id="4" xr3:uid="{FECEDA0B-3F17-4D04-AB3F-B1B848AA5DB2}" name="Production maximum en kW"/>
     <tableColumn id="6" xr3:uid="{F8EB0843-7F05-427F-9B41-0852730F32C9}" name="Description"/>
     <tableColumn id="10" xr3:uid="{9F9F9E98-6D66-4867-A354-22539BFC6A70}" name="Seuil de fonctionnement (%)"/>
@@ -2190,7 +2158,7 @@
     <tabColor theme="9" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:F35"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.7109375" bestFit="1" customWidth="1"/>
@@ -2202,10 +2170,10 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>189</v>
+        <v>177</v>
       </c>
       <c r="B1" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="C1" t="s">
         <v>136</v>
@@ -2217,7 +2185,7 @@
         <v>95</v>
       </c>
       <c r="F1" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="45" x14ac:dyDescent="0.25">
@@ -2225,7 +2193,7 @@
         <v>145</v>
       </c>
       <c r="B2" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="C2" t="s">
         <v>29</v>
@@ -2237,7 +2205,7 @@
         <v>35000</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -2257,7 +2225,7 @@
         <v>27000</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -2442,7 +2410,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="B14" t="s">
         <v>88</v>
@@ -2475,7 +2443,7 @@
         <v>2000</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>217</v>
+        <v>205</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -2498,7 +2466,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="B17" t="s">
         <v>89</v>
@@ -2531,7 +2499,7 @@
         <v>1050</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -2551,7 +2519,7 @@
         <v>1000</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>218</v>
+        <v>206</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -2571,7 +2539,7 @@
         <v>1000</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>219</v>
+        <v>207</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="75" x14ac:dyDescent="0.25">
@@ -2591,7 +2559,7 @@
         <v>920</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>211</v>
+        <v>199</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="135" x14ac:dyDescent="0.25">
@@ -2611,7 +2579,7 @@
         <v>900</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -2649,7 +2617,7 @@
         <v>750</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -2687,7 +2655,7 @@
         <v>580</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -2710,7 +2678,7 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="B28" t="s">
         <v>73</v>
@@ -2725,12 +2693,12 @@
         <v>450</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="B29" t="s">
         <v>76</v>
@@ -2745,12 +2713,12 @@
         <v>360</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>209</v>
+        <v>197</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="B30" t="s">
         <v>75</v>
@@ -2765,7 +2733,7 @@
         <v>320</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>208</v>
+        <v>196</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="60" x14ac:dyDescent="0.25">
@@ -2785,7 +2753,7 @@
         <v>240</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>207</v>
+        <v>195</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -2808,7 +2776,7 @@
     </row>
     <row r="33" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="B33" t="s">
         <v>74</v>
@@ -2823,7 +2791,7 @@
         <v>90</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -2847,16 +2815,16 @@
         <v>145</v>
       </c>
       <c r="B35" t="s">
-        <v>222</v>
+        <v>210</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="D35" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>224</v>
+        <v>212</v>
       </c>
     </row>
   </sheetData>
@@ -2873,7 +2841,7 @@
     <tabColor theme="9" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:P180"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.28515625" style="8" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="54.85546875" bestFit="1" customWidth="1"/>
@@ -2908,7 +2876,7 @@
         <v>148</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="H1" s="8" t="s">
         <v>149</v>
@@ -2935,7 +2903,7 @@
         <v>156</v>
       </c>
       <c r="P1" s="8" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
@@ -2943,7 +2911,7 @@
         <v>101</v>
       </c>
       <c r="B2" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="C2">
         <v>462</v>
@@ -2957,7 +2925,7 @@
         <v>102</v>
       </c>
       <c r="B3" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="C3">
         <v>119</v>
@@ -2983,7 +2951,7 @@
         <v>103</v>
       </c>
       <c r="B4" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="C4">
         <v>83</v>
@@ -3009,7 +2977,7 @@
         <v>104</v>
       </c>
       <c r="B5" t="s">
-        <v>228</v>
+        <v>216</v>
       </c>
       <c r="C5">
         <v>130</v>
@@ -3035,7 +3003,7 @@
         <v>105</v>
       </c>
       <c r="B6" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
       <c r="C6">
         <v>123</v>
@@ -3061,7 +3029,7 @@
         <v>106</v>
       </c>
       <c r="B7" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
       <c r="C7">
         <v>122</v>
@@ -3087,7 +3055,7 @@
         <v>107</v>
       </c>
       <c r="B8" t="s">
-        <v>231</v>
+        <v>219</v>
       </c>
       <c r="C8">
         <v>55</v>
@@ -3113,7 +3081,7 @@
         <v>108</v>
       </c>
       <c r="B9" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="C9">
         <v>96</v>
@@ -3139,7 +3107,7 @@
         <v>109</v>
       </c>
       <c r="B10" t="s">
-        <v>233</v>
+        <v>221</v>
       </c>
       <c r="C10">
         <v>123</v>
@@ -3165,7 +3133,7 @@
         <v>110</v>
       </c>
       <c r="B11" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="C11">
         <v>129</v>
@@ -3191,7 +3159,7 @@
         <v>111</v>
       </c>
       <c r="B12" t="s">
-        <v>235</v>
+        <v>223</v>
       </c>
       <c r="C12">
         <v>58</v>
@@ -3217,7 +3185,7 @@
         <v>112</v>
       </c>
       <c r="B13" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="C13">
         <v>91</v>
@@ -3243,7 +3211,7 @@
         <v>113</v>
       </c>
       <c r="B14" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="C14" s="8">
         <v>86</v>
@@ -3277,7 +3245,7 @@
         <v>114</v>
       </c>
       <c r="B15" t="s">
-        <v>238</v>
+        <v>226</v>
       </c>
       <c r="C15">
         <v>94</v>
@@ -3303,7 +3271,7 @@
         <v>115</v>
       </c>
       <c r="B16" t="s">
-        <v>239</v>
+        <v>227</v>
       </c>
       <c r="C16">
         <v>60</v>
@@ -3329,7 +3297,7 @@
         <v>116</v>
       </c>
       <c r="B17" t="s">
-        <v>240</v>
+        <v>228</v>
       </c>
       <c r="C17">
         <v>162</v>
@@ -3355,7 +3323,7 @@
         <v>117</v>
       </c>
       <c r="B18" t="s">
-        <v>241</v>
+        <v>229</v>
       </c>
       <c r="C18">
         <v>202</v>
@@ -3381,7 +3349,7 @@
         <v>118</v>
       </c>
       <c r="B19" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="C19">
         <v>294</v>
@@ -3407,7 +3375,7 @@
         <v>119</v>
       </c>
       <c r="B20" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="C20">
         <v>81</v>
@@ -3433,7 +3401,7 @@
         <v>120</v>
       </c>
       <c r="B21" t="s">
-        <v>393</v>
+        <v>381</v>
       </c>
       <c r="C21">
         <v>115</v>
@@ -3459,7 +3427,7 @@
         <v>121</v>
       </c>
       <c r="B22" t="s">
-        <v>394</v>
+        <v>382</v>
       </c>
       <c r="C22">
         <v>112</v>
@@ -3485,7 +3453,7 @@
         <v>122</v>
       </c>
       <c r="B23" t="s">
-        <v>395</v>
+        <v>383</v>
       </c>
       <c r="C23">
         <v>83</v>
@@ -3511,7 +3479,7 @@
         <v>123</v>
       </c>
       <c r="B24" t="s">
-        <v>396</v>
+        <v>384</v>
       </c>
       <c r="C24">
         <v>118</v>
@@ -3537,7 +3505,7 @@
         <v>124</v>
       </c>
       <c r="B25" t="s">
-        <v>397</v>
+        <v>385</v>
       </c>
       <c r="C25">
         <v>117</v>
@@ -3563,7 +3531,7 @@
         <v>125</v>
       </c>
       <c r="B26" t="s">
-        <v>398</v>
+        <v>386</v>
       </c>
       <c r="C26">
         <v>87</v>
@@ -3589,7 +3557,7 @@
         <v>126</v>
       </c>
       <c r="B27" t="s">
-        <v>399</v>
+        <v>387</v>
       </c>
       <c r="C27">
         <v>125</v>
@@ -3615,7 +3583,7 @@
         <v>127</v>
       </c>
       <c r="B28" t="s">
-        <v>400</v>
+        <v>388</v>
       </c>
       <c r="C28">
         <v>123</v>
@@ -3641,7 +3609,7 @@
         <v>128</v>
       </c>
       <c r="B29" t="s">
-        <v>401</v>
+        <v>389</v>
       </c>
       <c r="C29">
         <v>88</v>
@@ -3667,7 +3635,7 @@
         <v>129</v>
       </c>
       <c r="B30" t="s">
-        <v>403</v>
+        <v>391</v>
       </c>
       <c r="C30">
         <v>127</v>
@@ -3693,7 +3661,7 @@
         <v>130</v>
       </c>
       <c r="B31" t="s">
-        <v>402</v>
+        <v>390</v>
       </c>
       <c r="C31">
         <v>127</v>
@@ -3719,7 +3687,7 @@
         <v>132</v>
       </c>
       <c r="B32" t="s">
-        <v>404</v>
+        <v>392</v>
       </c>
       <c r="C32">
         <v>172</v>
@@ -3745,7 +3713,7 @@
         <v>133</v>
       </c>
       <c r="B33" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="C33">
         <v>218</v>
@@ -3771,7 +3739,7 @@
         <v>134</v>
       </c>
       <c r="B34" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
       <c r="C34">
         <v>102</v>
@@ -3797,7 +3765,7 @@
         <v>135</v>
       </c>
       <c r="B35" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="C35">
         <v>83</v>
@@ -3823,7 +3791,7 @@
         <v>201</v>
       </c>
       <c r="B36" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="C36">
         <v>401</v>
@@ -3837,7 +3805,7 @@
         <v>202</v>
       </c>
       <c r="B37" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="C37">
         <v>114</v>
@@ -3863,7 +3831,7 @@
         <v>203</v>
       </c>
       <c r="B38" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="C38">
         <v>84</v>
@@ -3889,7 +3857,7 @@
         <v>204</v>
       </c>
       <c r="B39" t="s">
-        <v>269</v>
+        <v>257</v>
       </c>
       <c r="C39">
         <v>81</v>
@@ -3915,7 +3883,7 @@
         <v>205</v>
       </c>
       <c r="B40" t="s">
-        <v>270</v>
+        <v>258</v>
       </c>
       <c r="C40">
         <v>118</v>
@@ -3941,7 +3909,7 @@
         <v>206</v>
       </c>
       <c r="B41" t="s">
-        <v>271</v>
+        <v>259</v>
       </c>
       <c r="C41">
         <v>120</v>
@@ -3967,7 +3935,7 @@
         <v>207</v>
       </c>
       <c r="B42" t="s">
-        <v>272</v>
+        <v>260</v>
       </c>
       <c r="C42">
         <v>89</v>
@@ -3993,7 +3961,7 @@
         <v>208</v>
       </c>
       <c r="B43" t="s">
-        <v>273</v>
+        <v>261</v>
       </c>
       <c r="C43">
         <v>84</v>
@@ -4019,7 +3987,7 @@
         <v>209</v>
       </c>
       <c r="B44" t="s">
-        <v>274</v>
+        <v>262</v>
       </c>
       <c r="C44">
         <v>124</v>
@@ -4045,7 +4013,7 @@
         <v>210</v>
       </c>
       <c r="B45" t="s">
-        <v>275</v>
+        <v>263</v>
       </c>
       <c r="C45">
         <v>126</v>
@@ -4071,7 +4039,7 @@
         <v>211</v>
       </c>
       <c r="B46" t="s">
-        <v>276</v>
+        <v>264</v>
       </c>
       <c r="C46">
         <v>91</v>
@@ -4097,7 +4065,7 @@
         <v>212</v>
       </c>
       <c r="B47" t="s">
-        <v>278</v>
+        <v>266</v>
       </c>
       <c r="C47">
         <v>88</v>
@@ -4123,7 +4091,7 @@
         <v>213</v>
       </c>
       <c r="B48" t="s">
-        <v>277</v>
+        <v>265</v>
       </c>
       <c r="C48">
         <v>131</v>
@@ -4149,7 +4117,7 @@
         <v>214</v>
       </c>
       <c r="B49" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="C49">
         <v>130</v>
@@ -4175,7 +4143,7 @@
         <v>215</v>
       </c>
       <c r="B50" t="s">
-        <v>280</v>
+        <v>268</v>
       </c>
       <c r="C50">
         <v>93</v>
@@ -4201,7 +4169,7 @@
         <v>216</v>
       </c>
       <c r="B51" t="s">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="C51">
         <v>59</v>
@@ -4227,7 +4195,7 @@
         <v>217</v>
       </c>
       <c r="B52" t="s">
-        <v>282</v>
+        <v>270</v>
       </c>
       <c r="C52">
         <v>166</v>
@@ -4253,7 +4221,7 @@
         <v>218</v>
       </c>
       <c r="B53" t="s">
-        <v>283</v>
+        <v>271</v>
       </c>
       <c r="C53">
         <v>186</v>
@@ -4279,7 +4247,7 @@
         <v>219</v>
       </c>
       <c r="B54" t="s">
-        <v>284</v>
+        <v>272</v>
       </c>
       <c r="C54">
         <v>61</v>
@@ -4305,7 +4273,7 @@
         <v>220</v>
       </c>
       <c r="B55" t="s">
-        <v>285</v>
+        <v>273</v>
       </c>
       <c r="C55">
         <v>171</v>
@@ -4331,7 +4299,7 @@
         <v>221</v>
       </c>
       <c r="B56" t="s">
-        <v>286</v>
+        <v>274</v>
       </c>
       <c r="C56">
         <v>178</v>
@@ -4357,7 +4325,7 @@
         <v>222</v>
       </c>
       <c r="B57" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="C57">
         <v>62</v>
@@ -4383,7 +4351,7 @@
         <v>223</v>
       </c>
       <c r="B58" t="s">
-        <v>264</v>
+        <v>252</v>
       </c>
       <c r="C58">
         <v>174</v>
@@ -4409,7 +4377,7 @@
         <v>224</v>
       </c>
       <c r="B59" t="s">
-        <v>265</v>
+        <v>253</v>
       </c>
       <c r="C59">
         <v>181</v>
@@ -4435,7 +4403,7 @@
         <v>225</v>
       </c>
       <c r="B60" t="s">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="C60" s="8">
         <v>197</v>
@@ -4469,7 +4437,7 @@
         <v>301</v>
       </c>
       <c r="B61" t="s">
-        <v>261</v>
+        <v>249</v>
       </c>
       <c r="C61">
         <v>169</v>
@@ -4489,7 +4457,7 @@
         <v>302</v>
       </c>
       <c r="B62" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="C62">
         <v>158</v>
@@ -4509,7 +4477,7 @@
         <v>303</v>
       </c>
       <c r="B63" t="s">
-        <v>260</v>
+        <v>248</v>
       </c>
       <c r="C63">
         <v>71</v>
@@ -4529,7 +4497,7 @@
         <v>305</v>
       </c>
       <c r="B64" t="s">
-        <v>259</v>
+        <v>247</v>
       </c>
       <c r="C64">
         <v>134</v>
@@ -4552,7 +4520,7 @@
         <v>306</v>
       </c>
       <c r="B65" t="s">
-        <v>258</v>
+        <v>246</v>
       </c>
       <c r="C65">
         <v>147</v>
@@ -4575,7 +4543,7 @@
         <v>307</v>
       </c>
       <c r="B66" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="C66">
         <v>155</v>
@@ -4598,7 +4566,7 @@
         <v>308</v>
       </c>
       <c r="B67" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="C67" s="8">
         <v>75</v>
@@ -4630,7 +4598,7 @@
         <v>310</v>
       </c>
       <c r="B68" t="s">
-        <v>255</v>
+        <v>243</v>
       </c>
       <c r="C68">
         <v>52</v>
@@ -4653,7 +4621,7 @@
         <v>311</v>
       </c>
       <c r="B69" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="C69">
         <v>193</v>
@@ -4676,7 +4644,7 @@
         <v>312</v>
       </c>
       <c r="B70" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="C70">
         <v>133</v>
@@ -4699,7 +4667,7 @@
         <v>313</v>
       </c>
       <c r="B71" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="C71">
         <v>72</v>
@@ -4719,7 +4687,7 @@
         <v>314</v>
       </c>
       <c r="B72" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="C72">
         <v>79</v>
@@ -4739,7 +4707,7 @@
         <v>315</v>
       </c>
       <c r="B73" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="C73">
         <v>85</v>
@@ -4762,7 +4730,7 @@
         <v>316</v>
       </c>
       <c r="B74" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="C74">
         <v>90</v>
@@ -4785,7 +4753,7 @@
         <v>401</v>
       </c>
       <c r="B75" t="s">
-        <v>299</v>
+        <v>287</v>
       </c>
       <c r="C75">
         <v>7</v>
@@ -4805,7 +4773,7 @@
         <v>402</v>
       </c>
       <c r="B76" t="s">
-        <v>300</v>
+        <v>288</v>
       </c>
       <c r="C76">
         <v>7</v>
@@ -4825,7 +4793,7 @@
         <v>403</v>
       </c>
       <c r="B77" t="s">
-        <v>301</v>
+        <v>289</v>
       </c>
       <c r="C77">
         <v>7</v>
@@ -4845,7 +4813,7 @@
         <v>404</v>
       </c>
       <c r="B78" t="s">
-        <v>302</v>
+        <v>290</v>
       </c>
       <c r="C78">
         <v>7</v>
@@ -4865,7 +4833,7 @@
         <v>405</v>
       </c>
       <c r="B79" t="s">
-        <v>303</v>
+        <v>291</v>
       </c>
       <c r="C79">
         <v>7</v>
@@ -4885,7 +4853,7 @@
         <v>406</v>
       </c>
       <c r="B80" t="s">
-        <v>304</v>
+        <v>292</v>
       </c>
       <c r="C80">
         <v>7</v>
@@ -4905,7 +4873,7 @@
         <v>407</v>
       </c>
       <c r="B81" t="s">
-        <v>305</v>
+        <v>293</v>
       </c>
       <c r="C81">
         <v>7</v>
@@ -4925,7 +4893,7 @@
         <v>408</v>
       </c>
       <c r="B82" t="s">
-        <v>306</v>
+        <v>294</v>
       </c>
       <c r="C82">
         <v>7</v>
@@ -4945,7 +4913,7 @@
         <v>409</v>
       </c>
       <c r="B83" t="s">
-        <v>307</v>
+        <v>295</v>
       </c>
       <c r="C83">
         <v>7</v>
@@ -4965,7 +4933,7 @@
         <v>410</v>
       </c>
       <c r="B84" t="s">
-        <v>308</v>
+        <v>296</v>
       </c>
       <c r="C84">
         <v>7</v>
@@ -4985,7 +4953,7 @@
         <v>411</v>
       </c>
       <c r="B85" t="s">
-        <v>309</v>
+        <v>297</v>
       </c>
       <c r="C85">
         <v>7</v>
@@ -5005,7 +4973,7 @@
         <v>412</v>
       </c>
       <c r="B86" t="s">
-        <v>287</v>
+        <v>275</v>
       </c>
       <c r="C86">
         <v>7</v>
@@ -5025,7 +4993,7 @@
         <v>413</v>
       </c>
       <c r="B87" t="s">
-        <v>310</v>
+        <v>298</v>
       </c>
       <c r="C87">
         <v>7</v>
@@ -5045,7 +5013,7 @@
         <v>414</v>
       </c>
       <c r="B88" t="s">
-        <v>311</v>
+        <v>299</v>
       </c>
       <c r="C88">
         <v>7</v>
@@ -5065,7 +5033,7 @@
         <v>415</v>
       </c>
       <c r="B89" t="s">
-        <v>312</v>
+        <v>300</v>
       </c>
       <c r="C89">
         <v>7</v>
@@ -5085,7 +5053,7 @@
         <v>416</v>
       </c>
       <c r="B90" t="s">
-        <v>313</v>
+        <v>301</v>
       </c>
       <c r="C90">
         <v>7</v>
@@ -5105,7 +5073,7 @@
         <v>417</v>
       </c>
       <c r="B91" t="s">
-        <v>314</v>
+        <v>302</v>
       </c>
       <c r="C91">
         <v>7</v>
@@ -5125,7 +5093,7 @@
         <v>418</v>
       </c>
       <c r="B92" t="s">
-        <v>315</v>
+        <v>303</v>
       </c>
       <c r="C92">
         <v>7</v>
@@ -5145,7 +5113,7 @@
         <v>419</v>
       </c>
       <c r="B93" t="s">
-        <v>316</v>
+        <v>304</v>
       </c>
       <c r="C93">
         <v>7</v>
@@ -5165,7 +5133,7 @@
         <v>420</v>
       </c>
       <c r="B94" t="s">
-        <v>317</v>
+        <v>305</v>
       </c>
       <c r="C94">
         <v>7</v>
@@ -5185,7 +5153,7 @@
         <v>421</v>
       </c>
       <c r="B95" t="s">
-        <v>318</v>
+        <v>306</v>
       </c>
       <c r="C95">
         <v>7</v>
@@ -5205,7 +5173,7 @@
         <v>422</v>
       </c>
       <c r="B96" t="s">
-        <v>319</v>
+        <v>307</v>
       </c>
       <c r="C96">
         <v>7</v>
@@ -5225,7 +5193,7 @@
         <v>423</v>
       </c>
       <c r="B97" t="s">
-        <v>320</v>
+        <v>308</v>
       </c>
       <c r="C97">
         <v>7</v>
@@ -5245,7 +5213,7 @@
         <v>424</v>
       </c>
       <c r="B98" t="s">
-        <v>321</v>
+        <v>309</v>
       </c>
       <c r="C98">
         <v>7</v>
@@ -5265,7 +5233,7 @@
         <v>425</v>
       </c>
       <c r="B99" t="s">
-        <v>322</v>
+        <v>310</v>
       </c>
       <c r="C99">
         <v>7</v>
@@ -5285,7 +5253,7 @@
         <v>426</v>
       </c>
       <c r="B100" t="s">
-        <v>323</v>
+        <v>311</v>
       </c>
       <c r="C100">
         <v>7</v>
@@ -5305,7 +5273,7 @@
         <v>427</v>
       </c>
       <c r="B101" t="s">
-        <v>324</v>
+        <v>312</v>
       </c>
       <c r="C101">
         <v>7</v>
@@ -5325,7 +5293,7 @@
         <v>428</v>
       </c>
       <c r="B102" t="s">
-        <v>325</v>
+        <v>313</v>
       </c>
       <c r="C102">
         <v>7</v>
@@ -5345,7 +5313,7 @@
         <v>429</v>
       </c>
       <c r="B103" t="s">
-        <v>326</v>
+        <v>314</v>
       </c>
       <c r="C103">
         <v>7</v>
@@ -5365,7 +5333,7 @@
         <v>430</v>
       </c>
       <c r="B104" t="s">
-        <v>327</v>
+        <v>315</v>
       </c>
       <c r="C104">
         <v>7</v>
@@ -5385,7 +5353,7 @@
         <v>431</v>
       </c>
       <c r="B105" t="s">
-        <v>328</v>
+        <v>316</v>
       </c>
       <c r="C105">
         <v>7</v>
@@ -5405,7 +5373,7 @@
         <v>432</v>
       </c>
       <c r="B106" t="s">
-        <v>329</v>
+        <v>317</v>
       </c>
       <c r="C106">
         <v>7</v>
@@ -5425,7 +5393,7 @@
         <v>433</v>
       </c>
       <c r="B107" t="s">
-        <v>330</v>
+        <v>318</v>
       </c>
       <c r="C107">
         <v>7</v>
@@ -5445,7 +5413,7 @@
         <v>434</v>
       </c>
       <c r="B108" t="s">
-        <v>331</v>
+        <v>319</v>
       </c>
       <c r="C108">
         <v>7</v>
@@ -5465,7 +5433,7 @@
         <v>435</v>
       </c>
       <c r="B109" t="s">
-        <v>332</v>
+        <v>320</v>
       </c>
       <c r="C109">
         <v>7</v>
@@ -5485,7 +5453,7 @@
         <v>436</v>
       </c>
       <c r="B110" t="s">
-        <v>333</v>
+        <v>321</v>
       </c>
       <c r="C110">
         <v>7</v>
@@ -5505,7 +5473,7 @@
         <v>437</v>
       </c>
       <c r="B111" t="s">
-        <v>334</v>
+        <v>322</v>
       </c>
       <c r="C111">
         <v>7</v>
@@ -5525,7 +5493,7 @@
         <v>438</v>
       </c>
       <c r="B112" t="s">
-        <v>335</v>
+        <v>323</v>
       </c>
       <c r="C112">
         <v>7</v>
@@ -5545,7 +5513,7 @@
         <v>439</v>
       </c>
       <c r="B113" t="s">
-        <v>336</v>
+        <v>324</v>
       </c>
       <c r="C113">
         <v>7</v>
@@ -5565,7 +5533,7 @@
         <v>440</v>
       </c>
       <c r="B114" t="s">
-        <v>337</v>
+        <v>325</v>
       </c>
       <c r="C114">
         <v>7</v>
@@ -5585,7 +5553,7 @@
         <v>441</v>
       </c>
       <c r="B115" t="s">
-        <v>338</v>
+        <v>326</v>
       </c>
       <c r="C115">
         <v>7</v>
@@ -5605,7 +5573,7 @@
         <v>442</v>
       </c>
       <c r="B116" t="s">
-        <v>339</v>
+        <v>327</v>
       </c>
       <c r="C116">
         <v>7</v>
@@ -5625,7 +5593,7 @@
         <v>443</v>
       </c>
       <c r="B117" t="s">
-        <v>340</v>
+        <v>328</v>
       </c>
       <c r="C117">
         <v>7</v>
@@ -5645,7 +5613,7 @@
         <v>444</v>
       </c>
       <c r="B118" t="s">
-        <v>341</v>
+        <v>329</v>
       </c>
       <c r="C118">
         <v>7</v>
@@ -5665,7 +5633,7 @@
         <v>445</v>
       </c>
       <c r="B119" t="s">
-        <v>342</v>
+        <v>330</v>
       </c>
       <c r="C119">
         <v>7</v>
@@ -5685,7 +5653,7 @@
         <v>446</v>
       </c>
       <c r="B120" t="s">
-        <v>343</v>
+        <v>331</v>
       </c>
       <c r="C120">
         <v>7</v>
@@ -5705,7 +5673,7 @@
         <v>447</v>
       </c>
       <c r="B121" t="s">
-        <v>344</v>
+        <v>332</v>
       </c>
       <c r="C121">
         <v>7</v>
@@ -5725,7 +5693,7 @@
         <v>448</v>
       </c>
       <c r="B122" t="s">
-        <v>345</v>
+        <v>333</v>
       </c>
       <c r="C122">
         <v>7</v>
@@ -5745,7 +5713,7 @@
         <v>449</v>
       </c>
       <c r="B123" t="s">
-        <v>346</v>
+        <v>334</v>
       </c>
       <c r="C123">
         <v>7</v>
@@ -5765,7 +5733,7 @@
         <v>450</v>
       </c>
       <c r="B124" t="s">
-        <v>347</v>
+        <v>335</v>
       </c>
       <c r="C124">
         <v>7</v>
@@ -5785,7 +5753,7 @@
         <v>451</v>
       </c>
       <c r="B125" t="s">
-        <v>348</v>
+        <v>336</v>
       </c>
       <c r="C125">
         <v>7</v>
@@ -5805,7 +5773,7 @@
         <v>452</v>
       </c>
       <c r="B126" t="s">
-        <v>349</v>
+        <v>337</v>
       </c>
       <c r="C126">
         <v>7</v>
@@ -5825,7 +5793,7 @@
         <v>453</v>
       </c>
       <c r="B127" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
       <c r="C127">
         <v>7</v>
@@ -5845,7 +5813,7 @@
         <v>454</v>
       </c>
       <c r="B128" t="s">
-        <v>289</v>
+        <v>277</v>
       </c>
       <c r="C128">
         <v>7</v>
@@ -5865,7 +5833,7 @@
         <v>455</v>
       </c>
       <c r="B129" t="s">
-        <v>290</v>
+        <v>278</v>
       </c>
       <c r="C129">
         <v>7</v>
@@ -5885,7 +5853,7 @@
         <v>456</v>
       </c>
       <c r="B130" t="s">
-        <v>291</v>
+        <v>279</v>
       </c>
       <c r="C130">
         <v>7</v>
@@ -5905,7 +5873,7 @@
         <v>457</v>
       </c>
       <c r="B131" t="s">
-        <v>292</v>
+        <v>280</v>
       </c>
       <c r="C131">
         <v>7</v>
@@ -5925,7 +5893,7 @@
         <v>458</v>
       </c>
       <c r="B132" t="s">
-        <v>293</v>
+        <v>281</v>
       </c>
       <c r="C132">
         <v>7</v>
@@ -5945,7 +5913,7 @@
         <v>459</v>
       </c>
       <c r="B133" t="s">
-        <v>294</v>
+        <v>282</v>
       </c>
       <c r="C133">
         <v>7</v>
@@ -5965,7 +5933,7 @@
         <v>460</v>
       </c>
       <c r="B134" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
       <c r="C134">
         <v>7</v>
@@ -5985,7 +5953,7 @@
         <v>461</v>
       </c>
       <c r="B135" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
       <c r="C135">
         <v>7</v>
@@ -6005,7 +5973,7 @@
         <v>462</v>
       </c>
       <c r="B136" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="C136">
         <v>7</v>
@@ -6025,7 +5993,7 @@
         <v>463</v>
       </c>
       <c r="B137" t="s">
-        <v>298</v>
+        <v>286</v>
       </c>
       <c r="C137">
         <v>7</v>
@@ -6045,7 +6013,7 @@
         <v>464</v>
       </c>
       <c r="B138" t="s">
-        <v>350</v>
+        <v>338</v>
       </c>
       <c r="C138">
         <v>7</v>
@@ -6065,7 +6033,7 @@
         <v>465</v>
       </c>
       <c r="B139" t="s">
-        <v>351</v>
+        <v>339</v>
       </c>
       <c r="C139">
         <v>7</v>
@@ -6085,7 +6053,7 @@
         <v>466</v>
       </c>
       <c r="B140" t="s">
-        <v>352</v>
+        <v>340</v>
       </c>
       <c r="C140">
         <v>7</v>
@@ -6105,7 +6073,7 @@
         <v>467</v>
       </c>
       <c r="B141" t="s">
-        <v>353</v>
+        <v>341</v>
       </c>
       <c r="C141">
         <v>7</v>
@@ -6125,7 +6093,7 @@
         <v>468</v>
       </c>
       <c r="B142" t="s">
-        <v>354</v>
+        <v>342</v>
       </c>
       <c r="C142">
         <v>7</v>
@@ -6145,7 +6113,7 @@
         <v>469</v>
       </c>
       <c r="B143" t="s">
-        <v>355</v>
+        <v>343</v>
       </c>
       <c r="C143">
         <v>7</v>
@@ -6165,7 +6133,7 @@
         <v>470</v>
       </c>
       <c r="B144" t="s">
-        <v>356</v>
+        <v>344</v>
       </c>
       <c r="C144">
         <v>7</v>
@@ -6185,7 +6153,7 @@
         <v>471</v>
       </c>
       <c r="B145" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
       <c r="C145">
         <v>7</v>
@@ -6205,7 +6173,7 @@
         <v>472</v>
       </c>
       <c r="B146" t="s">
-        <v>358</v>
+        <v>346</v>
       </c>
       <c r="C146">
         <v>7</v>
@@ -6225,7 +6193,7 @@
         <v>473</v>
       </c>
       <c r="B147" t="s">
-        <v>359</v>
+        <v>347</v>
       </c>
       <c r="C147">
         <v>7</v>
@@ -6245,7 +6213,7 @@
         <v>474</v>
       </c>
       <c r="B148" t="s">
-        <v>360</v>
+        <v>348</v>
       </c>
       <c r="C148">
         <v>7</v>
@@ -6265,7 +6233,7 @@
         <v>475</v>
       </c>
       <c r="B149" t="s">
-        <v>361</v>
+        <v>349</v>
       </c>
       <c r="C149">
         <v>7</v>
@@ -6285,7 +6253,7 @@
         <v>476</v>
       </c>
       <c r="B150" t="s">
-        <v>362</v>
+        <v>350</v>
       </c>
       <c r="C150">
         <v>7</v>
@@ -6305,7 +6273,7 @@
         <v>477</v>
       </c>
       <c r="B151" t="s">
-        <v>363</v>
+        <v>351</v>
       </c>
       <c r="C151">
         <v>7</v>
@@ -6325,7 +6293,7 @@
         <v>478</v>
       </c>
       <c r="B152" t="s">
-        <v>364</v>
+        <v>352</v>
       </c>
       <c r="C152">
         <v>7</v>
@@ -6345,7 +6313,7 @@
         <v>479</v>
       </c>
       <c r="B153" t="s">
-        <v>365</v>
+        <v>353</v>
       </c>
       <c r="C153">
         <v>7</v>
@@ -6365,7 +6333,7 @@
         <v>480</v>
       </c>
       <c r="B154" t="s">
-        <v>366</v>
+        <v>354</v>
       </c>
       <c r="C154">
         <v>7</v>
@@ -6385,7 +6353,7 @@
         <v>481</v>
       </c>
       <c r="B155" t="s">
-        <v>367</v>
+        <v>355</v>
       </c>
       <c r="C155">
         <v>7</v>
@@ -6405,7 +6373,7 @@
         <v>482</v>
       </c>
       <c r="B156" t="s">
-        <v>368</v>
+        <v>356</v>
       </c>
       <c r="C156">
         <v>7</v>
@@ -6425,7 +6393,7 @@
         <v>483</v>
       </c>
       <c r="B157" t="s">
-        <v>369</v>
+        <v>357</v>
       </c>
       <c r="C157">
         <v>7</v>
@@ -6445,7 +6413,7 @@
         <v>484</v>
       </c>
       <c r="B158" t="s">
-        <v>370</v>
+        <v>358</v>
       </c>
       <c r="C158">
         <v>7</v>
@@ -6465,7 +6433,7 @@
         <v>485</v>
       </c>
       <c r="B159" t="s">
-        <v>371</v>
+        <v>359</v>
       </c>
       <c r="C159">
         <v>7</v>
@@ -6485,7 +6453,7 @@
         <v>486</v>
       </c>
       <c r="B160" t="s">
-        <v>372</v>
+        <v>360</v>
       </c>
       <c r="C160">
         <v>7</v>
@@ -6505,7 +6473,7 @@
         <v>487</v>
       </c>
       <c r="B161" t="s">
-        <v>373</v>
+        <v>361</v>
       </c>
       <c r="C161">
         <v>7</v>
@@ -6525,7 +6493,7 @@
         <v>488</v>
       </c>
       <c r="B162" t="s">
-        <v>374</v>
+        <v>362</v>
       </c>
       <c r="C162">
         <v>7</v>
@@ -6545,7 +6513,7 @@
         <v>489</v>
       </c>
       <c r="B163" t="s">
-        <v>375</v>
+        <v>363</v>
       </c>
       <c r="C163">
         <v>7</v>
@@ -6565,7 +6533,7 @@
         <v>490</v>
       </c>
       <c r="B164" t="s">
-        <v>376</v>
+        <v>364</v>
       </c>
       <c r="C164">
         <v>7</v>
@@ -6585,7 +6553,7 @@
         <v>491</v>
       </c>
       <c r="B165" t="s">
-        <v>377</v>
+        <v>365</v>
       </c>
       <c r="C165">
         <v>7</v>
@@ -6605,7 +6573,7 @@
         <v>492</v>
       </c>
       <c r="B166" t="s">
-        <v>378</v>
+        <v>366</v>
       </c>
       <c r="C166">
         <v>7</v>
@@ -6625,7 +6593,7 @@
         <v>493</v>
       </c>
       <c r="B167" t="s">
-        <v>379</v>
+        <v>367</v>
       </c>
       <c r="C167">
         <v>7</v>
@@ -6645,7 +6613,7 @@
         <v>494</v>
       </c>
       <c r="B168" t="s">
-        <v>380</v>
+        <v>368</v>
       </c>
       <c r="C168">
         <v>7</v>
@@ -6665,7 +6633,7 @@
         <v>495</v>
       </c>
       <c r="B169" t="s">
-        <v>381</v>
+        <v>369</v>
       </c>
       <c r="C169">
         <v>7</v>
@@ -6685,7 +6653,7 @@
         <v>496</v>
       </c>
       <c r="B170" t="s">
-        <v>382</v>
+        <v>370</v>
       </c>
       <c r="C170">
         <v>7</v>
@@ -6705,7 +6673,7 @@
         <v>497</v>
       </c>
       <c r="B171" t="s">
-        <v>383</v>
+        <v>371</v>
       </c>
       <c r="C171">
         <v>7</v>
@@ -6725,7 +6693,7 @@
         <v>498</v>
       </c>
       <c r="B172" t="s">
-        <v>384</v>
+        <v>372</v>
       </c>
       <c r="C172">
         <v>7</v>
@@ -6745,7 +6713,7 @@
         <v>499</v>
       </c>
       <c r="B173" t="s">
-        <v>386</v>
+        <v>374</v>
       </c>
       <c r="C173">
         <v>7</v>
@@ -6765,7 +6733,7 @@
         <v>500</v>
       </c>
       <c r="B174" t="s">
-        <v>387</v>
+        <v>375</v>
       </c>
       <c r="C174">
         <v>7</v>
@@ -6785,7 +6753,7 @@
         <v>501</v>
       </c>
       <c r="B175" t="s">
-        <v>388</v>
+        <v>376</v>
       </c>
       <c r="C175">
         <v>7</v>
@@ -6805,7 +6773,7 @@
         <v>502</v>
       </c>
       <c r="B176" t="s">
-        <v>389</v>
+        <v>377</v>
       </c>
       <c r="C176">
         <v>1</v>
@@ -6823,7 +6791,7 @@
         <v>503</v>
       </c>
       <c r="B177" t="s">
-        <v>390</v>
+        <v>378</v>
       </c>
       <c r="C177">
         <v>1</v>
@@ -6841,7 +6809,7 @@
         <v>504</v>
       </c>
       <c r="B178" t="s">
-        <v>391</v>
+        <v>379</v>
       </c>
       <c r="C178">
         <v>1</v>
@@ -6859,7 +6827,7 @@
         <v>505</v>
       </c>
       <c r="B179" t="s">
-        <v>392</v>
+        <v>380</v>
       </c>
       <c r="C179">
         <v>1</v>
@@ -6877,7 +6845,7 @@
         <v>506</v>
       </c>
       <c r="B180" t="s">
-        <v>385</v>
+        <v>373</v>
       </c>
       <c r="C180">
         <v>7</v>
@@ -6905,8 +6873,8 @@
   <sheetPr>
     <tabColor theme="9" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:I45"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:I37"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="48.140625" customWidth="1"/>
     <col min="2" max="2" width="66.5703125" style="2" customWidth="1"/>
@@ -6915,7 +6883,7 @@
     <col min="5" max="5" width="11.85546875" style="4" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="8.28515625" style="6" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="71.5703125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="98.85546875" style="2" customWidth="1"/>
     <col min="9" max="9" width="48.85546875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -6927,7 +6895,7 @@
         <v>93</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="D1" t="s">
         <v>92</v>
@@ -6945,7 +6913,7 @@
         <v>136</v>
       </c>
       <c r="I1" t="s">
-        <v>204</v>
+        <v>192</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="45" x14ac:dyDescent="0.25">
@@ -6966,738 +6934,722 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>170</v>
+        <v>9</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>71</v>
+        <v>113</v>
       </c>
       <c r="D3" t="s">
-        <v>178</v>
+        <v>10</v>
       </c>
       <c r="E3" s="4">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="F3" s="6" t="s">
         <v>2</v>
       </c>
       <c r="G3" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>0</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>169</v>
+        <v>9</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>70</v>
+        <v>112</v>
       </c>
       <c r="D4" t="s">
-        <v>178</v>
+        <v>11</v>
       </c>
       <c r="E4" s="4">
-        <v>10000</v>
+        <v>2460</v>
       </c>
       <c r="F4" s="6" t="s">
         <v>2</v>
       </c>
       <c r="G4" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>10000</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+        <v>2460</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>170</v>
+        <v>28</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>182</v>
+        <v>28</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D5" t="s">
-        <v>178</v>
+        <v>27</v>
       </c>
       <c r="E5" s="4">
-        <v>1940</v>
+        <v>1051.2</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>2</v>
       </c>
       <c r="G5" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>1940</v>
+        <v>1051.2</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>172</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>169</v>
+        <v>8</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>70</v>
+        <v>116</v>
+      </c>
+      <c r="C6" t="s">
+        <v>66</v>
       </c>
       <c r="D6" t="s">
-        <v>178</v>
+        <v>90</v>
       </c>
       <c r="E6" s="4">
-        <v>18000</v>
+        <v>748.15</v>
       </c>
       <c r="F6" s="6" t="s">
         <v>2</v>
       </c>
       <c r="G6" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>18000</v>
+        <v>748.15</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+        <v>91</v>
+      </c>
+      <c r="I6" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>170</v>
+        <v>5</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>71</v>
+        <v>115</v>
+      </c>
+      <c r="C7" t="s">
+        <v>65</v>
       </c>
       <c r="D7" t="s">
-        <v>178</v>
+        <v>6</v>
       </c>
       <c r="E7" s="4">
-        <v>5710</v>
+        <v>6096.65</v>
       </c>
       <c r="F7" s="6" t="s">
         <v>2</v>
       </c>
       <c r="G7" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>5710</v>
+        <v>6096.65</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>173</v>
+        <v>100</v>
+      </c>
+      <c r="I7" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>169</v>
+        <v>5</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>70</v>
+        <v>114</v>
+      </c>
+      <c r="C8" t="s">
+        <v>65</v>
       </c>
       <c r="D8" t="s">
-        <v>178</v>
+        <v>7</v>
       </c>
       <c r="E8" s="4">
-        <v>20000</v>
+        <v>7502.9</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>2</v>
       </c>
       <c r="G8" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>20000</v>
+        <v>7502.9</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>170</v>
+        <v>20</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>71</v>
+        <v>126</v>
+      </c>
+      <c r="C9" t="s">
+        <v>72</v>
       </c>
       <c r="D9" t="s">
-        <v>178</v>
+        <v>80</v>
       </c>
       <c r="E9" s="4">
-        <v>10770</v>
+        <f>16750</f>
+        <v>16750</v>
       </c>
       <c r="F9" s="6" t="s">
         <v>2</v>
       </c>
       <c r="G9" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>10770</v>
+        <v>16750</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>169</v>
+        <v>20</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>70</v>
+        <v>187</v>
+      </c>
+      <c r="C10" t="s">
+        <v>72</v>
       </c>
       <c r="D10" t="s">
-        <v>178</v>
+        <v>80</v>
       </c>
       <c r="E10" s="4">
-        <v>25000</v>
+        <f>887</f>
+        <v>887</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>2</v>
       </c>
       <c r="G10" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>25000</v>
+        <v>887</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>171</v>
+        <v>135</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>113</v>
+        <v>128</v>
+      </c>
+      <c r="C11" t="s">
+        <v>72</v>
       </c>
       <c r="D11" t="s">
-        <v>10</v>
-      </c>
-      <c r="E11" s="4">
-        <v>3000</v>
+        <v>22</v>
       </c>
       <c r="F11" s="6" t="s">
         <v>2</v>
       </c>
       <c r="G11" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>3000</v>
+        <v>0</v>
+      </c>
+      <c r="H11" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>112</v>
+        <v>127</v>
+      </c>
+      <c r="C12" t="s">
+        <v>72</v>
       </c>
       <c r="D12" t="s">
-        <v>11</v>
-      </c>
-      <c r="E12" s="4">
-        <v>2460</v>
+        <v>21</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>2</v>
       </c>
       <c r="G12" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>2460</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="H12" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>67</v>
+        <v>119</v>
+      </c>
+      <c r="C13" t="s">
+        <v>55</v>
       </c>
       <c r="D13" t="s">
-        <v>27</v>
+        <v>105</v>
       </c>
       <c r="E13" s="4">
-        <v>1051.2</v>
+        <f>1140*12</f>
+        <v>13680</v>
       </c>
       <c r="F13" s="6" t="s">
         <v>2</v>
       </c>
       <c r="G13" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>1051.2</v>
+        <v>13680</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>28</v>
+        <v>102</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C14" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="D14" t="s">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="E14" s="4">
-        <v>748.15</v>
+        <f>2836.8*12</f>
+        <v>34041.600000000006</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>2</v>
       </c>
       <c r="G14" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>748.15</v>
+        <v>34041.600000000006</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="I14" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C15" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="D15" t="s">
-        <v>6</v>
+        <v>105</v>
       </c>
       <c r="E15" s="4">
-        <v>6096.65</v>
+        <f>1518*12</f>
+        <v>18216</v>
       </c>
       <c r="F15" s="6" t="s">
         <v>2</v>
       </c>
       <c r="G15" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>6096.65</v>
+        <v>18216</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="I15" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C16" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="D16" t="s">
-        <v>7</v>
+        <v>109</v>
       </c>
       <c r="E16" s="4">
-        <v>7502.9</v>
+        <v>516</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>2</v>
       </c>
       <c r="G16" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>7502.9</v>
+        <v>516</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C17" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D17" t="s">
-        <v>80</v>
+        <v>109</v>
       </c>
       <c r="E17" s="4">
-        <f>16750</f>
-        <v>16750</v>
+        <v>456</v>
       </c>
       <c r="F17" s="6" t="s">
         <v>2</v>
       </c>
       <c r="G17" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>16750</v>
+        <v>456</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="165" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>199</v>
+        <v>125</v>
       </c>
       <c r="C18" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D18" t="s">
-        <v>80</v>
+        <v>19</v>
       </c>
       <c r="E18" s="4">
-        <f>887</f>
-        <v>887</v>
+        <v>660</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>2</v>
       </c>
       <c r="G18" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>887</v>
+        <v>660</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>128</v>
+        <v>189</v>
       </c>
       <c r="C19" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D19" t="s">
-        <v>22</v>
+        <v>190</v>
+      </c>
+      <c r="E19" s="4">
+        <v>434.5</v>
       </c>
       <c r="F19" s="6" t="s">
         <v>2</v>
       </c>
       <c r="G19" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>0</v>
-      </c>
-      <c r="H19" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+        <v>434.5</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="C20" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="D20" t="s">
-        <v>21</v>
+        <v>79</v>
+      </c>
+      <c r="E20" s="4">
+        <v>2400</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G20" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>0</v>
-      </c>
-      <c r="H20" t="s">
-        <v>132</v>
+        <v>2880</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="I20" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>119</v>
+        <v>140</v>
       </c>
       <c r="C21" t="s">
-        <v>55</v>
+        <v>86</v>
       </c>
       <c r="D21" t="s">
-        <v>105</v>
+        <v>79</v>
       </c>
       <c r="E21" s="4">
-        <f>1140*12</f>
-        <v>13680</v>
+        <v>2400</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G21" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>13680</v>
+        <v>2880</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>102</v>
+        <v>133</v>
+      </c>
+      <c r="I21" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>117</v>
+        <v>142</v>
       </c>
       <c r="C22" t="s">
-        <v>55</v>
+        <v>87</v>
       </c>
       <c r="D22" t="s">
-        <v>108</v>
+        <v>79</v>
       </c>
       <c r="E22" s="4">
-        <f>2836.8*12</f>
-        <v>34041.600000000006</v>
+        <v>2450</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G22" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>34041.600000000006</v>
+        <v>2940</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>103</v>
+        <v>133</v>
+      </c>
+      <c r="I22" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>118</v>
+        <v>144</v>
       </c>
       <c r="C23" t="s">
-        <v>55</v>
+        <v>88</v>
       </c>
       <c r="D23" t="s">
-        <v>105</v>
+        <v>79</v>
       </c>
       <c r="E23" s="4">
-        <f>1518*12</f>
-        <v>18216</v>
+        <v>2200</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G23" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>18216</v>
+        <v>2640</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>103</v>
+        <v>134</v>
       </c>
       <c r="I23" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="C24" t="s">
-        <v>73</v>
+        <v>25</v>
       </c>
       <c r="D24" t="s">
-        <v>109</v>
+        <v>26</v>
       </c>
       <c r="E24" s="4">
-        <v>516</v>
+        <v>160</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>2</v>
       </c>
       <c r="G24" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>516</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>124</v>
+        <v>111</v>
       </c>
       <c r="C25" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="D25" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E25" s="4">
-        <v>456</v>
+        <f>2400*12</f>
+        <v>28800</v>
       </c>
       <c r="F25" s="6" t="s">
         <v>2</v>
       </c>
       <c r="G25" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>456</v>
+        <v>28800</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" ht="225" x14ac:dyDescent="0.25">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="C26" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="D26" t="s">
-        <v>19</v>
+        <v>108</v>
       </c>
       <c r="E26" s="4">
-        <v>660</v>
+        <f>1320*12</f>
+        <v>15840</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>2</v>
       </c>
       <c r="G26" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>660</v>
+        <v>15840</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>131</v>
+        <v>106</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="C27" t="s">
-        <v>73</v>
+        <v>122</v>
       </c>
       <c r="D27" t="s">
-        <v>202</v>
+        <v>17</v>
       </c>
       <c r="E27" s="4">
-        <v>434.5</v>
+        <v>3198.13</v>
       </c>
       <c r="F27" s="6" t="s">
         <v>2</v>
       </c>
       <c r="G27" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>434.5</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>200</v>
+        <v>3198.13</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="C28" t="s">
-        <v>85</v>
+        <v>121</v>
       </c>
       <c r="D28" t="s">
-        <v>79</v>
+        <v>16</v>
       </c>
       <c r="E28" s="4">
-        <v>2400</v>
+        <v>3322.8</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G28" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>2880</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="I28" t="s">
-        <v>200</v>
+        <v>3322.8</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="C29" t="s">
-        <v>86</v>
+        <v>120</v>
       </c>
       <c r="D29" t="s">
-        <v>79</v>
+        <v>15</v>
       </c>
       <c r="E29" s="4">
-        <v>2400</v>
+        <v>3138.27</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G29" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>2880</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="I29" t="s">
-        <v>200</v>
+        <v>3138.27</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
@@ -7705,29 +7657,26 @@
         <v>13</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C30" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D30" t="s">
         <v>79</v>
       </c>
       <c r="E30" s="4">
-        <v>2450</v>
+        <v>240</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>1</v>
       </c>
       <c r="G30" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>2940</v>
+        <v>288</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>133</v>
-      </c>
-      <c r="I30" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
@@ -7735,385 +7684,188 @@
         <v>13</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="C31" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D31" t="s">
         <v>79</v>
       </c>
       <c r="E31" s="4">
-        <v>2200</v>
+        <v>240</v>
       </c>
       <c r="F31" s="6" t="s">
         <v>1</v>
       </c>
       <c r="G31" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>2640</v>
+        <v>288</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="I31" t="s">
-        <v>200</v>
+        <v>133</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>25</v>
+        <v>141</v>
+      </c>
+      <c r="C32" t="s">
+        <v>87</v>
       </c>
       <c r="D32" t="s">
-        <v>26</v>
+        <v>79</v>
       </c>
       <c r="E32" s="4">
-        <v>160</v>
+        <v>240</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G32" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>160</v>
+        <v>288</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>111</v>
+        <v>143</v>
       </c>
       <c r="C33" t="s">
-        <v>55</v>
+        <v>88</v>
       </c>
       <c r="D33" t="s">
-        <v>108</v>
+        <v>79</v>
       </c>
       <c r="E33" s="4">
-        <f>2400*12</f>
-        <v>28800</v>
+        <v>240</v>
       </c>
       <c r="F33" s="6" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G33" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>28800</v>
+        <v>288</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>107</v>
+        <v>133</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>12</v>
+        <v>98</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="C34" t="s">
-        <v>55</v>
+        <v>171</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>67</v>
       </c>
       <c r="D34" t="s">
-        <v>108</v>
-      </c>
-      <c r="E34" s="4">
-        <f>1320*12</f>
-        <v>15840</v>
-      </c>
-      <c r="F34" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="E34" s="5">
+        <v>10000</v>
+      </c>
+      <c r="F34" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="G34" s="4">
+      <c r="G34" s="5">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>15840</v>
-      </c>
-      <c r="H34" s="2" t="s">
-        <v>106</v>
-      </c>
+        <v>10000</v>
+      </c>
+      <c r="H34" s="3"/>
+      <c r="I34" s="2"/>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>14</v>
+        <v>98</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>122</v>
+        <v>173</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>67</v>
       </c>
       <c r="D35" t="s">
-        <v>17</v>
-      </c>
-      <c r="E35" s="4">
-        <v>3198.13</v>
-      </c>
-      <c r="F35" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="E35" s="5">
+        <v>12500</v>
+      </c>
+      <c r="F35" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="G35" s="4">
+      <c r="G35" s="5">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>3198.13</v>
-      </c>
+        <v>12500</v>
+      </c>
+      <c r="H35" s="3"/>
+      <c r="I35" s="2"/>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>14</v>
+        <v>98</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>121</v>
+        <v>172</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>67</v>
       </c>
       <c r="D36" t="s">
-        <v>16</v>
-      </c>
-      <c r="E36" s="4">
-        <v>3322.8</v>
-      </c>
-      <c r="F36" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="E36" s="5">
+        <v>15000</v>
+      </c>
+      <c r="F36" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="G36" s="4">
+      <c r="G36" s="5">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>3322.8</v>
-      </c>
+        <v>15000</v>
+      </c>
+      <c r="H36" s="3"/>
+      <c r="I36" s="2"/>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>14</v>
+        <v>98</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>120</v>
+        <v>98</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>67</v>
       </c>
       <c r="D37" t="s">
-        <v>15</v>
-      </c>
-      <c r="E37" s="4">
-        <v>3138.27</v>
-      </c>
-      <c r="F37" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="E37" s="5">
+        <v>16800</v>
+      </c>
+      <c r="F37" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="G37" s="4">
-        <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>3138.27</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A38" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="C38" t="s">
-        <v>85</v>
-      </c>
-      <c r="D38" t="s">
-        <v>79</v>
-      </c>
-      <c r="E38" s="4">
-        <v>240</v>
-      </c>
-      <c r="F38" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="G38" s="4">
-        <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>288</v>
-      </c>
-      <c r="H38" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A39" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="C39" t="s">
-        <v>86</v>
-      </c>
-      <c r="D39" t="s">
-        <v>79</v>
-      </c>
-      <c r="E39" s="4">
-        <v>240</v>
-      </c>
-      <c r="F39" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="G39" s="4">
-        <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>288</v>
-      </c>
-      <c r="H39" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A40" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="C40" t="s">
-        <v>87</v>
-      </c>
-      <c r="D40" t="s">
-        <v>79</v>
-      </c>
-      <c r="E40" s="4">
-        <v>240</v>
-      </c>
-      <c r="F40" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="G40" s="4">
-        <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>288</v>
-      </c>
-      <c r="H40" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A41" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="C41" t="s">
-        <v>88</v>
-      </c>
-      <c r="D41" t="s">
-        <v>79</v>
-      </c>
-      <c r="E41" s="4">
-        <v>240</v>
-      </c>
-      <c r="F41" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="G41" s="4">
-        <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>288</v>
-      </c>
-      <c r="H41" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A42" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D42" t="s">
-        <v>178</v>
-      </c>
-      <c r="E42" s="5">
-        <v>10000</v>
-      </c>
-      <c r="F42" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="G42" s="5">
-        <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>10000</v>
-      </c>
-      <c r="H42" s="3"/>
-      <c r="I42" s="2"/>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A43" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D43" t="s">
-        <v>178</v>
-      </c>
-      <c r="E43" s="5">
-        <v>12500</v>
-      </c>
-      <c r="F43" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="G43" s="5">
-        <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>12500</v>
-      </c>
-      <c r="H43" s="3"/>
-      <c r="I43" s="2"/>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A44" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D44" t="s">
-        <v>178</v>
-      </c>
-      <c r="E44" s="5">
-        <v>15000</v>
-      </c>
-      <c r="F44" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="G44" s="5">
-        <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>15000</v>
-      </c>
-      <c r="H44" s="3"/>
-      <c r="I44" s="2"/>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A45" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D45" t="s">
-        <v>27</v>
-      </c>
-      <c r="E45" s="5">
-        <v>16800</v>
-      </c>
-      <c r="F45" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="G45" s="5">
+      <c r="G37" s="5">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
         <v>16800</v>
       </c>
-      <c r="H45" s="3" t="s">
+      <c r="H37" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="I45" s="2" t="s">
-        <v>200</v>
+      <c r="I37" s="2" t="s">
+        <v>188</v>
       </c>
     </row>
   </sheetData>
@@ -8142,7 +7894,7 @@
     <tabColor theme="9" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="25.85546875" bestFit="1" customWidth="1"/>
@@ -8151,18 +7903,18 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>195</v>
+        <v>183</v>
       </c>
       <c r="B1" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="C1" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="B2">
         <f>5735*2.5</f>
@@ -8186,7 +7938,7 @@
     <tabColor theme="9" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:J3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20.5703125" customWidth="1"/>
@@ -8202,39 +7954,39 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>191</v>
+        <v>179</v>
       </c>
       <c r="B1" t="s">
-        <v>192</v>
+        <v>180</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>408</v>
+        <v>396</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>411</v>
+        <v>398</v>
       </c>
       <c r="F1" s="12" t="s">
-        <v>412</v>
+        <v>399</v>
       </c>
       <c r="G1" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="H1" t="s">
         <v>136</v>
       </c>
       <c r="I1" t="s">
-        <v>415</v>
+        <v>402</v>
       </c>
       <c r="J1" t="s">
-        <v>414</v>
+        <v>401</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>406</v>
+        <v>394</v>
       </c>
       <c r="B2" s="11" t="s">
         <v>70</v>
@@ -8244,7 +7996,7 @@
         <v>9.6000000000000002E-2</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>409</v>
+        <v>397</v>
       </c>
       <c r="E2" s="1">
         <v>392</v>
@@ -8256,7 +8008,7 @@
         <v>120</v>
       </c>
       <c r="H2" t="s">
-        <v>405</v>
+        <v>393</v>
       </c>
       <c r="I2" s="13">
         <v>0.3</v>
@@ -8267,7 +8019,7 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>407</v>
+        <v>395</v>
       </c>
       <c r="B3" t="s">
         <v>71</v>
@@ -8276,7 +8028,7 @@
         <v>0.12559999999999999</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>410</v>
+        <v>403</v>
       </c>
       <c r="E3" s="1">
         <v>0.12559999999999999</v>
@@ -8288,7 +8040,7 @@
         <v>140</v>
       </c>
       <c r="H3" t="s">
-        <v>413</v>
+        <v>400</v>
       </c>
       <c r="I3" s="13">
         <v>0.08</v>

--- a/input.xlsx
+++ b/input.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/25a393584c41f6f2/Documents/Mon Patrimoine/Projet Immobilier/2023 Terrasses de Galieni/09 - Copropriété/Site de calcul des charges de copropriété/streamlit-copro-charges/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1315" documentId="13_ncr:1_{471232EB-3AAB-4D08-BC1C-7B7CD1C1D853}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AD65BE4F-F1BF-4F83-BAED-91D17FA905CE}"/>
+  <xr:revisionPtr revIDLastSave="1343" documentId="13_ncr:1_{471232EB-3AAB-4D08-BC1C-7B7CD1C1D853}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E2644BA5-F55D-4C7D-8DDE-9E4DFAE0EC91}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Provisions" sheetId="9" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="592" uniqueCount="404">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="593" uniqueCount="405">
   <si>
     <t>Taxes</t>
   </si>
@@ -1261,10 +1261,13 @@
     <t>Seuil de durée d'activation (mn)</t>
   </si>
   <si>
-    <t>Seuil de fonctionnement (%)</t>
-  </si>
-  <si>
     <t>kWh de gaz</t>
+  </si>
+  <si>
+    <t>Volume ballon d'ECS m3</t>
+  </si>
+  <si>
+    <t>Seuil de fonctionnement (kW)</t>
   </si>
 </sst>
 </file>
@@ -1336,7 +1339,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1356,14 +1359,13 @@
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Monétaire" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Pourcentage" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="30">
+  <dxfs count="31">
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -1698,6 +1700,9 @@
       </font>
     </dxf>
     <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
       <font>
         <b val="0"/>
         <i val="0"/>
@@ -1783,10 +1788,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{13C2BCD2-5CEA-4301-A571-688E40226767}" name="Provisions" displayName="Provisions" ref="A1:F35">
   <autoFilter ref="A1:F35" xr:uid="{13C2BCD2-5CEA-4301-A571-688E40226767}"/>
@@ -1798,7 +1799,7 @@
     <tableColumn id="4" xr3:uid="{84F1F30D-4827-43F2-8865-B7957E3E712D}" name="ID"/>
     <tableColumn id="7" xr3:uid="{512EABBD-B863-4251-833D-8B8D1F1626EF}" name="Description"/>
     <tableColumn id="2" xr3:uid="{D09C4BB0-FEBD-4A72-9E87-B5258D8B62D7}" name="Label de la provision"/>
-    <tableColumn id="3" xr3:uid="{347751FB-EF14-4BD7-9D47-427E04136B77}" name="Provision" totalsRowFunction="sum" dataDxfId="25" totalsRowDxfId="24"/>
+    <tableColumn id="3" xr3:uid="{347751FB-EF14-4BD7-9D47-427E04136B77}" name="Provision" totalsRowFunction="sum" dataDxfId="25" totalsRowDxfId="24" dataCellStyle="Monétaire"/>
     <tableColumn id="5" xr3:uid="{CA26B6F8-88AD-418A-B213-749ABA66E926}" name="Description longue" dataDxfId="23"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1859,14 +1860,15 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{0628909A-75FF-41C1-9EE4-F3C649717216}" name="Residence" displayName="Residence" ref="A1:C2" totalsRowShown="0">
-  <autoFilter ref="A1:C2" xr:uid="{0628909A-75FF-41C1-9EE4-F3C649717216}"/>
-  <tableColumns count="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{0628909A-75FF-41C1-9EE4-F3C649717216}" name="Residence" displayName="Residence" ref="A1:D2" totalsRowShown="0">
+  <autoFilter ref="A1:D2" xr:uid="{0628909A-75FF-41C1-9EE4-F3C649717216}"/>
+  <tableColumns count="4">
     <tableColumn id="4" xr3:uid="{B1EE509D-2894-4393-AA6B-5D042BB6CCBA}" name="Label"/>
     <tableColumn id="2" xr3:uid="{0EB0E801-9DD6-4459-8AAC-AA0D5AC1F393}" name="Volume à chauffer en m3">
       <calculatedColumnFormula>5735*2.5</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{194ABB34-607A-43C7-8DED-8E1BDC9DD34E}" name="Coefficient d'isolation"/>
+    <tableColumn id="1" xr3:uid="{7B038720-5CD6-40A0-9EAC-BA975F2B8827}" name="Volume ballon d'ECS m3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1878,13 +1880,13 @@
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{455C30A6-2C19-4BD7-B8A4-D1C6252917DD}" name="Type de chaudière"/>
     <tableColumn id="2" xr3:uid="{FAAC8507-DC80-422C-8508-496178C23374}" name="ID poste de provision"/>
-    <tableColumn id="3" xr3:uid="{17764D71-05D7-4B37-8536-4004CBBE2CD4}" name="Prix unitaire du kWh" dataDxfId="29"/>
-    <tableColumn id="7" xr3:uid="{39B6FB9A-9DCB-412D-8CBD-94E321E39A50}" name="Unité" dataDxfId="28"/>
-    <tableColumn id="8" xr3:uid="{C769AD0E-5A43-462D-8737-CE59FA9E9F57}" name="Prix de l'unité" dataDxfId="27"/>
-    <tableColumn id="9" xr3:uid="{C32F2A17-C994-4DCC-A33C-2604586EDB4F}" name="kWh par unité" dataDxfId="26"/>
+    <tableColumn id="3" xr3:uid="{17764D71-05D7-4B37-8536-4004CBBE2CD4}" name="Prix unitaire du kWh" dataDxfId="30"/>
+    <tableColumn id="7" xr3:uid="{39B6FB9A-9DCB-412D-8CBD-94E321E39A50}" name="Unité" dataDxfId="29"/>
+    <tableColumn id="8" xr3:uid="{C769AD0E-5A43-462D-8737-CE59FA9E9F57}" name="Prix de l'unité" dataDxfId="28"/>
+    <tableColumn id="9" xr3:uid="{C32F2A17-C994-4DCC-A33C-2604586EDB4F}" name="kWh par unité" dataDxfId="27"/>
     <tableColumn id="4" xr3:uid="{FECEDA0B-3F17-4D04-AB3F-B1B848AA5DB2}" name="Production maximum en kW"/>
     <tableColumn id="6" xr3:uid="{F8EB0843-7F05-427F-9B41-0852730F32C9}" name="Description"/>
-    <tableColumn id="10" xr3:uid="{9F9F9E98-6D66-4867-A354-22539BFC6A70}" name="Seuil de fonctionnement (%)"/>
+    <tableColumn id="10" xr3:uid="{9F9F9E98-6D66-4867-A354-22539BFC6A70}" name="Seuil de fonctionnement (kW)" dataDxfId="26"/>
     <tableColumn id="11" xr3:uid="{D0B5F61C-1D85-4C5E-A117-B774F88FE50E}" name="Seuil de durée d'activation (mn)"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -2164,7 +2166,7 @@
     <col min="2" max="2" width="15.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="42.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="42.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="147" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2807,7 +2809,9 @@
       <c r="D34" t="s">
         <v>35</v>
       </c>
-      <c r="E34" s="1"/>
+      <c r="E34" s="1">
+        <v>0</v>
+      </c>
       <c r="F34" s="2"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -2822,6 +2826,9 @@
       </c>
       <c r="D35" t="s">
         <v>211</v>
+      </c>
+      <c r="E35" s="1">
+        <v>0</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>212</v>
@@ -7033,7 +7040,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>5</v>
       </c>
@@ -7281,7 +7288,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>18</v>
       </c>
@@ -7308,7 +7315,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>18</v>
       </c>
@@ -7893,15 +7900,16 @@
   <sheetPr>
     <tabColor theme="9" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="25.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>183</v>
       </c>
@@ -7911,8 +7919,11 @@
       <c r="C1" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>184</v>
       </c>
@@ -7922,6 +7933,9 @@
       </c>
       <c r="C2">
         <v>0.5</v>
+      </c>
+      <c r="D2">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -7949,7 +7963,7 @@
     <col min="7" max="7" width="29" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="133.85546875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="36.7109375" customWidth="1"/>
-    <col min="10" max="10" width="27" customWidth="1"/>
+    <col min="10" max="10" width="32.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -7978,7 +7992,7 @@
         <v>136</v>
       </c>
       <c r="I1" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="J1" t="s">
         <v>401</v>
@@ -8010,8 +8024,8 @@
       <c r="H2" t="s">
         <v>393</v>
       </c>
-      <c r="I2" s="13">
-        <v>0.3</v>
+      <c r="I2">
+        <v>37</v>
       </c>
       <c r="J2">
         <v>30</v>
@@ -8028,7 +8042,7 @@
         <v>0.12559999999999999</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E3" s="1">
         <v>0.12559999999999999</v>
@@ -8042,8 +8056,9 @@
       <c r="H3" t="s">
         <v>400</v>
       </c>
-      <c r="I3" s="13">
-        <v>0.08</v>
+      <c r="I3">
+        <f>12</f>
+        <v>12</v>
       </c>
       <c r="J3">
         <v>10</v>

--- a/input.xlsx
+++ b/input.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/25a393584c41f6f2/Documents/Mon Patrimoine/Projet Immobilier/2023 Terrasses de Galieni/09 - Copropriété/Site de calcul des charges de copropriété/streamlit-copro-charges/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1343" documentId="13_ncr:1_{471232EB-3AAB-4D08-BC1C-7B7CD1C1D853}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E2644BA5-F55D-4C7D-8DDE-9E4DFAE0EC91}"/>
+  <xr:revisionPtr revIDLastSave="1352" documentId="13_ncr:1_{471232EB-3AAB-4D08-BC1C-7B7CD1C1D853}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ABBA670F-8EBD-46A0-88D7-23996C8CEBB2}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Provisions" sheetId="9" r:id="rId1"/>
@@ -1249,9 +1249,6 @@
     <t>tonne de granulé</t>
   </si>
   <si>
-    <t>Prix de l'unité</t>
-  </si>
-  <si>
     <t>kWh par unité</t>
   </si>
   <si>
@@ -1268,6 +1265,9 @@
   </si>
   <si>
     <t>Seuil de fonctionnement (kW)</t>
+  </si>
+  <si>
+    <t>Prix TTC de l'unité</t>
   </si>
 </sst>
 </file>
@@ -1366,6 +1366,82 @@
     <cellStyle name="Pourcentage" xfId="2" builtinId="5"/>
   </cellStyles>
   <dxfs count="31">
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -1699,82 +1775,6 @@
         <scheme val="minor"/>
       </font>
     </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1788,6 +1788,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{13C2BCD2-5CEA-4301-A571-688E40226767}" name="Provisions" displayName="Provisions" ref="A1:F35">
   <autoFilter ref="A1:F35" xr:uid="{13C2BCD2-5CEA-4301-A571-688E40226767}"/>
@@ -1799,8 +1803,8 @@
     <tableColumn id="4" xr3:uid="{84F1F30D-4827-43F2-8865-B7957E3E712D}" name="ID"/>
     <tableColumn id="7" xr3:uid="{512EABBD-B863-4251-833D-8B8D1F1626EF}" name="Description"/>
     <tableColumn id="2" xr3:uid="{D09C4BB0-FEBD-4A72-9E87-B5258D8B62D7}" name="Label de la provision"/>
-    <tableColumn id="3" xr3:uid="{347751FB-EF14-4BD7-9D47-427E04136B77}" name="Provision" totalsRowFunction="sum" dataDxfId="25" totalsRowDxfId="24" dataCellStyle="Monétaire"/>
-    <tableColumn id="5" xr3:uid="{CA26B6F8-88AD-418A-B213-749ABA66E926}" name="Description longue" dataDxfId="23"/>
+    <tableColumn id="3" xr3:uid="{347751FB-EF14-4BD7-9D47-427E04136B77}" name="Provision" totalsRowFunction="sum" dataDxfId="30" totalsRowDxfId="29" dataCellStyle="Monétaire"/>
+    <tableColumn id="5" xr3:uid="{CA26B6F8-88AD-418A-B213-749ABA66E926}" name="Description longue" dataDxfId="28"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1813,24 +1817,24 @@
     <sortCondition ref="A1:A180"/>
   </sortState>
   <tableColumns count="16">
-    <tableColumn id="3" xr3:uid="{1687C042-C916-4161-82C2-2A915364FCD2}" name="Numéro de lot" dataDxfId="22"/>
+    <tableColumn id="3" xr3:uid="{1687C042-C916-4161-82C2-2A915364FCD2}" name="Numéro de lot" dataDxfId="27"/>
     <tableColumn id="1" xr3:uid="{788DBA8C-5B77-4079-8161-FA45C58518AE}" name="Description"/>
-    <tableColumn id="2" xr3:uid="{BE5ACA99-AEAF-4E51-BE0A-B3FB8FCCF08B}" name="Tantièmes copropriété" dataDxfId="21">
+    <tableColumn id="2" xr3:uid="{BE5ACA99-AEAF-4E51-BE0A-B3FB8FCCF08B}" name="Tantièmes copropriété" dataDxfId="26">
       <calculatedColumnFormula>7/10000</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{D62FAA89-C46E-4AF6-A14F-7FD6F46E7F00}" name="Tantièmes ascenseur 1-1" dataDxfId="20"/>
-    <tableColumn id="9" xr3:uid="{C3B9BDED-CB2A-4305-9CBF-418F5971AC1E}" name="Tantièmes ascenseur 1-2" dataDxfId="19"/>
-    <tableColumn id="10" xr3:uid="{C2291DE1-C707-4F83-846E-F914B4B42E52}" name="Tantièmes ascenseur 2" dataDxfId="18"/>
-    <tableColumn id="11" xr3:uid="{4F70F08A-4C2F-41B0-88EB-711B1A0760CD}" name="Tantièmes ascenseur 3" dataDxfId="17"/>
-    <tableColumn id="14" xr3:uid="{80D23396-716C-46AC-9B55-BCBC6C981351}" name="Tantièmes chauffage" dataDxfId="16"/>
-    <tableColumn id="15" xr3:uid="{E3955139-B619-4DD0-8FC1-ECA97048DFE4}" name="Tantièmes Batiment 1" dataDxfId="15"/>
-    <tableColumn id="16" xr3:uid="{C73E9407-A858-4EF7-81C2-6C70C4B157A2}" name="Tantièmes Batiment 2" dataDxfId="14"/>
-    <tableColumn id="17" xr3:uid="{A07338CA-0096-4091-89B2-A46FF2D323C2}" name="Tantièmes Batiment 3" dataDxfId="13"/>
-    <tableColumn id="18" xr3:uid="{7A3012D8-2375-4F10-9E84-F2F5060C6A99}" name="Tantièmes Hall 1-1" dataDxfId="12"/>
-    <tableColumn id="19" xr3:uid="{67961B6E-B577-4A49-B099-623FB85519B4}" name="Tantièmes Hall 1-2" dataDxfId="11"/>
-    <tableColumn id="20" xr3:uid="{03C201C1-F8AA-4D3C-AEBC-425B180BC2D7}" name="Tantièmes Hall 2" dataDxfId="10"/>
-    <tableColumn id="21" xr3:uid="{4826FC05-81A9-4020-8D1D-83D3D5C5A05A}" name="Tantièmes Logement/Stationnements" dataDxfId="9"/>
-    <tableColumn id="6" xr3:uid="{7B87787E-3595-42D5-B815-AF76B67432D8}" name="Tantièmes Stationnement" dataDxfId="8"/>
+    <tableColumn id="8" xr3:uid="{D62FAA89-C46E-4AF6-A14F-7FD6F46E7F00}" name="Tantièmes ascenseur 1-1" dataDxfId="25"/>
+    <tableColumn id="9" xr3:uid="{C3B9BDED-CB2A-4305-9CBF-418F5971AC1E}" name="Tantièmes ascenseur 1-2" dataDxfId="24"/>
+    <tableColumn id="10" xr3:uid="{C2291DE1-C707-4F83-846E-F914B4B42E52}" name="Tantièmes ascenseur 2" dataDxfId="23"/>
+    <tableColumn id="11" xr3:uid="{4F70F08A-4C2F-41B0-88EB-711B1A0760CD}" name="Tantièmes ascenseur 3" dataDxfId="22"/>
+    <tableColumn id="14" xr3:uid="{80D23396-716C-46AC-9B55-BCBC6C981351}" name="Tantièmes chauffage" dataDxfId="21"/>
+    <tableColumn id="15" xr3:uid="{E3955139-B619-4DD0-8FC1-ECA97048DFE4}" name="Tantièmes Batiment 1" dataDxfId="20"/>
+    <tableColumn id="16" xr3:uid="{C73E9407-A858-4EF7-81C2-6C70C4B157A2}" name="Tantièmes Batiment 2" dataDxfId="19"/>
+    <tableColumn id="17" xr3:uid="{A07338CA-0096-4091-89B2-A46FF2D323C2}" name="Tantièmes Batiment 3" dataDxfId="18"/>
+    <tableColumn id="18" xr3:uid="{7A3012D8-2375-4F10-9E84-F2F5060C6A99}" name="Tantièmes Hall 1-1" dataDxfId="17"/>
+    <tableColumn id="19" xr3:uid="{67961B6E-B577-4A49-B099-623FB85519B4}" name="Tantièmes Hall 1-2" dataDxfId="16"/>
+    <tableColumn id="20" xr3:uid="{03C201C1-F8AA-4D3C-AEBC-425B180BC2D7}" name="Tantièmes Hall 2" dataDxfId="15"/>
+    <tableColumn id="21" xr3:uid="{4826FC05-81A9-4020-8D1D-83D3D5C5A05A}" name="Tantièmes Logement/Stationnements" dataDxfId="14"/>
+    <tableColumn id="6" xr3:uid="{7B87787E-3595-42D5-B815-AF76B67432D8}" name="Tantièmes Stationnement" dataDxfId="13"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1843,17 +1847,17 @@
     <sortCondition ref="B1:B37"/>
   </sortState>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{7753A616-C6B5-4B02-AE3F-2A95253630B8}" name="Type de prestation" dataDxfId="7"/>
-    <tableColumn id="2" xr3:uid="{D7B6EA29-CA0A-4C24-9A81-3DF01785BD0C}" name="Label de la prestation" dataDxfId="6"/>
-    <tableColumn id="8" xr3:uid="{91FE62B8-BF79-4277-91C2-4B3C13901105}" name="ID prestation" dataDxfId="5"/>
+    <tableColumn id="1" xr3:uid="{7753A616-C6B5-4B02-AE3F-2A95253630B8}" name="Type de prestation" dataDxfId="12"/>
+    <tableColumn id="2" xr3:uid="{D7B6EA29-CA0A-4C24-9A81-3DF01785BD0C}" name="Label de la prestation" dataDxfId="11"/>
+    <tableColumn id="8" xr3:uid="{91FE62B8-BF79-4277-91C2-4B3C13901105}" name="ID prestation" dataDxfId="10"/>
     <tableColumn id="3" xr3:uid="{2ADF6FF1-1416-43FA-A9BF-E696654CC8CD}" name="Prestataire"/>
-    <tableColumn id="4" xr3:uid="{1C295B62-0191-41FA-9660-5BADE532BEE7}" name="Cout" dataDxfId="4"/>
-    <tableColumn id="5" xr3:uid="{1E3C456B-12BB-4B06-B366-57CE3DA87819}" name="Taxes" dataDxfId="3"/>
-    <tableColumn id="6" xr3:uid="{20997A37-E6E3-4308-9ACD-8D77B289D813}" name="Total TTC" dataDxfId="2">
+    <tableColumn id="4" xr3:uid="{1C295B62-0191-41FA-9660-5BADE532BEE7}" name="Cout" dataDxfId="9"/>
+    <tableColumn id="5" xr3:uid="{1E3C456B-12BB-4B06-B366-57CE3DA87819}" name="Taxes" dataDxfId="8"/>
+    <tableColumn id="6" xr3:uid="{20997A37-E6E3-4308-9ACD-8D77B289D813}" name="Total TTC" dataDxfId="7">
       <calculatedColumnFormula>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{6BDB0ED6-23A7-4E1A-A654-9E18B0DA38B5}" name="Description" dataDxfId="1"/>
-    <tableColumn id="9" xr3:uid="{C919E254-DE7F-4D3B-8CF6-79E643BBF97F}" name="Prestation choisie actuellement" dataDxfId="0"/>
+    <tableColumn id="7" xr3:uid="{6BDB0ED6-23A7-4E1A-A654-9E18B0DA38B5}" name="Description" dataDxfId="6"/>
+    <tableColumn id="9" xr3:uid="{C919E254-DE7F-4D3B-8CF6-79E643BBF97F}" name="Prestation choisie actuellement" dataDxfId="5"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1880,13 +1884,13 @@
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{455C30A6-2C19-4BD7-B8A4-D1C6252917DD}" name="Type de chaudière"/>
     <tableColumn id="2" xr3:uid="{FAAC8507-DC80-422C-8508-496178C23374}" name="ID poste de provision"/>
-    <tableColumn id="3" xr3:uid="{17764D71-05D7-4B37-8536-4004CBBE2CD4}" name="Prix unitaire du kWh" dataDxfId="30"/>
-    <tableColumn id="7" xr3:uid="{39B6FB9A-9DCB-412D-8CBD-94E321E39A50}" name="Unité" dataDxfId="29"/>
-    <tableColumn id="8" xr3:uid="{C769AD0E-5A43-462D-8737-CE59FA9E9F57}" name="Prix de l'unité" dataDxfId="28"/>
-    <tableColumn id="9" xr3:uid="{C32F2A17-C994-4DCC-A33C-2604586EDB4F}" name="kWh par unité" dataDxfId="27"/>
+    <tableColumn id="3" xr3:uid="{17764D71-05D7-4B37-8536-4004CBBE2CD4}" name="Prix unitaire du kWh" dataDxfId="4"/>
+    <tableColumn id="7" xr3:uid="{39B6FB9A-9DCB-412D-8CBD-94E321E39A50}" name="Unité" dataDxfId="3"/>
+    <tableColumn id="8" xr3:uid="{C769AD0E-5A43-462D-8737-CE59FA9E9F57}" name="Prix TTC de l'unité" dataDxfId="2"/>
+    <tableColumn id="9" xr3:uid="{C32F2A17-C994-4DCC-A33C-2604586EDB4F}" name="kWh par unité" dataDxfId="1"/>
     <tableColumn id="4" xr3:uid="{FECEDA0B-3F17-4D04-AB3F-B1B848AA5DB2}" name="Production maximum en kW"/>
     <tableColumn id="6" xr3:uid="{F8EB0843-7F05-427F-9B41-0852730F32C9}" name="Description"/>
-    <tableColumn id="10" xr3:uid="{9F9F9E98-6D66-4867-A354-22539BFC6A70}" name="Seuil de fonctionnement (kW)" dataDxfId="26"/>
+    <tableColumn id="10" xr3:uid="{9F9F9E98-6D66-4867-A354-22539BFC6A70}" name="Seuil de fonctionnement (kW)" dataDxfId="0"/>
     <tableColumn id="11" xr3:uid="{D0B5F61C-1D85-4C5E-A117-B774F88FE50E}" name="Seuil de durée d'activation (mn)"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -6890,8 +6894,8 @@
     <col min="5" max="5" width="11.85546875" style="4" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="8.28515625" style="6" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="98.85546875" style="2" customWidth="1"/>
-    <col min="9" max="9" width="48.85546875" customWidth="1"/>
+    <col min="8" max="8" width="124.7109375" style="2" customWidth="1"/>
+    <col min="9" max="9" width="31.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -7115,11 +7119,11 @@
         <v>16750</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G9" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>16750</v>
+        <v>20100</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>185</v>
@@ -7143,11 +7147,11 @@
         <v>887</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G10" s="4">
         <f>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</f>
-        <v>887</v>
+        <v>1064.3999999999999</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>135</v>
@@ -7920,7 +7924,7 @@
         <v>178</v>
       </c>
       <c r="D1" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -7980,10 +7984,10 @@
         <v>396</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="F1" s="12" t="s">
         <v>398</v>
-      </c>
-      <c r="F1" s="12" t="s">
-        <v>399</v>
       </c>
       <c r="G1" t="s">
         <v>186</v>
@@ -7992,10 +7996,10 @@
         <v>136</v>
       </c>
       <c r="I1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="J1" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -8013,7 +8017,8 @@
         <v>397</v>
       </c>
       <c r="E2" s="1">
-        <v>392</v>
+        <f>392*1.2</f>
+        <v>470.4</v>
       </c>
       <c r="F2" s="12">
         <v>4900</v>
@@ -8042,7 +8047,7 @@
         <v>0.12559999999999999</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="E3" s="1">
         <v>0.12559999999999999</v>
@@ -8054,7 +8059,7 @@
         <v>140</v>
       </c>
       <c r="H3" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="I3">
         <f>12</f>

--- a/input.xlsx
+++ b/input.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="1352" documentId="13_ncr:1_{471232EB-3AAB-4D08-BC1C-7B7CD1C1D853}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ABBA670F-8EBD-46A0-88D7-23996C8CEBB2}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Provisions" sheetId="9" r:id="rId1"/>
@@ -1366,82 +1366,6 @@
     <cellStyle name="Pourcentage" xfId="2" builtinId="5"/>
   </cellStyles>
   <dxfs count="31">
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -1775,6 +1699,82 @@
         <scheme val="minor"/>
       </font>
     </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1788,10 +1788,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{13C2BCD2-5CEA-4301-A571-688E40226767}" name="Provisions" displayName="Provisions" ref="A1:F35">
   <autoFilter ref="A1:F35" xr:uid="{13C2BCD2-5CEA-4301-A571-688E40226767}"/>
@@ -1803,8 +1799,8 @@
     <tableColumn id="4" xr3:uid="{84F1F30D-4827-43F2-8865-B7957E3E712D}" name="ID"/>
     <tableColumn id="7" xr3:uid="{512EABBD-B863-4251-833D-8B8D1F1626EF}" name="Description"/>
     <tableColumn id="2" xr3:uid="{D09C4BB0-FEBD-4A72-9E87-B5258D8B62D7}" name="Label de la provision"/>
-    <tableColumn id="3" xr3:uid="{347751FB-EF14-4BD7-9D47-427E04136B77}" name="Provision" totalsRowFunction="sum" dataDxfId="30" totalsRowDxfId="29" dataCellStyle="Monétaire"/>
-    <tableColumn id="5" xr3:uid="{CA26B6F8-88AD-418A-B213-749ABA66E926}" name="Description longue" dataDxfId="28"/>
+    <tableColumn id="3" xr3:uid="{347751FB-EF14-4BD7-9D47-427E04136B77}" name="Provision" totalsRowFunction="sum" dataDxfId="25" totalsRowDxfId="24" dataCellStyle="Monétaire"/>
+    <tableColumn id="5" xr3:uid="{CA26B6F8-88AD-418A-B213-749ABA66E926}" name="Description longue" dataDxfId="23"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1817,24 +1813,24 @@
     <sortCondition ref="A1:A180"/>
   </sortState>
   <tableColumns count="16">
-    <tableColumn id="3" xr3:uid="{1687C042-C916-4161-82C2-2A915364FCD2}" name="Numéro de lot" dataDxfId="27"/>
+    <tableColumn id="3" xr3:uid="{1687C042-C916-4161-82C2-2A915364FCD2}" name="Numéro de lot" dataDxfId="22"/>
     <tableColumn id="1" xr3:uid="{788DBA8C-5B77-4079-8161-FA45C58518AE}" name="Description"/>
-    <tableColumn id="2" xr3:uid="{BE5ACA99-AEAF-4E51-BE0A-B3FB8FCCF08B}" name="Tantièmes copropriété" dataDxfId="26">
+    <tableColumn id="2" xr3:uid="{BE5ACA99-AEAF-4E51-BE0A-B3FB8FCCF08B}" name="Tantièmes copropriété" dataDxfId="21">
       <calculatedColumnFormula>7/10000</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{D62FAA89-C46E-4AF6-A14F-7FD6F46E7F00}" name="Tantièmes ascenseur 1-1" dataDxfId="25"/>
-    <tableColumn id="9" xr3:uid="{C3B9BDED-CB2A-4305-9CBF-418F5971AC1E}" name="Tantièmes ascenseur 1-2" dataDxfId="24"/>
-    <tableColumn id="10" xr3:uid="{C2291DE1-C707-4F83-846E-F914B4B42E52}" name="Tantièmes ascenseur 2" dataDxfId="23"/>
-    <tableColumn id="11" xr3:uid="{4F70F08A-4C2F-41B0-88EB-711B1A0760CD}" name="Tantièmes ascenseur 3" dataDxfId="22"/>
-    <tableColumn id="14" xr3:uid="{80D23396-716C-46AC-9B55-BCBC6C981351}" name="Tantièmes chauffage" dataDxfId="21"/>
-    <tableColumn id="15" xr3:uid="{E3955139-B619-4DD0-8FC1-ECA97048DFE4}" name="Tantièmes Batiment 1" dataDxfId="20"/>
-    <tableColumn id="16" xr3:uid="{C73E9407-A858-4EF7-81C2-6C70C4B157A2}" name="Tantièmes Batiment 2" dataDxfId="19"/>
-    <tableColumn id="17" xr3:uid="{A07338CA-0096-4091-89B2-A46FF2D323C2}" name="Tantièmes Batiment 3" dataDxfId="18"/>
-    <tableColumn id="18" xr3:uid="{7A3012D8-2375-4F10-9E84-F2F5060C6A99}" name="Tantièmes Hall 1-1" dataDxfId="17"/>
-    <tableColumn id="19" xr3:uid="{67961B6E-B577-4A49-B099-623FB85519B4}" name="Tantièmes Hall 1-2" dataDxfId="16"/>
-    <tableColumn id="20" xr3:uid="{03C201C1-F8AA-4D3C-AEBC-425B180BC2D7}" name="Tantièmes Hall 2" dataDxfId="15"/>
-    <tableColumn id="21" xr3:uid="{4826FC05-81A9-4020-8D1D-83D3D5C5A05A}" name="Tantièmes Logement/Stationnements" dataDxfId="14"/>
-    <tableColumn id="6" xr3:uid="{7B87787E-3595-42D5-B815-AF76B67432D8}" name="Tantièmes Stationnement" dataDxfId="13"/>
+    <tableColumn id="8" xr3:uid="{D62FAA89-C46E-4AF6-A14F-7FD6F46E7F00}" name="Tantièmes ascenseur 1-1" dataDxfId="20"/>
+    <tableColumn id="9" xr3:uid="{C3B9BDED-CB2A-4305-9CBF-418F5971AC1E}" name="Tantièmes ascenseur 1-2" dataDxfId="19"/>
+    <tableColumn id="10" xr3:uid="{C2291DE1-C707-4F83-846E-F914B4B42E52}" name="Tantièmes ascenseur 2" dataDxfId="18"/>
+    <tableColumn id="11" xr3:uid="{4F70F08A-4C2F-41B0-88EB-711B1A0760CD}" name="Tantièmes ascenseur 3" dataDxfId="17"/>
+    <tableColumn id="14" xr3:uid="{80D23396-716C-46AC-9B55-BCBC6C981351}" name="Tantièmes chauffage" dataDxfId="16"/>
+    <tableColumn id="15" xr3:uid="{E3955139-B619-4DD0-8FC1-ECA97048DFE4}" name="Tantièmes Batiment 1" dataDxfId="15"/>
+    <tableColumn id="16" xr3:uid="{C73E9407-A858-4EF7-81C2-6C70C4B157A2}" name="Tantièmes Batiment 2" dataDxfId="14"/>
+    <tableColumn id="17" xr3:uid="{A07338CA-0096-4091-89B2-A46FF2D323C2}" name="Tantièmes Batiment 3" dataDxfId="13"/>
+    <tableColumn id="18" xr3:uid="{7A3012D8-2375-4F10-9E84-F2F5060C6A99}" name="Tantièmes Hall 1-1" dataDxfId="12"/>
+    <tableColumn id="19" xr3:uid="{67961B6E-B577-4A49-B099-623FB85519B4}" name="Tantièmes Hall 1-2" dataDxfId="11"/>
+    <tableColumn id="20" xr3:uid="{03C201C1-F8AA-4D3C-AEBC-425B180BC2D7}" name="Tantièmes Hall 2" dataDxfId="10"/>
+    <tableColumn id="21" xr3:uid="{4826FC05-81A9-4020-8D1D-83D3D5C5A05A}" name="Tantièmes Logement/Stationnements" dataDxfId="9"/>
+    <tableColumn id="6" xr3:uid="{7B87787E-3595-42D5-B815-AF76B67432D8}" name="Tantièmes Stationnement" dataDxfId="8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1847,17 +1843,17 @@
     <sortCondition ref="B1:B37"/>
   </sortState>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{7753A616-C6B5-4B02-AE3F-2A95253630B8}" name="Type de prestation" dataDxfId="12"/>
-    <tableColumn id="2" xr3:uid="{D7B6EA29-CA0A-4C24-9A81-3DF01785BD0C}" name="Label de la prestation" dataDxfId="11"/>
-    <tableColumn id="8" xr3:uid="{91FE62B8-BF79-4277-91C2-4B3C13901105}" name="ID prestation" dataDxfId="10"/>
+    <tableColumn id="1" xr3:uid="{7753A616-C6B5-4B02-AE3F-2A95253630B8}" name="Type de prestation" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{D7B6EA29-CA0A-4C24-9A81-3DF01785BD0C}" name="Label de la prestation" dataDxfId="6"/>
+    <tableColumn id="8" xr3:uid="{91FE62B8-BF79-4277-91C2-4B3C13901105}" name="ID prestation" dataDxfId="5"/>
     <tableColumn id="3" xr3:uid="{2ADF6FF1-1416-43FA-A9BF-E696654CC8CD}" name="Prestataire"/>
-    <tableColumn id="4" xr3:uid="{1C295B62-0191-41FA-9660-5BADE532BEE7}" name="Cout" dataDxfId="9"/>
-    <tableColumn id="5" xr3:uid="{1E3C456B-12BB-4B06-B366-57CE3DA87819}" name="Taxes" dataDxfId="8"/>
-    <tableColumn id="6" xr3:uid="{20997A37-E6E3-4308-9ACD-8D77B289D813}" name="Total TTC" dataDxfId="7">
+    <tableColumn id="4" xr3:uid="{1C295B62-0191-41FA-9660-5BADE532BEE7}" name="Cout" dataDxfId="4"/>
+    <tableColumn id="5" xr3:uid="{1E3C456B-12BB-4B06-B366-57CE3DA87819}" name="Taxes" dataDxfId="3"/>
+    <tableColumn id="6" xr3:uid="{20997A37-E6E3-4308-9ACD-8D77B289D813}" name="Total TTC" dataDxfId="2">
       <calculatedColumnFormula>IF(Prestations[[#This Row],[Taxes]]="TTC",Prestations[[#This Row],[Cout]],Prestations[[#This Row],[Cout]]*1.2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{6BDB0ED6-23A7-4E1A-A654-9E18B0DA38B5}" name="Description" dataDxfId="6"/>
-    <tableColumn id="9" xr3:uid="{C919E254-DE7F-4D3B-8CF6-79E643BBF97F}" name="Prestation choisie actuellement" dataDxfId="5"/>
+    <tableColumn id="7" xr3:uid="{6BDB0ED6-23A7-4E1A-A654-9E18B0DA38B5}" name="Description" dataDxfId="1"/>
+    <tableColumn id="9" xr3:uid="{C919E254-DE7F-4D3B-8CF6-79E643BBF97F}" name="Prestation choisie actuellement" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1884,13 +1880,13 @@
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{455C30A6-2C19-4BD7-B8A4-D1C6252917DD}" name="Type de chaudière"/>
     <tableColumn id="2" xr3:uid="{FAAC8507-DC80-422C-8508-496178C23374}" name="ID poste de provision"/>
-    <tableColumn id="3" xr3:uid="{17764D71-05D7-4B37-8536-4004CBBE2CD4}" name="Prix unitaire du kWh" dataDxfId="4"/>
-    <tableColumn id="7" xr3:uid="{39B6FB9A-9DCB-412D-8CBD-94E321E39A50}" name="Unité" dataDxfId="3"/>
-    <tableColumn id="8" xr3:uid="{C769AD0E-5A43-462D-8737-CE59FA9E9F57}" name="Prix TTC de l'unité" dataDxfId="2"/>
-    <tableColumn id="9" xr3:uid="{C32F2A17-C994-4DCC-A33C-2604586EDB4F}" name="kWh par unité" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{17764D71-05D7-4B37-8536-4004CBBE2CD4}" name="Prix unitaire du kWh" dataDxfId="30"/>
+    <tableColumn id="7" xr3:uid="{39B6FB9A-9DCB-412D-8CBD-94E321E39A50}" name="Unité" dataDxfId="29"/>
+    <tableColumn id="8" xr3:uid="{C769AD0E-5A43-462D-8737-CE59FA9E9F57}" name="Prix TTC de l'unité" dataDxfId="28"/>
+    <tableColumn id="9" xr3:uid="{C32F2A17-C994-4DCC-A33C-2604586EDB4F}" name="kWh par unité" dataDxfId="27"/>
     <tableColumn id="4" xr3:uid="{FECEDA0B-3F17-4D04-AB3F-B1B848AA5DB2}" name="Production maximum en kW"/>
     <tableColumn id="6" xr3:uid="{F8EB0843-7F05-427F-9B41-0852730F32C9}" name="Description"/>
-    <tableColumn id="10" xr3:uid="{9F9F9E98-6D66-4867-A354-22539BFC6A70}" name="Seuil de fonctionnement (kW)" dataDxfId="0"/>
+    <tableColumn id="10" xr3:uid="{9F9F9E98-6D66-4867-A354-22539BFC6A70}" name="Seuil de fonctionnement (kW)" dataDxfId="26"/>
     <tableColumn id="11" xr3:uid="{D0B5F61C-1D85-4C5E-A117-B774F88FE50E}" name="Seuil de durée d'activation (mn)"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -7292,7 +7288,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>18</v>
       </c>
@@ -7319,7 +7315,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>18</v>
       </c>
@@ -7346,7 +7342,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="165" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" ht="135" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>18</v>
       </c>
